--- a/5000_analyze_results/results_spreadsheet.xlsx
+++ b/5000_analyze_results/results_spreadsheet.xlsx
@@ -1,44 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\src\vivarium_gates_lsff_by_wealth_quintile\5000_analyze_results\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E8E2E52-73DC-46EB-B645-0C0EE0B811D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Model Results" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="J39" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="J39" authorId="0">
       <text>
         <r>
           <rPr>
@@ -51,7 +32,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K39" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="K39" authorId="0">
       <text>
         <r>
           <rPr>
@@ -64,7 +45,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W39" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="W39" authorId="0">
       <text>
         <r>
           <rPr>
@@ -77,7 +58,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X39" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="X39" authorId="0">
       <text>
         <r>
           <rPr>
@@ -90,7 +71,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J48" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="J48" authorId="0">
       <text>
         <r>
           <rPr>
@@ -103,7 +84,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K48" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="K48" authorId="0">
       <text>
         <r>
           <rPr>
@@ -116,7 +97,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W48" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="W48" authorId="0">
       <text>
         <r>
           <rPr>
@@ -129,7 +110,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X48" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+    <comment ref="X48" authorId="0">
       <text>
         <r>
           <rPr>
@@ -272,12 +253,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0%;\-0.0%;&quot;-&quot;"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* (#,##0);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.0%;-0.0%;&quot;-&quot;"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -359,21 +340,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -411,7 +384,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -445,7 +418,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -480,10 +452,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -656,9 +627,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AD54"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="1.7109375" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" customWidth="1"/>
@@ -667,7 +638,7 @@
     <col min="19" max="30" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30">
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
@@ -751,2454 +722,2454 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30">
       <c r="A2" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30">
       <c r="B3" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="3">
         <f>C5+C6+C7+C8+C9</f>
-        <v>1354.9744725859973</v>
+        <v>0</v>
       </c>
       <c r="D3" s="3">
         <f>D5+D6+D7+D8+D9</f>
-        <v>76.159986174637623</v>
+        <v>0</v>
       </c>
       <c r="E3" s="3">
         <f>E5+E6+E7+E8+E9</f>
-        <v>1278.8144864113599</v>
+        <v>0</v>
       </c>
       <c r="F3" s="3">
         <f>F5+F6+F7+F8+F9</f>
-        <v>1475.2008350402737</v>
+        <v>0</v>
       </c>
       <c r="G3" s="3">
         <f>G5+G6+G7+G8+G9</f>
-        <v>76.159986174637623</v>
+        <v>0</v>
       </c>
       <c r="H3" s="4">
         <f>IF(F3=0,0,G3/F3)</f>
-        <v>5.1626859452366308E-2</v>
+        <v>0</v>
       </c>
       <c r="I3" s="3">
         <f>I5+I6+I7+I8+I9</f>
-        <v>18048.889405534985</v>
+        <v>0</v>
       </c>
       <c r="J3" s="3">
         <f>J5+J6+J7+J8+J9</f>
-        <v>1113.8472905386166</v>
+        <v>0</v>
       </c>
       <c r="K3" s="4">
         <f>IF(I3=0,0,J3/I3)</f>
-        <v>6.1712788278099659E-2</v>
+        <v>0</v>
       </c>
       <c r="L3" s="3">
         <f>L5+L6+L7+L8+L9</f>
-        <v>72937.581127560086</v>
+        <v>0</v>
       </c>
       <c r="M3" s="3">
         <f>M5+M6+M7+M8+M9</f>
-        <v>133.93810810954682</v>
+        <v>0</v>
       </c>
       <c r="N3" s="4">
         <f>IF(L3=0,0,M3/L3)</f>
-        <v>1.8363387713023179E-3</v>
+        <v>0</v>
       </c>
       <c r="O3" s="3">
         <f>O5+O6+O7+O8+O9</f>
-        <v>2197.413253833623</v>
+        <v>0</v>
       </c>
       <c r="P3" s="3">
         <f>P5+P6+P7+P8+P9</f>
-        <v>31.0290877631965</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="4">
         <f>IF(O3=0,0,P3/O3)</f>
-        <v>1.4120733871547799E-2</v>
+        <v>0</v>
       </c>
       <c r="S3" s="3">
         <f>S5+S6+S7+S8+S9</f>
-        <v>21308.331458638695</v>
+        <v>0</v>
       </c>
       <c r="T3" s="3">
         <f>T5+T6+T7+T8+T9</f>
-        <v>1100.0822333795754</v>
+        <v>0</v>
       </c>
       <c r="U3" s="4">
         <f>IF(S3=0,0,T3/S3)</f>
-        <v>5.1626859452366308E-2</v>
+        <v>0</v>
       </c>
       <c r="V3" s="3">
         <f>V5+V6+V7+V8+V9</f>
-        <v>586271135.92958963</v>
+        <v>0</v>
       </c>
       <c r="W3" s="3">
         <f>W5+W6+W7+W8+W9</f>
-        <v>28540637.209694162</v>
+        <v>0</v>
       </c>
       <c r="X3" s="4">
         <f>IF(V3=0,0,W3/V3)</f>
-        <v>4.8681634589497945E-2</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="3">
         <f>Y5+Y6+Y7+Y8+Y9</f>
-        <v>23683592.035162695</v>
+        <v>0</v>
       </c>
       <c r="Z3" s="3">
         <f>Z5+Z6+Z7+Z8+Z9</f>
-        <v>357929.85937569803</v>
+        <v>0</v>
       </c>
       <c r="AA3" s="4">
         <f>IF(Y3=0,0,Z3/Y3)</f>
-        <v>1.5112988724188654E-2</v>
+        <v>0</v>
       </c>
       <c r="AB3" s="3">
         <f>AB5+AB6+AB7+AB8+AB9</f>
-        <v>813962.31168455421</v>
+        <v>0</v>
       </c>
       <c r="AC3" s="3">
         <f>AC5+AC6+AC7+AC8+AC9</f>
-        <v>1488.4676120195945</v>
+        <v>0</v>
       </c>
       <c r="AD3" s="4">
         <f>IF(AB3=0,0,AC3/AB3)</f>
-        <v>1.8286689575824494E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30">
       <c r="A4" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30">
       <c r="B5" t="s">
         <v>30</v>
       </c>
       <c r="C5" s="3">
         <f>J5+M5+G5+P5</f>
-        <v>394.43866086505562</v>
+        <v>0</v>
       </c>
       <c r="D5" s="3">
         <f>G5</f>
-        <v>25.612291312667828</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3">
         <f>J5+M5+P5</f>
-        <v>368.8263695523878</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3">
-        <v>363.2412074975357</v>
+        <v>363.2526709502005</v>
       </c>
       <c r="G5" s="3">
-        <v>25.612291312667828</v>
+        <v>25.6326821076292</v>
       </c>
       <c r="H5" s="4">
         <f>IF(F5=0,0,G5/F5)</f>
-        <v>7.0510423333072933E-2</v>
+        <v>0</v>
       </c>
       <c r="I5" s="3">
-        <v>4215.705028068518</v>
+        <v>4770.530839135346</v>
       </c>
       <c r="J5" s="3">
-        <v>311.12629295529291</v>
+        <v>313.1435897498429</v>
       </c>
       <c r="K5" s="4">
         <f>IF(I5=0,0,J5/I5)</f>
-        <v>7.3801722578735449E-2</v>
+        <v>0</v>
       </c>
       <c r="L5" s="3">
-        <v>18587.84837263764</v>
+        <v>17201.81753387347</v>
       </c>
       <c r="M5" s="3">
-        <v>48.273576582159848</v>
+        <v>34.65351871059835</v>
       </c>
       <c r="N5" s="4">
         <f>IF(L5=0,0,M5/L5)</f>
-        <v>2.5970502671638571E-3</v>
+        <v>0</v>
       </c>
       <c r="O5" s="3">
-        <v>591.47191788042619</v>
+        <v>563.6740462937513</v>
       </c>
       <c r="P5" s="3">
-        <v>9.4265000149350389</v>
+        <v>3.055884731480386</v>
       </c>
       <c r="Q5" s="4">
         <f>IF(O5=0,0,P5/O5)</f>
-        <v>1.5937358528728542E-2</v>
+        <v>0</v>
       </c>
       <c r="S5" s="3">
-        <v>5246.7866509730784</v>
+        <v>5246.952233206521</v>
       </c>
       <c r="T5" s="3">
-        <v>369.95314789842809</v>
+        <v>370.2476798749703</v>
       </c>
       <c r="U5" s="4">
         <f>IF(S5=0,0,T5/S5)</f>
-        <v>7.0510423333073002E-2</v>
+        <v>0</v>
       </c>
       <c r="V5" s="3">
-        <v>130504106.3683567</v>
+        <v>131633584.5027684</v>
       </c>
       <c r="W5" s="3">
-        <v>7529815.8321291059</v>
+        <v>6824406.427104607</v>
       </c>
       <c r="X5" s="4">
         <f>IF(V5=0,0,W5/V5)</f>
-        <v>5.7697922629926214E-2</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3">
-        <v>6056561.9935170701</v>
+        <v>4146720.811068905</v>
       </c>
       <c r="Z5" s="3">
-        <v>113528.6322764717</v>
+        <v>85316.94233367266</v>
       </c>
       <c r="AA5" s="4">
         <f>IF(Y5=0,0,Z5/Y5)</f>
-        <v>1.8744732143085877E-2</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="3">
-        <v>207427.26465751129</v>
+        <v>191901.8894224531</v>
       </c>
       <c r="AC5" s="3">
-        <v>536.46853516536066</v>
+        <v>385.1518101805414</v>
       </c>
       <c r="AD5" s="4">
         <f>IF(AB5=0,0,AC5/AB5)</f>
-        <v>2.5862971102238574E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30">
       <c r="B6" t="s">
         <v>31</v>
       </c>
       <c r="C6" s="3">
         <f>J6+M6+G6+P6</f>
-        <v>330.44823457246008</v>
+        <v>0</v>
       </c>
       <c r="D6" s="3">
         <f>G6</f>
-        <v>19.301616793786408</v>
+        <v>0</v>
       </c>
       <c r="E6" s="3">
         <f>J6+M6+P6</f>
-        <v>311.14661777867366</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3">
-        <v>320.88569787796308</v>
+        <v>320.895824642032</v>
       </c>
       <c r="G6" s="3">
-        <v>19.301616793786408</v>
+        <v>19.31417561181431</v>
       </c>
       <c r="H6" s="4">
         <f>IF(F6=0,0,G6/F6)</f>
-        <v>6.015106600708349E-2</v>
+        <v>0</v>
       </c>
       <c r="I6" s="3">
-        <v>3777.348955767648</v>
+        <v>4315.124647651387</v>
       </c>
       <c r="J6" s="3">
-        <v>273.87484500182188</v>
+        <v>279.2957221772522</v>
       </c>
       <c r="K6" s="4">
         <f>IF(I6=0,0,J6/I6)</f>
-        <v>7.2504512611587385E-2</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3">
-        <v>15367.676054976309</v>
+        <v>14287.00731827389</v>
       </c>
       <c r="M6" s="3">
-        <v>30.710367296976969</v>
+        <v>-8.665332839692011</v>
       </c>
       <c r="N6" s="4">
         <f>IF(L6=0,0,M6/L6)</f>
-        <v>1.9983741970558029E-3</v>
+        <v>0</v>
       </c>
       <c r="O6" s="3">
-        <v>469.23439497722012</v>
+        <v>368.9620181288427</v>
       </c>
       <c r="P6" s="3">
-        <v>6.5614054798748107</v>
+        <v>9.87815318115428</v>
       </c>
       <c r="Q6" s="4">
         <f>IF(O6=0,0,P6/O6)</f>
-        <v>1.3983215105519592E-2</v>
+        <v>0</v>
       </c>
       <c r="S6" s="3">
-        <v>4634.9884356820912</v>
+        <v>4635.134710304677</v>
       </c>
       <c r="T6" s="3">
-        <v>278.79949533678251</v>
+        <v>278.9808994215082</v>
       </c>
       <c r="U6" s="4">
         <f>IF(S6=0,0,T6/S6)</f>
-        <v>6.0151066007083573E-2</v>
+        <v>0</v>
       </c>
       <c r="V6" s="3">
-        <v>120904784.0220684</v>
+        <v>123302339.5131656</v>
       </c>
       <c r="W6" s="3">
-        <v>6963839.795960322</v>
+        <v>6420550.044813901</v>
       </c>
       <c r="X6" s="4">
         <f>IF(V6=0,0,W6/V6)</f>
-        <v>5.7597719166259234E-2</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="3">
-        <v>5132795.0536682894</v>
+        <v>2492610.938112688</v>
       </c>
       <c r="Z6" s="3">
-        <v>85655.404223025776</v>
+        <v>58192.50294461334</v>
       </c>
       <c r="AA6" s="4">
         <f>IF(Y6=0,0,Z6/Y6)</f>
-        <v>1.6687867590156332E-2</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="3">
-        <v>171483.87280142889</v>
+        <v>159452.8494147427</v>
       </c>
       <c r="AC6" s="3">
-        <v>341.10716108785709</v>
+        <v>-96.28795254512806</v>
       </c>
       <c r="AD6" s="4">
         <f>IF(AB6=0,0,AC6/AB6)</f>
-        <v>1.9891500904160521E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30">
       <c r="B7" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="3">
         <f>J7+M7+G7+P7</f>
-        <v>281.88409811441397</v>
+        <v>0</v>
       </c>
       <c r="D7" s="3">
         <f>G7</f>
-        <v>14.649488393760979</v>
+        <v>0</v>
       </c>
       <c r="E7" s="3">
         <f>J7+M7+P7</f>
-        <v>267.234609720653</v>
+        <v>0</v>
       </c>
       <c r="F7" s="3">
-        <v>288.07994042728268</v>
+        <v>288.0890318813705</v>
       </c>
       <c r="G7" s="3">
-        <v>14.649488393760979</v>
+        <v>14.66402391696896</v>
       </c>
       <c r="H7" s="4">
         <f>IF(F7=0,0,G7/F7)</f>
-        <v>5.0852164062630427E-2</v>
+        <v>0</v>
       </c>
       <c r="I7" s="3">
-        <v>3687.8736715650298</v>
+        <v>4219.443085372338</v>
       </c>
       <c r="J7" s="3">
-        <v>237.34124995700179</v>
+        <v>242.8847629563259</v>
       </c>
       <c r="K7" s="4">
         <f>IF(I7=0,0,J7/I7)</f>
-        <v>6.4357207186080442E-2</v>
+        <v>0</v>
       </c>
       <c r="L7" s="3">
-        <v>13749.346945394889</v>
+        <v>12956.12081462672</v>
       </c>
       <c r="M7" s="3">
-        <v>26.21495619864762</v>
+        <v>47.6477209922336</v>
       </c>
       <c r="N7" s="4">
         <f>IF(L7=0,0,M7/L7)</f>
-        <v>1.9066328242904565E-3</v>
+        <v>0</v>
       </c>
       <c r="O7" s="3">
-        <v>412.21408373118408</v>
+        <v>413.9741355821696</v>
       </c>
       <c r="P7" s="3">
-        <v>3.6784035650035949</v>
+        <v>8.572203573752777</v>
       </c>
       <c r="Q7" s="4">
         <f>IF(O7=0,0,P7/O7)</f>
-        <v>8.9235271432462297E-3</v>
+        <v>0</v>
       </c>
       <c r="S7" s="3">
-        <v>4161.1302755545457</v>
+        <v>4161.261595787386</v>
       </c>
       <c r="T7" s="3">
-        <v>211.6024794584778</v>
+        <v>211.8124357838028</v>
       </c>
       <c r="U7" s="4">
         <f>IF(S7=0,0,T7/S7)</f>
-        <v>5.0852164062630302E-2</v>
+        <v>0</v>
       </c>
       <c r="V7" s="3">
-        <v>118273982.46310391</v>
+        <v>120996996.1158803</v>
       </c>
       <c r="W7" s="3">
-        <v>6057749.0648616999</v>
+        <v>5621454.428166643</v>
       </c>
       <c r="X7" s="4">
         <f>IF(V7=0,0,W7/V7)</f>
-        <v>5.1217934314095173E-2</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3">
-        <v>4603060.9719898822</v>
+        <v>2977965.268457345</v>
       </c>
       <c r="Z7" s="3">
-        <v>67998.015264652669</v>
+        <v>54152.6928228382</v>
       </c>
       <c r="AA7" s="4">
         <f>IF(Y7=0,0,Z7/Y7)</f>
-        <v>1.4772347287691355E-2</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="3">
-        <v>153442.40495407421</v>
+        <v>144576.3607465195</v>
       </c>
       <c r="AC7" s="3">
-        <v>291.49157402050332</v>
+        <v>529.583738998248</v>
       </c>
       <c r="AD7" s="4">
         <f>IF(AB7=0,0,AC7/AB7)</f>
-        <v>1.8996806919687401E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30">
       <c r="B8" t="s">
         <v>33</v>
       </c>
       <c r="C8" s="3">
         <f>J8+M8+G8+P8</f>
-        <v>233.43504013339646</v>
+        <v>0</v>
       </c>
       <c r="D8" s="3">
         <f>G8</f>
-        <v>12.01133418925607</v>
+        <v>0</v>
       </c>
       <c r="E8" s="3">
         <f>J8+M8+P8</f>
-        <v>221.42370594414038</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3">
-        <v>271.64518669470311</v>
+        <v>271.6537594878637</v>
       </c>
       <c r="G8" s="3">
-        <v>12.01133418925607</v>
+        <v>12.01915901086331</v>
       </c>
       <c r="H8" s="4">
         <f>IF(F8=0,0,G8/F8)</f>
-        <v>4.4216996205257195E-2</v>
+        <v>0</v>
       </c>
       <c r="I8" s="3">
-        <v>3375.6401243953728</v>
+        <v>3865.802402615053</v>
       </c>
       <c r="J8" s="3">
-        <v>193.18814640416059</v>
+        <v>198.6845367286932</v>
       </c>
       <c r="K8" s="4">
         <f>IF(I8=0,0,J8/I8)</f>
-        <v>5.7230077640093066E-2</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3">
-        <v>12894.33743826528</v>
+        <v>11750.93232102557</v>
       </c>
       <c r="M8" s="3">
-        <v>21.206282171037049</v>
+        <v>4.333740511480719</v>
       </c>
       <c r="N8" s="4">
         <f>IF(L8=0,0,M8/L8)</f>
-        <v>1.6446197621682534E-3</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3">
-        <v>377.03051903276793</v>
+        <v>341.5371321492009</v>
       </c>
       <c r="P8" s="3">
-        <v>7.0292773689427417</v>
+        <v>0.003013071803143248</v>
       </c>
       <c r="Q8" s="4">
         <f>IF(O8=0,0,P8/O8)</f>
-        <v>1.8643788802496977E-2</v>
+        <v>0</v>
       </c>
       <c r="S8" s="3">
-        <v>3923.740781421468</v>
+        <v>3923.864609929325</v>
       </c>
       <c r="T8" s="3">
-        <v>173.49603124252641</v>
+        <v>173.6090557802372</v>
       </c>
       <c r="U8" s="4">
         <f>IF(S8=0,0,T8/S8)</f>
-        <v>4.4216996205257313E-2</v>
+        <v>0</v>
       </c>
       <c r="V8" s="3">
-        <v>111762860.6181328</v>
+        <v>114899915.8905035</v>
       </c>
       <c r="W8" s="3">
-        <v>5173153.5519152125</v>
+        <v>4852495.274701983</v>
       </c>
       <c r="X8" s="4">
         <f>IF(V8=0,0,W8/V8)</f>
-        <v>4.6286874935947207E-2</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="3">
-        <v>4143959.5493767709</v>
+        <v>2573310.954592903</v>
       </c>
       <c r="Z8" s="3">
-        <v>58840.378214361153</v>
+        <v>41023.30992707005</v>
       </c>
       <c r="AA8" s="4">
         <f>IF(Y8=0,0,Z8/Y8)</f>
-        <v>1.4199071567484395E-2</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="3">
-        <v>143913.11126295681</v>
+        <v>131096.0473902006</v>
       </c>
       <c r="AC8" s="3">
-        <v>235.6740385697631</v>
+        <v>48.14397627257858</v>
       </c>
       <c r="AD8" s="4">
         <f>IF(AB8=0,0,AC8/AB8)</f>
-        <v>1.6376133939536718E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30">
       <c r="B9" t="s">
         <v>34</v>
       </c>
       <c r="C9" s="3">
         <f>J9+M9+G9+P9</f>
-        <v>114.76843890067131</v>
+        <v>0</v>
       </c>
       <c r="D9" s="3">
         <f>G9</f>
-        <v>4.5852554851663303</v>
+        <v>0</v>
       </c>
       <c r="E9" s="3">
         <f>J9+M9+P9</f>
-        <v>110.18318341550498</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3">
-        <v>231.34880254278889</v>
+        <v>231.35610363086</v>
       </c>
       <c r="G9" s="3">
-        <v>4.5852554851663303</v>
+        <v>4.583485389322275</v>
       </c>
       <c r="H9" s="4">
         <f>IF(F9=0,0,G9/F9)</f>
-        <v>1.981966379237372E-2</v>
+        <v>0</v>
       </c>
       <c r="I9" s="3">
-        <v>2992.321625738417</v>
+        <v>3364.499225271484</v>
       </c>
       <c r="J9" s="3">
-        <v>98.316756220339329</v>
+        <v>100.8917196531021</v>
       </c>
       <c r="K9" s="4">
         <f>IF(I9=0,0,J9/I9)</f>
-        <v>3.2856346515250559E-2</v>
+        <v>0</v>
       </c>
       <c r="L9" s="3">
-        <v>12338.372316285961</v>
+        <v>11621.53898497677</v>
       </c>
       <c r="M9" s="3">
-        <v>7.5329258607253431</v>
+        <v>12.99365256417356</v>
       </c>
       <c r="N9" s="4">
         <f>IF(L9=0,0,M9/L9)</f>
-        <v>6.1052833125989424E-4</v>
+        <v>0</v>
       </c>
       <c r="O9" s="3">
-        <v>347.46233821202492</v>
+        <v>214.6066033532331</v>
       </c>
       <c r="P9" s="3">
-        <v>4.3335013344403119</v>
+        <v>2.982047942264675</v>
       </c>
       <c r="Q9" s="4">
         <f>IF(O9=0,0,P9/O9)</f>
-        <v>1.2471859127926454E-2</v>
+        <v>0</v>
       </c>
       <c r="S9" s="3">
-        <v>3341.6853150075108</v>
+        <v>3341.790774549652</v>
       </c>
       <c r="T9" s="3">
-        <v>66.231079443360613</v>
+        <v>66.20551154232589</v>
       </c>
       <c r="U9" s="4">
         <f>IF(S9=0,0,T9/S9)</f>
-        <v>1.9819663792373505E-2</v>
+        <v>0</v>
       </c>
       <c r="V9" s="3">
-        <v>104825402.45792779</v>
+        <v>107028313.8412168</v>
       </c>
       <c r="W9" s="3">
-        <v>2816078.9648278211</v>
+        <v>2678093.45510754</v>
       </c>
       <c r="X9" s="4">
         <f>IF(V9=0,0,W9/V9)</f>
-        <v>2.6864470813341916E-2</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3">
-        <v>3747214.4666106808</v>
+        <v>1541764.677188765</v>
       </c>
       <c r="Z9" s="3">
-        <v>31907.42939718673</v>
+        <v>16543.98430822045</v>
       </c>
       <c r="AA9" s="4">
         <f>IF(Y9=0,0,Z9/Y9)</f>
-        <v>8.5149728368888074E-3</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="3">
-        <v>137695.65800858309</v>
+        <v>129651.7281020236</v>
       </c>
       <c r="AC9" s="3">
-        <v>83.726303176110378</v>
+        <v>144.4319288176921</v>
       </c>
       <c r="AD9" s="4">
         <f>IF(AB9=0,0,AC9/AB9)</f>
-        <v>6.0805332852900413E-4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30">
       <c r="A11" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30">
       <c r="B12" t="s">
         <v>28</v>
       </c>
       <c r="C12" s="3">
         <f>C14+C15+C16+C17+C18</f>
-        <v>1831.3001558514102</v>
+        <v>0</v>
       </c>
       <c r="D12" s="3">
         <f>D14+D15+D16+D17+D18</f>
-        <v>552.48566944005017</v>
+        <v>0</v>
       </c>
       <c r="E12" s="3">
         <f>E14+E15+E16+E17+E18</f>
-        <v>1278.8144864113599</v>
+        <v>0</v>
       </c>
       <c r="F12" s="3">
         <f>F14+F15+F16+F17+F18</f>
-        <v>1475.2008350402737</v>
+        <v>0</v>
       </c>
       <c r="G12" s="3">
         <f>G14+G15+G16+G17+G18</f>
-        <v>552.48566944005017</v>
+        <v>0</v>
       </c>
       <c r="H12" s="4">
         <f>IF(F12=0,0,G12/F12)</f>
-        <v>0.3745155617573705</v>
+        <v>0</v>
       </c>
       <c r="I12" s="3">
         <f>I14+I15+I16+I17+I18</f>
-        <v>18048.889405534985</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3">
         <f>J14+J15+J16+J17+J18</f>
-        <v>1113.8472905386166</v>
+        <v>0</v>
       </c>
       <c r="K12" s="4">
         <f>IF(I12=0,0,J12/I12)</f>
-        <v>6.1712788278099659E-2</v>
+        <v>0</v>
       </c>
       <c r="L12" s="3">
         <f>L14+L15+L16+L17+L18</f>
-        <v>72937.581127560086</v>
+        <v>0</v>
       </c>
       <c r="M12" s="3">
         <f>M14+M15+M16+M17+M18</f>
-        <v>133.93810810954682</v>
+        <v>0</v>
       </c>
       <c r="N12" s="4">
         <f>IF(L12=0,0,M12/L12)</f>
-        <v>1.8363387713023179E-3</v>
+        <v>0</v>
       </c>
       <c r="O12" s="3">
         <f>O14+O15+O16+O17+O18</f>
-        <v>2197.413253833623</v>
+        <v>0</v>
       </c>
       <c r="P12" s="3">
         <f>P14+P15+P16+P17+P18</f>
-        <v>31.0290877631965</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="4">
         <f>IF(O12=0,0,P12/O12)</f>
-        <v>1.4120733871547799E-2</v>
+        <v>0</v>
       </c>
       <c r="S12" s="3">
         <f>S14+S15+S16+S17+S18</f>
-        <v>21308.331458638695</v>
+        <v>0</v>
       </c>
       <c r="T12" s="3">
         <f>T14+T15+T16+T17+T18</f>
-        <v>7980.3017263443235</v>
+        <v>0</v>
       </c>
       <c r="U12" s="4">
         <f>IF(S12=0,0,T12/S12)</f>
-        <v>0.37451556175737061</v>
+        <v>0</v>
       </c>
       <c r="V12" s="3">
         <f>V14+V15+V16+V17+V18</f>
-        <v>586271135.92958963</v>
+        <v>0</v>
       </c>
       <c r="W12" s="3">
         <f>W14+W15+W16+W17+W18</f>
-        <v>28540637.209694162</v>
+        <v>0</v>
       </c>
       <c r="X12" s="4">
         <f>IF(V12=0,0,W12/V12)</f>
-        <v>4.8681634589497945E-2</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="3">
         <f>Y14+Y15+Y16+Y17+Y18</f>
-        <v>23683592.035162695</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="3">
         <f>Z14+Z15+Z16+Z17+Z18</f>
-        <v>357929.85937569803</v>
+        <v>0</v>
       </c>
       <c r="AA12" s="4">
         <f>IF(Y12=0,0,Z12/Y12)</f>
-        <v>1.5112988724188654E-2</v>
+        <v>0</v>
       </c>
       <c r="AB12" s="3">
         <f>AB14+AB15+AB16+AB17+AB18</f>
-        <v>813962.31168455421</v>
+        <v>0</v>
       </c>
       <c r="AC12" s="3">
         <f>AC14+AC15+AC16+AC17+AC18</f>
-        <v>1488.4676120195945</v>
+        <v>0</v>
       </c>
       <c r="AD12" s="4">
         <f>IF(AB12=0,0,AC12/AB12)</f>
-        <v>1.8286689575824494E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30">
       <c r="A13" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30">
       <c r="B14" t="s">
         <v>30</v>
       </c>
       <c r="C14" s="3">
         <f>J14+M14+G14+P14</f>
-        <v>540.52142931971321</v>
+        <v>0</v>
       </c>
       <c r="D14" s="3">
         <f>G14</f>
-        <v>171.69505976732529</v>
+        <v>0</v>
       </c>
       <c r="E14" s="3">
         <f>J14+M14+P14</f>
-        <v>368.8263695523878</v>
+        <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>363.2412074975357</v>
+        <v>363.2526709502005</v>
       </c>
       <c r="G14" s="3">
-        <v>171.69505976732529</v>
+        <v>171.7832348530698</v>
       </c>
       <c r="H14" s="4">
         <f>IF(F14=0,0,G14/F14)</f>
-        <v>0.47267506060278169</v>
+        <v>0</v>
       </c>
       <c r="I14" s="3">
-        <v>4215.705028068518</v>
+        <v>4770.530839135346</v>
       </c>
       <c r="J14" s="3">
-        <v>311.12629295529291</v>
+        <v>313.1435897498429</v>
       </c>
       <c r="K14" s="4">
         <f>IF(I14=0,0,J14/I14)</f>
-        <v>7.3801722578735449E-2</v>
+        <v>0</v>
       </c>
       <c r="L14" s="3">
-        <v>18587.84837263764</v>
+        <v>17201.81753387347</v>
       </c>
       <c r="M14" s="3">
-        <v>48.273576582159848</v>
+        <v>34.65351871059835</v>
       </c>
       <c r="N14" s="4">
         <f>IF(L14=0,0,M14/L14)</f>
-        <v>2.5970502671638571E-3</v>
+        <v>0</v>
       </c>
       <c r="O14" s="3">
-        <v>591.47191788042619</v>
+        <v>563.6740462937513</v>
       </c>
       <c r="P14" s="3">
-        <v>9.4265000149350389</v>
+        <v>3.055884731480386</v>
       </c>
       <c r="Q14" s="4">
         <f>IF(O14=0,0,P14/O14)</f>
-        <v>1.5937358528728542E-2</v>
+        <v>0</v>
       </c>
       <c r="S14" s="3">
-        <v>5246.7866509730784</v>
+        <v>5246.952233206521</v>
       </c>
       <c r="T14" s="3">
-        <v>2480.0251982185669</v>
+        <v>2481.2988308717</v>
       </c>
       <c r="U14" s="4">
         <f>IF(S14=0,0,T14/S14)</f>
-        <v>0.47267506060278192</v>
+        <v>0</v>
       </c>
       <c r="V14" s="3">
-        <v>130504106.3683567</v>
+        <v>131633584.5027684</v>
       </c>
       <c r="W14" s="3">
-        <v>7529815.8321291059</v>
+        <v>6824406.427104607</v>
       </c>
       <c r="X14" s="4">
         <f>IF(V14=0,0,W14/V14)</f>
-        <v>5.7697922629926214E-2</v>
+        <v>0</v>
       </c>
       <c r="Y14" s="3">
-        <v>6056561.9935170701</v>
+        <v>4146720.811068905</v>
       </c>
       <c r="Z14" s="3">
-        <v>113528.6322764717</v>
+        <v>85316.94233367266</v>
       </c>
       <c r="AA14" s="4">
         <f>IF(Y14=0,0,Z14/Y14)</f>
-        <v>1.8744732143085877E-2</v>
+        <v>0</v>
       </c>
       <c r="AB14" s="3">
-        <v>207427.26465751129</v>
+        <v>191901.8894224531</v>
       </c>
       <c r="AC14" s="3">
-        <v>536.46853516536066</v>
+        <v>385.1518101805414</v>
       </c>
       <c r="AD14" s="4">
         <f>IF(AB14=0,0,AC14/AB14)</f>
-        <v>2.5862971102238574E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30">
       <c r="B15" t="s">
         <v>31</v>
       </c>
       <c r="C15" s="3">
         <f>J15+M15+G15+P15</f>
-        <v>447.92399817572056</v>
+        <v>0</v>
       </c>
       <c r="D15" s="3">
         <f>G15</f>
-        <v>136.7773803970469</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
         <f>J15+M15+P15</f>
-        <v>311.14661777867366</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
-        <v>320.88569787796308</v>
+        <v>320.895824642032</v>
       </c>
       <c r="G15" s="3">
-        <v>136.7773803970469</v>
+        <v>136.8384360524177</v>
       </c>
       <c r="H15" s="4">
         <f>IF(F15=0,0,G15/F15)</f>
-        <v>0.42624953776863272</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>3777.348955767648</v>
+        <v>4315.124647651387</v>
       </c>
       <c r="J15" s="3">
-        <v>273.87484500182188</v>
+        <v>279.2957221772522</v>
       </c>
       <c r="K15" s="4">
         <f>IF(I15=0,0,J15/I15)</f>
-        <v>7.2504512611587385E-2</v>
+        <v>0</v>
       </c>
       <c r="L15" s="3">
-        <v>15367.676054976309</v>
+        <v>14287.00731827389</v>
       </c>
       <c r="M15" s="3">
-        <v>30.710367296976969</v>
+        <v>-8.665332839692011</v>
       </c>
       <c r="N15" s="4">
         <f>IF(L15=0,0,M15/L15)</f>
-        <v>1.9983741970558029E-3</v>
+        <v>0</v>
       </c>
       <c r="O15" s="3">
-        <v>469.23439497722012</v>
+        <v>368.9620181288427</v>
       </c>
       <c r="P15" s="3">
-        <v>6.5614054798748107</v>
+        <v>9.87815318115428</v>
       </c>
       <c r="Q15" s="4">
         <f>IF(O15=0,0,P15/O15)</f>
-        <v>1.3983215105519592E-2</v>
+        <v>0</v>
       </c>
       <c r="S15" s="3">
-        <v>4634.9884356820912</v>
+        <v>4635.134710304677</v>
       </c>
       <c r="T15" s="3">
-        <v>1975.66167827245</v>
+        <v>1976.543588119003</v>
       </c>
       <c r="U15" s="4">
         <f>IF(S15=0,0,T15/S15)</f>
-        <v>0.42624953776863284</v>
+        <v>0</v>
       </c>
       <c r="V15" s="3">
-        <v>120904784.0220684</v>
+        <v>123302339.5131656</v>
       </c>
       <c r="W15" s="3">
-        <v>6963839.795960322</v>
+        <v>6420550.044813901</v>
       </c>
       <c r="X15" s="4">
         <f>IF(V15=0,0,W15/V15)</f>
-        <v>5.7597719166259234E-2</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="3">
-        <v>5132795.0536682894</v>
+        <v>2492610.938112688</v>
       </c>
       <c r="Z15" s="3">
-        <v>85655.404223025776</v>
+        <v>58192.50294461334</v>
       </c>
       <c r="AA15" s="4">
         <f>IF(Y15=0,0,Z15/Y15)</f>
-        <v>1.6687867590156332E-2</v>
+        <v>0</v>
       </c>
       <c r="AB15" s="3">
-        <v>171483.87280142889</v>
+        <v>159452.8494147427</v>
       </c>
       <c r="AC15" s="3">
-        <v>341.10716108785709</v>
+        <v>-96.28795254512806</v>
       </c>
       <c r="AD15" s="4">
         <f>IF(AB15=0,0,AC15/AB15)</f>
-        <v>1.9891500904160521E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30">
       <c r="B16" t="s">
         <v>32</v>
       </c>
       <c r="C16" s="3">
         <f>J16+M16+G16+P16</f>
-        <v>376.59508038259258</v>
+        <v>0</v>
       </c>
       <c r="D16" s="3">
         <f>G16</f>
-        <v>109.3604706619396</v>
+        <v>0</v>
       </c>
       <c r="E16" s="3">
         <f>J16+M16+P16</f>
-        <v>267.234609720653</v>
+        <v>0</v>
       </c>
       <c r="F16" s="3">
-        <v>288.07994042728268</v>
+        <v>288.0890318813705</v>
       </c>
       <c r="G16" s="3">
-        <v>109.3604706619396</v>
+        <v>109.4383939321504</v>
       </c>
       <c r="H16" s="4">
         <f>IF(F16=0,0,G16/F16)</f>
-        <v>0.37961848540976229</v>
+        <v>0</v>
       </c>
       <c r="I16" s="3">
-        <v>3687.8736715650298</v>
+        <v>4219.443085372338</v>
       </c>
       <c r="J16" s="3">
-        <v>237.34124995700179</v>
+        <v>242.8847629563259</v>
       </c>
       <c r="K16" s="4">
         <f>IF(I16=0,0,J16/I16)</f>
-        <v>6.4357207186080442E-2</v>
+        <v>0</v>
       </c>
       <c r="L16" s="3">
-        <v>13749.346945394889</v>
+        <v>12956.12081462672</v>
       </c>
       <c r="M16" s="3">
-        <v>26.21495619864762</v>
+        <v>47.6477209922336</v>
       </c>
       <c r="N16" s="4">
         <f>IF(L16=0,0,M16/L16)</f>
-        <v>1.9066328242904565E-3</v>
+        <v>0</v>
       </c>
       <c r="O16" s="3">
-        <v>412.21408373118408</v>
+        <v>413.9741355821696</v>
       </c>
       <c r="P16" s="3">
-        <v>3.6784035650035949</v>
+        <v>8.572203573752777</v>
       </c>
       <c r="Q16" s="4">
         <f>IF(O16=0,0,P16/O16)</f>
-        <v>8.9235271432462297E-3</v>
+        <v>0</v>
       </c>
       <c r="S16" s="3">
-        <v>4161.1302755545457</v>
+        <v>4161.261595787386</v>
       </c>
       <c r="T16" s="3">
-        <v>1579.6419727987229</v>
+        <v>1580.767524540937</v>
       </c>
       <c r="U16" s="4">
         <f>IF(S16=0,0,T16/S16)</f>
-        <v>0.37961848540976217</v>
+        <v>0</v>
       </c>
       <c r="V16" s="3">
-        <v>118273982.46310391</v>
+        <v>120996996.1158803</v>
       </c>
       <c r="W16" s="3">
-        <v>6057749.0648616999</v>
+        <v>5621454.428166643</v>
       </c>
       <c r="X16" s="4">
         <f>IF(V16=0,0,W16/V16)</f>
-        <v>5.1217934314095173E-2</v>
+        <v>0</v>
       </c>
       <c r="Y16" s="3">
-        <v>4603060.9719898822</v>
+        <v>2977965.268457345</v>
       </c>
       <c r="Z16" s="3">
-        <v>67998.015264652669</v>
+        <v>54152.6928228382</v>
       </c>
       <c r="AA16" s="4">
         <f>IF(Y16=0,0,Z16/Y16)</f>
-        <v>1.4772347287691355E-2</v>
+        <v>0</v>
       </c>
       <c r="AB16" s="3">
-        <v>153442.40495407421</v>
+        <v>144576.3607465195</v>
       </c>
       <c r="AC16" s="3">
-        <v>291.49157402050332</v>
+        <v>529.583738998248</v>
       </c>
       <c r="AD16" s="4">
         <f>IF(AB16=0,0,AC16/AB16)</f>
-        <v>1.8996806919687401E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30">
       <c r="B17" t="s">
         <v>33</v>
       </c>
       <c r="C17" s="3">
         <f>J17+M17+G17+P17</f>
-        <v>314.61496024507142</v>
+        <v>0</v>
       </c>
       <c r="D17" s="3">
         <f>G17</f>
-        <v>93.191254300931007</v>
+        <v>0</v>
       </c>
       <c r="E17" s="3">
         <f>J17+M17+P17</f>
-        <v>221.42370594414038</v>
+        <v>0</v>
       </c>
       <c r="F17" s="3">
-        <v>271.64518669470311</v>
+        <v>271.6537594878637</v>
       </c>
       <c r="G17" s="3">
-        <v>93.191254300931007</v>
+        <v>93.23687772785759</v>
       </c>
       <c r="H17" s="4">
         <f>IF(F17=0,0,G17/F17)</f>
-        <v>0.34306241695225359</v>
+        <v>0</v>
       </c>
       <c r="I17" s="3">
-        <v>3375.6401243953728</v>
+        <v>3865.802402615053</v>
       </c>
       <c r="J17" s="3">
-        <v>193.18814640416059</v>
+        <v>198.6845367286932</v>
       </c>
       <c r="K17" s="4">
         <f>IF(I17=0,0,J17/I17)</f>
-        <v>5.7230077640093066E-2</v>
+        <v>0</v>
       </c>
       <c r="L17" s="3">
-        <v>12894.33743826528</v>
+        <v>11750.93232102557</v>
       </c>
       <c r="M17" s="3">
-        <v>21.206282171037049</v>
+        <v>4.333740511480719</v>
       </c>
       <c r="N17" s="4">
         <f>IF(L17=0,0,M17/L17)</f>
-        <v>1.6446197621682534E-3</v>
+        <v>0</v>
       </c>
       <c r="O17" s="3">
-        <v>377.03051903276793</v>
+        <v>341.5371321492009</v>
       </c>
       <c r="P17" s="3">
-        <v>7.0292773689427417</v>
+        <v>0.00301307180308504</v>
       </c>
       <c r="Q17" s="4">
         <f>IF(O17=0,0,P17/O17)</f>
-        <v>1.8643788802496977E-2</v>
+        <v>0</v>
       </c>
       <c r="S17" s="3">
-        <v>3923.740781421468</v>
+        <v>3923.864609929325</v>
       </c>
       <c r="T17" s="3">
-        <v>1346.0879959685731</v>
+        <v>1346.746997156844</v>
       </c>
       <c r="U17" s="4">
         <f>IF(S17=0,0,T17/S17)</f>
-        <v>0.34306241695225359</v>
+        <v>0</v>
       </c>
       <c r="V17" s="3">
-        <v>111762860.6181328</v>
+        <v>114899915.8905035</v>
       </c>
       <c r="W17" s="3">
-        <v>5173153.5519152125</v>
+        <v>4852495.274701983</v>
       </c>
       <c r="X17" s="4">
         <f>IF(V17=0,0,W17/V17)</f>
-        <v>4.6286874935947207E-2</v>
+        <v>0</v>
       </c>
       <c r="Y17" s="3">
-        <v>4143959.5493767709</v>
+        <v>2573310.954592903</v>
       </c>
       <c r="Z17" s="3">
-        <v>58840.378214361153</v>
+        <v>41023.30992707051</v>
       </c>
       <c r="AA17" s="4">
         <f>IF(Y17=0,0,Z17/Y17)</f>
-        <v>1.4199071567484395E-2</v>
+        <v>0</v>
       </c>
       <c r="AB17" s="3">
-        <v>143913.11126295681</v>
+        <v>131096.0473902006</v>
       </c>
       <c r="AC17" s="3">
-        <v>235.6740385697631</v>
+        <v>48.14397627257858</v>
       </c>
       <c r="AD17" s="4">
         <f>IF(AB17=0,0,AC17/AB17)</f>
-        <v>1.6376133939536718E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30">
       <c r="B18" t="s">
         <v>34</v>
       </c>
       <c r="C18" s="3">
         <f>J18+M18+G18+P18</f>
-        <v>151.64468772831239</v>
+        <v>0</v>
       </c>
       <c r="D18" s="3">
         <f>G18</f>
-        <v>41.461504312807413</v>
+        <v>0</v>
       </c>
       <c r="E18" s="3">
         <f>J18+M18+P18</f>
-        <v>110.18318341550498</v>
+        <v>0</v>
       </c>
       <c r="F18" s="3">
-        <v>231.34880254278889</v>
+        <v>231.35610363086</v>
       </c>
       <c r="G18" s="3">
-        <v>41.461504312807413</v>
+        <v>41.44778951961637</v>
       </c>
       <c r="H18" s="4">
         <f>IF(F18=0,0,G18/F18)</f>
-        <v>0.17921642064751531</v>
+        <v>0</v>
       </c>
       <c r="I18" s="3">
-        <v>2992.321625738417</v>
+        <v>3364.499225271484</v>
       </c>
       <c r="J18" s="3">
-        <v>98.316756220339329</v>
+        <v>100.8917196531021</v>
       </c>
       <c r="K18" s="4">
         <f>IF(I18=0,0,J18/I18)</f>
-        <v>3.2856346515250559E-2</v>
+        <v>0</v>
       </c>
       <c r="L18" s="3">
-        <v>12338.372316285961</v>
+        <v>11621.53898497677</v>
       </c>
       <c r="M18" s="3">
-        <v>7.5329258607253431</v>
+        <v>12.99365256417356</v>
       </c>
       <c r="N18" s="4">
         <f>IF(L18=0,0,M18/L18)</f>
-        <v>6.1052833125989424E-4</v>
+        <v>0</v>
       </c>
       <c r="O18" s="3">
-        <v>347.46233821202492</v>
+        <v>214.6066033532331</v>
       </c>
       <c r="P18" s="3">
-        <v>4.3335013344403119</v>
+        <v>2.982047942264675</v>
       </c>
       <c r="Q18" s="4">
         <f>IF(O18=0,0,P18/O18)</f>
-        <v>1.2471859127926454E-2</v>
+        <v>0</v>
       </c>
       <c r="S18" s="3">
-        <v>3341.6853150075108</v>
+        <v>3341.790774549652</v>
       </c>
       <c r="T18" s="3">
-        <v>598.88488108601132</v>
+        <v>598.6867796802512</v>
       </c>
       <c r="U18" s="4">
         <f>IF(S18=0,0,T18/S18)</f>
-        <v>0.17921642064751547</v>
+        <v>0</v>
       </c>
       <c r="V18" s="3">
-        <v>104825402.45792779</v>
+        <v>107028313.8412168</v>
       </c>
       <c r="W18" s="3">
-        <v>2816078.9648278211</v>
+        <v>2678093.45510754</v>
       </c>
       <c r="X18" s="4">
         <f>IF(V18=0,0,W18/V18)</f>
-        <v>2.6864470813341916E-2</v>
+        <v>0</v>
       </c>
       <c r="Y18" s="3">
-        <v>3747214.4666106808</v>
+        <v>1541764.677188765</v>
       </c>
       <c r="Z18" s="3">
-        <v>31907.42939718673</v>
+        <v>16543.98430822045</v>
       </c>
       <c r="AA18" s="4">
         <f>IF(Y18=0,0,Z18/Y18)</f>
-        <v>8.5149728368888074E-3</v>
+        <v>0</v>
       </c>
       <c r="AB18" s="3">
-        <v>137695.65800858309</v>
+        <v>129651.7281020236</v>
       </c>
       <c r="AC18" s="3">
-        <v>83.726303176110378</v>
+        <v>144.4319288176921</v>
       </c>
       <c r="AD18" s="4">
         <f>IF(AB18=0,0,AC18/AB18)</f>
-        <v>6.0805332852900413E-4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30">
       <c r="A20" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30">
       <c r="B21" t="s">
         <v>28</v>
       </c>
       <c r="C21" s="3">
         <f>C23+C24+C25+C26+C27</f>
-        <v>1978.042623631017</v>
+        <v>0</v>
       </c>
       <c r="D21" s="3">
         <f>D23+D24+D25+D26+D27</f>
-        <v>1041.7813801093714</v>
+        <v>0</v>
       </c>
       <c r="E21" s="3">
         <f>E23+E24+E25+E26+E27</f>
-        <v>936.26124352164572</v>
+        <v>0</v>
       </c>
       <c r="F21" s="3">
         <f>F23+F24+F25+F26+F27</f>
-        <v>1859.1790728805329</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3">
         <f>G23+G24+G25+G26+G27</f>
-        <v>1041.7813801093714</v>
+        <v>0</v>
       </c>
       <c r="H21" s="4">
         <f>IF(F21=0,0,G21/F21)</f>
-        <v>0.56034482923437801</v>
+        <v>0</v>
       </c>
       <c r="I21" s="3">
         <f>I23+I24+I25+I26+I27</f>
-        <v>3682.4352162782898</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3">
         <f>J23+J24+J25+J26+J27</f>
-        <v>585.89953258422668</v>
+        <v>0</v>
       </c>
       <c r="K21" s="4">
         <f>IF(I21=0,0,J21/I21)</f>
-        <v>0.15910654177818098</v>
+        <v>0</v>
       </c>
       <c r="L21" s="3">
         <f>L23+L24+L25+L26+L27</f>
-        <v>75120.106151105079</v>
+        <v>0</v>
       </c>
       <c r="M21" s="3">
         <f>M23+M24+M25+M26+M27</f>
-        <v>270.09622799380867</v>
+        <v>0</v>
       </c>
       <c r="N21" s="4">
         <f>IF(L21=0,0,M21/L21)</f>
-        <v>3.5955251108206179E-3</v>
+        <v>0</v>
       </c>
       <c r="O21" s="3">
         <f>O23+O24+O25+O26+O27</f>
-        <v>1936.1737568351107</v>
+        <v>0</v>
       </c>
       <c r="P21" s="3">
         <f>P23+P24+P25+P26+P27</f>
-        <v>80.265482943610337</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="4">
         <f>IF(O21=0,0,P21/O21)</f>
-        <v>4.1455723000198653E-2</v>
+        <v>0</v>
       </c>
       <c r="S21" s="3">
         <f>S23+S24+S25+S26+S27</f>
-        <v>34100.200929874198</v>
+        <v>0</v>
       </c>
       <c r="T21" s="3">
         <f>T23+T24+T25+T26+T27</f>
-        <v>19107.871266908332</v>
+        <v>0</v>
       </c>
       <c r="U21" s="4">
         <f>IF(S21=0,0,T21/S21)</f>
-        <v>0.56034482923437789</v>
+        <v>0</v>
       </c>
       <c r="V21" s="3">
         <f>V23+V24+V25+V26+V27</f>
-        <v>106670224.92367341</v>
+        <v>0</v>
       </c>
       <c r="W21" s="3">
         <f>W23+W24+W25+W26+W27</f>
-        <v>13782093.295542261</v>
+        <v>0</v>
       </c>
       <c r="X21" s="4">
         <f>IF(V21=0,0,W21/V21)</f>
-        <v>0.12920281461301755</v>
+        <v>0</v>
       </c>
       <c r="Y21" s="3">
         <f>Y23+Y24+Y25+Y26+Y27</f>
-        <v>8082003.8383214176</v>
+        <v>0</v>
       </c>
       <c r="Z21" s="3">
         <f>Z23+Z24+Z25+Z26+Z27</f>
-        <v>334084.07649866142</v>
+        <v>0</v>
       </c>
       <c r="AA21" s="4">
         <f>IF(Y21=0,0,Z21/Y21)</f>
-        <v>4.1336787655875284E-2</v>
+        <v>0</v>
       </c>
       <c r="AB21" s="3">
         <f>AB23+AB24+AB25+AB26+AB27</f>
-        <v>844449.53447731666</v>
+        <v>0</v>
       </c>
       <c r="AC21" s="3">
         <f>AC23+AC24+AC25+AC26+AC27</f>
-        <v>2999.0317686344206</v>
+        <v>0</v>
       </c>
       <c r="AD21" s="4">
         <f>IF(AB21=0,0,AC21/AB21)</f>
-        <v>3.5514635821200509E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30">
       <c r="A22" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30">
       <c r="B23" t="s">
         <v>30</v>
       </c>
       <c r="C23" s="3">
         <f>J23+M23+G23+P23</f>
-        <v>516.60971559081213</v>
+        <v>0</v>
       </c>
       <c r="D23" s="3">
         <f>G23</f>
-        <v>268.73883356068632</v>
+        <v>0</v>
       </c>
       <c r="E23" s="3">
         <f>J23+M23+P23</f>
-        <v>247.87088203012584</v>
+        <v>0</v>
       </c>
       <c r="F23" s="3">
-        <v>414.1174655591563</v>
+        <v>414.1484899324265</v>
       </c>
       <c r="G23" s="3">
-        <v>268.73883356068632</v>
+        <v>268.7589666257657</v>
       </c>
       <c r="H23" s="4">
         <f>IF(F23=0,0,G23/F23)</f>
-        <v>0.64894349046067279</v>
+        <v>0</v>
       </c>
       <c r="I23" s="3">
-        <v>991.82050542122556</v>
+        <v>1107.546596802289</v>
       </c>
       <c r="J23" s="3">
-        <v>137.38025624613479</v>
+        <v>152.4997145741357</v>
       </c>
       <c r="K23" s="4">
         <f>IF(I23=0,0,J23/I23)</f>
-        <v>0.13851322441432029</v>
+        <v>0</v>
       </c>
       <c r="L23" s="3">
-        <v>18248.150900694091</v>
+        <v>16120.82381005316</v>
       </c>
       <c r="M23" s="3">
-        <v>92.706822166558354</v>
+        <v>76.40795565851592</v>
       </c>
       <c r="N23" s="4">
         <f>IF(L23=0,0,M23/L23)</f>
-        <v>5.0803406148418103E-3</v>
+        <v>0</v>
       </c>
       <c r="O23" s="3">
-        <v>476.04818802351332</v>
+        <v>723.3754445227719</v>
       </c>
       <c r="P23" s="3">
-        <v>17.78380361743271</v>
+        <v>15.17958729541011</v>
       </c>
       <c r="Q23" s="4">
         <f>IF(O23=0,0,P23/O23)</f>
-        <v>3.7357150105472768E-2</v>
+        <v>0</v>
       </c>
       <c r="S23" s="3">
-        <v>7595.5506331395254</v>
+        <v>7596.119667815998</v>
       </c>
       <c r="T23" s="3">
-        <v>4929.0831398403361</v>
+        <v>4929.45241118948</v>
       </c>
       <c r="U23" s="4">
         <f>IF(S23=0,0,T23/S23)</f>
-        <v>0.64894349046067268</v>
+        <v>0</v>
       </c>
       <c r="V23" s="3">
-        <v>25699987.560610589</v>
+        <v>27397369.30964229</v>
       </c>
       <c r="W23" s="3">
-        <v>2724438.1987594548</v>
+        <v>2862889.007549949</v>
       </c>
       <c r="X23" s="4">
         <f>IF(V23=0,0,W23/V23)</f>
-        <v>0.10600931974516203</v>
+        <v>0</v>
       </c>
       <c r="Y23" s="3">
-        <v>1959206.3612258229</v>
+        <v>3466946.620193956</v>
       </c>
       <c r="Z23" s="3">
-        <v>81685.476824872196</v>
+        <v>63540.57065191539</v>
       </c>
       <c r="AA23" s="4">
         <f>IF(Y23=0,0,Z23/Y23)</f>
-        <v>4.1693145980683619E-2</v>
+        <v>0</v>
       </c>
       <c r="AB23" s="3">
-        <v>205054.68928072241</v>
+        <v>181415.2838767417</v>
       </c>
       <c r="AC23" s="3">
-        <v>1029.3601439886841</v>
+        <v>848.497460117942</v>
       </c>
       <c r="AD23" s="4">
         <f>IF(AB23=0,0,AC23/AB23)</f>
-        <v>5.0199297933610151E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30">
       <c r="B24" t="s">
         <v>31</v>
       </c>
       <c r="C24" s="3">
         <f>J24+M24+G24+P24</f>
-        <v>493.50667596471601</v>
+        <v>0</v>
       </c>
       <c r="D24" s="3">
         <f>G24</f>
-        <v>265.1770602919006</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3">
         <f>J24+M24+P24</f>
-        <v>228.32961567281538</v>
+        <v>0</v>
       </c>
       <c r="F24" s="3">
-        <v>423.46088348022653</v>
+        <v>423.4926078328729</v>
       </c>
       <c r="G24" s="3">
-        <v>265.1770602919006</v>
+        <v>265.1969265201698</v>
       </c>
       <c r="H24" s="4">
         <f>IF(F24=0,0,G24/F24)</f>
-        <v>0.62621382667634995</v>
+        <v>0</v>
       </c>
       <c r="I24" s="3">
-        <v>847.52939170447485</v>
+        <v>948.9774541166404</v>
       </c>
       <c r="J24" s="3">
-        <v>129.63861091745869</v>
+        <v>142.748964041745</v>
       </c>
       <c r="K24" s="4">
         <f>IF(I24=0,0,J24/I24)</f>
-        <v>0.15296060784009058</v>
+        <v>0</v>
       </c>
       <c r="L24" s="3">
-        <v>18442.648959675</v>
+        <v>16501.50561536042</v>
       </c>
       <c r="M24" s="3">
-        <v>78.360818720057608</v>
+        <v>52.78168463824876</v>
       </c>
       <c r="N24" s="4">
         <f>IF(L24=0,0,M24/L24)</f>
-        <v>4.2488917341209588E-3</v>
+        <v>0</v>
       </c>
       <c r="O24" s="3">
-        <v>476.56393826290048</v>
+        <v>624.3217401430248</v>
       </c>
       <c r="P24" s="3">
-        <v>20.330186035299089</v>
+        <v>19.32593902341917</v>
       </c>
       <c r="Q24" s="4">
         <f>IF(O24=0,0,P24/O24)</f>
-        <v>4.2659933752863553E-2</v>
+        <v>0</v>
       </c>
       <c r="S24" s="3">
-        <v>7766.9232744992596</v>
+        <v>7767.505147873048</v>
       </c>
       <c r="T24" s="3">
-        <v>4863.7547452257877</v>
+        <v>4864.119122377824</v>
       </c>
       <c r="U24" s="4">
         <f>IF(S24=0,0,T24/S24)</f>
-        <v>0.62621382667634995</v>
+        <v>0</v>
       </c>
       <c r="V24" s="3">
-        <v>23322467.600951109</v>
+        <v>24895849.84707717</v>
       </c>
       <c r="W24" s="3">
-        <v>2821008.1417387952</v>
+        <v>2971447.301604643</v>
       </c>
       <c r="X24" s="4">
         <f>IF(V24=0,0,W24/V24)</f>
-        <v>0.12095667534012362</v>
+        <v>0</v>
       </c>
       <c r="Y24" s="3">
-        <v>2033978.1299748039</v>
+        <v>3460960.206983536</v>
       </c>
       <c r="Z24" s="3">
-        <v>83922.171154072974</v>
+        <v>80686.43892306788</v>
       </c>
       <c r="AA24" s="4">
         <f>IF(Y24=0,0,Z24/Y24)</f>
-        <v>4.1260114805222889E-2</v>
+        <v>0</v>
       </c>
       <c r="AB24" s="3">
-        <v>207305.28823611679</v>
+        <v>185755.6747304216</v>
       </c>
       <c r="AC24" s="3">
-        <v>870.34467375359964</v>
+        <v>587.4213185431727</v>
       </c>
       <c r="AD24" s="4">
         <f>IF(AB24=0,0,AC24/AB24)</f>
-        <v>4.1983717885782706E-3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30">
       <c r="B25" t="s">
         <v>32</v>
       </c>
       <c r="C25" s="3">
         <f>J25+M25+G25+P25</f>
-        <v>391.06609673602094</v>
+        <v>0</v>
       </c>
       <c r="D25" s="3">
         <f>G25</f>
-        <v>207.67060060169669</v>
+        <v>0</v>
       </c>
       <c r="E25" s="3">
         <f>J25+M25+P25</f>
-        <v>183.39549613432428</v>
+        <v>0</v>
       </c>
       <c r="F25" s="3">
-        <v>383.34862378459758</v>
+        <v>383.3773430533705</v>
       </c>
       <c r="G25" s="3">
-        <v>207.67060060169669</v>
+        <v>207.6861586275373</v>
       </c>
       <c r="H25" s="4">
         <f>IF(F25=0,0,G25/F25)</f>
-        <v>0.54172778436368185</v>
+        <v>0</v>
       </c>
       <c r="I25" s="3">
-        <v>721.62080381298233</v>
+        <v>812.8523144403116</v>
       </c>
       <c r="J25" s="3">
-        <v>117.9993820939182</v>
+        <v>128.6294993462358</v>
       </c>
       <c r="K25" s="4">
         <f>IF(I25=0,0,J25/I25)</f>
-        <v>0.16351992829255976</v>
+        <v>0</v>
       </c>
       <c r="L25" s="3">
-        <v>15355.961975565249</v>
+        <v>13855.15332898719</v>
       </c>
       <c r="M25" s="3">
-        <v>48.616281052693722</v>
+        <v>41.16427105860598</v>
       </c>
       <c r="N25" s="4">
         <f>IF(L25=0,0,M25/L25)</f>
-        <v>3.1659547692325001E-3</v>
+        <v>0</v>
       </c>
       <c r="O25" s="3">
-        <v>391.5266582641886</v>
+        <v>428.594830790502</v>
       </c>
       <c r="P25" s="3">
-        <v>16.77983298771235</v>
+        <v>9.669849821887212</v>
       </c>
       <c r="Q25" s="4">
         <f>IF(O25=0,0,P25/O25)</f>
-        <v>4.2857446954199227E-2</v>
+        <v>0</v>
       </c>
       <c r="S25" s="3">
-        <v>7031.2027969376404</v>
+        <v>7031.729552455706</v>
       </c>
       <c r="T25" s="3">
-        <v>3808.997912596752</v>
+        <v>3809.283270696449</v>
       </c>
       <c r="U25" s="4">
         <f>IF(S25=0,0,T25/S25)</f>
-        <v>0.54172778436368207</v>
+        <v>0</v>
       </c>
       <c r="V25" s="3">
-        <v>21162807.846375171</v>
+        <v>22560876.23580789</v>
       </c>
       <c r="W25" s="3">
-        <v>2800683.8604466021</v>
+        <v>2932316.708162963</v>
       </c>
       <c r="X25" s="4">
         <f>IF(V25=0,0,W25/V25)</f>
-        <v>0.13233989935443805</v>
+        <v>0</v>
       </c>
       <c r="Y25" s="3">
-        <v>1664123.912966297</v>
+        <v>2375109.44123459</v>
       </c>
       <c r="Z25" s="3">
-        <v>70162.630031719338</v>
+        <v>90804.77864285558</v>
       </c>
       <c r="AA25" s="4">
         <f>IF(Y25=0,0,Z25/Y25)</f>
-        <v>4.2161902419066026E-2</v>
+        <v>0</v>
       </c>
       <c r="AB25" s="3">
-        <v>172634.6152091868</v>
+        <v>155960.3600732053</v>
       </c>
       <c r="AC25" s="3">
-        <v>539.59249566448852</v>
+        <v>456.883247755788</v>
       </c>
       <c r="AD25" s="4">
         <f>IF(AB25=0,0,AC25/AB25)</f>
-        <v>3.1256332631242425E-3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30">
       <c r="B26" t="s">
         <v>33</v>
       </c>
       <c r="C26" s="3">
         <f>J26+M26+G26+P26</f>
-        <v>320.34355948644912</v>
+        <v>0</v>
       </c>
       <c r="D26" s="3">
         <f>G26</f>
-        <v>163.9528075835068</v>
+        <v>0</v>
       </c>
       <c r="E26" s="3">
         <f>J26+M26+P26</f>
-        <v>156.39075190294236</v>
+        <v>0</v>
       </c>
       <c r="F26" s="3">
-        <v>339.79970462374757</v>
+        <v>339.8251613449683</v>
       </c>
       <c r="G26" s="3">
-        <v>163.9528075835068</v>
+        <v>163.9650904102992</v>
       </c>
       <c r="H26" s="4">
         <f>IF(F26=0,0,G26/F26)</f>
-        <v>0.48249838170120829</v>
+        <v>0</v>
       </c>
       <c r="I26" s="3">
-        <v>656.23600296293523</v>
+        <v>744.1458417101434</v>
       </c>
       <c r="J26" s="3">
-        <v>111.9114792464019</v>
+        <v>121.7279523800384</v>
       </c>
       <c r="K26" s="4">
         <f>IF(I26=0,0,J26/I26)</f>
-        <v>0.17053541521817839</v>
+        <v>0</v>
       </c>
       <c r="L26" s="3">
-        <v>12320.893910346331</v>
+        <v>11219.30117507262</v>
       </c>
       <c r="M26" s="3">
-        <v>30.922360504940151</v>
+        <v>32.47551412506215</v>
       </c>
       <c r="N26" s="4">
         <f>IF(L26=0,0,M26/L26)</f>
-        <v>2.5097497576026888E-3</v>
+        <v>0</v>
       </c>
       <c r="O26" s="3">
-        <v>305.89771512841492</v>
+        <v>368.2018508453923</v>
       </c>
       <c r="P26" s="3">
-        <v>13.55691215160029</v>
+        <v>10.56337113784649</v>
       </c>
       <c r="Q26" s="4">
         <f>IF(O26=0,0,P26/O26)</f>
-        <v>4.4318448556927403E-2</v>
+        <v>0</v>
       </c>
       <c r="S26" s="3">
-        <v>6232.4487041632419</v>
+        <v>6232.915619546114</v>
       </c>
       <c r="T26" s="3">
-        <v>3007.1464137945559</v>
+        <v>3007.371699711184</v>
       </c>
       <c r="U26" s="4">
         <f>IF(S26=0,0,T26/S26)</f>
-        <v>0.48249838170120812</v>
+        <v>0</v>
       </c>
       <c r="V26" s="3">
-        <v>20232379.411657181</v>
+        <v>21620696.94544948</v>
       </c>
       <c r="W26" s="3">
-        <v>2815905.181914039</v>
+        <v>2935395.492038567</v>
       </c>
       <c r="X26" s="4">
         <f>IF(V26=0,0,W26/V26)</f>
-        <v>0.13917815223905963</v>
+        <v>0</v>
       </c>
       <c r="Y26" s="3">
-        <v>1291512.2728871789</v>
+        <v>1994907.132664039</v>
       </c>
       <c r="Z26" s="3">
-        <v>51650.776301899918</v>
+        <v>62564.5250197819</v>
       </c>
       <c r="AA26" s="4">
         <f>IF(Y26=0,0,Z26/Y26)</f>
-        <v>3.9992478109739119E-2</v>
+        <v>0</v>
       </c>
       <c r="AB26" s="3">
-        <v>138538.51808137319</v>
+        <v>126393.4870398669</v>
       </c>
       <c r="AC26" s="3">
-        <v>343.4734157078783</v>
+        <v>358.979694665235</v>
       </c>
       <c r="AD26" s="4">
         <f>IF(AB26=0,0,AC26/AB26)</f>
-        <v>2.479262954914335E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30">
       <c r="B27" t="s">
         <v>34</v>
       </c>
       <c r="C27" s="3">
         <f>J27+M27+G27+P27</f>
-        <v>256.51657585301888</v>
+        <v>0</v>
       </c>
       <c r="D27" s="3">
         <f>G27</f>
-        <v>136.24207807158101</v>
+        <v>0</v>
       </c>
       <c r="E27" s="3">
         <f>J27+M27+P27</f>
-        <v>120.27449778143787</v>
+        <v>0</v>
       </c>
       <c r="F27" s="3">
-        <v>298.45239543280491</v>
+        <v>298.4747545441425</v>
       </c>
       <c r="G27" s="3">
-        <v>136.24207807158101</v>
+        <v>136.2522848979928</v>
       </c>
       <c r="H27" s="4">
         <f>IF(F27=0,0,G27/F27)</f>
-        <v>0.45649517362394648</v>
+        <v>0</v>
       </c>
       <c r="I27" s="3">
-        <v>465.22851237667129</v>
+        <v>535.1312945240268</v>
       </c>
       <c r="J27" s="3">
-        <v>88.969804080313125</v>
+        <v>94.96583666364202</v>
       </c>
       <c r="K27" s="4">
         <f>IF(I27=0,0,J27/I27)</f>
-        <v>0.19123893251039376</v>
+        <v>0</v>
       </c>
       <c r="L27" s="3">
-        <v>10752.450404824391</v>
+        <v>9724.757436662885</v>
       </c>
       <c r="M27" s="3">
-        <v>19.489945549558851</v>
+        <v>14.68107258266397</v>
       </c>
       <c r="N27" s="4">
         <f>IF(L27=0,0,M27/L27)</f>
-        <v>1.8126050170679359E-3</v>
+        <v>0</v>
       </c>
       <c r="O27" s="3">
-        <v>286.13725715609343</v>
+        <v>253.2735972279527</v>
       </c>
       <c r="P27" s="3">
-        <v>11.814748151565899</v>
+        <v>7.899866345518909</v>
       </c>
       <c r="Q27" s="4">
         <f>IF(O27=0,0,P27/O27)</f>
-        <v>4.12904920840865E-2</v>
+        <v>0</v>
       </c>
       <c r="S27" s="3">
-        <v>5474.0755211345286</v>
+        <v>5474.485621592494</v>
       </c>
       <c r="T27" s="3">
-        <v>2498.8890554509012</v>
+        <v>2499.076264330658</v>
       </c>
       <c r="U27" s="4">
         <f>IF(S27=0,0,T27/S27)</f>
-        <v>0.45649517362394637</v>
+        <v>0</v>
       </c>
       <c r="V27" s="3">
-        <v>16252582.504079361</v>
+        <v>17458494.1520531</v>
       </c>
       <c r="W27" s="3">
-        <v>2620057.9126833701</v>
+        <v>2691934.235133365</v>
       </c>
       <c r="X27" s="4">
         <f>IF(V27=0,0,W27/V27)</f>
-        <v>0.16120871326299938</v>
+        <v>0</v>
       </c>
       <c r="Y27" s="3">
-        <v>1133183.161267315</v>
+        <v>1352213.618758281</v>
       </c>
       <c r="Z27" s="3">
-        <v>46663.02218609699</v>
+        <v>56513.04210055154</v>
       </c>
       <c r="AA27" s="4">
         <f>IF(Y27=0,0,Z27/Y27)</f>
-        <v>4.1178711245506497E-2</v>
+        <v>0</v>
       </c>
       <c r="AB27" s="3">
-        <v>120916.42366991749</v>
+        <v>109586.7104259936</v>
       </c>
       <c r="AC27" s="3">
-        <v>216.26103951976981</v>
+        <v>163.1725884842017</v>
       </c>
       <c r="AD27" s="4">
         <f>IF(AB27=0,0,AC27/AB27)</f>
-        <v>1.7885166709042592E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30">
       <c r="A29" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30">
       <c r="B30" t="s">
         <v>28</v>
       </c>
       <c r="C30" s="3">
         <f>C32+C33+C34+C35+C36</f>
-        <v>280.67849666325867</v>
+        <v>0</v>
       </c>
       <c r="D30" s="3">
         <f>D32+D33+D34+D35+D36</f>
-        <v>189.72309826269347</v>
+        <v>0</v>
       </c>
       <c r="E30" s="3">
         <f>E32+E33+E34+E35+E36</f>
-        <v>90.955398400565215</v>
+        <v>0</v>
       </c>
       <c r="F30" s="3">
         <f>F32+F33+F34+F35+F36</f>
-        <v>1859.1790728805329</v>
+        <v>0</v>
       </c>
       <c r="G30" s="3">
         <f>G32+G33+G34+G35+G36</f>
-        <v>189.72309826269347</v>
+        <v>0</v>
       </c>
       <c r="H30" s="4">
         <f>IF(F30=0,0,G30/F30)</f>
-        <v>0.1020467049302274</v>
+        <v>0</v>
       </c>
       <c r="I30" s="3">
         <f>I32+I33+I34+I35+I36</f>
-        <v>3682.4352162782898</v>
+        <v>0</v>
       </c>
       <c r="J30" s="3">
         <f>J32+J33+J34+J35+J36</f>
-        <v>73.986991036804866</v>
+        <v>0</v>
       </c>
       <c r="K30" s="4">
         <f>IF(I30=0,0,J30/I30)</f>
-        <v>2.0091864945714095E-2</v>
+        <v>0</v>
       </c>
       <c r="L30" s="3">
         <f>L32+L33+L34+L35+L36</f>
-        <v>75120.106151105079</v>
+        <v>0</v>
       </c>
       <c r="M30" s="3">
         <f>M32+M33+M34+M35+M36</f>
-        <v>7.7175543162524711</v>
+        <v>0</v>
       </c>
       <c r="N30" s="4">
         <f>IF(L30=0,0,M30/L30)</f>
-        <v>1.0273620088779572E-4</v>
+        <v>0</v>
       </c>
       <c r="O30" s="3">
         <f>O32+O33+O34+O35+O36</f>
-        <v>1936.1737568351107</v>
+        <v>0</v>
       </c>
       <c r="P30" s="3">
         <f>P32+P33+P34+P35+P36</f>
-        <v>9.2508530475078743</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="4">
         <f>IF(O30=0,0,P30/O30)</f>
-        <v>4.7779043667183123E-3</v>
+        <v>0</v>
       </c>
       <c r="S30" s="3">
         <f>S32+S33+S34+S35+S36</f>
-        <v>34100.200929874198</v>
+        <v>0</v>
       </c>
       <c r="T30" s="3">
         <f>T32+T33+T34+T35+T36</f>
-        <v>3479.8131423523364</v>
+        <v>0</v>
       </c>
       <c r="U30" s="4">
         <f>IF(S30=0,0,T30/S30)</f>
-        <v>0.10204670493022734</v>
+        <v>0</v>
       </c>
       <c r="V30" s="3">
         <f>V32+V33+V34+V35+V36</f>
-        <v>106670224.92367341</v>
+        <v>0</v>
       </c>
       <c r="W30" s="3">
         <f>W32+W33+W34+W35+W36</f>
-        <v>1767252.4081023186</v>
+        <v>0</v>
       </c>
       <c r="X30" s="4">
         <f>IF(V30=0,0,W30/V30)</f>
-        <v>1.6567438658415267E-2</v>
+        <v>0</v>
       </c>
       <c r="Y30" s="3">
         <f>Y32+Y33+Y34+Y35+Y36</f>
-        <v>8082003.8383214176</v>
+        <v>0</v>
       </c>
       <c r="Z30" s="3">
         <f>Z32+Z33+Z34+Z35+Z36</f>
-        <v>39755.677394214319</v>
+        <v>0</v>
       </c>
       <c r="AA30" s="4">
         <f>IF(Y30=0,0,Z30/Y30)</f>
-        <v>4.9190371830448582E-3</v>
+        <v>0</v>
       </c>
       <c r="AB30" s="3">
         <f>AB32+AB33+AB34+AB35+AB36</f>
-        <v>844449.53447731666</v>
+        <v>0</v>
       </c>
       <c r="AC30" s="3">
         <f>AC32+AC33+AC34+AC35+AC36</f>
-        <v>85.868353927085991</v>
+        <v>0</v>
       </c>
       <c r="AD30" s="4">
         <f>IF(AB30=0,0,AC30/AB30)</f>
-        <v>1.0168559567059903E-4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30">
       <c r="A31" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30">
       <c r="B32" t="s">
         <v>30</v>
       </c>
       <c r="C32" s="3">
         <f>J32+M32+G32+P32</f>
-        <v>31.460329582100499</v>
+        <v>0</v>
       </c>
       <c r="D32" s="3">
         <f>G32</f>
-        <v>17.33188958193897</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
         <f>J32+M32+P32</f>
-        <v>14.128440000161532</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>414.1174655591563</v>
+        <v>414.1484899324265</v>
       </c>
       <c r="G32" s="3">
-        <v>17.33188958193897</v>
+        <v>17.33318803239486</v>
       </c>
       <c r="H32" s="4">
         <f>IF(F32=0,0,G32/F32)</f>
-        <v>4.1852592617741512E-2</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>991.82050542122556</v>
+        <v>1107.546596802289</v>
       </c>
       <c r="J32" s="3">
-        <v>11.67126541163598</v>
+        <v>12.89635673957388</v>
       </c>
       <c r="K32" s="4">
         <f>IF(I32=0,0,J32/I32)</f>
-        <v>1.1767517759354251E-2</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3">
-        <v>18248.150900694091</v>
+        <v>16120.82381005316</v>
       </c>
       <c r="M32" s="3">
-        <v>1.0535630249716339</v>
+        <v>2.936306209890172</v>
       </c>
       <c r="N32" s="4">
         <f>IF(L32=0,0,M32/L32)</f>
-        <v>5.773533059349922E-5</v>
+        <v>0</v>
       </c>
       <c r="O32" s="3">
-        <v>476.04818802351332</v>
+        <v>723.3754445227719</v>
       </c>
       <c r="P32" s="3">
-        <v>1.403611563553917</v>
+        <v>0.0001449837468098849</v>
       </c>
       <c r="Q32" s="4">
         <f>IF(O32=0,0,P32/O32)</f>
-        <v>2.9484653000813204E-3</v>
+        <v>0</v>
       </c>
       <c r="S32" s="3">
-        <v>7595.5506331395254</v>
+        <v>7596.119667815998</v>
       </c>
       <c r="T32" s="3">
-        <v>317.89348635621809</v>
+        <v>317.9173019327191</v>
       </c>
       <c r="U32" s="4">
         <f>IF(S32=0,0,T32/S32)</f>
-        <v>4.1852592617741637E-2</v>
+        <v>0</v>
       </c>
       <c r="V32" s="3">
-        <v>25699987.560610589</v>
+        <v>27397369.30964229</v>
       </c>
       <c r="W32" s="3">
-        <v>227272.75268540901</v>
+        <v>238301.4702603519</v>
       </c>
       <c r="X32" s="4">
         <f>IF(V32=0,0,W32/V32)</f>
-        <v>8.8433020502212793E-3</v>
+        <v>0</v>
       </c>
       <c r="Y32" s="3">
-        <v>1959206.3612258229</v>
+        <v>3466946.620193956</v>
       </c>
       <c r="Z32" s="3">
-        <v>6013.3033886032636</v>
+        <v>4652.484179838095</v>
       </c>
       <c r="AA32" s="4">
         <f>IF(Y32=0,0,Z32/Y32)</f>
-        <v>3.0692547286549749E-3</v>
+        <v>0</v>
       </c>
       <c r="AB32" s="3">
-        <v>205054.68928072241</v>
+        <v>181415.2838767417</v>
       </c>
       <c r="AC32" s="3">
-        <v>11.66113448393298</v>
+        <v>32.63451769686071</v>
       </c>
       <c r="AD32" s="4">
         <f>IF(AB32=0,0,AC32/AB32)</f>
-        <v>5.686841166538134E-5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:30">
       <c r="B33" t="s">
         <v>31</v>
       </c>
       <c r="C33" s="3">
         <f>J33+M33+G33+P33</f>
-        <v>51.199869194986363</v>
+        <v>0</v>
       </c>
       <c r="D33" s="3">
         <f>G33</f>
-        <v>33.493628411801069</v>
+        <v>0</v>
       </c>
       <c r="E33" s="3">
         <f>J33+M33+P33</f>
-        <v>17.706240783185294</v>
+        <v>0</v>
       </c>
       <c r="F33" s="3">
-        <v>423.46088348022653</v>
+        <v>423.4926078328729</v>
       </c>
       <c r="G33" s="3">
-        <v>33.493628411801069</v>
+        <v>33.49613764871197</v>
       </c>
       <c r="H33" s="4">
         <f>IF(F33=0,0,G33/F33)</f>
-        <v>7.9094975990539274E-2</v>
+        <v>0</v>
       </c>
       <c r="I33" s="3">
-        <v>847.52939170447485</v>
+        <v>948.9774541166404</v>
       </c>
       <c r="J33" s="3">
-        <v>14.3231196181163</v>
+        <v>15.74554330159084</v>
       </c>
       <c r="K33" s="4">
         <f>IF(I33=0,0,J33/I33)</f>
-        <v>1.6899850032706158E-2</v>
+        <v>0</v>
       </c>
       <c r="L33" s="3">
-        <v>18442.648959675</v>
+        <v>16501.50561536042</v>
       </c>
       <c r="M33" s="3">
-        <v>1.708336847607046</v>
+        <v>2.9357372400444</v>
       </c>
       <c r="N33" s="4">
         <f>IF(L33=0,0,M33/L33)</f>
-        <v>9.2629689549605278E-5</v>
+        <v>0</v>
       </c>
       <c r="O33" s="3">
-        <v>476.56393826290048</v>
+        <v>624.3217401430248</v>
       </c>
       <c r="P33" s="3">
-        <v>1.6747843174619479</v>
+        <v>2.406011030815425</v>
       </c>
       <c r="Q33" s="4">
         <f>IF(O33=0,0,P33/O33)</f>
-        <v>3.514290912498795E-3</v>
+        <v>0</v>
       </c>
       <c r="S33" s="3">
-        <v>7766.9232744992596</v>
+        <v>7767.505147873048</v>
       </c>
       <c r="T33" s="3">
-        <v>614.32460991687913</v>
+        <v>614.3706331774092</v>
       </c>
       <c r="U33" s="4">
         <f>IF(S33=0,0,T33/S33)</f>
-        <v>7.9094975990539204E-2</v>
+        <v>0</v>
       </c>
       <c r="V33" s="3">
-        <v>23322467.600951109</v>
+        <v>24895849.84707717</v>
       </c>
       <c r="W33" s="3">
-        <v>307442.101903148</v>
+        <v>323332.1851536892</v>
       </c>
       <c r="X33" s="4">
         <f>IF(V33=0,0,W33/V33)</f>
-        <v>1.3182228705962926E-2</v>
+        <v>0</v>
       </c>
       <c r="Y33" s="3">
-        <v>2033978.1299748039</v>
+        <v>3460960.206983536</v>
       </c>
       <c r="Z33" s="3">
-        <v>8632.8553056851961</v>
+        <v>8784.410689205397</v>
       </c>
       <c r="AA33" s="4">
         <f>IF(Y33=0,0,Z33/Y33)</f>
-        <v>4.244320614102245E-3</v>
+        <v>0</v>
       </c>
       <c r="AB33" s="3">
-        <v>207305.28823611679</v>
+        <v>185755.6747304216</v>
       </c>
       <c r="AC33" s="3">
-        <v>19.081856428296309</v>
+        <v>32.63451769688982</v>
       </c>
       <c r="AD33" s="4">
         <f>IF(AB33=0,0,AC33/AB33)</f>
-        <v>9.2047128129999444E-5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:30">
       <c r="B34" t="s">
         <v>32</v>
       </c>
       <c r="C34" s="3">
         <f>J34+M34+G34+P34</f>
-        <v>61.694651508568448</v>
+        <v>0</v>
       </c>
       <c r="D34" s="3">
         <f>G34</f>
-        <v>41.906726289321213</v>
+        <v>0</v>
       </c>
       <c r="E34" s="3">
         <f>J34+M34+P34</f>
-        <v>19.787925219247239</v>
+        <v>0</v>
       </c>
       <c r="F34" s="3">
-        <v>383.34862378459758</v>
+        <v>383.3773430533705</v>
       </c>
       <c r="G34" s="3">
-        <v>41.906726289321213</v>
+        <v>41.90986580896727</v>
       </c>
       <c r="H34" s="4">
         <f>IF(F34=0,0,G34/F34)</f>
-        <v>0.10931753419537114</v>
+        <v>0</v>
       </c>
       <c r="I34" s="3">
-        <v>721.62080381298233</v>
+        <v>812.8523144403116</v>
       </c>
       <c r="J34" s="3">
-        <v>15.78004529479356</v>
+        <v>17.25960862774099</v>
       </c>
       <c r="K34" s="4">
         <f>IF(I34=0,0,J34/I34)</f>
-        <v>2.1867503280688632E-2</v>
+        <v>0</v>
       </c>
       <c r="L34" s="3">
-        <v>15355.961975565249</v>
+        <v>13855.15332898719</v>
       </c>
       <c r="M34" s="3">
-        <v>1.813587757010013</v>
+        <v>0.0005689698457717895</v>
       </c>
       <c r="N34" s="4">
         <f>IF(L34=0,0,M34/L34)</f>
-        <v>1.181031680005352E-4</v>
+        <v>0</v>
       </c>
       <c r="O34" s="3">
-        <v>391.5266582641886</v>
+        <v>428.594830790502</v>
       </c>
       <c r="P34" s="3">
-        <v>2.194292167443666</v>
+        <v>0.0004414568266365677</v>
       </c>
       <c r="Q34" s="4">
         <f>IF(O34=0,0,P34/O34)</f>
-        <v>5.6044515006256198E-3</v>
+        <v>0</v>
       </c>
       <c r="S34" s="3">
-        <v>7031.2027969376404</v>
+        <v>7031.729552455706</v>
       </c>
       <c r="T34" s="3">
-        <v>768.63375218881993</v>
+        <v>768.6913358031779</v>
       </c>
       <c r="U34" s="4">
         <f>IF(S34=0,0,T34/S34)</f>
-        <v>0.10931753419537117</v>
+        <v>0</v>
       </c>
       <c r="V34" s="3">
-        <v>21162807.846375171</v>
+        <v>22560876.23580789</v>
       </c>
       <c r="W34" s="3">
-        <v>369371.39764320478</v>
+        <v>387281.120965641</v>
       </c>
       <c r="X34" s="4">
         <f>IF(V34=0,0,W34/V34)</f>
-        <v>1.7453799152009584E-2</v>
+        <v>0</v>
       </c>
       <c r="Y34" s="3">
-        <v>1664123.912966297</v>
+        <v>2375109.44123459</v>
       </c>
       <c r="Z34" s="3">
-        <v>9278.7286326091271</v>
+        <v>12916.33719857177</v>
       </c>
       <c r="AA34" s="4">
         <f>IF(Y34=0,0,Z34/Y34)</f>
-        <v>5.5757438255122568E-3</v>
+        <v>0</v>
       </c>
       <c r="AB34" s="3">
-        <v>172634.6152091868</v>
+        <v>155960.3600732053</v>
       </c>
       <c r="AC34" s="3">
-        <v>20.141959563101409</v>
+        <v>0</v>
       </c>
       <c r="AD34" s="4">
         <f>IF(AB34=0,0,AC34/AB34)</f>
-        <v>1.1667393320102554E-4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:30">
       <c r="B35" t="s">
         <v>33</v>
       </c>
       <c r="C35" s="3">
         <f>J35+M35+G35+P35</f>
-        <v>69.409153233409029</v>
+        <v>0</v>
       </c>
       <c r="D35" s="3">
         <f>G35</f>
-        <v>49.152212620382947</v>
+        <v>0</v>
       </c>
       <c r="E35" s="3">
         <f>J35+M35+P35</f>
-        <v>20.256940613026089</v>
+        <v>0</v>
       </c>
       <c r="F35" s="3">
-        <v>339.79970462374757</v>
+        <v>339.8251613449683</v>
       </c>
       <c r="G35" s="3">
-        <v>49.152212620382947</v>
+        <v>49.15589494899305</v>
       </c>
       <c r="H35" s="4">
         <f>IF(F35=0,0,G35/F35)</f>
-        <v>0.14465054545826656</v>
+        <v>0</v>
       </c>
       <c r="I35" s="3">
-        <v>656.23600296293523</v>
+        <v>744.1458417101434</v>
       </c>
       <c r="J35" s="3">
-        <v>17.337373260950319</v>
+        <v>18.85750915282103</v>
       </c>
       <c r="K35" s="4">
         <f>IF(I35=0,0,J35/I35)</f>
-        <v>2.6419417987844761E-2</v>
+        <v>0</v>
       </c>
       <c r="L35" s="3">
-        <v>12320.893910346331</v>
+        <v>11219.30117507262</v>
       </c>
       <c r="M35" s="3">
-        <v>0.76115932066179814</v>
+        <v>5.872163870286196</v>
       </c>
       <c r="N35" s="4">
         <f>IF(L35=0,0,M35/L35)</f>
-        <v>6.1777929929469097E-5</v>
+        <v>0</v>
       </c>
       <c r="O35" s="3">
-        <v>305.89771512841492</v>
+        <v>368.2018508453923</v>
       </c>
       <c r="P35" s="3">
-        <v>2.158408031413972</v>
+        <v>0.000322572767152451</v>
       </c>
       <c r="Q35" s="4">
         <f>IF(O35=0,0,P35/O35)</f>
-        <v>7.0559795796705412E-3</v>
+        <v>0</v>
       </c>
       <c r="S35" s="3">
-        <v>6232.4487041632419</v>
+        <v>6232.915619546114</v>
       </c>
       <c r="T35" s="3">
-        <v>901.52710459787795</v>
+        <v>901.5946441626938</v>
       </c>
       <c r="U35" s="4">
         <f>IF(S35=0,0,T35/S35)</f>
-        <v>0.14465054545826631</v>
+        <v>0</v>
       </c>
       <c r="V35" s="3">
-        <v>20232379.411657181</v>
+        <v>21620696.94544948</v>
       </c>
       <c r="W35" s="3">
-        <v>430534.00670235232</v>
+        <v>448888.7868992649</v>
       </c>
       <c r="X35" s="4">
         <f>IF(V35=0,0,W35/V35)</f>
-        <v>2.1279454973758244E-2</v>
+        <v>0</v>
       </c>
       <c r="Y35" s="3">
-        <v>1291512.2728871789</v>
+        <v>1994907.132664039</v>
       </c>
       <c r="Z35" s="3">
-        <v>8071.8257655487396</v>
+        <v>9630.316903721308</v>
       </c>
       <c r="AA35" s="4">
         <f>IF(Y35=0,0,Z35/Y35)</f>
-        <v>6.2499024864116487E-3</v>
+        <v>0</v>
       </c>
       <c r="AB35" s="3">
-        <v>138538.51808137319</v>
+        <v>126393.4870398669</v>
       </c>
       <c r="AC35" s="3">
-        <v>8.4808250792266335</v>
+        <v>65.26903539367777</v>
       </c>
       <c r="AD35" s="4">
         <f>IF(AB35=0,0,AC35/AB35)</f>
-        <v>6.1216369257286713E-5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:30">
       <c r="B36" t="s">
         <v>34</v>
       </c>
       <c r="C36" s="3">
         <f>J36+M36+G36+P36</f>
-        <v>66.914493144194338</v>
+        <v>0</v>
       </c>
       <c r="D36" s="3">
         <f>G36</f>
-        <v>47.838641359249273</v>
+        <v>0</v>
       </c>
       <c r="E36" s="3">
         <f>J36+M36+P36</f>
-        <v>19.075851784945058</v>
+        <v>0</v>
       </c>
       <c r="F36" s="3">
-        <v>298.45239543280491</v>
+        <v>298.4747545441425</v>
       </c>
       <c r="G36" s="3">
-        <v>47.838641359249273</v>
+        <v>47.84222527924707</v>
       </c>
       <c r="H36" s="4">
         <f>IF(F36=0,0,G36/F36)</f>
-        <v>0.16028901791816882</v>
+        <v>0</v>
       </c>
       <c r="I36" s="3">
-        <v>465.22851237667129</v>
+        <v>535.1312945240268</v>
       </c>
       <c r="J36" s="3">
-        <v>14.87518745130871</v>
+        <v>15.89358763886744</v>
       </c>
       <c r="K36" s="4">
         <f>IF(I36=0,0,J36/I36)</f>
-        <v>3.1973937657683901E-2</v>
+        <v>0</v>
       </c>
       <c r="L36" s="3">
-        <v>10752.450404824391</v>
+        <v>9724.757436662885</v>
       </c>
       <c r="M36" s="3">
-        <v>2.3809073660019791</v>
+        <v>2.936306209890172</v>
       </c>
       <c r="N36" s="4">
         <f>IF(L36=0,0,M36/L36)</f>
-        <v>2.2142928136024861E-4</v>
+        <v>0</v>
       </c>
       <c r="O36" s="3">
-        <v>286.13725715609343</v>
+        <v>253.2735972279527</v>
       </c>
       <c r="P36" s="3">
-        <v>1.8197569676343699</v>
+        <v>0.0003739841311180499</v>
       </c>
       <c r="Q36" s="4">
         <f>IF(O36=0,0,P36/O36)</f>
-        <v>6.3597344355672538E-3</v>
+        <v>0</v>
       </c>
       <c r="S36" s="3">
-        <v>5474.0755211345286</v>
+        <v>5474.485621592494</v>
       </c>
       <c r="T36" s="3">
-        <v>877.4341892925413</v>
+        <v>877.4999238921964</v>
       </c>
       <c r="U36" s="4">
         <f>IF(S36=0,0,T36/S36)</f>
-        <v>0.16028901791816874</v>
+        <v>0</v>
       </c>
       <c r="V36" s="3">
-        <v>16252582.504079361</v>
+        <v>17458494.1520531</v>
       </c>
       <c r="W36" s="3">
-        <v>432632.14916820452</v>
+        <v>444956.1308084317</v>
       </c>
       <c r="X36" s="4">
         <f>IF(V36=0,0,W36/V36)</f>
-        <v>2.6619286446299524E-2</v>
+        <v>0</v>
       </c>
       <c r="Y36" s="3">
-        <v>1133183.161267315</v>
+        <v>1352213.618758281</v>
       </c>
       <c r="Z36" s="3">
-        <v>7758.9643017679919</v>
+        <v>9435.107777294004</v>
       </c>
       <c r="AA36" s="4">
         <f>IF(Y36=0,0,Z36/Y36)</f>
-        <v>6.8470522391901939E-3</v>
+        <v>0</v>
       </c>
       <c r="AB36" s="3">
-        <v>120916.42366991749</v>
+        <v>109586.7104259936</v>
       </c>
       <c r="AC36" s="3">
-        <v>26.50257837252866</v>
+        <v>32.63451769686071</v>
       </c>
       <c r="AD36" s="4">
         <f>IF(AB36=0,0,AC36/AB36)</f>
-        <v>2.1918096457166532E-4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:30">
       <c r="A38" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:30">
       <c r="B39" t="s">
         <v>28</v>
       </c>
       <c r="C39" s="3">
         <f>C41+C42+C43+C44+C45</f>
-        <v>278.75634518647166</v>
+        <v>0</v>
       </c>
       <c r="D39" s="3">
         <f>D41+D42+D43+D44+D45</f>
-        <v>278.75634518647166</v>
+        <v>0</v>
       </c>
       <c r="E39" s="3">
         <f>E41+E42+E43+E44+E45</f>
@@ -3206,27 +3177,27 @@
       </c>
       <c r="F39" s="3">
         <f>F41+F42+F43+F44+F45</f>
-        <v>651.08593726395497</v>
+        <v>0</v>
       </c>
       <c r="G39" s="3">
         <f>G41+G42+G43+G44+G45</f>
-        <v>270.32651231194274</v>
+        <v>0</v>
       </c>
       <c r="H39" s="4">
         <f>IF(F39=0,0,G39/F39)</f>
-        <v>0.41519328991796423</v>
+        <v>0</v>
       </c>
       <c r="I39" s="3">
         <f>I41+I42+I43+I44+I45</f>
-        <v>814.53034621778045</v>
+        <v>0</v>
       </c>
       <c r="J39" s="6">
         <f>J41+J42+J43+J44+J45</f>
-        <v>8.4298328745289179</v>
+        <v>0</v>
       </c>
       <c r="K39" s="7">
         <f>IF(I39=0,0,J39/I39)</f>
-        <v>1.0349317141678402E-2</v>
+        <v>0</v>
       </c>
       <c r="L39" s="3">
         <f>L41+L42+L43+L44+L45</f>
@@ -3254,27 +3225,27 @@
       </c>
       <c r="S39" s="3">
         <f>S41+S42+S43+S44+S45</f>
-        <v>8683.3005265167885</v>
+        <v>0</v>
       </c>
       <c r="T39" s="3">
         <f>T41+T42+T43+T44+T45</f>
-        <v>3605.2481129508969</v>
+        <v>0</v>
       </c>
       <c r="U39" s="4">
         <f>IF(S39=0,0,T39/S39)</f>
-        <v>0.41519328991796428</v>
+        <v>0</v>
       </c>
       <c r="V39" s="3">
         <f>V41+V42+V43+V44+V45</f>
-        <v>26890169.836246081</v>
+        <v>0</v>
       </c>
       <c r="W39" s="6">
         <f>W41+W42+W43+W44+W45</f>
-        <v>317460.72176834382</v>
+        <v>0</v>
       </c>
       <c r="X39" s="7">
         <f>IF(V39=0,0,W39/V39)</f>
-        <v>1.1805828066598108E-2</v>
+        <v>0</v>
       </c>
       <c r="Y39" s="3">
         <f>Y41+Y42+Y43+Y44+Y45</f>
@@ -3301,46 +3272,46 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:30">
       <c r="A40" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:30">
       <c r="B41" t="s">
         <v>30</v>
       </c>
       <c r="C41" s="3">
         <f>J41+M41+G41+P41</f>
-        <v>74.745208573138058</v>
+        <v>0</v>
       </c>
       <c r="D41" s="3">
         <f>J41+G41</f>
-        <v>74.745208573138058</v>
+        <v>0</v>
       </c>
       <c r="E41" s="3">
-        <f>M41+P41</f>
+        <f>P41+M41</f>
         <v>0</v>
       </c>
       <c r="F41" s="3">
-        <v>155.69318362382799</v>
+        <v>155.6880585335985</v>
       </c>
       <c r="G41" s="3">
-        <v>72.167708957411648</v>
+        <v>72.16533334910662</v>
       </c>
       <c r="H41" s="4">
         <f>IF(F41=0,0,G41/F41)</f>
-        <v>0.46352516711185532</v>
+        <v>0</v>
       </c>
       <c r="I41" s="3">
-        <v>289.90090139463632</v>
+        <v>382.3073643284127</v>
       </c>
       <c r="J41" s="6">
-        <v>2.5774996157264098</v>
+        <v>3.356936426061671</v>
       </c>
       <c r="K41" s="7">
         <f>IF(I41=0,0,J41/I41)</f>
-        <v>8.8909679249934825E-3</v>
+        <v>0</v>
       </c>
       <c r="L41" s="3">
         <v>0</v>
@@ -3363,24 +3334,24 @@
         <v>0</v>
       </c>
       <c r="S41" s="3">
-        <v>2076.4243642199531</v>
+        <v>2076.356012722646</v>
       </c>
       <c r="T41" s="3">
-        <v>962.47495042018159</v>
+        <v>962.4432677809709</v>
       </c>
       <c r="U41" s="4">
         <f>IF(S41=0,0,T41/S41)</f>
-        <v>0.46352516711185526</v>
+        <v>0</v>
       </c>
       <c r="V41" s="3">
-        <v>7917202.4300766056</v>
+        <v>9070418.669545408</v>
       </c>
       <c r="W41" s="6">
-        <v>75888.026322795078</v>
+        <v>78807.32897765189</v>
       </c>
       <c r="X41" s="7">
         <f>IF(V41=0,0,W41/V41)</f>
-        <v>9.585207274037175E-3</v>
+        <v>0</v>
       </c>
       <c r="Y41" s="3">
         <v>0</v>
@@ -3403,41 +3374,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:30">
       <c r="B42" t="s">
         <v>31</v>
       </c>
       <c r="C42" s="3">
         <f>J42+M42+G42+P42</f>
-        <v>75.003443181858643</v>
+        <v>0</v>
       </c>
       <c r="D42" s="3">
         <f>J42+G42</f>
-        <v>75.003443181858643</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <f>M42+P42</f>
+        <f>P42+M42</f>
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>148.09982986674899</v>
+        <v>148.0949547336612</v>
       </c>
       <c r="G42" s="3">
-        <v>72.910490479003187</v>
+        <v>72.90809041990182</v>
       </c>
       <c r="H42" s="4">
         <f>IF(F42=0,0,G42/F42)</f>
-        <v>0.4923063756697324</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>172.51020331953049</v>
+        <v>245.090682899663</v>
       </c>
       <c r="J42" s="6">
-        <v>2.0929527028554591</v>
+        <v>2.9365686601786</v>
       </c>
       <c r="K42" s="7">
         <f>IF(I42=0,0,J42/I42)</f>
-        <v>1.2132341522888394E-2</v>
+        <v>0</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
@@ -3460,24 +3431,24 @@
         <v>0</v>
       </c>
       <c r="S42" s="3">
-        <v>1975.1545181010979</v>
+        <v>1975.089500192884</v>
       </c>
       <c r="T42" s="3">
-        <v>972.38116219404844</v>
+        <v>972.3491534633023</v>
       </c>
       <c r="U42" s="4">
         <f>IF(S42=0,0,T42/S42)</f>
-        <v>0.49230637566973245</v>
+        <v>0</v>
       </c>
       <c r="V42" s="3">
-        <v>5775458.9344058</v>
+        <v>7100767.677214347</v>
       </c>
       <c r="W42" s="6">
-        <v>81365.067625927739</v>
+        <v>91738.12470871955</v>
       </c>
       <c r="X42" s="7">
         <f>IF(V42=0,0,W42/V42)</f>
-        <v>1.4088069632218564E-2</v>
+        <v>0</v>
       </c>
       <c r="Y42" s="3">
         <v>0</v>
@@ -3500,41 +3471,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:30">
       <c r="B43" t="s">
         <v>32</v>
       </c>
       <c r="C43" s="3">
         <f>J43+M43+G43+P43</f>
-        <v>75.235790083751482</v>
+        <v>0</v>
       </c>
       <c r="D43" s="3">
         <f>J43+G43</f>
-        <v>75.235790083751482</v>
+        <v>0</v>
       </c>
       <c r="E43" s="3">
-        <f>M43+P43</f>
+        <f>P43+M43</f>
         <v>0</v>
       </c>
       <c r="F43" s="3">
-        <v>134.796744990006</v>
+        <v>134.7923077663291</v>
       </c>
       <c r="G43" s="3">
-        <v>72.948475873586105</v>
+        <v>72.94607456408596</v>
       </c>
       <c r="H43" s="4">
         <f>IF(F43=0,0,G43/F43)</f>
-        <v>0.54117386795203837</v>
+        <v>0</v>
       </c>
       <c r="I43" s="3">
-        <v>135.45605543604131</v>
+        <v>200.4130880433794</v>
       </c>
       <c r="J43" s="6">
-        <v>2.2873142101653792</v>
+        <v>3.271171722685744</v>
       </c>
       <c r="K43" s="7">
         <f>IF(I43=0,0,J43/I43)</f>
-        <v>1.6886024052615255E-2</v>
+        <v>0</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -3557,24 +3528,24 @@
         <v>0</v>
       </c>
       <c r="S43" s="3">
-        <v>1797.736028001397</v>
+        <v>1797.676850334541</v>
       </c>
       <c r="T43" s="3">
-        <v>972.88775983024993</v>
+        <v>972.8557344233816</v>
       </c>
       <c r="U43" s="4">
         <f>IF(S43=0,0,T43/S43)</f>
-        <v>0.54117386795203837</v>
+        <v>0</v>
       </c>
       <c r="V43" s="3">
-        <v>4941006.3189266957</v>
+        <v>6292834.208210533</v>
       </c>
       <c r="W43" s="6">
-        <v>93694.982139615342</v>
+        <v>108314.0966329305</v>
       </c>
       <c r="X43" s="7">
         <f>IF(V43=0,0,W43/V43)</f>
-        <v>1.8962732709066465E-2</v>
+        <v>0</v>
       </c>
       <c r="Y43" s="3">
         <v>0</v>
@@ -3597,41 +3568,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:30">
       <c r="B44" t="s">
         <v>33</v>
       </c>
       <c r="C44" s="3">
         <f>J44+M44+G44+P44</f>
-        <v>34.066310779577314</v>
+        <v>0</v>
       </c>
       <c r="D44" s="3">
         <f>J44+G44</f>
-        <v>34.066310779577314</v>
+        <v>0</v>
       </c>
       <c r="E44" s="3">
-        <f>M44+P44</f>
+        <f>P44+M44</f>
         <v>0</v>
       </c>
       <c r="F44" s="3">
-        <v>118.7859525719791</v>
+        <v>118.7820423897171</v>
       </c>
       <c r="G44" s="3">
-        <v>33.213641030588931</v>
+        <v>33.21254770779109</v>
       </c>
       <c r="H44" s="4">
         <f>IF(F44=0,0,G44/F44)</f>
-        <v>0.27960916515328627</v>
+        <v>0</v>
       </c>
       <c r="I44" s="3">
-        <v>131.31388542968341</v>
+        <v>193.9015574705648</v>
       </c>
       <c r="J44" s="6">
-        <v>0.85266974898838088</v>
+        <v>1.247128400560556</v>
       </c>
       <c r="K44" s="7">
         <f>IF(I44=0,0,J44/I44)</f>
-        <v>6.4933707977514118E-3</v>
+        <v>0</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3654,24 +3625,24 @@
         <v>0</v>
       </c>
       <c r="S44" s="3">
-        <v>1584.2058098283051</v>
+        <v>1584.153661124499</v>
       </c>
       <c r="T44" s="3">
-        <v>442.95846391707801</v>
+        <v>442.9438826615435</v>
       </c>
       <c r="U44" s="4">
         <f>IF(S44=0,0,T44/S44)</f>
-        <v>0.27960916515328615</v>
+        <v>0</v>
       </c>
       <c r="V44" s="3">
-        <v>4714339.9302510964</v>
+        <v>6053045.584847068</v>
       </c>
       <c r="W44" s="6">
-        <v>37175.273221418262</v>
+        <v>44071.79961647</v>
       </c>
       <c r="X44" s="7">
         <f>IF(V44=0,0,W44/V44)</f>
-        <v>7.885573329761612E-3</v>
+        <v>0</v>
       </c>
       <c r="Y44" s="3">
         <v>0</v>
@@ -3694,41 +3665,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:30">
       <c r="B45" t="s">
         <v>34</v>
       </c>
       <c r="C45" s="3">
         <f>J45+M45+G45+P45</f>
-        <v>19.70559256814618</v>
+        <v>0</v>
       </c>
       <c r="D45" s="3">
         <f>J45+G45</f>
-        <v>19.70559256814618</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3">
-        <f>M45+P45</f>
+        <f>P45+M45</f>
         <v>0</v>
       </c>
       <c r="F45" s="3">
-        <v>93.71022621139285</v>
+        <v>93.70714146899384</v>
       </c>
       <c r="G45" s="3">
-        <v>19.08619597135289</v>
+        <v>19.08556769415914</v>
       </c>
       <c r="H45" s="4">
         <f>IF(F45=0,0,G45/F45)</f>
-        <v>0.20367249918165792</v>
+        <v>0</v>
       </c>
       <c r="I45" s="3">
-        <v>85.349300637888987</v>
+        <v>136.6145524202559</v>
       </c>
       <c r="J45" s="6">
-        <v>0.61939659679328907</v>
+        <v>0.9404859014340036</v>
       </c>
       <c r="K45" s="7">
         <f>IF(I45=0,0,J45/I45)</f>
-        <v>7.2571959250281341E-3</v>
+        <v>0</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -3751,24 +3722,24 @@
         <v>0</v>
       </c>
       <c r="S45" s="3">
-        <v>1249.7798063660359</v>
+        <v>1249.738666258772</v>
       </c>
       <c r="T45" s="3">
-        <v>254.545776589339</v>
+        <v>254.5373974808759</v>
       </c>
       <c r="U45" s="4">
         <f>IF(S45=0,0,T45/S45)</f>
-        <v>0.20367249918165789</v>
+        <v>0</v>
       </c>
       <c r="V45" s="3">
-        <v>3542162.2225858839</v>
+        <v>4890905.466101354</v>
       </c>
       <c r="W45" s="6">
-        <v>29337.372458587401</v>
+        <v>36723.80325047113</v>
       </c>
       <c r="X45" s="7">
         <f>IF(V45=0,0,W45/V45)</f>
-        <v>8.2823345219830858E-3</v>
+        <v>0</v>
       </c>
       <c r="Y45" s="3">
         <v>0</v>
@@ -3791,22 +3762,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:30">
       <c r="A47" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:30">
       <c r="B48" t="s">
         <v>28</v>
       </c>
       <c r="C48" s="3">
         <f>C50+C51+C52+C53+C54</f>
-        <v>528.42153794517515</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3">
         <f>D50+D51+D52+D53+D54</f>
-        <v>528.42153794517515</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3">
         <f>E50+E51+E52+E53+E54</f>
@@ -3814,27 +3785,27 @@
       </c>
       <c r="F48" s="3">
         <f>F50+F51+F52+F53+F54</f>
-        <v>651.08593726395497</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3">
         <f>G50+G51+G52+G53+G54</f>
-        <v>497.58010436954146</v>
+        <v>0</v>
       </c>
       <c r="H48" s="4">
         <f>IF(F48=0,0,G48/F48)</f>
-        <v>0.76423107287574366</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3">
         <f>I50+I51+I52+I53+I54</f>
-        <v>814.53034621778045</v>
+        <v>0</v>
       </c>
       <c r="J48" s="6">
         <f>J50+J51+J52+J53+J54</f>
-        <v>30.841433575633754</v>
+        <v>0</v>
       </c>
       <c r="K48" s="7">
         <f>IF(I48=0,0,J48/I48)</f>
-        <v>3.7864069422144896E-2</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3">
         <f>L50+L51+L52+L53+L54</f>
@@ -3862,27 +3833,27 @@
       </c>
       <c r="S48" s="3">
         <f>S50+S51+S52+S53+S54</f>
-        <v>8683.3005265167885</v>
+        <v>0</v>
       </c>
       <c r="T48" s="3">
         <f>T50+T51+T52+T53+T54</f>
-        <v>6636.0480774824346</v>
+        <v>0</v>
       </c>
       <c r="U48" s="4">
         <f>IF(S48=0,0,T48/S48)</f>
-        <v>0.76423107287574354</v>
+        <v>0</v>
       </c>
       <c r="V48" s="3">
         <f>V50+V51+V52+V53+V54</f>
-        <v>26890169.836246081</v>
+        <v>0</v>
       </c>
       <c r="W48" s="6">
         <f>W50+W51+W52+W53+W54</f>
-        <v>1188772.635306214</v>
+        <v>0</v>
       </c>
       <c r="X48" s="7">
         <f>IF(V48=0,0,W48/V48)</f>
-        <v>4.420844652694722E-2</v>
+        <v>0</v>
       </c>
       <c r="Y48" s="3">
         <f>Y50+Y51+Y52+Y53+Y54</f>
@@ -3909,46 +3880,46 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:30">
       <c r="A49" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="50" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:30">
       <c r="B50" t="s">
         <v>30</v>
       </c>
       <c r="C50" s="3">
         <f>J50+M50+G50+P50</f>
-        <v>137.72092160936992</v>
+        <v>0</v>
       </c>
       <c r="D50" s="3">
         <f>J50+G50</f>
-        <v>137.72092160936992</v>
+        <v>0</v>
       </c>
       <c r="E50" s="3">
-        <f>M50+P50</f>
+        <f>P50+M50</f>
         <v>0</v>
       </c>
       <c r="F50" s="3">
-        <v>155.69318362382799</v>
+        <v>155.6880585335985</v>
       </c>
       <c r="G50" s="3">
-        <v>128.14136087094829</v>
+        <v>128.1371427284369</v>
       </c>
       <c r="H50" s="4">
         <f>IF(F50=0,0,G50/F50)</f>
-        <v>0.82303770716483027</v>
+        <v>0</v>
       </c>
       <c r="I50" s="3">
-        <v>289.90090139463632</v>
+        <v>382.3073643284127</v>
       </c>
       <c r="J50" s="6">
-        <v>9.5795607384216268</v>
+        <v>12.60698597415583</v>
       </c>
       <c r="K50" s="7">
         <f>IF(I50=0,0,J50/I50)</f>
-        <v>3.3044259925846732E-2</v>
+        <v>0</v>
       </c>
       <c r="L50" s="3">
         <v>0</v>
@@ -3971,24 +3942,24 @@
         <v>0</v>
       </c>
       <c r="S50" s="3">
-        <v>2076.4243642199531</v>
+        <v>2076.356012722646</v>
       </c>
       <c r="T50" s="3">
-        <v>1708.9755478287809</v>
+        <v>1708.919291969157</v>
       </c>
       <c r="U50" s="4">
         <f>IF(S50=0,0,T50/S50)</f>
-        <v>0.82303770716483038</v>
+        <v>0</v>
       </c>
       <c r="V50" s="3">
-        <v>7917202.4300766056</v>
+        <v>9070418.669545408</v>
       </c>
       <c r="W50" s="6">
-        <v>289948.80979634362</v>
+        <v>304695.9033628255</v>
       </c>
       <c r="X50" s="7">
         <f>IF(V50=0,0,W50/V50)</f>
-        <v>3.6622634365752617E-2</v>
+        <v>0</v>
       </c>
       <c r="Y50" s="3">
         <v>0</v>
@@ -4011,41 +3982,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:30">
       <c r="B51" t="s">
         <v>31</v>
       </c>
       <c r="C51" s="3">
         <f>J51+M51+G51+P51</f>
-        <v>132.24626801308187</v>
+        <v>0</v>
       </c>
       <c r="D51" s="3">
         <f>J51+G51</f>
-        <v>132.24626801308187</v>
+        <v>0</v>
       </c>
       <c r="E51" s="3">
-        <f>M51+P51</f>
+        <f>P51+M51</f>
         <v>0</v>
       </c>
       <c r="F51" s="3">
-        <v>148.09982986674899</v>
+        <v>148.0949547336612</v>
       </c>
       <c r="G51" s="3">
-        <v>124.690141566094</v>
+        <v>124.6860370304208</v>
       </c>
       <c r="H51" s="4">
         <f>IF(F51=0,0,G51/F51)</f>
-        <v>0.84193305068805568</v>
+        <v>0</v>
       </c>
       <c r="I51" s="3">
-        <v>172.51020331953049</v>
+        <v>245.090682899663</v>
       </c>
       <c r="J51" s="6">
-        <v>7.5561264469878804</v>
+        <v>10.76043447512289</v>
       </c>
       <c r="K51" s="7">
         <f>IF(I51=0,0,J51/I51)</f>
-        <v>4.3801040759265192E-2</v>
+        <v>0</v>
       </c>
       <c r="L51" s="3">
         <v>0</v>
@@ -4068,24 +4039,24 @@
         <v>0</v>
       </c>
       <c r="S51" s="3">
-        <v>1975.1545181010979</v>
+        <v>1975.089500192884</v>
       </c>
       <c r="T51" s="3">
-        <v>1662.9478690051531</v>
+        <v>1662.893128279342</v>
       </c>
       <c r="U51" s="4">
         <f>IF(S51=0,0,T51/S51)</f>
-        <v>0.84193305068805524</v>
+        <v>0</v>
       </c>
       <c r="V51" s="3">
-        <v>5775458.9344058</v>
+        <v>7100767.677214347</v>
       </c>
       <c r="W51" s="6">
-        <v>301589.20337983972</v>
+        <v>346368.6063864464</v>
       </c>
       <c r="X51" s="7">
         <f>IF(V51=0,0,W51/V51)</f>
-        <v>5.2219088873301511E-2</v>
+        <v>0</v>
       </c>
       <c r="Y51" s="3">
         <v>0</v>
@@ -4108,41 +4079,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:30">
       <c r="B52" t="s">
         <v>32</v>
       </c>
       <c r="C52" s="3">
         <f>J52+M52+G52+P52</f>
-        <v>125.40247723253992</v>
+        <v>0</v>
       </c>
       <c r="D52" s="3">
         <f>J52+G52</f>
-        <v>125.40247723253992</v>
+        <v>0</v>
       </c>
       <c r="E52" s="3">
-        <f>M52+P52</f>
+        <f>P52+M52</f>
         <v>0</v>
       </c>
       <c r="F52" s="3">
-        <v>134.796744990006</v>
+        <v>134.7923077663291</v>
       </c>
       <c r="G52" s="3">
-        <v>117.3169351601271</v>
+        <v>117.3130733348106</v>
       </c>
       <c r="H52" s="4">
         <f>IF(F52=0,0,G52/F52)</f>
-        <v>0.87032468898878179</v>
+        <v>0</v>
       </c>
       <c r="I52" s="3">
-        <v>135.45605543604131</v>
+        <v>200.4130880433794</v>
       </c>
       <c r="J52" s="6">
-        <v>8.0855420724128191</v>
+        <v>11.7730736107835</v>
       </c>
       <c r="K52" s="7">
         <f>IF(I52=0,0,J52/I52)</f>
-        <v>5.9691255930825429E-2</v>
+        <v>0</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -4165,24 +4136,24 @@
         <v>0</v>
       </c>
       <c r="S52" s="3">
-        <v>1797.736028001397</v>
+        <v>1797.676850334541</v>
       </c>
       <c r="T52" s="3">
-        <v>1564.614049454244</v>
+        <v>1564.562545669743</v>
       </c>
       <c r="U52" s="4">
         <f>IF(S52=0,0,T52/S52)</f>
-        <v>0.8703246889887819</v>
+        <v>0</v>
       </c>
       <c r="V52" s="3">
-        <v>4941006.3189266957</v>
+        <v>6292834.208210533</v>
       </c>
       <c r="W52" s="6">
-        <v>340742.81144367717</v>
+        <v>402841.1074284222</v>
       </c>
       <c r="X52" s="7">
         <f>IF(V52=0,0,W52/V52)</f>
-        <v>6.8962229442704831E-2</v>
+        <v>0</v>
       </c>
       <c r="Y52" s="3">
         <v>0</v>
@@ -4205,41 +4176,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:30">
       <c r="B53" t="s">
         <v>33</v>
       </c>
       <c r="C53" s="3">
         <f>J53+M53+G53+P53</f>
-        <v>80.327792038537325</v>
+        <v>0</v>
       </c>
       <c r="D53" s="3">
         <f>J53+G53</f>
-        <v>80.327792038537325</v>
+        <v>0</v>
       </c>
       <c r="E53" s="3">
-        <f>M53+P53</f>
+        <f>P53+M53</f>
         <v>0</v>
       </c>
       <c r="F53" s="3">
-        <v>118.7859525719791</v>
+        <v>118.7820423897171</v>
       </c>
       <c r="G53" s="3">
-        <v>77.087486119977598</v>
+        <v>77.08494856301644</v>
       </c>
       <c r="H53" s="4">
         <f>IF(F53=0,0,G53/F53)</f>
-        <v>0.64896129930233926</v>
+        <v>0</v>
       </c>
       <c r="I53" s="3">
-        <v>131.31388542968341</v>
+        <v>193.9015574705648</v>
       </c>
       <c r="J53" s="6">
-        <v>3.2403059185597232</v>
+        <v>4.775947591036063</v>
       </c>
       <c r="K53" s="7">
         <f>IF(I53=0,0,J53/I53)</f>
-        <v>2.467603412964928E-2</v>
+        <v>0</v>
       </c>
       <c r="L53" s="3">
         <v>0</v>
@@ -4262,24 +4233,24 @@
         <v>0</v>
       </c>
       <c r="S53" s="3">
-        <v>1584.2058098283051</v>
+        <v>1584.153661124499</v>
       </c>
       <c r="T53" s="3">
-        <v>1028.0882607084909</v>
+        <v>1028.054418217914</v>
       </c>
       <c r="U53" s="4">
         <f>IF(S53=0,0,T53/S53)</f>
-        <v>0.64896129930233892</v>
+        <v>0</v>
       </c>
       <c r="V53" s="3">
-        <v>4714339.9302510964</v>
+        <v>6053045.584847068</v>
       </c>
       <c r="W53" s="6">
-        <v>142904.16362350431</v>
+        <v>171043.9846910052</v>
       </c>
       <c r="X53" s="7">
         <f>IF(V53=0,0,W53/V53)</f>
-        <v>3.0312655798643888E-2</v>
+        <v>0</v>
       </c>
       <c r="Y53" s="3">
         <v>0</v>
@@ -4302,41 +4273,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:30">
       <c r="B54" t="s">
         <v>34</v>
       </c>
       <c r="C54" s="3">
         <f>J54+M54+G54+P54</f>
-        <v>52.724079051646143</v>
+        <v>0</v>
       </c>
       <c r="D54" s="3">
         <f>J54+G54</f>
-        <v>52.724079051646143</v>
+        <v>0</v>
       </c>
       <c r="E54" s="3">
-        <f>M54+P54</f>
+        <f>P54+M54</f>
         <v>0</v>
       </c>
       <c r="F54" s="3">
-        <v>93.71022621139285</v>
+        <v>93.70714146899384</v>
       </c>
       <c r="G54" s="3">
-        <v>50.344180652394442</v>
+        <v>50.34252342847255</v>
       </c>
       <c r="H54" s="4">
         <f>IF(F54=0,0,G54/F54)</f>
-        <v>0.53723251653269222</v>
+        <v>0</v>
       </c>
       <c r="I54" s="3">
-        <v>85.349300637888987</v>
+        <v>136.6145524202559</v>
       </c>
       <c r="J54" s="6">
-        <v>2.3798983992517022</v>
+        <v>3.636206208529707</v>
       </c>
       <c r="K54" s="7">
         <f>IF(I54=0,0,J54/I54)</f>
-        <v>2.7884216759418851E-2</v>
+        <v>0</v>
       </c>
       <c r="L54" s="3">
         <v>0</v>
@@ -4359,24 +4330,24 @@
         <v>0</v>
       </c>
       <c r="S54" s="3">
-        <v>1249.7798063660359</v>
+        <v>1249.738666258772</v>
       </c>
       <c r="T54" s="3">
-        <v>671.4223504857664</v>
+        <v>671.4002486824103</v>
       </c>
       <c r="U54" s="4">
         <f>IF(S54=0,0,T54/S54)</f>
-        <v>0.53723251653269233</v>
+        <v>0</v>
       </c>
       <c r="V54" s="3">
-        <v>3542162.2225858839</v>
+        <v>4890905.466101354</v>
       </c>
       <c r="W54" s="6">
-        <v>113587.6470628493</v>
+        <v>143249.1869890932</v>
       </c>
       <c r="X54" s="7">
         <f>IF(V54=0,0,W54/V54)</f>
-        <v>3.2067319316597231E-2</v>
+        <v>0</v>
       </c>
       <c r="Y54" s="3">
         <v>0</v>

--- a/5000_analyze_results/results_spreadsheet.xlsx
+++ b/5000_analyze_results/results_spreadsheet.xlsx
@@ -872,10 +872,10 @@
         <v>0</v>
       </c>
       <c r="I5" s="3">
-        <v>4770.530839135346</v>
+        <v>4770.634143246331</v>
       </c>
       <c r="J5" s="3">
-        <v>313.1435897498429</v>
+        <v>313.1491918410863</v>
       </c>
       <c r="K5" s="4">
         <f>IF(I5=0,0,J5/I5)</f>
@@ -912,10 +912,10 @@
         <v>0</v>
       </c>
       <c r="V5" s="3">
-        <v>131633584.5027684</v>
+        <v>131635505.1358041</v>
       </c>
       <c r="W5" s="3">
-        <v>6824406.427104607</v>
+        <v>6824470.841005474</v>
       </c>
       <c r="X5" s="4">
         <f>IF(V5=0,0,W5/V5)</f>
@@ -969,10 +969,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="3">
-        <v>4315.124647651387</v>
+        <v>4315.187437526984</v>
       </c>
       <c r="J6" s="3">
-        <v>279.2957221772522</v>
+        <v>279.300660644656</v>
       </c>
       <c r="K6" s="4">
         <f>IF(I6=0,0,J6/I6)</f>
@@ -1009,10 +1009,10 @@
         <v>0</v>
       </c>
       <c r="V6" s="3">
-        <v>123302339.5131656</v>
+        <v>123303471.7218903</v>
       </c>
       <c r="W6" s="3">
-        <v>6420550.044813901</v>
+        <v>6420585.248220176</v>
       </c>
       <c r="X6" s="4">
         <f>IF(V6=0,0,W6/V6)</f>
@@ -1066,10 +1066,10 @@
         <v>0</v>
       </c>
       <c r="I7" s="3">
-        <v>4219.443085372338</v>
+        <v>4219.528255961915</v>
       </c>
       <c r="J7" s="3">
-        <v>242.8847629563259</v>
+        <v>242.8912775303489</v>
       </c>
       <c r="K7" s="4">
         <f>IF(I7=0,0,J7/I7)</f>
@@ -1106,10 +1106,10 @@
         <v>0</v>
       </c>
       <c r="V7" s="3">
-        <v>120996996.1158803</v>
+        <v>120998582.0234882</v>
       </c>
       <c r="W7" s="3">
-        <v>5621454.428166643</v>
+        <v>5621483.696693212</v>
       </c>
       <c r="X7" s="4">
         <f>IF(V7=0,0,W7/V7)</f>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="3">
-        <v>3865.802402615053</v>
+        <v>3865.876824341832</v>
       </c>
       <c r="J8" s="3">
-        <v>198.6845367286932</v>
+        <v>198.691617226379</v>
       </c>
       <c r="K8" s="4">
         <f>IF(I8=0,0,J8/I8)</f>
@@ -1203,10 +1203,10 @@
         <v>0</v>
       </c>
       <c r="V8" s="3">
-        <v>114899915.8905035</v>
+        <v>114901246.7176108</v>
       </c>
       <c r="W8" s="3">
-        <v>4852495.274701983</v>
+        <v>4852463.408646479</v>
       </c>
       <c r="X8" s="4">
         <f>IF(V8=0,0,W8/V8)</f>
@@ -1260,10 +1260,10 @@
         <v>0</v>
       </c>
       <c r="I9" s="3">
-        <v>3364.499225271484</v>
+        <v>3364.535483097304</v>
       </c>
       <c r="J9" s="3">
-        <v>100.8917196531021</v>
+        <v>100.8940939517273</v>
       </c>
       <c r="K9" s="4">
         <f>IF(I9=0,0,J9/I9)</f>
@@ -1300,10 +1300,10 @@
         <v>0</v>
       </c>
       <c r="V9" s="3">
-        <v>107028313.8412168</v>
+        <v>107029191.5550522</v>
       </c>
       <c r="W9" s="3">
-        <v>2678093.45510754</v>
+        <v>2678087.60536024</v>
       </c>
       <c r="X9" s="4">
         <f>IF(V9=0,0,W9/V9)</f>
@@ -1480,10 +1480,10 @@
         <v>0</v>
       </c>
       <c r="I14" s="3">
-        <v>4770.530839135346</v>
+        <v>4770.634143246331</v>
       </c>
       <c r="J14" s="3">
-        <v>313.1435897498429</v>
+        <v>313.1491918410863</v>
       </c>
       <c r="K14" s="4">
         <f>IF(I14=0,0,J14/I14)</f>
@@ -1520,10 +1520,10 @@
         <v>0</v>
       </c>
       <c r="V14" s="3">
-        <v>131633584.5027684</v>
+        <v>131635505.1358041</v>
       </c>
       <c r="W14" s="3">
-        <v>6824406.427104607</v>
+        <v>6824470.841005474</v>
       </c>
       <c r="X14" s="4">
         <f>IF(V14=0,0,W14/V14)</f>
@@ -1577,10 +1577,10 @@
         <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>4315.124647651387</v>
+        <v>4315.187437526984</v>
       </c>
       <c r="J15" s="3">
-        <v>279.2957221772522</v>
+        <v>279.300660644656</v>
       </c>
       <c r="K15" s="4">
         <f>IF(I15=0,0,J15/I15)</f>
@@ -1617,10 +1617,10 @@
         <v>0</v>
       </c>
       <c r="V15" s="3">
-        <v>123302339.5131656</v>
+        <v>123303471.7218903</v>
       </c>
       <c r="W15" s="3">
-        <v>6420550.044813901</v>
+        <v>6420585.248220176</v>
       </c>
       <c r="X15" s="4">
         <f>IF(V15=0,0,W15/V15)</f>
@@ -1674,10 +1674,10 @@
         <v>0</v>
       </c>
       <c r="I16" s="3">
-        <v>4219.443085372338</v>
+        <v>4219.528255961915</v>
       </c>
       <c r="J16" s="3">
-        <v>242.8847629563259</v>
+        <v>242.8912775303489</v>
       </c>
       <c r="K16" s="4">
         <f>IF(I16=0,0,J16/I16)</f>
@@ -1714,10 +1714,10 @@
         <v>0</v>
       </c>
       <c r="V16" s="3">
-        <v>120996996.1158803</v>
+        <v>120998582.0234882</v>
       </c>
       <c r="W16" s="3">
-        <v>5621454.428166643</v>
+        <v>5621483.696693212</v>
       </c>
       <c r="X16" s="4">
         <f>IF(V16=0,0,W16/V16)</f>
@@ -1771,10 +1771,10 @@
         <v>0</v>
       </c>
       <c r="I17" s="3">
-        <v>3865.802402615053</v>
+        <v>3865.876824341832</v>
       </c>
       <c r="J17" s="3">
-        <v>198.6845367286932</v>
+        <v>198.691617226379</v>
       </c>
       <c r="K17" s="4">
         <f>IF(I17=0,0,J17/I17)</f>
@@ -1811,10 +1811,10 @@
         <v>0</v>
       </c>
       <c r="V17" s="3">
-        <v>114899915.8905035</v>
+        <v>114901246.7176108</v>
       </c>
       <c r="W17" s="3">
-        <v>4852495.274701983</v>
+        <v>4852463.408646479</v>
       </c>
       <c r="X17" s="4">
         <f>IF(V17=0,0,W17/V17)</f>
@@ -1868,10 +1868,10 @@
         <v>0</v>
       </c>
       <c r="I18" s="3">
-        <v>3364.499225271484</v>
+        <v>3364.535483097304</v>
       </c>
       <c r="J18" s="3">
-        <v>100.8917196531021</v>
+        <v>100.8940939517273</v>
       </c>
       <c r="K18" s="4">
         <f>IF(I18=0,0,J18/I18)</f>
@@ -1908,10 +1908,10 @@
         <v>0</v>
       </c>
       <c r="V18" s="3">
-        <v>107028313.8412168</v>
+        <v>107029191.5550522</v>
       </c>
       <c r="W18" s="3">
-        <v>2678093.45510754</v>
+        <v>2678087.60536024</v>
       </c>
       <c r="X18" s="4">
         <f>IF(V18=0,0,W18/V18)</f>
@@ -2088,10 +2088,10 @@
         <v>0</v>
       </c>
       <c r="I23" s="3">
-        <v>1107.546596802289</v>
+        <v>1107.74060100339</v>
       </c>
       <c r="J23" s="3">
-        <v>152.4997145741357</v>
+        <v>152.5234548186974</v>
       </c>
       <c r="K23" s="4">
         <f>IF(I23=0,0,J23/I23)</f>
@@ -2128,10 +2128,10 @@
         <v>0</v>
       </c>
       <c r="V23" s="3">
-        <v>27397369.30964229</v>
+        <v>27400977.74118312</v>
       </c>
       <c r="W23" s="3">
-        <v>2862889.007549949</v>
+        <v>2862892.530974068</v>
       </c>
       <c r="X23" s="4">
         <f>IF(V23=0,0,W23/V23)</f>
@@ -2185,10 +2185,10 @@
         <v>0</v>
       </c>
       <c r="I24" s="3">
-        <v>948.9774541166404</v>
+        <v>949.1425284410024</v>
       </c>
       <c r="J24" s="3">
-        <v>142.748964041745</v>
+        <v>142.7687617122045</v>
       </c>
       <c r="K24" s="4">
         <f>IF(I24=0,0,J24/I24)</f>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="V24" s="3">
-        <v>24895849.84707717</v>
+        <v>24898549.32347565</v>
       </c>
       <c r="W24" s="3">
-        <v>2971447.301604643</v>
+        <v>2971388.847040191</v>
       </c>
       <c r="X24" s="4">
         <f>IF(V24=0,0,W24/V24)</f>
@@ -2282,10 +2282,10 @@
         <v>0</v>
       </c>
       <c r="I25" s="3">
-        <v>812.8523144403116</v>
+        <v>812.9560846367958</v>
       </c>
       <c r="J25" s="3">
-        <v>128.6294993462358</v>
+        <v>128.6424463031638</v>
       </c>
       <c r="K25" s="4">
         <f>IF(I25=0,0,J25/I25)</f>
@@ -2322,10 +2322,10 @@
         <v>0</v>
       </c>
       <c r="V25" s="3">
-        <v>22560876.23580789</v>
+        <v>22562854.77262445</v>
       </c>
       <c r="W25" s="3">
-        <v>2932316.708162963</v>
+        <v>2932258.19492485</v>
       </c>
       <c r="X25" s="4">
         <f>IF(V25=0,0,W25/V25)</f>
@@ -2379,10 +2379,10 @@
         <v>0</v>
       </c>
       <c r="I26" s="3">
-        <v>744.1458417101434</v>
+        <v>744.2357882678732</v>
       </c>
       <c r="J26" s="3">
-        <v>121.7279523800384</v>
+        <v>121.7392737967667</v>
       </c>
       <c r="K26" s="4">
         <f>IF(I26=0,0,J26/I26)</f>
@@ -2419,10 +2419,10 @@
         <v>0</v>
       </c>
       <c r="V26" s="3">
-        <v>21620696.94544948</v>
+        <v>21622572.40808716</v>
       </c>
       <c r="W26" s="3">
-        <v>2935395.492038567</v>
+        <v>2935451.82360588</v>
       </c>
       <c r="X26" s="4">
         <f>IF(V26=0,0,W26/V26)</f>
@@ -2476,10 +2476,10 @@
         <v>0</v>
       </c>
       <c r="I27" s="3">
-        <v>535.1312945240268</v>
+        <v>535.1979996604247</v>
       </c>
       <c r="J27" s="3">
-        <v>94.96583666364202</v>
+        <v>94.97819750327513</v>
       </c>
       <c r="K27" s="4">
         <f>IF(I27=0,0,J27/I27)</f>
@@ -2516,10 +2516,10 @@
         <v>0</v>
       </c>
       <c r="V27" s="3">
-        <v>17458494.1520531</v>
+        <v>17459766.58234148</v>
       </c>
       <c r="W27" s="3">
-        <v>2691934.235133365</v>
+        <v>2691942.302341633</v>
       </c>
       <c r="X27" s="4">
         <f>IF(V27=0,0,W27/V27)</f>
@@ -2696,10 +2696,10 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>1107.546596802289</v>
+        <v>1107.74060100339</v>
       </c>
       <c r="J32" s="3">
-        <v>12.89635673957388</v>
+        <v>12.89904290266591</v>
       </c>
       <c r="K32" s="4">
         <f>IF(I32=0,0,J32/I32)</f>
@@ -2736,10 +2736,10 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
-        <v>27397369.30964229</v>
+        <v>27400977.74118312</v>
       </c>
       <c r="W32" s="3">
-        <v>238301.4702603519</v>
+        <v>238294.5097751431</v>
       </c>
       <c r="X32" s="4">
         <f>IF(V32=0,0,W32/V32)</f>
@@ -2793,10 +2793,10 @@
         <v>0</v>
       </c>
       <c r="I33" s="3">
-        <v>948.9774541166404</v>
+        <v>949.1425284410024</v>
       </c>
       <c r="J33" s="3">
-        <v>15.74554330159084</v>
+        <v>15.74760157094255</v>
       </c>
       <c r="K33" s="4">
         <f>IF(I33=0,0,J33/I33)</f>
@@ -2833,10 +2833,10 @@
         <v>0</v>
       </c>
       <c r="V33" s="3">
-        <v>24895849.84707717</v>
+        <v>24898549.32347565</v>
       </c>
       <c r="W33" s="3">
-        <v>323332.1851536892</v>
+        <v>323318.289719075</v>
       </c>
       <c r="X33" s="4">
         <f>IF(V33=0,0,W33/V33)</f>
@@ -2890,10 +2890,10 @@
         <v>0</v>
       </c>
       <c r="I34" s="3">
-        <v>812.8523144403116</v>
+        <v>812.9560846367958</v>
       </c>
       <c r="J34" s="3">
-        <v>17.25960862774099</v>
+        <v>17.25944775724935</v>
       </c>
       <c r="K34" s="4">
         <f>IF(I34=0,0,J34/I34)</f>
@@ -2930,10 +2930,10 @@
         <v>0</v>
       </c>
       <c r="V34" s="3">
-        <v>22560876.23580789</v>
+        <v>22562854.77262445</v>
       </c>
       <c r="W34" s="3">
-        <v>387281.120965641</v>
+        <v>387268.950704027</v>
       </c>
       <c r="X34" s="4">
         <f>IF(V34=0,0,W34/V34)</f>
@@ -2987,10 +2987,10 @@
         <v>0</v>
       </c>
       <c r="I35" s="3">
-        <v>744.1458417101434</v>
+        <v>744.2357882678732</v>
       </c>
       <c r="J35" s="3">
-        <v>18.85750915282103</v>
+        <v>18.86143738575524</v>
       </c>
       <c r="K35" s="4">
         <f>IF(I35=0,0,J35/I35)</f>
@@ -3027,10 +3027,10 @@
         <v>0</v>
       </c>
       <c r="V35" s="3">
-        <v>21620696.94544948</v>
+        <v>21622572.40808716</v>
       </c>
       <c r="W35" s="3">
-        <v>448888.7868992649</v>
+        <v>448880.7426355034</v>
       </c>
       <c r="X35" s="4">
         <f>IF(V35=0,0,W35/V35)</f>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="I36" s="3">
-        <v>535.1312945240268</v>
+        <v>535.1979996604247</v>
       </c>
       <c r="J36" s="3">
-        <v>15.89358763886744</v>
+        <v>15.89674518991169</v>
       </c>
       <c r="K36" s="4">
         <f>IF(I36=0,0,J36/I36)</f>
@@ -3124,10 +3124,10 @@
         <v>0</v>
       </c>
       <c r="V36" s="3">
-        <v>17458494.1520531</v>
+        <v>17459766.58234148</v>
       </c>
       <c r="W36" s="3">
-        <v>444956.1308084317</v>
+        <v>444980.2908772007</v>
       </c>
       <c r="X36" s="4">
         <f>IF(V36=0,0,W36/V36)</f>
@@ -3286,7 +3286,7 @@
         <v>0</v>
       </c>
       <c r="D41" s="3">
-        <f>J41+G41</f>
+        <f>G41+J41</f>
         <v>0</v>
       </c>
       <c r="E41" s="3">
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="D42" s="3">
-        <f>J42+G42</f>
+        <f>G42+J42</f>
         <v>0</v>
       </c>
       <c r="E42" s="3">
@@ -3480,7 +3480,7 @@
         <v>0</v>
       </c>
       <c r="D43" s="3">
-        <f>J43+G43</f>
+        <f>G43+J43</f>
         <v>0</v>
       </c>
       <c r="E43" s="3">
@@ -3577,7 +3577,7 @@
         <v>0</v>
       </c>
       <c r="D44" s="3">
-        <f>J44+G44</f>
+        <f>G44+J44</f>
         <v>0</v>
       </c>
       <c r="E44" s="3">
@@ -3674,7 +3674,7 @@
         <v>0</v>
       </c>
       <c r="D45" s="3">
-        <f>J45+G45</f>
+        <f>G45+J45</f>
         <v>0</v>
       </c>
       <c r="E45" s="3">
@@ -3894,7 +3894,7 @@
         <v>0</v>
       </c>
       <c r="D50" s="3">
-        <f>J50+G50</f>
+        <f>G50+J50</f>
         <v>0</v>
       </c>
       <c r="E50" s="3">
@@ -3991,7 +3991,7 @@
         <v>0</v>
       </c>
       <c r="D51" s="3">
-        <f>J51+G51</f>
+        <f>G51+J51</f>
         <v>0</v>
       </c>
       <c r="E51" s="3">
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="D52" s="3">
-        <f>J52+G52</f>
+        <f>G52+J52</f>
         <v>0</v>
       </c>
       <c r="E52" s="3">
@@ -4185,7 +4185,7 @@
         <v>0</v>
       </c>
       <c r="D53" s="3">
-        <f>J53+G53</f>
+        <f>G53+J53</f>
         <v>0</v>
       </c>
       <c r="E53" s="3">
@@ -4282,7 +4282,7 @@
         <v>0</v>
       </c>
       <c r="D54" s="3">
-        <f>J54+G54</f>
+        <f>G54+J54</f>
         <v>0</v>
       </c>
       <c r="E54" s="3">

--- a/5000_analyze_results/results_spreadsheet.xlsx
+++ b/5000_analyze_results/results_spreadsheet.xlsx
@@ -1,44 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\src\vivarium_gates_lsff_by_wealth_quintile\5000_analyze_results\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E8E2E52-73DC-46EB-B645-0C0EE0B811D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Model Results" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="J39" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="J39" authorId="0">
       <text>
         <r>
           <rPr>
@@ -51,7 +32,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K39" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="K39" authorId="0">
       <text>
         <r>
           <rPr>
@@ -64,7 +45,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W39" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="W39" authorId="0">
       <text>
         <r>
           <rPr>
@@ -77,7 +58,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X39" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="X39" authorId="0">
       <text>
         <r>
           <rPr>
@@ -90,7 +71,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J48" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="J48" authorId="0">
       <text>
         <r>
           <rPr>
@@ -103,7 +84,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K48" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="K48" authorId="0">
       <text>
         <r>
           <rPr>
@@ -116,7 +97,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W48" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="W48" authorId="0">
       <text>
         <r>
           <rPr>
@@ -129,7 +110,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X48" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+    <comment ref="X48" authorId="0">
       <text>
         <r>
           <rPr>
@@ -272,12 +253,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0%;\-0.0%;&quot;-&quot;"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* (#,##0);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.0%;-0.0%;&quot;-&quot;"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -359,21 +340,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -411,7 +384,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -445,7 +418,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -480,10 +452,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -656,9 +627,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AD54"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="1.7109375" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" customWidth="1"/>
@@ -667,7 +638,7 @@
     <col min="19" max="30" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30">
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
@@ -751,1584 +722,1584 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30">
       <c r="A2" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30">
       <c r="B3" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="3">
         <f>C5+C6+C7+C8+C9</f>
-        <v>1354.9744725859973</v>
+        <v>0</v>
       </c>
       <c r="D3" s="3">
         <f>D5+D6+D7+D8+D9</f>
-        <v>76.159986174637623</v>
+        <v>0</v>
       </c>
       <c r="E3" s="3">
         <f>E5+E6+E7+E8+E9</f>
-        <v>1278.8144864113599</v>
+        <v>0</v>
       </c>
       <c r="F3" s="3">
         <f>F5+F6+F7+F8+F9</f>
-        <v>1475.2008350402737</v>
+        <v>0</v>
       </c>
       <c r="G3" s="3">
         <f>G5+G6+G7+G8+G9</f>
-        <v>76.159986174637623</v>
+        <v>0</v>
       </c>
       <c r="H3" s="4">
         <f>IF(F3=0,0,G3/F3)</f>
-        <v>5.1626859452366308E-2</v>
+        <v>0</v>
       </c>
       <c r="I3" s="3">
         <f>I5+I6+I7+I8+I9</f>
-        <v>18048.889405534985</v>
+        <v>0</v>
       </c>
       <c r="J3" s="3">
         <f>J5+J6+J7+J8+J9</f>
-        <v>1113.8472905386166</v>
+        <v>0</v>
       </c>
       <c r="K3" s="4">
         <f>IF(I3=0,0,J3/I3)</f>
-        <v>6.1712788278099659E-2</v>
+        <v>0</v>
       </c>
       <c r="L3" s="3">
         <f>L5+L6+L7+L8+L9</f>
-        <v>72937.581127560086</v>
+        <v>0</v>
       </c>
       <c r="M3" s="3">
         <f>M5+M6+M7+M8+M9</f>
-        <v>133.93810810954682</v>
+        <v>0</v>
       </c>
       <c r="N3" s="4">
         <f>IF(L3=0,0,M3/L3)</f>
-        <v>1.8363387713023179E-3</v>
+        <v>0</v>
       </c>
       <c r="O3" s="3">
         <f>O5+O6+O7+O8+O9</f>
-        <v>2197.413253833623</v>
+        <v>0</v>
       </c>
       <c r="P3" s="3">
         <f>P5+P6+P7+P8+P9</f>
-        <v>31.0290877631965</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="4">
         <f>IF(O3=0,0,P3/O3)</f>
-        <v>1.4120733871547799E-2</v>
+        <v>0</v>
       </c>
       <c r="S3" s="3">
         <f>S5+S6+S7+S8+S9</f>
-        <v>21308.331458638695</v>
+        <v>0</v>
       </c>
       <c r="T3" s="3">
         <f>T5+T6+T7+T8+T9</f>
-        <v>1100.0822333795754</v>
+        <v>0</v>
       </c>
       <c r="U3" s="4">
         <f>IF(S3=0,0,T3/S3)</f>
-        <v>5.1626859452366308E-2</v>
+        <v>0</v>
       </c>
       <c r="V3" s="3">
         <f>V5+V6+V7+V8+V9</f>
-        <v>586271135.92958963</v>
+        <v>0</v>
       </c>
       <c r="W3" s="3">
         <f>W5+W6+W7+W8+W9</f>
-        <v>28540637.209694162</v>
+        <v>0</v>
       </c>
       <c r="X3" s="4">
         <f>IF(V3=0,0,W3/V3)</f>
-        <v>4.8681634589497945E-2</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="3">
         <f>Y5+Y6+Y7+Y8+Y9</f>
-        <v>23683592.035162695</v>
+        <v>0</v>
       </c>
       <c r="Z3" s="3">
         <f>Z5+Z6+Z7+Z8+Z9</f>
-        <v>357929.85937569803</v>
+        <v>0</v>
       </c>
       <c r="AA3" s="4">
         <f>IF(Y3=0,0,Z3/Y3)</f>
-        <v>1.5112988724188654E-2</v>
+        <v>0</v>
       </c>
       <c r="AB3" s="3">
         <f>AB5+AB6+AB7+AB8+AB9</f>
-        <v>813962.31168455421</v>
+        <v>0</v>
       </c>
       <c r="AC3" s="3">
         <f>AC5+AC6+AC7+AC8+AC9</f>
-        <v>1488.4676120195945</v>
+        <v>0</v>
       </c>
       <c r="AD3" s="4">
         <f>IF(AB3=0,0,AC3/AB3)</f>
-        <v>1.8286689575824494E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30">
       <c r="A4" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30">
       <c r="B5" t="s">
         <v>30</v>
       </c>
       <c r="C5" s="3">
         <f>J5+M5+G5+P5</f>
-        <v>394.43866086505562</v>
+        <v>0</v>
       </c>
       <c r="D5" s="3">
         <f>G5</f>
-        <v>25.612291312667828</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3">
         <f>J5+M5+P5</f>
-        <v>368.8263695523878</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3">
-        <v>363.2412074975357</v>
+        <v>363.2527888669509</v>
       </c>
       <c r="G5" s="3">
-        <v>25.612291312667828</v>
+        <v>25.61310791992815</v>
       </c>
       <c r="H5" s="4">
         <f>IF(F5=0,0,G5/F5)</f>
-        <v>7.0510423333072933E-2</v>
+        <v>0</v>
       </c>
       <c r="I5" s="3">
-        <v>4215.705028068518</v>
+        <v>4696.75253329159</v>
       </c>
       <c r="J5" s="3">
-        <v>311.12629295529291</v>
+        <v>308.8367897111615</v>
       </c>
       <c r="K5" s="4">
         <f>IF(I5=0,0,J5/I5)</f>
-        <v>7.3801722578735449E-2</v>
+        <v>0</v>
       </c>
       <c r="L5" s="3">
-        <v>18587.84837263764</v>
+        <v>17149.74236158763</v>
       </c>
       <c r="M5" s="3">
-        <v>48.273576582159848</v>
+        <v>43.31725056460872</v>
       </c>
       <c r="N5" s="4">
         <f>IF(L5=0,0,M5/L5)</f>
-        <v>2.5970502671638571E-3</v>
+        <v>0</v>
       </c>
       <c r="O5" s="3">
-        <v>591.47191788042619</v>
+        <v>422.618887365441</v>
       </c>
       <c r="P5" s="3">
-        <v>9.4265000149350389</v>
+        <v>9.181329847155197</v>
       </c>
       <c r="Q5" s="4">
         <f>IF(O5=0,0,P5/O5)</f>
-        <v>1.5937358528728542E-2</v>
+        <v>0</v>
       </c>
       <c r="S5" s="3">
-        <v>5246.7866509730784</v>
+        <v>5246.953936438476</v>
       </c>
       <c r="T5" s="3">
-        <v>369.95314789842809</v>
+        <v>369.9649432674123</v>
       </c>
       <c r="U5" s="4">
         <f>IF(S5=0,0,T5/S5)</f>
-        <v>7.0510423333073002E-2</v>
+        <v>0</v>
       </c>
       <c r="V5" s="3">
-        <v>130504106.3683567</v>
+        <v>129715335.2891872</v>
       </c>
       <c r="W5" s="3">
-        <v>7529815.8321291059</v>
+        <v>6741067.098559976</v>
       </c>
       <c r="X5" s="4">
         <f>IF(V5=0,0,W5/V5)</f>
-        <v>5.7697922629926214E-2</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3">
-        <v>6056561.9935170701</v>
+        <v>3017209.138211729</v>
       </c>
       <c r="Z5" s="3">
-        <v>113528.6322764717</v>
+        <v>79401.50608393084</v>
       </c>
       <c r="AA5" s="4">
         <f>IF(Y5=0,0,Z5/Y5)</f>
-        <v>1.8744732143085877E-2</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="3">
-        <v>207427.26465751129</v>
+        <v>191324.1617071823</v>
       </c>
       <c r="AC5" s="3">
-        <v>536.46853516536066</v>
+        <v>481.4397627256985</v>
       </c>
       <c r="AD5" s="4">
         <f>IF(AB5=0,0,AC5/AB5)</f>
-        <v>2.5862971102238574E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30">
       <c r="B6" t="s">
         <v>31</v>
       </c>
       <c r="C6" s="3">
         <f>J6+M6+G6+P6</f>
-        <v>330.44823457246008</v>
+        <v>0</v>
       </c>
       <c r="D6" s="3">
         <f>G6</f>
-        <v>19.301616793786408</v>
+        <v>0</v>
       </c>
       <c r="E6" s="3">
         <f>J6+M6+P6</f>
-        <v>311.14661777867366</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3">
-        <v>320.88569787796308</v>
+        <v>320.8959288091749</v>
       </c>
       <c r="G6" s="3">
-        <v>19.301616793786408</v>
+        <v>19.30223219520511</v>
       </c>
       <c r="H6" s="4">
         <f>IF(F6=0,0,G6/F6)</f>
-        <v>6.015106600708349E-2</v>
+        <v>0</v>
       </c>
       <c r="I6" s="3">
-        <v>3777.348955767648</v>
+        <v>4237.11396849146</v>
       </c>
       <c r="J6" s="3">
-        <v>273.87484500182188</v>
+        <v>274.6201343981107</v>
       </c>
       <c r="K6" s="4">
         <f>IF(I6=0,0,J6/I6)</f>
-        <v>7.2504512611587385E-2</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3">
-        <v>15367.676054976309</v>
+        <v>14282.44480906486</v>
       </c>
       <c r="M6" s="3">
-        <v>30.710367296976969</v>
+        <v>-0.001600985677912831</v>
       </c>
       <c r="N6" s="4">
         <f>IF(L6=0,0,M6/L6)</f>
-        <v>1.9983741970558029E-3</v>
+        <v>0</v>
       </c>
       <c r="O6" s="3">
-        <v>469.23439497722012</v>
+        <v>250.7127871641806</v>
       </c>
       <c r="P6" s="3">
-        <v>6.5614054798748107</v>
+        <v>5.289893505631073</v>
       </c>
       <c r="Q6" s="4">
         <f>IF(O6=0,0,P6/O6)</f>
-        <v>1.3983215105519592E-2</v>
+        <v>0</v>
       </c>
       <c r="S6" s="3">
-        <v>4634.9884356820912</v>
+        <v>4635.136214932357</v>
       </c>
       <c r="T6" s="3">
-        <v>278.79949533678251</v>
+        <v>278.8083844162202</v>
       </c>
       <c r="U6" s="4">
         <f>IF(S6=0,0,T6/S6)</f>
-        <v>6.0151066007083573E-2</v>
+        <v>0</v>
       </c>
       <c r="V6" s="3">
-        <v>120904784.0220684</v>
+        <v>121193659.6151606</v>
       </c>
       <c r="W6" s="3">
-        <v>6963839.795960322</v>
+        <v>6324800.906607285</v>
       </c>
       <c r="X6" s="4">
         <f>IF(V6=0,0,W6/V6)</f>
-        <v>5.7597719166259234E-2</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="3">
-        <v>5132795.0536682894</v>
+        <v>1790068.720744995</v>
       </c>
       <c r="Z6" s="3">
-        <v>85655.404223025776</v>
+        <v>46409.72342276992</v>
       </c>
       <c r="AA6" s="4">
         <f>IF(Y6=0,0,Z6/Y6)</f>
-        <v>1.6687867590156332E-2</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="3">
-        <v>171483.87280142889</v>
+        <v>159404.7054384702</v>
       </c>
       <c r="AC6" s="3">
-        <v>341.10716108785709</v>
+        <v>0</v>
       </c>
       <c r="AD6" s="4">
         <f>IF(AB6=0,0,AC6/AB6)</f>
-        <v>1.9891500904160521E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30">
       <c r="B7" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="3">
         <f>J7+M7+G7+P7</f>
-        <v>281.88409811441397</v>
+        <v>0</v>
       </c>
       <c r="D7" s="3">
         <f>G7</f>
-        <v>14.649488393760979</v>
+        <v>0</v>
       </c>
       <c r="E7" s="3">
         <f>J7+M7+P7</f>
-        <v>267.234609720653</v>
+        <v>0</v>
       </c>
       <c r="F7" s="3">
-        <v>288.07994042728268</v>
+        <v>288.0891253989829</v>
       </c>
       <c r="G7" s="3">
-        <v>14.649488393760979</v>
+        <v>14.64995546944888</v>
       </c>
       <c r="H7" s="4">
         <f>IF(F7=0,0,G7/F7)</f>
-        <v>5.0852164062630427E-2</v>
+        <v>0</v>
       </c>
       <c r="I7" s="3">
-        <v>3687.8736715650298</v>
+        <v>4136.060848493457</v>
       </c>
       <c r="J7" s="3">
-        <v>237.34124995700179</v>
+        <v>238.3348830829528</v>
       </c>
       <c r="K7" s="4">
         <f>IF(I7=0,0,J7/I7)</f>
-        <v>6.4357207186080442E-2</v>
+        <v>0</v>
       </c>
       <c r="L7" s="3">
-        <v>13749.346945394889</v>
+        <v>12947.56214154672</v>
       </c>
       <c r="M7" s="3">
-        <v>26.21495619864762</v>
+        <v>51.97910640976765</v>
       </c>
       <c r="N7" s="4">
         <f>IF(L7=0,0,M7/L7)</f>
-        <v>1.9066328242904565E-3</v>
+        <v>0</v>
       </c>
       <c r="O7" s="3">
-        <v>412.21408373118408</v>
+        <v>319.3114946363287</v>
       </c>
       <c r="P7" s="3">
-        <v>3.6784035650035949</v>
+        <v>6.277070487439225</v>
       </c>
       <c r="Q7" s="4">
         <f>IF(O7=0,0,P7/O7)</f>
-        <v>8.9235271432462297E-3</v>
+        <v>0</v>
       </c>
       <c r="S7" s="3">
-        <v>4161.1302755545457</v>
+        <v>4161.262946589416</v>
       </c>
       <c r="T7" s="3">
-        <v>211.6024794584778</v>
+        <v>211.609226067711</v>
       </c>
       <c r="U7" s="4">
         <f>IF(S7=0,0,T7/S7)</f>
-        <v>5.0852164062630302E-2</v>
+        <v>0</v>
       </c>
       <c r="V7" s="3">
-        <v>118273982.46310391</v>
+        <v>118707434.9358999</v>
       </c>
       <c r="W7" s="3">
-        <v>6057749.0648616999</v>
+        <v>5528190.844559968</v>
       </c>
       <c r="X7" s="4">
         <f>IF(V7=0,0,W7/V7)</f>
-        <v>5.1217934314095173E-2</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3">
-        <v>4603060.9719898822</v>
+        <v>2254598.791771456</v>
       </c>
       <c r="Z7" s="3">
-        <v>67998.015264652669</v>
+        <v>49247.20910354005</v>
       </c>
       <c r="AA7" s="4">
         <f>IF(Y7=0,0,Z7/Y7)</f>
-        <v>1.4772347287691355E-2</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="3">
-        <v>153442.40495407421</v>
+        <v>144480.0727939743</v>
       </c>
       <c r="AC7" s="3">
-        <v>291.49157402050332</v>
+        <v>577.7277152707975</v>
       </c>
       <c r="AD7" s="4">
         <f>IF(AB7=0,0,AC7/AB7)</f>
-        <v>1.8996806919687401E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30">
       <c r="B8" t="s">
         <v>33</v>
       </c>
       <c r="C8" s="3">
         <f>J8+M8+G8+P8</f>
-        <v>233.43504013339646</v>
+        <v>0</v>
       </c>
       <c r="D8" s="3">
         <f>G8</f>
-        <v>12.01133418925607</v>
+        <v>0</v>
       </c>
       <c r="E8" s="3">
         <f>J8+M8+P8</f>
-        <v>221.42370594414038</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3">
-        <v>271.64518669470311</v>
+        <v>271.6538476703636</v>
       </c>
       <c r="G8" s="3">
-        <v>12.01133418925607</v>
+        <v>12.01171715158402</v>
       </c>
       <c r="H8" s="4">
         <f>IF(F8=0,0,G8/F8)</f>
-        <v>4.4216996205257195E-2</v>
+        <v>0</v>
       </c>
       <c r="I8" s="3">
-        <v>3375.6401243953728</v>
+        <v>3783.135075071727</v>
       </c>
       <c r="J8" s="3">
-        <v>193.18814640416059</v>
+        <v>194.7161588536995</v>
       </c>
       <c r="K8" s="4">
         <f>IF(I8=0,0,J8/I8)</f>
-        <v>5.7230077640093066E-2</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3">
-        <v>12894.33743826528</v>
+        <v>11725.45888147103</v>
       </c>
       <c r="M8" s="3">
-        <v>21.206282171037049</v>
+        <v>0.00196340936422348</v>
       </c>
       <c r="N8" s="4">
         <f>IF(L8=0,0,M8/L8)</f>
-        <v>1.6446197621682534E-3</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3">
-        <v>377.03051903276793</v>
+        <v>255.2722093275565</v>
       </c>
       <c r="P8" s="3">
-        <v>7.0292773689427417</v>
+        <v>6.028111707371194</v>
       </c>
       <c r="Q8" s="4">
         <f>IF(O8=0,0,P8/O8)</f>
-        <v>1.8643788802496977E-2</v>
+        <v>0</v>
       </c>
       <c r="S8" s="3">
-        <v>3923.740781421468</v>
+        <v>3923.86588366907</v>
       </c>
       <c r="T8" s="3">
-        <v>173.49603124252641</v>
+        <v>173.5015628881338</v>
       </c>
       <c r="U8" s="4">
         <f>IF(S8=0,0,T8/S8)</f>
-        <v>4.4216996205257313E-2</v>
+        <v>0</v>
       </c>
       <c r="V8" s="3">
-        <v>111762860.6181328</v>
+        <v>112495719.1634136</v>
       </c>
       <c r="W8" s="3">
-        <v>5173153.5519152125</v>
+        <v>4763589.916187599</v>
       </c>
       <c r="X8" s="4">
         <f>IF(V8=0,0,W8/V8)</f>
-        <v>4.6286874935947207E-2</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="3">
-        <v>4143959.5493767709</v>
+        <v>2008987.954963077</v>
       </c>
       <c r="Z8" s="3">
-        <v>58840.378214361153</v>
+        <v>37127.77873821603</v>
       </c>
       <c r="AA8" s="4">
         <f>IF(Y8=0,0,Z8/Y8)</f>
-        <v>1.4199071567484395E-2</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="3">
-        <v>143913.11126295681</v>
+        <v>130807.1835325652</v>
       </c>
       <c r="AC8" s="3">
-        <v>235.6740385697631</v>
+        <v>0</v>
       </c>
       <c r="AD8" s="4">
         <f>IF(AB8=0,0,AC8/AB8)</f>
-        <v>1.6376133939536718E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30">
       <c r="B9" t="s">
         <v>34</v>
       </c>
       <c r="C9" s="3">
         <f>J9+M9+G9+P9</f>
-        <v>114.76843890067131</v>
+        <v>0</v>
       </c>
       <c r="D9" s="3">
         <f>G9</f>
-        <v>4.5852554851663303</v>
+        <v>0</v>
       </c>
       <c r="E9" s="3">
         <f>J9+M9+P9</f>
-        <v>110.18318341550498</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3">
-        <v>231.34880254278889</v>
+        <v>231.3561787321935</v>
       </c>
       <c r="G9" s="3">
-        <v>4.5852554851663303</v>
+        <v>4.585401678760419</v>
       </c>
       <c r="H9" s="4">
         <f>IF(F9=0,0,G9/F9)</f>
-        <v>1.981966379237372E-2</v>
+        <v>0</v>
       </c>
       <c r="I9" s="3">
-        <v>2992.321625738417</v>
+        <v>3283.865109392673</v>
       </c>
       <c r="J9" s="3">
-        <v>98.316756220339329</v>
+        <v>98.62837958013452</v>
       </c>
       <c r="K9" s="4">
         <f>IF(I9=0,0,J9/I9)</f>
-        <v>3.2856346515250559E-2</v>
+        <v>0</v>
       </c>
       <c r="L9" s="3">
-        <v>12338.372316285961</v>
+        <v>11643.22668281579</v>
       </c>
       <c r="M9" s="3">
-        <v>7.5329258607253431</v>
+        <v>8.662714833144099</v>
       </c>
       <c r="N9" s="4">
         <f>IF(L9=0,0,M9/L9)</f>
-        <v>6.1052833125989424E-4</v>
+        <v>0</v>
       </c>
       <c r="O9" s="3">
-        <v>347.46233821202492</v>
+        <v>175.1115957679361</v>
       </c>
       <c r="P9" s="3">
-        <v>4.3335013344403119</v>
+        <v>0.001510296575113898</v>
       </c>
       <c r="Q9" s="4">
         <f>IF(O9=0,0,P9/O9)</f>
-        <v>1.2471859127926454E-2</v>
+        <v>0</v>
       </c>
       <c r="S9" s="3">
-        <v>3341.6853150075108</v>
+        <v>3341.791859340324</v>
       </c>
       <c r="T9" s="3">
-        <v>66.231079443360613</v>
+        <v>66.2331911162164</v>
       </c>
       <c r="U9" s="4">
         <f>IF(S9=0,0,T9/S9)</f>
-        <v>1.9819663792373505E-2</v>
+        <v>0</v>
       </c>
       <c r="V9" s="3">
-        <v>104825402.45792779</v>
+        <v>104453537.4780618</v>
       </c>
       <c r="W9" s="3">
-        <v>2816078.9648278211</v>
+        <v>2623914.142659664</v>
       </c>
       <c r="X9" s="4">
         <f>IF(V9=0,0,W9/V9)</f>
-        <v>2.6864470813341916E-2</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3">
-        <v>3747214.4666106808</v>
+        <v>1264989.590869552</v>
       </c>
       <c r="Z9" s="3">
-        <v>31907.42939718673</v>
+        <v>16063.05453181895</v>
       </c>
       <c r="AA9" s="4">
         <f>IF(Y9=0,0,Z9/Y9)</f>
-        <v>8.5149728368888074E-3</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="3">
-        <v>137695.65800858309</v>
+        <v>129892.4479833864</v>
       </c>
       <c r="AC9" s="3">
-        <v>83.726303176110378</v>
+        <v>96.28795254514262</v>
       </c>
       <c r="AD9" s="4">
         <f>IF(AB9=0,0,AC9/AB9)</f>
-        <v>6.0805332852900413E-4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30">
       <c r="A11" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30">
       <c r="B12" t="s">
         <v>28</v>
       </c>
       <c r="C12" s="3">
         <f>C14+C15+C16+C17+C18</f>
-        <v>1831.3001558514102</v>
+        <v>0</v>
       </c>
       <c r="D12" s="3">
         <f>D14+D15+D16+D17+D18</f>
-        <v>552.48566944005017</v>
+        <v>0</v>
       </c>
       <c r="E12" s="3">
         <f>E14+E15+E16+E17+E18</f>
-        <v>1278.8144864113599</v>
+        <v>0</v>
       </c>
       <c r="F12" s="3">
         <f>F14+F15+F16+F17+F18</f>
-        <v>1475.2008350402737</v>
+        <v>0</v>
       </c>
       <c r="G12" s="3">
         <f>G14+G15+G16+G17+G18</f>
-        <v>552.48566944005017</v>
+        <v>0</v>
       </c>
       <c r="H12" s="4">
         <f>IF(F12=0,0,G12/F12)</f>
-        <v>0.3745155617573705</v>
+        <v>0</v>
       </c>
       <c r="I12" s="3">
         <f>I14+I15+I16+I17+I18</f>
-        <v>18048.889405534985</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3">
         <f>J14+J15+J16+J17+J18</f>
-        <v>1113.8472905386166</v>
+        <v>0</v>
       </c>
       <c r="K12" s="4">
         <f>IF(I12=0,0,J12/I12)</f>
-        <v>6.1712788278099659E-2</v>
+        <v>0</v>
       </c>
       <c r="L12" s="3">
         <f>L14+L15+L16+L17+L18</f>
-        <v>72937.581127560086</v>
+        <v>0</v>
       </c>
       <c r="M12" s="3">
         <f>M14+M15+M16+M17+M18</f>
-        <v>133.93810810954682</v>
+        <v>0</v>
       </c>
       <c r="N12" s="4">
         <f>IF(L12=0,0,M12/L12)</f>
-        <v>1.8363387713023179E-3</v>
+        <v>0</v>
       </c>
       <c r="O12" s="3">
         <f>O14+O15+O16+O17+O18</f>
-        <v>2197.413253833623</v>
+        <v>0</v>
       </c>
       <c r="P12" s="3">
         <f>P14+P15+P16+P17+P18</f>
-        <v>31.0290877631965</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="4">
         <f>IF(O12=0,0,P12/O12)</f>
-        <v>1.4120733871547799E-2</v>
+        <v>0</v>
       </c>
       <c r="S12" s="3">
         <f>S14+S15+S16+S17+S18</f>
-        <v>21308.331458638695</v>
+        <v>0</v>
       </c>
       <c r="T12" s="3">
         <f>T14+T15+T16+T17+T18</f>
-        <v>7980.3017263443235</v>
+        <v>0</v>
       </c>
       <c r="U12" s="4">
         <f>IF(S12=0,0,T12/S12)</f>
-        <v>0.37451556175737061</v>
+        <v>0</v>
       </c>
       <c r="V12" s="3">
         <f>V14+V15+V16+V17+V18</f>
-        <v>586271135.92958963</v>
+        <v>0</v>
       </c>
       <c r="W12" s="3">
         <f>W14+W15+W16+W17+W18</f>
-        <v>28540637.209694162</v>
+        <v>0</v>
       </c>
       <c r="X12" s="4">
         <f>IF(V12=0,0,W12/V12)</f>
-        <v>4.8681634589497945E-2</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="3">
         <f>Y14+Y15+Y16+Y17+Y18</f>
-        <v>23683592.035162695</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="3">
         <f>Z14+Z15+Z16+Z17+Z18</f>
-        <v>357929.85937569803</v>
+        <v>0</v>
       </c>
       <c r="AA12" s="4">
         <f>IF(Y12=0,0,Z12/Y12)</f>
-        <v>1.5112988724188654E-2</v>
+        <v>0</v>
       </c>
       <c r="AB12" s="3">
         <f>AB14+AB15+AB16+AB17+AB18</f>
-        <v>813962.31168455421</v>
+        <v>0</v>
       </c>
       <c r="AC12" s="3">
         <f>AC14+AC15+AC16+AC17+AC18</f>
-        <v>1488.4676120195945</v>
+        <v>0</v>
       </c>
       <c r="AD12" s="4">
         <f>IF(AB12=0,0,AC12/AB12)</f>
-        <v>1.8286689575824494E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30">
       <c r="A13" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30">
       <c r="B14" t="s">
         <v>30</v>
       </c>
       <c r="C14" s="3">
         <f>J14+M14+G14+P14</f>
-        <v>540.52142931971321</v>
+        <v>0</v>
       </c>
       <c r="D14" s="3">
         <f>G14</f>
-        <v>171.69505976732529</v>
+        <v>0</v>
       </c>
       <c r="E14" s="3">
         <f>J14+M14+P14</f>
-        <v>368.8263695523878</v>
+        <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>363.2412074975357</v>
+        <v>363.2527888669509</v>
       </c>
       <c r="G14" s="3">
-        <v>171.69505976732529</v>
+        <v>171.7005339918157</v>
       </c>
       <c r="H14" s="4">
         <f>IF(F14=0,0,G14/F14)</f>
-        <v>0.47267506060278169</v>
+        <v>0</v>
       </c>
       <c r="I14" s="3">
-        <v>4215.705028068518</v>
+        <v>4696.75253329159</v>
       </c>
       <c r="J14" s="3">
-        <v>311.12629295529291</v>
+        <v>308.8367897111615</v>
       </c>
       <c r="K14" s="4">
         <f>IF(I14=0,0,J14/I14)</f>
-        <v>7.3801722578735449E-2</v>
+        <v>0</v>
       </c>
       <c r="L14" s="3">
-        <v>18587.84837263764</v>
+        <v>17149.74236158763</v>
       </c>
       <c r="M14" s="3">
-        <v>48.273576582159848</v>
+        <v>43.31725056460872</v>
       </c>
       <c r="N14" s="4">
         <f>IF(L14=0,0,M14/L14)</f>
-        <v>2.5970502671638571E-3</v>
+        <v>0</v>
       </c>
       <c r="O14" s="3">
-        <v>591.47191788042619</v>
+        <v>422.618887365441</v>
       </c>
       <c r="P14" s="3">
-        <v>9.4265000149350389</v>
+        <v>9.181329847155197</v>
       </c>
       <c r="Q14" s="4">
         <f>IF(O14=0,0,P14/O14)</f>
-        <v>1.5937358528728542E-2</v>
+        <v>0</v>
       </c>
       <c r="S14" s="3">
-        <v>5246.7866509730784</v>
+        <v>5246.953936438476</v>
       </c>
       <c r="T14" s="3">
-        <v>2480.0251982185669</v>
+        <v>2480.104269886063</v>
       </c>
       <c r="U14" s="4">
         <f>IF(S14=0,0,T14/S14)</f>
-        <v>0.47267506060278192</v>
+        <v>0</v>
       </c>
       <c r="V14" s="3">
-        <v>130504106.3683567</v>
+        <v>129715335.2891872</v>
       </c>
       <c r="W14" s="3">
-        <v>7529815.8321291059</v>
+        <v>6741067.09856002</v>
       </c>
       <c r="X14" s="4">
         <f>IF(V14=0,0,W14/V14)</f>
-        <v>5.7697922629926214E-2</v>
+        <v>0</v>
       </c>
       <c r="Y14" s="3">
-        <v>6056561.9935170701</v>
+        <v>3017209.138211729</v>
       </c>
       <c r="Z14" s="3">
-        <v>113528.6322764717</v>
+        <v>79401.50608393084</v>
       </c>
       <c r="AA14" s="4">
         <f>IF(Y14=0,0,Z14/Y14)</f>
-        <v>1.8744732143085877E-2</v>
+        <v>0</v>
       </c>
       <c r="AB14" s="3">
-        <v>207427.26465751129</v>
+        <v>191324.1617071823</v>
       </c>
       <c r="AC14" s="3">
-        <v>536.46853516536066</v>
+        <v>481.4397627256985</v>
       </c>
       <c r="AD14" s="4">
         <f>IF(AB14=0,0,AC14/AB14)</f>
-        <v>2.5862971102238574E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30">
       <c r="B15" t="s">
         <v>31</v>
       </c>
       <c r="C15" s="3">
         <f>J15+M15+G15+P15</f>
-        <v>447.92399817572056</v>
+        <v>0</v>
       </c>
       <c r="D15" s="3">
         <f>G15</f>
-        <v>136.7773803970469</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
         <f>J15+M15+P15</f>
-        <v>311.14661777867366</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
-        <v>320.88569787796308</v>
+        <v>320.8959288091749</v>
       </c>
       <c r="G15" s="3">
-        <v>136.7773803970469</v>
+        <v>136.7817413267469</v>
       </c>
       <c r="H15" s="4">
         <f>IF(F15=0,0,G15/F15)</f>
-        <v>0.42624953776863272</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>3777.348955767648</v>
+        <v>4237.11396849146</v>
       </c>
       <c r="J15" s="3">
-        <v>273.87484500182188</v>
+        <v>274.6201343981107</v>
       </c>
       <c r="K15" s="4">
         <f>IF(I15=0,0,J15/I15)</f>
-        <v>7.2504512611587385E-2</v>
+        <v>0</v>
       </c>
       <c r="L15" s="3">
-        <v>15367.676054976309</v>
+        <v>14282.44480906486</v>
       </c>
       <c r="M15" s="3">
-        <v>30.710367296976969</v>
+        <v>-0.001600985677912831</v>
       </c>
       <c r="N15" s="4">
         <f>IF(L15=0,0,M15/L15)</f>
-        <v>1.9983741970558029E-3</v>
+        <v>0</v>
       </c>
       <c r="O15" s="3">
-        <v>469.23439497722012</v>
+        <v>250.7127871641806</v>
       </c>
       <c r="P15" s="3">
-        <v>6.5614054798748107</v>
+        <v>5.289893505631073</v>
       </c>
       <c r="Q15" s="4">
         <f>IF(O15=0,0,P15/O15)</f>
-        <v>1.3983215105519592E-2</v>
+        <v>0</v>
       </c>
       <c r="S15" s="3">
-        <v>4634.9884356820912</v>
+        <v>4635.136214932357</v>
       </c>
       <c r="T15" s="3">
-        <v>1975.66167827245</v>
+        <v>1975.724669109567</v>
       </c>
       <c r="U15" s="4">
         <f>IF(S15=0,0,T15/S15)</f>
-        <v>0.42624953776863284</v>
+        <v>0</v>
       </c>
       <c r="V15" s="3">
-        <v>120904784.0220684</v>
+        <v>121193659.6151606</v>
       </c>
       <c r="W15" s="3">
-        <v>6963839.795960322</v>
+        <v>6324800.906607285</v>
       </c>
       <c r="X15" s="4">
         <f>IF(V15=0,0,W15/V15)</f>
-        <v>5.7597719166259234E-2</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="3">
-        <v>5132795.0536682894</v>
+        <v>1790068.720744995</v>
       </c>
       <c r="Z15" s="3">
-        <v>85655.404223025776</v>
+        <v>46409.72342276992</v>
       </c>
       <c r="AA15" s="4">
         <f>IF(Y15=0,0,Z15/Y15)</f>
-        <v>1.6687867590156332E-2</v>
+        <v>0</v>
       </c>
       <c r="AB15" s="3">
-        <v>171483.87280142889</v>
+        <v>159404.7054384702</v>
       </c>
       <c r="AC15" s="3">
-        <v>341.10716108785709</v>
+        <v>0</v>
       </c>
       <c r="AD15" s="4">
         <f>IF(AB15=0,0,AC15/AB15)</f>
-        <v>1.9891500904160521E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30">
       <c r="B16" t="s">
         <v>32</v>
       </c>
       <c r="C16" s="3">
         <f>J16+M16+G16+P16</f>
-        <v>376.59508038259258</v>
+        <v>0</v>
       </c>
       <c r="D16" s="3">
         <f>G16</f>
-        <v>109.3604706619396</v>
+        <v>0</v>
       </c>
       <c r="E16" s="3">
         <f>J16+M16+P16</f>
-        <v>267.234609720653</v>
+        <v>0</v>
       </c>
       <c r="F16" s="3">
-        <v>288.07994042728268</v>
+        <v>288.0891253989829</v>
       </c>
       <c r="G16" s="3">
-        <v>109.3604706619396</v>
+        <v>109.3639574469849</v>
       </c>
       <c r="H16" s="4">
         <f>IF(F16=0,0,G16/F16)</f>
-        <v>0.37961848540976229</v>
+        <v>0</v>
       </c>
       <c r="I16" s="3">
-        <v>3687.8736715650298</v>
+        <v>4136.060848493457</v>
       </c>
       <c r="J16" s="3">
-        <v>237.34124995700179</v>
+        <v>238.3348830829528</v>
       </c>
       <c r="K16" s="4">
         <f>IF(I16=0,0,J16/I16)</f>
-        <v>6.4357207186080442E-2</v>
+        <v>0</v>
       </c>
       <c r="L16" s="3">
-        <v>13749.346945394889</v>
+        <v>12947.56214154672</v>
       </c>
       <c r="M16" s="3">
-        <v>26.21495619864762</v>
+        <v>51.97910640976765</v>
       </c>
       <c r="N16" s="4">
         <f>IF(L16=0,0,M16/L16)</f>
-        <v>1.9066328242904565E-3</v>
+        <v>0</v>
       </c>
       <c r="O16" s="3">
-        <v>412.21408373118408</v>
+        <v>319.3114946363287</v>
       </c>
       <c r="P16" s="3">
-        <v>3.6784035650035949</v>
+        <v>6.277070487439283</v>
       </c>
       <c r="Q16" s="4">
         <f>IF(O16=0,0,P16/O16)</f>
-        <v>8.9235271432462297E-3</v>
+        <v>0</v>
       </c>
       <c r="S16" s="3">
-        <v>4161.1302755545457</v>
+        <v>4161.262946589416</v>
       </c>
       <c r="T16" s="3">
-        <v>1579.6419727987229</v>
+        <v>1579.692337176038</v>
       </c>
       <c r="U16" s="4">
         <f>IF(S16=0,0,T16/S16)</f>
-        <v>0.37961848540976217</v>
+        <v>0</v>
       </c>
       <c r="V16" s="3">
-        <v>118273982.46310391</v>
+        <v>118707434.9358999</v>
       </c>
       <c r="W16" s="3">
-        <v>6057749.0648616999</v>
+        <v>5528190.844559968</v>
       </c>
       <c r="X16" s="4">
         <f>IF(V16=0,0,W16/V16)</f>
-        <v>5.1217934314095173E-2</v>
+        <v>0</v>
       </c>
       <c r="Y16" s="3">
-        <v>4603060.9719898822</v>
+        <v>2254598.791771456</v>
       </c>
       <c r="Z16" s="3">
-        <v>67998.015264652669</v>
+        <v>49247.20910354005</v>
       </c>
       <c r="AA16" s="4">
         <f>IF(Y16=0,0,Z16/Y16)</f>
-        <v>1.4772347287691355E-2</v>
+        <v>0</v>
       </c>
       <c r="AB16" s="3">
-        <v>153442.40495407421</v>
+        <v>144480.0727939743</v>
       </c>
       <c r="AC16" s="3">
-        <v>291.49157402050332</v>
+        <v>577.7277152707975</v>
       </c>
       <c r="AD16" s="4">
         <f>IF(AB16=0,0,AC16/AB16)</f>
-        <v>1.8996806919687401E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30">
       <c r="B17" t="s">
         <v>33</v>
       </c>
       <c r="C17" s="3">
         <f>J17+M17+G17+P17</f>
-        <v>314.61496024507142</v>
+        <v>0</v>
       </c>
       <c r="D17" s="3">
         <f>G17</f>
-        <v>93.191254300931007</v>
+        <v>0</v>
       </c>
       <c r="E17" s="3">
         <f>J17+M17+P17</f>
-        <v>221.42370594414038</v>
+        <v>0</v>
       </c>
       <c r="F17" s="3">
-        <v>271.64518669470311</v>
+        <v>271.6538476703636</v>
       </c>
       <c r="G17" s="3">
-        <v>93.191254300931007</v>
+        <v>93.19422555617429</v>
       </c>
       <c r="H17" s="4">
         <f>IF(F17=0,0,G17/F17)</f>
-        <v>0.34306241695225359</v>
+        <v>0</v>
       </c>
       <c r="I17" s="3">
-        <v>3375.6401243953728</v>
+        <v>3783.135075071727</v>
       </c>
       <c r="J17" s="3">
-        <v>193.18814640416059</v>
+        <v>194.7161588536995</v>
       </c>
       <c r="K17" s="4">
         <f>IF(I17=0,0,J17/I17)</f>
-        <v>5.7230077640093066E-2</v>
+        <v>0</v>
       </c>
       <c r="L17" s="3">
-        <v>12894.33743826528</v>
+        <v>11725.45888147103</v>
       </c>
       <c r="M17" s="3">
-        <v>21.206282171037049</v>
+        <v>0.00196340936422348</v>
       </c>
       <c r="N17" s="4">
         <f>IF(L17=0,0,M17/L17)</f>
-        <v>1.6446197621682534E-3</v>
+        <v>0</v>
       </c>
       <c r="O17" s="3">
-        <v>377.03051903276793</v>
+        <v>255.2722093275565</v>
       </c>
       <c r="P17" s="3">
-        <v>7.0292773689427417</v>
+        <v>6.028111707371194</v>
       </c>
       <c r="Q17" s="4">
         <f>IF(O17=0,0,P17/O17)</f>
-        <v>1.8643788802496977E-2</v>
+        <v>0</v>
       </c>
       <c r="S17" s="3">
-        <v>3923.740781421468</v>
+        <v>3923.86588366907</v>
       </c>
       <c r="T17" s="3">
-        <v>1346.0879959685731</v>
+        <v>1346.130913848001</v>
       </c>
       <c r="U17" s="4">
         <f>IF(S17=0,0,T17/S17)</f>
-        <v>0.34306241695225359</v>
+        <v>0</v>
       </c>
       <c r="V17" s="3">
-        <v>111762860.6181328</v>
+        <v>112495719.1634136</v>
       </c>
       <c r="W17" s="3">
-        <v>5173153.5519152125</v>
+        <v>4763589.916187599</v>
       </c>
       <c r="X17" s="4">
         <f>IF(V17=0,0,W17/V17)</f>
-        <v>4.6286874935947207E-2</v>
+        <v>0</v>
       </c>
       <c r="Y17" s="3">
-        <v>4143959.5493767709</v>
+        <v>2008987.954963077</v>
       </c>
       <c r="Z17" s="3">
-        <v>58840.378214361153</v>
+        <v>37127.77873821603</v>
       </c>
       <c r="AA17" s="4">
         <f>IF(Y17=0,0,Z17/Y17)</f>
-        <v>1.4199071567484395E-2</v>
+        <v>0</v>
       </c>
       <c r="AB17" s="3">
-        <v>143913.11126295681</v>
+        <v>130807.1835325652</v>
       </c>
       <c r="AC17" s="3">
-        <v>235.6740385697631</v>
+        <v>0</v>
       </c>
       <c r="AD17" s="4">
         <f>IF(AB17=0,0,AC17/AB17)</f>
-        <v>1.6376133939536718E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30">
       <c r="B18" t="s">
         <v>34</v>
       </c>
       <c r="C18" s="3">
         <f>J18+M18+G18+P18</f>
-        <v>151.64468772831239</v>
+        <v>0</v>
       </c>
       <c r="D18" s="3">
         <f>G18</f>
-        <v>41.461504312807413</v>
+        <v>0</v>
       </c>
       <c r="E18" s="3">
         <f>J18+M18+P18</f>
-        <v>110.18318341550498</v>
+        <v>0</v>
       </c>
       <c r="F18" s="3">
-        <v>231.34880254278889</v>
+        <v>231.3561787321935</v>
       </c>
       <c r="G18" s="3">
-        <v>41.461504312807413</v>
+        <v>41.46282624707057</v>
       </c>
       <c r="H18" s="4">
         <f>IF(F18=0,0,G18/F18)</f>
-        <v>0.17921642064751531</v>
+        <v>0</v>
       </c>
       <c r="I18" s="3">
-        <v>2992.321625738417</v>
+        <v>3283.865109392673</v>
       </c>
       <c r="J18" s="3">
-        <v>98.316756220339329</v>
+        <v>98.62837958013452</v>
       </c>
       <c r="K18" s="4">
         <f>IF(I18=0,0,J18/I18)</f>
-        <v>3.2856346515250559E-2</v>
+        <v>0</v>
       </c>
       <c r="L18" s="3">
-        <v>12338.372316285961</v>
+        <v>11643.22668281579</v>
       </c>
       <c r="M18" s="3">
-        <v>7.5329258607253431</v>
+        <v>8.662714833144099</v>
       </c>
       <c r="N18" s="4">
         <f>IF(L18=0,0,M18/L18)</f>
-        <v>6.1052833125989424E-4</v>
+        <v>0</v>
       </c>
       <c r="O18" s="3">
-        <v>347.46233821202492</v>
+        <v>175.1115957679361</v>
       </c>
       <c r="P18" s="3">
-        <v>4.3335013344403119</v>
+        <v>0.001510296575113898</v>
       </c>
       <c r="Q18" s="4">
         <f>IF(O18=0,0,P18/O18)</f>
-        <v>1.2471859127926454E-2</v>
+        <v>0</v>
       </c>
       <c r="S18" s="3">
-        <v>3341.6853150075108</v>
+        <v>3341.791859340324</v>
       </c>
       <c r="T18" s="3">
-        <v>598.88488108601132</v>
+        <v>598.9039755799786</v>
       </c>
       <c r="U18" s="4">
         <f>IF(S18=0,0,T18/S18)</f>
-        <v>0.17921642064751547</v>
+        <v>0</v>
       </c>
       <c r="V18" s="3">
-        <v>104825402.45792779</v>
+        <v>104453537.4780618</v>
       </c>
       <c r="W18" s="3">
-        <v>2816078.9648278211</v>
+        <v>2623914.142659664</v>
       </c>
       <c r="X18" s="4">
         <f>IF(V18=0,0,W18/V18)</f>
-        <v>2.6864470813341916E-2</v>
+        <v>0</v>
       </c>
       <c r="Y18" s="3">
-        <v>3747214.4666106808</v>
+        <v>1264989.590869552</v>
       </c>
       <c r="Z18" s="3">
-        <v>31907.42939718673</v>
+        <v>16063.05453181895</v>
       </c>
       <c r="AA18" s="4">
         <f>IF(Y18=0,0,Z18/Y18)</f>
-        <v>8.5149728368888074E-3</v>
+        <v>0</v>
       </c>
       <c r="AB18" s="3">
-        <v>137695.65800858309</v>
+        <v>129892.4479833864</v>
       </c>
       <c r="AC18" s="3">
-        <v>83.726303176110378</v>
+        <v>96.28795254514262</v>
       </c>
       <c r="AD18" s="4">
         <f>IF(AB18=0,0,AC18/AB18)</f>
-        <v>6.0805332852900413E-4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30">
       <c r="A20" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30">
       <c r="B21" t="s">
         <v>28</v>
       </c>
       <c r="C21" s="3">
         <f>C23+C24+C25+C26+C27</f>
-        <v>1978.042623631017</v>
+        <v>0</v>
       </c>
       <c r="D21" s="3">
         <f>D23+D24+D25+D26+D27</f>
-        <v>1041.7813801093714</v>
+        <v>0</v>
       </c>
       <c r="E21" s="3">
         <f>E23+E24+E25+E26+E27</f>
-        <v>936.26124352164572</v>
+        <v>0</v>
       </c>
       <c r="F21" s="3">
         <f>F23+F24+F25+F26+F27</f>
-        <v>1859.1790728805329</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3">
         <f>G23+G24+G25+G26+G27</f>
-        <v>1041.7813801093714</v>
+        <v>0</v>
       </c>
       <c r="H21" s="4">
         <f>IF(F21=0,0,G21/F21)</f>
-        <v>0.56034482923437801</v>
+        <v>0</v>
       </c>
       <c r="I21" s="3">
         <f>I23+I24+I25+I26+I27</f>
-        <v>3682.4352162782898</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3">
         <f>J23+J24+J25+J26+J27</f>
-        <v>585.89953258422668</v>
+        <v>0</v>
       </c>
       <c r="K21" s="4">
         <f>IF(I21=0,0,J21/I21)</f>
-        <v>0.15910654177818098</v>
+        <v>0</v>
       </c>
       <c r="L21" s="3">
         <f>L23+L24+L25+L26+L27</f>
-        <v>75120.106151105079</v>
+        <v>0</v>
       </c>
       <c r="M21" s="3">
         <f>M23+M24+M25+M26+M27</f>
-        <v>270.09622799380867</v>
+        <v>0</v>
       </c>
       <c r="N21" s="4">
         <f>IF(L21=0,0,M21/L21)</f>
-        <v>3.5955251108206179E-3</v>
+        <v>0</v>
       </c>
       <c r="O21" s="3">
         <f>O23+O24+O25+O26+O27</f>
-        <v>1936.1737568351107</v>
+        <v>0</v>
       </c>
       <c r="P21" s="3">
         <f>P23+P24+P25+P26+P27</f>
-        <v>80.265482943610337</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="4">
         <f>IF(O21=0,0,P21/O21)</f>
-        <v>4.1455723000198653E-2</v>
+        <v>0</v>
       </c>
       <c r="S21" s="3">
         <f>S23+S24+S25+S26+S27</f>
-        <v>34100.200929874198</v>
+        <v>0</v>
       </c>
       <c r="T21" s="3">
         <f>T23+T24+T25+T26+T27</f>
-        <v>19107.871266908332</v>
+        <v>0</v>
       </c>
       <c r="U21" s="4">
         <f>IF(S21=0,0,T21/S21)</f>
-        <v>0.56034482923437789</v>
+        <v>0</v>
       </c>
       <c r="V21" s="3">
         <f>V23+V24+V25+V26+V27</f>
-        <v>106670224.92367341</v>
+        <v>0</v>
       </c>
       <c r="W21" s="3">
         <f>W23+W24+W25+W26+W27</f>
-        <v>13782093.295542261</v>
+        <v>0</v>
       </c>
       <c r="X21" s="4">
         <f>IF(V21=0,0,W21/V21)</f>
-        <v>0.12920281461301755</v>
+        <v>0</v>
       </c>
       <c r="Y21" s="3">
         <f>Y23+Y24+Y25+Y26+Y27</f>
-        <v>8082003.8383214176</v>
+        <v>0</v>
       </c>
       <c r="Z21" s="3">
         <f>Z23+Z24+Z25+Z26+Z27</f>
-        <v>334084.07649866142</v>
+        <v>0</v>
       </c>
       <c r="AA21" s="4">
         <f>IF(Y21=0,0,Z21/Y21)</f>
-        <v>4.1336787655875284E-2</v>
+        <v>0</v>
       </c>
       <c r="AB21" s="3">
         <f>AB23+AB24+AB25+AB26+AB27</f>
-        <v>844449.53447731666</v>
+        <v>0</v>
       </c>
       <c r="AC21" s="3">
         <f>AC23+AC24+AC25+AC26+AC27</f>
-        <v>2999.0317686344206</v>
+        <v>0</v>
       </c>
       <c r="AD21" s="4">
         <f>IF(AB21=0,0,AC21/AB21)</f>
-        <v>3.5514635821200509E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30">
       <c r="A22" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30">
       <c r="B23" t="s">
         <v>30</v>
       </c>
       <c r="C23" s="3">
         <f>J23+M23+G23+P23</f>
-        <v>516.60971559081213</v>
+        <v>0</v>
       </c>
       <c r="D23" s="3">
         <f>G23</f>
-        <v>268.73883356068632</v>
+        <v>0</v>
       </c>
       <c r="E23" s="3">
         <f>J23+M23+P23</f>
-        <v>247.87088203012584</v>
+        <v>0</v>
       </c>
       <c r="F23" s="3">
         <v>414.1174655591563</v>
       </c>
       <c r="G23" s="3">
-        <v>268.73883356068632</v>
+        <v>268.7388335606863</v>
       </c>
       <c r="H23" s="4">
         <f>IF(F23=0,0,G23/F23)</f>
-        <v>0.64894349046067279</v>
+        <v>0</v>
       </c>
       <c r="I23" s="3">
-        <v>991.82050542122556</v>
+        <v>991.8205054212256</v>
       </c>
       <c r="J23" s="3">
-        <v>137.38025624613479</v>
+        <v>137.3802562461348</v>
       </c>
       <c r="K23" s="4">
         <f>IF(I23=0,0,J23/I23)</f>
-        <v>0.13851322441432029</v>
+        <v>0</v>
       </c>
       <c r="L23" s="3">
-        <v>18248.150900694091</v>
+        <v>18248.15090069409</v>
       </c>
       <c r="M23" s="3">
-        <v>92.706822166558354</v>
+        <v>92.70682216655835</v>
       </c>
       <c r="N23" s="4">
         <f>IF(L23=0,0,M23/L23)</f>
-        <v>5.0803406148418103E-3</v>
+        <v>0</v>
       </c>
       <c r="O23" s="3">
-        <v>476.04818802351332</v>
+        <v>476.0481880235133</v>
       </c>
       <c r="P23" s="3">
         <v>17.78380361743271</v>
       </c>
       <c r="Q23" s="4">
         <f>IF(O23=0,0,P23/O23)</f>
-        <v>3.7357150105472768E-2</v>
+        <v>0</v>
       </c>
       <c r="S23" s="3">
-        <v>7595.5506331395254</v>
+        <v>7595.550633139525</v>
       </c>
       <c r="T23" s="3">
-        <v>4929.0831398403361</v>
+        <v>4929.083139840336</v>
       </c>
       <c r="U23" s="4">
         <f>IF(S23=0,0,T23/S23)</f>
-        <v>0.64894349046067268</v>
+        <v>0</v>
       </c>
       <c r="V23" s="3">
-        <v>25699987.560610589</v>
+        <v>25699987.56061059</v>
       </c>
       <c r="W23" s="3">
-        <v>2724438.1987594548</v>
+        <v>2724438.198759455</v>
       </c>
       <c r="X23" s="4">
         <f>IF(V23=0,0,W23/V23)</f>
-        <v>0.10600931974516203</v>
+        <v>0</v>
       </c>
       <c r="Y23" s="3">
-        <v>1959206.3612258229</v>
+        <v>1959206.361225823</v>
       </c>
       <c r="Z23" s="3">
-        <v>81685.476824872196</v>
+        <v>81685.4768248722</v>
       </c>
       <c r="AA23" s="4">
         <f>IF(Y23=0,0,Z23/Y23)</f>
-        <v>4.1693145980683619E-2</v>
+        <v>0</v>
       </c>
       <c r="AB23" s="3">
-        <v>205054.68928072241</v>
+        <v>205054.6892807224</v>
       </c>
       <c r="AC23" s="3">
-        <v>1029.3601439886841</v>
+        <v>1029.360143988684</v>
       </c>
       <c r="AD23" s="4">
         <f>IF(AB23=0,0,AC23/AB23)</f>
-        <v>5.0199297933610151E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30">
       <c r="B24" t="s">
         <v>31</v>
       </c>
       <c r="C24" s="3">
         <f>J24+M24+G24+P24</f>
-        <v>493.50667596471601</v>
+        <v>0</v>
       </c>
       <c r="D24" s="3">
         <f>G24</f>
-        <v>265.1770602919006</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3">
         <f>J24+M24+P24</f>
-        <v>228.32961567281538</v>
+        <v>0</v>
       </c>
       <c r="F24" s="3">
-        <v>423.46088348022653</v>
+        <v>423.4608834802265</v>
       </c>
       <c r="G24" s="3">
         <v>265.1770602919006</v>
       </c>
       <c r="H24" s="4">
         <f>IF(F24=0,0,G24/F24)</f>
-        <v>0.62621382667634995</v>
+        <v>0</v>
       </c>
       <c r="I24" s="3">
-        <v>847.52939170447485</v>
+        <v>847.5293917044748</v>
       </c>
       <c r="J24" s="3">
-        <v>129.63861091745869</v>
+        <v>129.6386109174587</v>
       </c>
       <c r="K24" s="4">
         <f>IF(I24=0,0,J24/I24)</f>
-        <v>0.15296060784009058</v>
+        <v>0</v>
       </c>
       <c r="L24" s="3">
         <v>18442.648959675</v>
       </c>
       <c r="M24" s="3">
-        <v>78.360818720057608</v>
+        <v>78.36081872005761</v>
       </c>
       <c r="N24" s="4">
         <f>IF(L24=0,0,M24/L24)</f>
-        <v>4.2488917341209588E-3</v>
+        <v>0</v>
       </c>
       <c r="O24" s="3">
-        <v>476.56393826290048</v>
+        <v>476.5639382629005</v>
       </c>
       <c r="P24" s="3">
-        <v>20.330186035299089</v>
+        <v>20.33018603529909</v>
       </c>
       <c r="Q24" s="4">
         <f>IF(O24=0,0,P24/O24)</f>
-        <v>4.2659933752863553E-2</v>
+        <v>0</v>
       </c>
       <c r="S24" s="3">
-        <v>7766.9232744992596</v>
+        <v>7766.92327449926</v>
       </c>
       <c r="T24" s="3">
-        <v>4863.7547452257877</v>
+        <v>4863.754745225788</v>
       </c>
       <c r="U24" s="4">
         <f>IF(S24=0,0,T24/S24)</f>
-        <v>0.62621382667634995</v>
+        <v>0</v>
       </c>
       <c r="V24" s="3">
-        <v>23322467.600951109</v>
+        <v>23322467.60095111</v>
       </c>
       <c r="W24" s="3">
-        <v>2821008.1417387952</v>
+        <v>2821008.141738795</v>
       </c>
       <c r="X24" s="4">
         <f>IF(V24=0,0,W24/V24)</f>
-        <v>0.12095667534012362</v>
+        <v>0</v>
       </c>
       <c r="Y24" s="3">
-        <v>2033978.1299748039</v>
+        <v>2033978.129974804</v>
       </c>
       <c r="Z24" s="3">
-        <v>83922.171154072974</v>
+        <v>83922.17115407297</v>
       </c>
       <c r="AA24" s="4">
         <f>IF(Y24=0,0,Z24/Y24)</f>
-        <v>4.1260114805222889E-2</v>
+        <v>0</v>
       </c>
       <c r="AB24" s="3">
-        <v>207305.28823611679</v>
+        <v>207305.2882361168</v>
       </c>
       <c r="AC24" s="3">
-        <v>870.34467375359964</v>
+        <v>870.3446737535996</v>
       </c>
       <c r="AD24" s="4">
         <f>IF(AB24=0,0,AC24/AB24)</f>
-        <v>4.1983717885782706E-3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30">
       <c r="B25" t="s">
         <v>32</v>
       </c>
       <c r="C25" s="3">
         <f>J25+M25+G25+P25</f>
-        <v>391.06609673602094</v>
+        <v>0</v>
       </c>
       <c r="D25" s="3">
         <f>G25</f>
-        <v>207.67060060169669</v>
+        <v>0</v>
       </c>
       <c r="E25" s="3">
         <f>J25+M25+P25</f>
-        <v>183.39549613432428</v>
+        <v>0</v>
       </c>
       <c r="F25" s="3">
-        <v>383.34862378459758</v>
+        <v>383.3486237845976</v>
       </c>
       <c r="G25" s="3">
-        <v>207.67060060169669</v>
+        <v>207.6706006016967</v>
       </c>
       <c r="H25" s="4">
         <f>IF(F25=0,0,G25/F25)</f>
-        <v>0.54172778436368185</v>
+        <v>0</v>
       </c>
       <c r="I25" s="3">
-        <v>721.62080381298233</v>
+        <v>721.6208038129823</v>
       </c>
       <c r="J25" s="3">
         <v>117.9993820939182</v>
       </c>
       <c r="K25" s="4">
         <f>IF(I25=0,0,J25/I25)</f>
-        <v>0.16351992829255976</v>
+        <v>0</v>
       </c>
       <c r="L25" s="3">
-        <v>15355.961975565249</v>
+        <v>15355.96197556525</v>
       </c>
       <c r="M25" s="3">
-        <v>48.616281052693722</v>
+        <v>48.61628105269372</v>
       </c>
       <c r="N25" s="4">
         <f>IF(L25=0,0,M25/L25)</f>
-        <v>3.1659547692325001E-3</v>
+        <v>0</v>
       </c>
       <c r="O25" s="3">
         <v>391.5266582641886</v>
@@ -2338,221 +2309,221 @@
       </c>
       <c r="Q25" s="4">
         <f>IF(O25=0,0,P25/O25)</f>
-        <v>4.2857446954199227E-2</v>
+        <v>0</v>
       </c>
       <c r="S25" s="3">
-        <v>7031.2027969376404</v>
+        <v>7031.20279693764</v>
       </c>
       <c r="T25" s="3">
         <v>3808.997912596752</v>
       </c>
       <c r="U25" s="4">
         <f>IF(S25=0,0,T25/S25)</f>
-        <v>0.54172778436368207</v>
+        <v>0</v>
       </c>
       <c r="V25" s="3">
-        <v>21162807.846375171</v>
+        <v>21162807.84637517</v>
       </c>
       <c r="W25" s="3">
-        <v>2800683.8604466021</v>
+        <v>2800683.860446602</v>
       </c>
       <c r="X25" s="4">
         <f>IF(V25=0,0,W25/V25)</f>
-        <v>0.13233989935443805</v>
+        <v>0</v>
       </c>
       <c r="Y25" s="3">
         <v>1664123.912966297</v>
       </c>
       <c r="Z25" s="3">
-        <v>70162.630031719338</v>
+        <v>70162.63003171934</v>
       </c>
       <c r="AA25" s="4">
         <f>IF(Y25=0,0,Z25/Y25)</f>
-        <v>4.2161902419066026E-2</v>
+        <v>0</v>
       </c>
       <c r="AB25" s="3">
         <v>172634.6152091868</v>
       </c>
       <c r="AC25" s="3">
-        <v>539.59249566448852</v>
+        <v>539.5924956644885</v>
       </c>
       <c r="AD25" s="4">
         <f>IF(AB25=0,0,AC25/AB25)</f>
-        <v>3.1256332631242425E-3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30">
       <c r="B26" t="s">
         <v>33</v>
       </c>
       <c r="C26" s="3">
         <f>J26+M26+G26+P26</f>
-        <v>320.34355948644912</v>
+        <v>0</v>
       </c>
       <c r="D26" s="3">
         <f>G26</f>
-        <v>163.9528075835068</v>
+        <v>0</v>
       </c>
       <c r="E26" s="3">
         <f>J26+M26+P26</f>
-        <v>156.39075190294236</v>
+        <v>0</v>
       </c>
       <c r="F26" s="3">
-        <v>339.79970462374757</v>
+        <v>339.7997046237476</v>
       </c>
       <c r="G26" s="3">
         <v>163.9528075835068</v>
       </c>
       <c r="H26" s="4">
         <f>IF(F26=0,0,G26/F26)</f>
-        <v>0.48249838170120829</v>
+        <v>0</v>
       </c>
       <c r="I26" s="3">
-        <v>656.23600296293523</v>
+        <v>656.2360029629352</v>
       </c>
       <c r="J26" s="3">
         <v>111.9114792464019</v>
       </c>
       <c r="K26" s="4">
         <f>IF(I26=0,0,J26/I26)</f>
-        <v>0.17053541521817839</v>
+        <v>0</v>
       </c>
       <c r="L26" s="3">
-        <v>12320.893910346331</v>
+        <v>12320.89391034633</v>
       </c>
       <c r="M26" s="3">
-        <v>30.922360504940151</v>
+        <v>30.92236050494015</v>
       </c>
       <c r="N26" s="4">
         <f>IF(L26=0,0,M26/L26)</f>
-        <v>2.5097497576026888E-3</v>
+        <v>0</v>
       </c>
       <c r="O26" s="3">
-        <v>305.89771512841492</v>
+        <v>305.8977151284149</v>
       </c>
       <c r="P26" s="3">
         <v>13.55691215160029</v>
       </c>
       <c r="Q26" s="4">
         <f>IF(O26=0,0,P26/O26)</f>
-        <v>4.4318448556927403E-2</v>
+        <v>0</v>
       </c>
       <c r="S26" s="3">
-        <v>6232.4487041632419</v>
+        <v>6232.448704163242</v>
       </c>
       <c r="T26" s="3">
-        <v>3007.1464137945559</v>
+        <v>3007.146413794556</v>
       </c>
       <c r="U26" s="4">
         <f>IF(S26=0,0,T26/S26)</f>
-        <v>0.48249838170120812</v>
+        <v>0</v>
       </c>
       <c r="V26" s="3">
-        <v>20232379.411657181</v>
+        <v>20232379.41165718</v>
       </c>
       <c r="W26" s="3">
         <v>2815905.181914039</v>
       </c>
       <c r="X26" s="4">
         <f>IF(V26=0,0,W26/V26)</f>
-        <v>0.13917815223905963</v>
+        <v>0</v>
       </c>
       <c r="Y26" s="3">
-        <v>1291512.2728871789</v>
+        <v>1291512.272887179</v>
       </c>
       <c r="Z26" s="3">
-        <v>51650.776301899918</v>
+        <v>51650.77630189992</v>
       </c>
       <c r="AA26" s="4">
         <f>IF(Y26=0,0,Z26/Y26)</f>
-        <v>3.9992478109739119E-2</v>
+        <v>0</v>
       </c>
       <c r="AB26" s="3">
-        <v>138538.51808137319</v>
+        <v>138538.5180813732</v>
       </c>
       <c r="AC26" s="3">
         <v>343.4734157078783</v>
       </c>
       <c r="AD26" s="4">
         <f>IF(AB26=0,0,AC26/AB26)</f>
-        <v>2.479262954914335E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30">
       <c r="B27" t="s">
         <v>34</v>
       </c>
       <c r="C27" s="3">
         <f>J27+M27+G27+P27</f>
-        <v>256.51657585301888</v>
+        <v>0</v>
       </c>
       <c r="D27" s="3">
         <f>G27</f>
-        <v>136.24207807158101</v>
+        <v>0</v>
       </c>
       <c r="E27" s="3">
         <f>J27+M27+P27</f>
-        <v>120.27449778143787</v>
+        <v>0</v>
       </c>
       <c r="F27" s="3">
-        <v>298.45239543280491</v>
+        <v>298.4523954328049</v>
       </c>
       <c r="G27" s="3">
-        <v>136.24207807158101</v>
+        <v>136.242078071581</v>
       </c>
       <c r="H27" s="4">
         <f>IF(F27=0,0,G27/F27)</f>
-        <v>0.45649517362394648</v>
+        <v>0</v>
       </c>
       <c r="I27" s="3">
-        <v>465.22851237667129</v>
+        <v>465.2285123766713</v>
       </c>
       <c r="J27" s="3">
-        <v>88.969804080313125</v>
+        <v>88.96980408031312</v>
       </c>
       <c r="K27" s="4">
         <f>IF(I27=0,0,J27/I27)</f>
-        <v>0.19123893251039376</v>
+        <v>0</v>
       </c>
       <c r="L27" s="3">
-        <v>10752.450404824391</v>
+        <v>10752.45040482439</v>
       </c>
       <c r="M27" s="3">
-        <v>19.489945549558851</v>
+        <v>19.48994554955885</v>
       </c>
       <c r="N27" s="4">
         <f>IF(L27=0,0,M27/L27)</f>
-        <v>1.8126050170679359E-3</v>
+        <v>0</v>
       </c>
       <c r="O27" s="3">
-        <v>286.13725715609343</v>
+        <v>286.1372571560934</v>
       </c>
       <c r="P27" s="3">
-        <v>11.814748151565899</v>
+        <v>11.8147481515659</v>
       </c>
       <c r="Q27" s="4">
         <f>IF(O27=0,0,P27/O27)</f>
-        <v>4.12904920840865E-2</v>
+        <v>0</v>
       </c>
       <c r="S27" s="3">
-        <v>5474.0755211345286</v>
+        <v>5474.075521134529</v>
       </c>
       <c r="T27" s="3">
-        <v>2498.8890554509012</v>
+        <v>2498.889055450901</v>
       </c>
       <c r="U27" s="4">
         <f>IF(S27=0,0,T27/S27)</f>
-        <v>0.45649517362394637</v>
+        <v>0</v>
       </c>
       <c r="V27" s="3">
-        <v>16252582.504079361</v>
+        <v>16252582.50407936</v>
       </c>
       <c r="W27" s="3">
-        <v>2620057.9126833701</v>
+        <v>2620057.91268337</v>
       </c>
       <c r="X27" s="4">
         <f>IF(V27=0,0,W27/V27)</f>
-        <v>0.16120871326299938</v>
+        <v>0</v>
       </c>
       <c r="Y27" s="3">
         <v>1133183.161267315</v>
@@ -2562,157 +2533,157 @@
       </c>
       <c r="AA27" s="4">
         <f>IF(Y27=0,0,Z27/Y27)</f>
-        <v>4.1178711245506497E-2</v>
+        <v>0</v>
       </c>
       <c r="AB27" s="3">
-        <v>120916.42366991749</v>
+        <v>120916.4236699175</v>
       </c>
       <c r="AC27" s="3">
-        <v>216.26103951976981</v>
+        <v>216.2610395197698</v>
       </c>
       <c r="AD27" s="4">
         <f>IF(AB27=0,0,AC27/AB27)</f>
-        <v>1.7885166709042592E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30">
       <c r="A29" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30">
       <c r="B30" t="s">
         <v>28</v>
       </c>
       <c r="C30" s="3">
         <f>C32+C33+C34+C35+C36</f>
-        <v>280.67849666325867</v>
+        <v>0</v>
       </c>
       <c r="D30" s="3">
         <f>D32+D33+D34+D35+D36</f>
-        <v>189.72309826269347</v>
+        <v>0</v>
       </c>
       <c r="E30" s="3">
         <f>E32+E33+E34+E35+E36</f>
-        <v>90.955398400565215</v>
+        <v>0</v>
       </c>
       <c r="F30" s="3">
         <f>F32+F33+F34+F35+F36</f>
-        <v>1859.1790728805329</v>
+        <v>0</v>
       </c>
       <c r="G30" s="3">
         <f>G32+G33+G34+G35+G36</f>
-        <v>189.72309826269347</v>
+        <v>0</v>
       </c>
       <c r="H30" s="4">
         <f>IF(F30=0,0,G30/F30)</f>
-        <v>0.1020467049302274</v>
+        <v>0</v>
       </c>
       <c r="I30" s="3">
         <f>I32+I33+I34+I35+I36</f>
-        <v>3682.4352162782898</v>
+        <v>0</v>
       </c>
       <c r="J30" s="3">
         <f>J32+J33+J34+J35+J36</f>
-        <v>73.986991036804866</v>
+        <v>0</v>
       </c>
       <c r="K30" s="4">
         <f>IF(I30=0,0,J30/I30)</f>
-        <v>2.0091864945714095E-2</v>
+        <v>0</v>
       </c>
       <c r="L30" s="3">
         <f>L32+L33+L34+L35+L36</f>
-        <v>75120.106151105079</v>
+        <v>0</v>
       </c>
       <c r="M30" s="3">
         <f>M32+M33+M34+M35+M36</f>
-        <v>7.7175543162524711</v>
+        <v>0</v>
       </c>
       <c r="N30" s="4">
         <f>IF(L30=0,0,M30/L30)</f>
-        <v>1.0273620088779572E-4</v>
+        <v>0</v>
       </c>
       <c r="O30" s="3">
         <f>O32+O33+O34+O35+O36</f>
-        <v>1936.1737568351107</v>
+        <v>0</v>
       </c>
       <c r="P30" s="3">
         <f>P32+P33+P34+P35+P36</f>
-        <v>9.2508530475078743</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="4">
         <f>IF(O30=0,0,P30/O30)</f>
-        <v>4.7779043667183123E-3</v>
+        <v>0</v>
       </c>
       <c r="S30" s="3">
         <f>S32+S33+S34+S35+S36</f>
-        <v>34100.200929874198</v>
+        <v>0</v>
       </c>
       <c r="T30" s="3">
         <f>T32+T33+T34+T35+T36</f>
-        <v>3479.8131423523364</v>
+        <v>0</v>
       </c>
       <c r="U30" s="4">
         <f>IF(S30=0,0,T30/S30)</f>
-        <v>0.10204670493022734</v>
+        <v>0</v>
       </c>
       <c r="V30" s="3">
         <f>V32+V33+V34+V35+V36</f>
-        <v>106670224.92367341</v>
+        <v>0</v>
       </c>
       <c r="W30" s="3">
         <f>W32+W33+W34+W35+W36</f>
-        <v>1767252.4081023186</v>
+        <v>0</v>
       </c>
       <c r="X30" s="4">
         <f>IF(V30=0,0,W30/V30)</f>
-        <v>1.6567438658415267E-2</v>
+        <v>0</v>
       </c>
       <c r="Y30" s="3">
         <f>Y32+Y33+Y34+Y35+Y36</f>
-        <v>8082003.8383214176</v>
+        <v>0</v>
       </c>
       <c r="Z30" s="3">
         <f>Z32+Z33+Z34+Z35+Z36</f>
-        <v>39755.677394214319</v>
+        <v>0</v>
       </c>
       <c r="AA30" s="4">
         <f>IF(Y30=0,0,Z30/Y30)</f>
-        <v>4.9190371830448582E-3</v>
+        <v>0</v>
       </c>
       <c r="AB30" s="3">
         <f>AB32+AB33+AB34+AB35+AB36</f>
-        <v>844449.53447731666</v>
+        <v>0</v>
       </c>
       <c r="AC30" s="3">
         <f>AC32+AC33+AC34+AC35+AC36</f>
-        <v>85.868353927085991</v>
+        <v>0</v>
       </c>
       <c r="AD30" s="4">
         <f>IF(AB30=0,0,AC30/AB30)</f>
-        <v>1.0168559567059903E-4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30">
       <c r="A31" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30">
       <c r="B32" t="s">
         <v>30</v>
       </c>
       <c r="C32" s="3">
         <f>J32+M32+G32+P32</f>
-        <v>31.460329582100499</v>
+        <v>0</v>
       </c>
       <c r="D32" s="3">
         <f>G32</f>
-        <v>17.33188958193897</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
         <f>J32+M32+P32</f>
-        <v>14.128440000161532</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
         <v>414.1174655591563</v>
@@ -2722,114 +2693,114 @@
       </c>
       <c r="H32" s="4">
         <f>IF(F32=0,0,G32/F32)</f>
-        <v>4.1852592617741512E-2</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>991.82050542122556</v>
+        <v>991.8205054212256</v>
       </c>
       <c r="J32" s="3">
         <v>11.67126541163598</v>
       </c>
       <c r="K32" s="4">
         <f>IF(I32=0,0,J32/I32)</f>
-        <v>1.1767517759354251E-2</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3">
-        <v>18248.150900694091</v>
+        <v>18248.15090069409</v>
       </c>
       <c r="M32" s="3">
-        <v>1.0535630249716339</v>
+        <v>1.053563024971634</v>
       </c>
       <c r="N32" s="4">
         <f>IF(L32=0,0,M32/L32)</f>
-        <v>5.773533059349922E-5</v>
+        <v>0</v>
       </c>
       <c r="O32" s="3">
-        <v>476.04818802351332</v>
+        <v>476.0481880235133</v>
       </c>
       <c r="P32" s="3">
         <v>1.403611563553917</v>
       </c>
       <c r="Q32" s="4">
         <f>IF(O32=0,0,P32/O32)</f>
-        <v>2.9484653000813204E-3</v>
+        <v>0</v>
       </c>
       <c r="S32" s="3">
-        <v>7595.5506331395254</v>
+        <v>7595.550633139525</v>
       </c>
       <c r="T32" s="3">
-        <v>317.89348635621809</v>
+        <v>317.8934863562181</v>
       </c>
       <c r="U32" s="4">
         <f>IF(S32=0,0,T32/S32)</f>
-        <v>4.1852592617741637E-2</v>
+        <v>0</v>
       </c>
       <c r="V32" s="3">
-        <v>25699987.560610589</v>
+        <v>25699987.56061059</v>
       </c>
       <c r="W32" s="3">
-        <v>227272.75268540901</v>
+        <v>227272.752685409</v>
       </c>
       <c r="X32" s="4">
         <f>IF(V32=0,0,W32/V32)</f>
-        <v>8.8433020502212793E-3</v>
+        <v>0</v>
       </c>
       <c r="Y32" s="3">
-        <v>1959206.3612258229</v>
+        <v>1959206.361225823</v>
       </c>
       <c r="Z32" s="3">
-        <v>6013.3033886032636</v>
+        <v>6013.303388603264</v>
       </c>
       <c r="AA32" s="4">
         <f>IF(Y32=0,0,Z32/Y32)</f>
-        <v>3.0692547286549749E-3</v>
+        <v>0</v>
       </c>
       <c r="AB32" s="3">
-        <v>205054.68928072241</v>
+        <v>205054.6892807224</v>
       </c>
       <c r="AC32" s="3">
         <v>11.66113448393298</v>
       </c>
       <c r="AD32" s="4">
         <f>IF(AB32=0,0,AC32/AB32)</f>
-        <v>5.686841166538134E-5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:30">
       <c r="B33" t="s">
         <v>31</v>
       </c>
       <c r="C33" s="3">
         <f>J33+M33+G33+P33</f>
-        <v>51.199869194986363</v>
+        <v>0</v>
       </c>
       <c r="D33" s="3">
         <f>G33</f>
-        <v>33.493628411801069</v>
+        <v>0</v>
       </c>
       <c r="E33" s="3">
         <f>J33+M33+P33</f>
-        <v>17.706240783185294</v>
+        <v>0</v>
       </c>
       <c r="F33" s="3">
-        <v>423.46088348022653</v>
+        <v>423.4608834802265</v>
       </c>
       <c r="G33" s="3">
-        <v>33.493628411801069</v>
+        <v>33.49362841180107</v>
       </c>
       <c r="H33" s="4">
         <f>IF(F33=0,0,G33/F33)</f>
-        <v>7.9094975990539274E-2</v>
+        <v>0</v>
       </c>
       <c r="I33" s="3">
-        <v>847.52939170447485</v>
+        <v>847.5293917044748</v>
       </c>
       <c r="J33" s="3">
         <v>14.3231196181163</v>
       </c>
       <c r="K33" s="4">
         <f>IF(I33=0,0,J33/I33)</f>
-        <v>1.6899850032706158E-2</v>
+        <v>0</v>
       </c>
       <c r="L33" s="3">
         <v>18442.648959675</v>
@@ -2839,104 +2810,104 @@
       </c>
       <c r="N33" s="4">
         <f>IF(L33=0,0,M33/L33)</f>
-        <v>9.2629689549605278E-5</v>
+        <v>0</v>
       </c>
       <c r="O33" s="3">
-        <v>476.56393826290048</v>
+        <v>476.5639382629005</v>
       </c>
       <c r="P33" s="3">
-        <v>1.6747843174619479</v>
+        <v>1.674784317461948</v>
       </c>
       <c r="Q33" s="4">
         <f>IF(O33=0,0,P33/O33)</f>
-        <v>3.514290912498795E-3</v>
+        <v>0</v>
       </c>
       <c r="S33" s="3">
-        <v>7766.9232744992596</v>
+        <v>7766.92327449926</v>
       </c>
       <c r="T33" s="3">
-        <v>614.32460991687913</v>
+        <v>614.3246099168791</v>
       </c>
       <c r="U33" s="4">
         <f>IF(S33=0,0,T33/S33)</f>
-        <v>7.9094975990539204E-2</v>
+        <v>0</v>
       </c>
       <c r="V33" s="3">
-        <v>23322467.600951109</v>
+        <v>23322467.60095111</v>
       </c>
       <c r="W33" s="3">
         <v>307442.101903148</v>
       </c>
       <c r="X33" s="4">
         <f>IF(V33=0,0,W33/V33)</f>
-        <v>1.3182228705962926E-2</v>
+        <v>0</v>
       </c>
       <c r="Y33" s="3">
-        <v>2033978.1299748039</v>
+        <v>2033978.129974804</v>
       </c>
       <c r="Z33" s="3">
-        <v>8632.8553056851961</v>
+        <v>8632.855305685196</v>
       </c>
       <c r="AA33" s="4">
         <f>IF(Y33=0,0,Z33/Y33)</f>
-        <v>4.244320614102245E-3</v>
+        <v>0</v>
       </c>
       <c r="AB33" s="3">
-        <v>207305.28823611679</v>
+        <v>207305.2882361168</v>
       </c>
       <c r="AC33" s="3">
-        <v>19.081856428296309</v>
+        <v>19.08185642829631</v>
       </c>
       <c r="AD33" s="4">
         <f>IF(AB33=0,0,AC33/AB33)</f>
-        <v>9.2047128129999444E-5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:30">
       <c r="B34" t="s">
         <v>32</v>
       </c>
       <c r="C34" s="3">
         <f>J34+M34+G34+P34</f>
-        <v>61.694651508568448</v>
+        <v>0</v>
       </c>
       <c r="D34" s="3">
         <f>G34</f>
-        <v>41.906726289321213</v>
+        <v>0</v>
       </c>
       <c r="E34" s="3">
         <f>J34+M34+P34</f>
-        <v>19.787925219247239</v>
+        <v>0</v>
       </c>
       <c r="F34" s="3">
-        <v>383.34862378459758</v>
+        <v>383.3486237845976</v>
       </c>
       <c r="G34" s="3">
-        <v>41.906726289321213</v>
+        <v>41.90672628932121</v>
       </c>
       <c r="H34" s="4">
         <f>IF(F34=0,0,G34/F34)</f>
-        <v>0.10931753419537114</v>
+        <v>0</v>
       </c>
       <c r="I34" s="3">
-        <v>721.62080381298233</v>
+        <v>721.6208038129823</v>
       </c>
       <c r="J34" s="3">
         <v>15.78004529479356</v>
       </c>
       <c r="K34" s="4">
         <f>IF(I34=0,0,J34/I34)</f>
-        <v>2.1867503280688632E-2</v>
+        <v>0</v>
       </c>
       <c r="L34" s="3">
-        <v>15355.961975565249</v>
+        <v>15355.96197556525</v>
       </c>
       <c r="M34" s="3">
         <v>1.813587757010013</v>
       </c>
       <c r="N34" s="4">
         <f>IF(L34=0,0,M34/L34)</f>
-        <v>1.181031680005352E-4</v>
+        <v>0</v>
       </c>
       <c r="O34" s="3">
         <v>391.5266582641886</v>
@@ -2946,259 +2917,259 @@
       </c>
       <c r="Q34" s="4">
         <f>IF(O34=0,0,P34/O34)</f>
-        <v>5.6044515006256198E-3</v>
+        <v>0</v>
       </c>
       <c r="S34" s="3">
-        <v>7031.2027969376404</v>
+        <v>7031.20279693764</v>
       </c>
       <c r="T34" s="3">
-        <v>768.63375218881993</v>
+        <v>768.6337521888199</v>
       </c>
       <c r="U34" s="4">
         <f>IF(S34=0,0,T34/S34)</f>
-        <v>0.10931753419537117</v>
+        <v>0</v>
       </c>
       <c r="V34" s="3">
-        <v>21162807.846375171</v>
+        <v>21162807.84637517</v>
       </c>
       <c r="W34" s="3">
-        <v>369371.39764320478</v>
+        <v>369371.3976432048</v>
       </c>
       <c r="X34" s="4">
         <f>IF(V34=0,0,W34/V34)</f>
-        <v>1.7453799152009584E-2</v>
+        <v>0</v>
       </c>
       <c r="Y34" s="3">
         <v>1664123.912966297</v>
       </c>
       <c r="Z34" s="3">
-        <v>9278.7286326091271</v>
+        <v>9278.728632609127</v>
       </c>
       <c r="AA34" s="4">
         <f>IF(Y34=0,0,Z34/Y34)</f>
-        <v>5.5757438255122568E-3</v>
+        <v>0</v>
       </c>
       <c r="AB34" s="3">
         <v>172634.6152091868</v>
       </c>
       <c r="AC34" s="3">
-        <v>20.141959563101409</v>
+        <v>20.14195956310141</v>
       </c>
       <c r="AD34" s="4">
         <f>IF(AB34=0,0,AC34/AB34)</f>
-        <v>1.1667393320102554E-4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:30">
       <c r="B35" t="s">
         <v>33</v>
       </c>
       <c r="C35" s="3">
         <f>J35+M35+G35+P35</f>
-        <v>69.409153233409029</v>
+        <v>0</v>
       </c>
       <c r="D35" s="3">
         <f>G35</f>
-        <v>49.152212620382947</v>
+        <v>0</v>
       </c>
       <c r="E35" s="3">
         <f>J35+M35+P35</f>
-        <v>20.256940613026089</v>
+        <v>0</v>
       </c>
       <c r="F35" s="3">
-        <v>339.79970462374757</v>
+        <v>339.7997046237476</v>
       </c>
       <c r="G35" s="3">
-        <v>49.152212620382947</v>
+        <v>49.15221262038295</v>
       </c>
       <c r="H35" s="4">
         <f>IF(F35=0,0,G35/F35)</f>
-        <v>0.14465054545826656</v>
+        <v>0</v>
       </c>
       <c r="I35" s="3">
-        <v>656.23600296293523</v>
+        <v>656.2360029629352</v>
       </c>
       <c r="J35" s="3">
-        <v>17.337373260950319</v>
+        <v>17.33737326095032</v>
       </c>
       <c r="K35" s="4">
         <f>IF(I35=0,0,J35/I35)</f>
-        <v>2.6419417987844761E-2</v>
+        <v>0</v>
       </c>
       <c r="L35" s="3">
-        <v>12320.893910346331</v>
+        <v>12320.89391034633</v>
       </c>
       <c r="M35" s="3">
-        <v>0.76115932066179814</v>
+        <v>0.7611593206617981</v>
       </c>
       <c r="N35" s="4">
         <f>IF(L35=0,0,M35/L35)</f>
-        <v>6.1777929929469097E-5</v>
+        <v>0</v>
       </c>
       <c r="O35" s="3">
-        <v>305.89771512841492</v>
+        <v>305.8977151284149</v>
       </c>
       <c r="P35" s="3">
         <v>2.158408031413972</v>
       </c>
       <c r="Q35" s="4">
         <f>IF(O35=0,0,P35/O35)</f>
-        <v>7.0559795796705412E-3</v>
+        <v>0</v>
       </c>
       <c r="S35" s="3">
-        <v>6232.4487041632419</v>
+        <v>6232.448704163242</v>
       </c>
       <c r="T35" s="3">
-        <v>901.52710459787795</v>
+        <v>901.527104597878</v>
       </c>
       <c r="U35" s="4">
         <f>IF(S35=0,0,T35/S35)</f>
-        <v>0.14465054545826631</v>
+        <v>0</v>
       </c>
       <c r="V35" s="3">
-        <v>20232379.411657181</v>
+        <v>20232379.41165718</v>
       </c>
       <c r="W35" s="3">
-        <v>430534.00670235232</v>
+        <v>430534.0067023523</v>
       </c>
       <c r="X35" s="4">
         <f>IF(V35=0,0,W35/V35)</f>
-        <v>2.1279454973758244E-2</v>
+        <v>0</v>
       </c>
       <c r="Y35" s="3">
-        <v>1291512.2728871789</v>
+        <v>1291512.272887179</v>
       </c>
       <c r="Z35" s="3">
-        <v>8071.8257655487396</v>
+        <v>8071.82576554874</v>
       </c>
       <c r="AA35" s="4">
         <f>IF(Y35=0,0,Z35/Y35)</f>
-        <v>6.2499024864116487E-3</v>
+        <v>0</v>
       </c>
       <c r="AB35" s="3">
-        <v>138538.51808137319</v>
+        <v>138538.5180813732</v>
       </c>
       <c r="AC35" s="3">
-        <v>8.4808250792266335</v>
+        <v>8.480825079226634</v>
       </c>
       <c r="AD35" s="4">
         <f>IF(AB35=0,0,AC35/AB35)</f>
-        <v>6.1216369257286713E-5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:30">
       <c r="B36" t="s">
         <v>34</v>
       </c>
       <c r="C36" s="3">
         <f>J36+M36+G36+P36</f>
-        <v>66.914493144194338</v>
+        <v>0</v>
       </c>
       <c r="D36" s="3">
         <f>G36</f>
-        <v>47.838641359249273</v>
+        <v>0</v>
       </c>
       <c r="E36" s="3">
         <f>J36+M36+P36</f>
-        <v>19.075851784945058</v>
+        <v>0</v>
       </c>
       <c r="F36" s="3">
-        <v>298.45239543280491</v>
+        <v>298.4523954328049</v>
       </c>
       <c r="G36" s="3">
-        <v>47.838641359249273</v>
+        <v>47.83864135924927</v>
       </c>
       <c r="H36" s="4">
         <f>IF(F36=0,0,G36/F36)</f>
-        <v>0.16028901791816882</v>
+        <v>0</v>
       </c>
       <c r="I36" s="3">
-        <v>465.22851237667129</v>
+        <v>465.2285123766713</v>
       </c>
       <c r="J36" s="3">
         <v>14.87518745130871</v>
       </c>
       <c r="K36" s="4">
         <f>IF(I36=0,0,J36/I36)</f>
-        <v>3.1973937657683901E-2</v>
+        <v>0</v>
       </c>
       <c r="L36" s="3">
-        <v>10752.450404824391</v>
+        <v>10752.45040482439</v>
       </c>
       <c r="M36" s="3">
-        <v>2.3809073660019791</v>
+        <v>2.380907366001979</v>
       </c>
       <c r="N36" s="4">
         <f>IF(L36=0,0,M36/L36)</f>
-        <v>2.2142928136024861E-4</v>
+        <v>0</v>
       </c>
       <c r="O36" s="3">
-        <v>286.13725715609343</v>
+        <v>286.1372571560934</v>
       </c>
       <c r="P36" s="3">
-        <v>1.8197569676343699</v>
+        <v>1.81975696763437</v>
       </c>
       <c r="Q36" s="4">
         <f>IF(O36=0,0,P36/O36)</f>
-        <v>6.3597344355672538E-3</v>
+        <v>0</v>
       </c>
       <c r="S36" s="3">
-        <v>5474.0755211345286</v>
+        <v>5474.075521134529</v>
       </c>
       <c r="T36" s="3">
         <v>877.4341892925413</v>
       </c>
       <c r="U36" s="4">
         <f>IF(S36=0,0,T36/S36)</f>
-        <v>0.16028901791816874</v>
+        <v>0</v>
       </c>
       <c r="V36" s="3">
-        <v>16252582.504079361</v>
+        <v>16252582.50407936</v>
       </c>
       <c r="W36" s="3">
-        <v>432632.14916820452</v>
+        <v>432632.1491682045</v>
       </c>
       <c r="X36" s="4">
         <f>IF(V36=0,0,W36/V36)</f>
-        <v>2.6619286446299524E-2</v>
+        <v>0</v>
       </c>
       <c r="Y36" s="3">
         <v>1133183.161267315</v>
       </c>
       <c r="Z36" s="3">
-        <v>7758.9643017679919</v>
+        <v>7758.964301767992</v>
       </c>
       <c r="AA36" s="4">
         <f>IF(Y36=0,0,Z36/Y36)</f>
-        <v>6.8470522391901939E-3</v>
+        <v>0</v>
       </c>
       <c r="AB36" s="3">
-        <v>120916.42366991749</v>
+        <v>120916.4236699175</v>
       </c>
       <c r="AC36" s="3">
         <v>26.50257837252866</v>
       </c>
       <c r="AD36" s="4">
         <f>IF(AB36=0,0,AC36/AB36)</f>
-        <v>2.1918096457166532E-4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:30">
       <c r="A38" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:30">
       <c r="B39" t="s">
         <v>28</v>
       </c>
       <c r="C39" s="3">
         <f>C41+C42+C43+C44+C45</f>
-        <v>278.75634518647166</v>
+        <v>0</v>
       </c>
       <c r="D39" s="3">
         <f>D41+D42+D43+D44+D45</f>
-        <v>278.75634518647166</v>
+        <v>0</v>
       </c>
       <c r="E39" s="3">
         <f>E41+E42+E43+E44+E45</f>
@@ -3206,27 +3177,27 @@
       </c>
       <c r="F39" s="3">
         <f>F41+F42+F43+F44+F45</f>
-        <v>651.08593726395497</v>
+        <v>0</v>
       </c>
       <c r="G39" s="3">
         <f>G41+G42+G43+G44+G45</f>
-        <v>270.32651231194274</v>
+        <v>0</v>
       </c>
       <c r="H39" s="4">
         <f>IF(F39=0,0,G39/F39)</f>
-        <v>0.41519328991796423</v>
+        <v>0</v>
       </c>
       <c r="I39" s="3">
         <f>I41+I42+I43+I44+I45</f>
-        <v>814.53034621778045</v>
+        <v>0</v>
       </c>
       <c r="J39" s="6">
         <f>J41+J42+J43+J44+J45</f>
-        <v>8.4298328745289179</v>
+        <v>0</v>
       </c>
       <c r="K39" s="7">
         <f>IF(I39=0,0,J39/I39)</f>
-        <v>1.0349317141678402E-2</v>
+        <v>0</v>
       </c>
       <c r="L39" s="3">
         <f>L41+L42+L43+L44+L45</f>
@@ -3254,27 +3225,27 @@
       </c>
       <c r="S39" s="3">
         <f>S41+S42+S43+S44+S45</f>
-        <v>8683.3005265167885</v>
+        <v>0</v>
       </c>
       <c r="T39" s="3">
         <f>T41+T42+T43+T44+T45</f>
-        <v>3605.2481129508969</v>
+        <v>0</v>
       </c>
       <c r="U39" s="4">
         <f>IF(S39=0,0,T39/S39)</f>
-        <v>0.41519328991796428</v>
+        <v>0</v>
       </c>
       <c r="V39" s="3">
         <f>V41+V42+V43+V44+V45</f>
-        <v>26890169.836246081</v>
+        <v>0</v>
       </c>
       <c r="W39" s="6">
         <f>W41+W42+W43+W44+W45</f>
-        <v>317460.72176834382</v>
+        <v>0</v>
       </c>
       <c r="X39" s="7">
         <f>IF(V39=0,0,W39/V39)</f>
-        <v>1.1805828066598108E-2</v>
+        <v>0</v>
       </c>
       <c r="Y39" s="3">
         <f>Y41+Y42+Y43+Y44+Y45</f>
@@ -3301,46 +3272,46 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:30">
       <c r="A40" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:30">
       <c r="B41" t="s">
         <v>30</v>
       </c>
       <c r="C41" s="3">
         <f>J41+M41+G41+P41</f>
-        <v>74.745208573138058</v>
+        <v>0</v>
       </c>
       <c r="D41" s="3">
-        <f>J41+G41</f>
-        <v>74.745208573138058</v>
+        <f>G41+J41</f>
+        <v>0</v>
       </c>
       <c r="E41" s="3">
-        <f>M41+P41</f>
+        <f>P41+M41</f>
         <v>0</v>
       </c>
       <c r="F41" s="3">
-        <v>155.69318362382799</v>
+        <v>155.693183623828</v>
       </c>
       <c r="G41" s="3">
-        <v>72.167708957411648</v>
+        <v>72.16770895741165</v>
       </c>
       <c r="H41" s="4">
         <f>IF(F41=0,0,G41/F41)</f>
-        <v>0.46352516711185532</v>
+        <v>0</v>
       </c>
       <c r="I41" s="3">
-        <v>289.90090139463632</v>
+        <v>289.9009013946363</v>
       </c>
       <c r="J41" s="6">
-        <v>2.5774996157264098</v>
+        <v>2.57749961572641</v>
       </c>
       <c r="K41" s="7">
         <f>IF(I41=0,0,J41/I41)</f>
-        <v>8.8909679249934825E-3</v>
+        <v>0</v>
       </c>
       <c r="L41" s="3">
         <v>0</v>
@@ -3363,24 +3334,24 @@
         <v>0</v>
       </c>
       <c r="S41" s="3">
-        <v>2076.4243642199531</v>
+        <v>2076.424364219953</v>
       </c>
       <c r="T41" s="3">
-        <v>962.47495042018159</v>
+        <v>962.4749504201816</v>
       </c>
       <c r="U41" s="4">
         <f>IF(S41=0,0,T41/S41)</f>
-        <v>0.46352516711185526</v>
+        <v>0</v>
       </c>
       <c r="V41" s="3">
-        <v>7917202.4300766056</v>
+        <v>7917202.430076606</v>
       </c>
       <c r="W41" s="6">
-        <v>75888.026322795078</v>
+        <v>75888.02632279508</v>
       </c>
       <c r="X41" s="7">
         <f>IF(V41=0,0,W41/V41)</f>
-        <v>9.585207274037175E-3</v>
+        <v>0</v>
       </c>
       <c r="Y41" s="3">
         <v>0</v>
@@ -3403,41 +3374,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:30">
       <c r="B42" t="s">
         <v>31</v>
       </c>
       <c r="C42" s="3">
         <f>J42+M42+G42+P42</f>
-        <v>75.003443181858643</v>
+        <v>0</v>
       </c>
       <c r="D42" s="3">
-        <f>J42+G42</f>
-        <v>75.003443181858643</v>
+        <f>G42+J42</f>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <f>M42+P42</f>
+        <f>P42+M42</f>
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>148.09982986674899</v>
+        <v>148.099829866749</v>
       </c>
       <c r="G42" s="3">
-        <v>72.910490479003187</v>
+        <v>72.91049047900319</v>
       </c>
       <c r="H42" s="4">
         <f>IF(F42=0,0,G42/F42)</f>
-        <v>0.4923063756697324</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>172.51020331953049</v>
+        <v>172.5102033195305</v>
       </c>
       <c r="J42" s="6">
-        <v>2.0929527028554591</v>
+        <v>2.092952702855459</v>
       </c>
       <c r="K42" s="7">
         <f>IF(I42=0,0,J42/I42)</f>
-        <v>1.2132341522888394E-2</v>
+        <v>0</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
@@ -3460,24 +3431,24 @@
         <v>0</v>
       </c>
       <c r="S42" s="3">
-        <v>1975.1545181010979</v>
+        <v>1975.154518101098</v>
       </c>
       <c r="T42" s="3">
-        <v>972.38116219404844</v>
+        <v>972.3811621940484</v>
       </c>
       <c r="U42" s="4">
         <f>IF(S42=0,0,T42/S42)</f>
-        <v>0.49230637566973245</v>
+        <v>0</v>
       </c>
       <c r="V42" s="3">
         <v>5775458.9344058</v>
       </c>
       <c r="W42" s="6">
-        <v>81365.067625927739</v>
+        <v>81365.06762592774</v>
       </c>
       <c r="X42" s="7">
         <f>IF(V42=0,0,W42/V42)</f>
-        <v>1.4088069632218564E-2</v>
+        <v>0</v>
       </c>
       <c r="Y42" s="3">
         <v>0</v>
@@ -3500,41 +3471,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:30">
       <c r="B43" t="s">
         <v>32</v>
       </c>
       <c r="C43" s="3">
         <f>J43+M43+G43+P43</f>
-        <v>75.235790083751482</v>
+        <v>0</v>
       </c>
       <c r="D43" s="3">
-        <f>J43+G43</f>
-        <v>75.235790083751482</v>
+        <f>G43+J43</f>
+        <v>0</v>
       </c>
       <c r="E43" s="3">
-        <f>M43+P43</f>
+        <f>P43+M43</f>
         <v>0</v>
       </c>
       <c r="F43" s="3">
         <v>134.796744990006</v>
       </c>
       <c r="G43" s="3">
-        <v>72.948475873586105</v>
+        <v>72.9484758735861</v>
       </c>
       <c r="H43" s="4">
         <f>IF(F43=0,0,G43/F43)</f>
-        <v>0.54117386795203837</v>
+        <v>0</v>
       </c>
       <c r="I43" s="3">
-        <v>135.45605543604131</v>
+        <v>135.4560554360413</v>
       </c>
       <c r="J43" s="6">
-        <v>2.2873142101653792</v>
+        <v>2.287314210165379</v>
       </c>
       <c r="K43" s="7">
         <f>IF(I43=0,0,J43/I43)</f>
-        <v>1.6886024052615255E-2</v>
+        <v>0</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -3560,21 +3531,21 @@
         <v>1797.736028001397</v>
       </c>
       <c r="T43" s="3">
-        <v>972.88775983024993</v>
+        <v>972.8877598302499</v>
       </c>
       <c r="U43" s="4">
         <f>IF(S43=0,0,T43/S43)</f>
-        <v>0.54117386795203837</v>
+        <v>0</v>
       </c>
       <c r="V43" s="3">
-        <v>4941006.3189266957</v>
+        <v>4941006.318926696</v>
       </c>
       <c r="W43" s="6">
-        <v>93694.982139615342</v>
+        <v>93694.98213961534</v>
       </c>
       <c r="X43" s="7">
         <f>IF(V43=0,0,W43/V43)</f>
-        <v>1.8962732709066465E-2</v>
+        <v>0</v>
       </c>
       <c r="Y43" s="3">
         <v>0</v>
@@ -3597,41 +3568,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:30">
       <c r="B44" t="s">
         <v>33</v>
       </c>
       <c r="C44" s="3">
         <f>J44+M44+G44+P44</f>
-        <v>34.066310779577314</v>
+        <v>0</v>
       </c>
       <c r="D44" s="3">
-        <f>J44+G44</f>
-        <v>34.066310779577314</v>
+        <f>G44+J44</f>
+        <v>0</v>
       </c>
       <c r="E44" s="3">
-        <f>M44+P44</f>
+        <f>P44+M44</f>
         <v>0</v>
       </c>
       <c r="F44" s="3">
         <v>118.7859525719791</v>
       </c>
       <c r="G44" s="3">
-        <v>33.213641030588931</v>
+        <v>33.21364103058893</v>
       </c>
       <c r="H44" s="4">
         <f>IF(F44=0,0,G44/F44)</f>
-        <v>0.27960916515328627</v>
+        <v>0</v>
       </c>
       <c r="I44" s="3">
-        <v>131.31388542968341</v>
+        <v>131.3138854296834</v>
       </c>
       <c r="J44" s="6">
-        <v>0.85266974898838088</v>
+        <v>0.8526697489883809</v>
       </c>
       <c r="K44" s="7">
         <f>IF(I44=0,0,J44/I44)</f>
-        <v>6.4933707977514118E-3</v>
+        <v>0</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3654,24 +3625,24 @@
         <v>0</v>
       </c>
       <c r="S44" s="3">
-        <v>1584.2058098283051</v>
+        <v>1584.205809828305</v>
       </c>
       <c r="T44" s="3">
-        <v>442.95846391707801</v>
+        <v>442.958463917078</v>
       </c>
       <c r="U44" s="4">
         <f>IF(S44=0,0,T44/S44)</f>
-        <v>0.27960916515328615</v>
+        <v>0</v>
       </c>
       <c r="V44" s="3">
-        <v>4714339.9302510964</v>
+        <v>4714339.930251096</v>
       </c>
       <c r="W44" s="6">
-        <v>37175.273221418262</v>
+        <v>37175.27322141826</v>
       </c>
       <c r="X44" s="7">
         <f>IF(V44=0,0,W44/V44)</f>
-        <v>7.885573329761612E-3</v>
+        <v>0</v>
       </c>
       <c r="Y44" s="3">
         <v>0</v>
@@ -3694,20 +3665,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:30">
       <c r="B45" t="s">
         <v>34</v>
       </c>
       <c r="C45" s="3">
         <f>J45+M45+G45+P45</f>
-        <v>19.70559256814618</v>
+        <v>0</v>
       </c>
       <c r="D45" s="3">
-        <f>J45+G45</f>
-        <v>19.70559256814618</v>
+        <f>G45+J45</f>
+        <v>0</v>
       </c>
       <c r="E45" s="3">
-        <f>M45+P45</f>
+        <f>P45+M45</f>
         <v>0</v>
       </c>
       <c r="F45" s="3">
@@ -3718,17 +3689,17 @@
       </c>
       <c r="H45" s="4">
         <f>IF(F45=0,0,G45/F45)</f>
-        <v>0.20367249918165792</v>
+        <v>0</v>
       </c>
       <c r="I45" s="3">
-        <v>85.349300637888987</v>
+        <v>85.34930063788899</v>
       </c>
       <c r="J45" s="6">
-        <v>0.61939659679328907</v>
+        <v>0.6193965967932891</v>
       </c>
       <c r="K45" s="7">
         <f>IF(I45=0,0,J45/I45)</f>
-        <v>7.2571959250281341E-3</v>
+        <v>0</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -3751,24 +3722,24 @@
         <v>0</v>
       </c>
       <c r="S45" s="3">
-        <v>1249.7798063660359</v>
+        <v>1249.779806366036</v>
       </c>
       <c r="T45" s="3">
         <v>254.545776589339</v>
       </c>
       <c r="U45" s="4">
         <f>IF(S45=0,0,T45/S45)</f>
-        <v>0.20367249918165789</v>
+        <v>0</v>
       </c>
       <c r="V45" s="3">
-        <v>3542162.2225858839</v>
+        <v>3542162.222585884</v>
       </c>
       <c r="W45" s="6">
-        <v>29337.372458587401</v>
+        <v>29337.3724585874</v>
       </c>
       <c r="X45" s="7">
         <f>IF(V45=0,0,W45/V45)</f>
-        <v>8.2823345219830858E-3</v>
+        <v>0</v>
       </c>
       <c r="Y45" s="3">
         <v>0</v>
@@ -3791,22 +3762,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:30">
       <c r="A47" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:30">
       <c r="B48" t="s">
         <v>28</v>
       </c>
       <c r="C48" s="3">
         <f>C50+C51+C52+C53+C54</f>
-        <v>528.42153794517515</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3">
         <f>D50+D51+D52+D53+D54</f>
-        <v>528.42153794517515</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3">
         <f>E50+E51+E52+E53+E54</f>
@@ -3814,27 +3785,27 @@
       </c>
       <c r="F48" s="3">
         <f>F50+F51+F52+F53+F54</f>
-        <v>651.08593726395497</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3">
         <f>G50+G51+G52+G53+G54</f>
-        <v>497.58010436954146</v>
+        <v>0</v>
       </c>
       <c r="H48" s="4">
         <f>IF(F48=0,0,G48/F48)</f>
-        <v>0.76423107287574366</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3">
         <f>I50+I51+I52+I53+I54</f>
-        <v>814.53034621778045</v>
+        <v>0</v>
       </c>
       <c r="J48" s="6">
         <f>J50+J51+J52+J53+J54</f>
-        <v>30.841433575633754</v>
+        <v>0</v>
       </c>
       <c r="K48" s="7">
         <f>IF(I48=0,0,J48/I48)</f>
-        <v>3.7864069422144896E-2</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3">
         <f>L50+L51+L52+L53+L54</f>
@@ -3862,27 +3833,27 @@
       </c>
       <c r="S48" s="3">
         <f>S50+S51+S52+S53+S54</f>
-        <v>8683.3005265167885</v>
+        <v>0</v>
       </c>
       <c r="T48" s="3">
         <f>T50+T51+T52+T53+T54</f>
-        <v>6636.0480774824346</v>
+        <v>0</v>
       </c>
       <c r="U48" s="4">
         <f>IF(S48=0,0,T48/S48)</f>
-        <v>0.76423107287574354</v>
+        <v>0</v>
       </c>
       <c r="V48" s="3">
         <f>V50+V51+V52+V53+V54</f>
-        <v>26890169.836246081</v>
+        <v>0</v>
       </c>
       <c r="W48" s="6">
         <f>W50+W51+W52+W53+W54</f>
-        <v>1188772.635306214</v>
+        <v>0</v>
       </c>
       <c r="X48" s="7">
         <f>IF(V48=0,0,W48/V48)</f>
-        <v>4.420844652694722E-2</v>
+        <v>0</v>
       </c>
       <c r="Y48" s="3">
         <f>Y50+Y51+Y52+Y53+Y54</f>
@@ -3909,46 +3880,46 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:30">
       <c r="A49" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="50" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:30">
       <c r="B50" t="s">
         <v>30</v>
       </c>
       <c r="C50" s="3">
         <f>J50+M50+G50+P50</f>
-        <v>137.72092160936992</v>
+        <v>0</v>
       </c>
       <c r="D50" s="3">
-        <f>J50+G50</f>
-        <v>137.72092160936992</v>
+        <f>G50+J50</f>
+        <v>0</v>
       </c>
       <c r="E50" s="3">
-        <f>M50+P50</f>
+        <f>P50+M50</f>
         <v>0</v>
       </c>
       <c r="F50" s="3">
-        <v>155.69318362382799</v>
+        <v>155.693183623828</v>
       </c>
       <c r="G50" s="3">
-        <v>128.14136087094829</v>
+        <v>128.1413608709483</v>
       </c>
       <c r="H50" s="4">
         <f>IF(F50=0,0,G50/F50)</f>
-        <v>0.82303770716483027</v>
+        <v>0</v>
       </c>
       <c r="I50" s="3">
-        <v>289.90090139463632</v>
+        <v>289.9009013946363</v>
       </c>
       <c r="J50" s="6">
-        <v>9.5795607384216268</v>
+        <v>9.579560738421627</v>
       </c>
       <c r="K50" s="7">
         <f>IF(I50=0,0,J50/I50)</f>
-        <v>3.3044259925846732E-2</v>
+        <v>0</v>
       </c>
       <c r="L50" s="3">
         <v>0</v>
@@ -3971,24 +3942,24 @@
         <v>0</v>
       </c>
       <c r="S50" s="3">
-        <v>2076.4243642199531</v>
+        <v>2076.424364219953</v>
       </c>
       <c r="T50" s="3">
-        <v>1708.9755478287809</v>
+        <v>1708.975547828781</v>
       </c>
       <c r="U50" s="4">
         <f>IF(S50=0,0,T50/S50)</f>
-        <v>0.82303770716483038</v>
+        <v>0</v>
       </c>
       <c r="V50" s="3">
-        <v>7917202.4300766056</v>
+        <v>7917202.430076606</v>
       </c>
       <c r="W50" s="6">
-        <v>289948.80979634362</v>
+        <v>289948.8097963436</v>
       </c>
       <c r="X50" s="7">
         <f>IF(V50=0,0,W50/V50)</f>
-        <v>3.6622634365752617E-2</v>
+        <v>0</v>
       </c>
       <c r="Y50" s="3">
         <v>0</v>
@@ -4011,41 +3982,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:30">
       <c r="B51" t="s">
         <v>31</v>
       </c>
       <c r="C51" s="3">
         <f>J51+M51+G51+P51</f>
-        <v>132.24626801308187</v>
+        <v>0</v>
       </c>
       <c r="D51" s="3">
-        <f>J51+G51</f>
-        <v>132.24626801308187</v>
+        <f>G51+J51</f>
+        <v>0</v>
       </c>
       <c r="E51" s="3">
-        <f>M51+P51</f>
+        <f>P51+M51</f>
         <v>0</v>
       </c>
       <c r="F51" s="3">
-        <v>148.09982986674899</v>
+        <v>148.099829866749</v>
       </c>
       <c r="G51" s="3">
         <v>124.690141566094</v>
       </c>
       <c r="H51" s="4">
         <f>IF(F51=0,0,G51/F51)</f>
-        <v>0.84193305068805568</v>
+        <v>0</v>
       </c>
       <c r="I51" s="3">
-        <v>172.51020331953049</v>
+        <v>172.5102033195305</v>
       </c>
       <c r="J51" s="6">
-        <v>7.5561264469878804</v>
+        <v>7.55612644698788</v>
       </c>
       <c r="K51" s="7">
         <f>IF(I51=0,0,J51/I51)</f>
-        <v>4.3801040759265192E-2</v>
+        <v>0</v>
       </c>
       <c r="L51" s="3">
         <v>0</v>
@@ -4068,24 +4039,24 @@
         <v>0</v>
       </c>
       <c r="S51" s="3">
-        <v>1975.1545181010979</v>
+        <v>1975.154518101098</v>
       </c>
       <c r="T51" s="3">
-        <v>1662.9478690051531</v>
+        <v>1662.947869005153</v>
       </c>
       <c r="U51" s="4">
         <f>IF(S51=0,0,T51/S51)</f>
-        <v>0.84193305068805524</v>
+        <v>0</v>
       </c>
       <c r="V51" s="3">
         <v>5775458.9344058</v>
       </c>
       <c r="W51" s="6">
-        <v>301589.20337983972</v>
+        <v>301589.2033798397</v>
       </c>
       <c r="X51" s="7">
         <f>IF(V51=0,0,W51/V51)</f>
-        <v>5.2219088873301511E-2</v>
+        <v>0</v>
       </c>
       <c r="Y51" s="3">
         <v>0</v>
@@ -4108,20 +4079,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:30">
       <c r="B52" t="s">
         <v>32</v>
       </c>
       <c r="C52" s="3">
         <f>J52+M52+G52+P52</f>
-        <v>125.40247723253992</v>
+        <v>0</v>
       </c>
       <c r="D52" s="3">
-        <f>J52+G52</f>
-        <v>125.40247723253992</v>
+        <f>G52+J52</f>
+        <v>0</v>
       </c>
       <c r="E52" s="3">
-        <f>M52+P52</f>
+        <f>P52+M52</f>
         <v>0</v>
       </c>
       <c r="F52" s="3">
@@ -4132,17 +4103,17 @@
       </c>
       <c r="H52" s="4">
         <f>IF(F52=0,0,G52/F52)</f>
-        <v>0.87032468898878179</v>
+        <v>0</v>
       </c>
       <c r="I52" s="3">
-        <v>135.45605543604131</v>
+        <v>135.4560554360413</v>
       </c>
       <c r="J52" s="6">
-        <v>8.0855420724128191</v>
+        <v>8.085542072412819</v>
       </c>
       <c r="K52" s="7">
         <f>IF(I52=0,0,J52/I52)</f>
-        <v>5.9691255930825429E-2</v>
+        <v>0</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -4172,17 +4143,17 @@
       </c>
       <c r="U52" s="4">
         <f>IF(S52=0,0,T52/S52)</f>
-        <v>0.8703246889887819</v>
+        <v>0</v>
       </c>
       <c r="V52" s="3">
-        <v>4941006.3189266957</v>
+        <v>4941006.318926696</v>
       </c>
       <c r="W52" s="6">
-        <v>340742.81144367717</v>
+        <v>340742.8114436772</v>
       </c>
       <c r="X52" s="7">
         <f>IF(V52=0,0,W52/V52)</f>
-        <v>6.8962229442704831E-2</v>
+        <v>0</v>
       </c>
       <c r="Y52" s="3">
         <v>0</v>
@@ -4205,41 +4176,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:30">
       <c r="B53" t="s">
         <v>33</v>
       </c>
       <c r="C53" s="3">
         <f>J53+M53+G53+P53</f>
-        <v>80.327792038537325</v>
+        <v>0</v>
       </c>
       <c r="D53" s="3">
-        <f>J53+G53</f>
-        <v>80.327792038537325</v>
+        <f>G53+J53</f>
+        <v>0</v>
       </c>
       <c r="E53" s="3">
-        <f>M53+P53</f>
+        <f>P53+M53</f>
         <v>0</v>
       </c>
       <c r="F53" s="3">
         <v>118.7859525719791</v>
       </c>
       <c r="G53" s="3">
-        <v>77.087486119977598</v>
+        <v>77.0874861199776</v>
       </c>
       <c r="H53" s="4">
         <f>IF(F53=0,0,G53/F53)</f>
-        <v>0.64896129930233926</v>
+        <v>0</v>
       </c>
       <c r="I53" s="3">
-        <v>131.31388542968341</v>
+        <v>131.3138854296834</v>
       </c>
       <c r="J53" s="6">
-        <v>3.2403059185597232</v>
+        <v>3.240305918559723</v>
       </c>
       <c r="K53" s="7">
         <f>IF(I53=0,0,J53/I53)</f>
-        <v>2.467603412964928E-2</v>
+        <v>0</v>
       </c>
       <c r="L53" s="3">
         <v>0</v>
@@ -4262,24 +4233,24 @@
         <v>0</v>
       </c>
       <c r="S53" s="3">
-        <v>1584.2058098283051</v>
+        <v>1584.205809828305</v>
       </c>
       <c r="T53" s="3">
-        <v>1028.0882607084909</v>
+        <v>1028.088260708491</v>
       </c>
       <c r="U53" s="4">
         <f>IF(S53=0,0,T53/S53)</f>
-        <v>0.64896129930233892</v>
+        <v>0</v>
       </c>
       <c r="V53" s="3">
-        <v>4714339.9302510964</v>
+        <v>4714339.930251096</v>
       </c>
       <c r="W53" s="6">
-        <v>142904.16362350431</v>
+        <v>142904.1636235043</v>
       </c>
       <c r="X53" s="7">
         <f>IF(V53=0,0,W53/V53)</f>
-        <v>3.0312655798643888E-2</v>
+        <v>0</v>
       </c>
       <c r="Y53" s="3">
         <v>0</v>
@@ -4302,41 +4273,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:30">
       <c r="B54" t="s">
         <v>34</v>
       </c>
       <c r="C54" s="3">
         <f>J54+M54+G54+P54</f>
-        <v>52.724079051646143</v>
+        <v>0</v>
       </c>
       <c r="D54" s="3">
-        <f>J54+G54</f>
-        <v>52.724079051646143</v>
+        <f>G54+J54</f>
+        <v>0</v>
       </c>
       <c r="E54" s="3">
-        <f>M54+P54</f>
+        <f>P54+M54</f>
         <v>0</v>
       </c>
       <c r="F54" s="3">
         <v>93.71022621139285</v>
       </c>
       <c r="G54" s="3">
-        <v>50.344180652394442</v>
+        <v>50.34418065239444</v>
       </c>
       <c r="H54" s="4">
         <f>IF(F54=0,0,G54/F54)</f>
-        <v>0.53723251653269222</v>
+        <v>0</v>
       </c>
       <c r="I54" s="3">
-        <v>85.349300637888987</v>
+        <v>85.34930063788899</v>
       </c>
       <c r="J54" s="6">
-        <v>2.3798983992517022</v>
+        <v>2.379898399251702</v>
       </c>
       <c r="K54" s="7">
         <f>IF(I54=0,0,J54/I54)</f>
-        <v>2.7884216759418851E-2</v>
+        <v>0</v>
       </c>
       <c r="L54" s="3">
         <v>0</v>
@@ -4359,24 +4330,24 @@
         <v>0</v>
       </c>
       <c r="S54" s="3">
-        <v>1249.7798063660359</v>
+        <v>1249.779806366036</v>
       </c>
       <c r="T54" s="3">
         <v>671.4223504857664</v>
       </c>
       <c r="U54" s="4">
         <f>IF(S54=0,0,T54/S54)</f>
-        <v>0.53723251653269233</v>
+        <v>0</v>
       </c>
       <c r="V54" s="3">
-        <v>3542162.2225858839</v>
+        <v>3542162.222585884</v>
       </c>
       <c r="W54" s="6">
         <v>113587.6470628493</v>
       </c>
       <c r="X54" s="7">
         <f>IF(V54=0,0,W54/V54)</f>
-        <v>3.2067319316597231E-2</v>
+        <v>0</v>
       </c>
       <c r="Y54" s="3">
         <v>0</v>

--- a/5000_analyze_results/results_spreadsheet.xlsx
+++ b/5000_analyze_results/results_spreadsheet.xlsx
@@ -865,37 +865,37 @@
         <v>363.2527888669509</v>
       </c>
       <c r="G5" s="3">
-        <v>25.61310791992815</v>
+        <v>25.63269042834587</v>
       </c>
       <c r="H5" s="4">
         <f>IF(F5=0,0,G5/F5)</f>
         <v>0</v>
       </c>
       <c r="I5" s="3">
-        <v>4696.75253329159</v>
+        <v>4771.668377035696</v>
       </c>
       <c r="J5" s="3">
-        <v>308.8367897111615</v>
+        <v>313.5874213735713</v>
       </c>
       <c r="K5" s="4">
         <f>IF(I5=0,0,J5/I5)</f>
         <v>0</v>
       </c>
       <c r="L5" s="3">
-        <v>17149.74236158763</v>
+        <v>17342.74644129576</v>
       </c>
       <c r="M5" s="3">
-        <v>43.31725056460872</v>
+        <v>34.67868384804204</v>
       </c>
       <c r="N5" s="4">
         <f>IF(L5=0,0,M5/L5)</f>
         <v>0</v>
       </c>
       <c r="O5" s="3">
-        <v>422.618887365441</v>
+        <v>419.9952041897751</v>
       </c>
       <c r="P5" s="3">
-        <v>9.181329847155197</v>
+        <v>19.4095228180929</v>
       </c>
       <c r="Q5" s="4">
         <f>IF(O5=0,0,P5/O5)</f>
@@ -905,37 +905,37 @@
         <v>5246.953936438476</v>
       </c>
       <c r="T5" s="3">
-        <v>369.9649432674123</v>
+        <v>370.2478000623951</v>
       </c>
       <c r="U5" s="4">
         <f>IF(S5=0,0,T5/S5)</f>
         <v>0</v>
       </c>
       <c r="V5" s="3">
-        <v>129715335.2891872</v>
+        <v>131689124.8136304</v>
       </c>
       <c r="W5" s="3">
-        <v>6741067.098559976</v>
+        <v>6832789.946041524</v>
       </c>
       <c r="X5" s="4">
         <f>IF(V5=0,0,W5/V5)</f>
         <v>0</v>
       </c>
       <c r="Y5" s="3">
-        <v>3017209.138211729</v>
+        <v>3021681.785132265</v>
       </c>
       <c r="Z5" s="3">
-        <v>79401.50608393084</v>
+        <v>83056.57238458376</v>
       </c>
       <c r="AA5" s="4">
         <f>IF(Y5=0,0,Z5/Y5)</f>
         <v>0</v>
       </c>
       <c r="AB5" s="3">
-        <v>191324.1617071823</v>
+        <v>193528.0028851792</v>
       </c>
       <c r="AC5" s="3">
-        <v>481.4397627256985</v>
+        <v>385.5139499704819</v>
       </c>
       <c r="AD5" s="4">
         <f>IF(AB5=0,0,AC5/AB5)</f>
@@ -962,37 +962,37 @@
         <v>320.8959288091749</v>
       </c>
       <c r="G6" s="3">
-        <v>19.30223219520511</v>
+        <v>19.3141818814585</v>
       </c>
       <c r="H6" s="4">
         <f>IF(F6=0,0,G6/F6)</f>
         <v>0</v>
       </c>
       <c r="I6" s="3">
-        <v>4237.11396849146</v>
+        <v>4315.742780998208</v>
       </c>
       <c r="J6" s="3">
-        <v>274.6201343981107</v>
+        <v>279.4333559181248</v>
       </c>
       <c r="K6" s="4">
         <f>IF(I6=0,0,J6/I6)</f>
         <v>0</v>
       </c>
       <c r="L6" s="3">
-        <v>14282.44480906486</v>
+        <v>14283.90029035187</v>
       </c>
       <c r="M6" s="3">
-        <v>-0.001600985677912831</v>
+        <v>30.34748269250803</v>
       </c>
       <c r="N6" s="4">
         <f>IF(L6=0,0,M6/L6)</f>
         <v>0</v>
       </c>
       <c r="O6" s="3">
-        <v>250.7127871641806</v>
+        <v>214.4087795755616</v>
       </c>
       <c r="P6" s="3">
-        <v>5.289893505631073</v>
+        <v>5.588637967688701</v>
       </c>
       <c r="Q6" s="4">
         <f>IF(O6=0,0,P6/O6)</f>
@@ -1002,37 +1002,37 @@
         <v>4635.136214932357</v>
       </c>
       <c r="T6" s="3">
-        <v>278.8083844162202</v>
+        <v>278.980989982505</v>
       </c>
       <c r="U6" s="4">
         <f>IF(S6=0,0,T6/S6)</f>
         <v>0</v>
       </c>
       <c r="V6" s="3">
-        <v>121193659.6151606</v>
+        <v>123358149.8591988</v>
       </c>
       <c r="W6" s="3">
-        <v>6324800.906607285</v>
+        <v>6427621.054781124</v>
       </c>
       <c r="X6" s="4">
         <f>IF(V6=0,0,W6/V6)</f>
         <v>0</v>
       </c>
       <c r="Y6" s="3">
-        <v>1790068.720744995</v>
+        <v>1781844.821568525</v>
       </c>
       <c r="Z6" s="3">
-        <v>46409.72342276992</v>
+        <v>46313.53746748972</v>
       </c>
       <c r="AA6" s="4">
         <f>IF(Y6=0,0,Z6/Y6)</f>
         <v>0</v>
       </c>
       <c r="AB6" s="3">
-        <v>159404.7054384702</v>
+        <v>159361.8290690457</v>
       </c>
       <c r="AC6" s="3">
-        <v>0</v>
+        <v>337.3247062241426</v>
       </c>
       <c r="AD6" s="4">
         <f>IF(AB6=0,0,AC6/AB6)</f>
@@ -1059,37 +1059,37 @@
         <v>288.0891253989829</v>
       </c>
       <c r="G7" s="3">
-        <v>14.64995546944888</v>
+        <v>14.66402867711027</v>
       </c>
       <c r="H7" s="4">
         <f>IF(F7=0,0,G7/F7)</f>
         <v>0</v>
       </c>
       <c r="I7" s="3">
-        <v>4136.060848493457</v>
+        <v>4219.995713516021</v>
       </c>
       <c r="J7" s="3">
-        <v>238.3348830829528</v>
+        <v>243.0103178216233</v>
       </c>
       <c r="K7" s="4">
         <f>IF(I7=0,0,J7/I7)</f>
         <v>0</v>
       </c>
       <c r="L7" s="3">
-        <v>12947.56214154672</v>
+        <v>12700.07744999716</v>
       </c>
       <c r="M7" s="3">
-        <v>51.97910640976765</v>
+        <v>52.02292426651717</v>
       </c>
       <c r="N7" s="4">
         <f>IF(L7=0,0,M7/L7)</f>
         <v>0</v>
       </c>
       <c r="O7" s="3">
-        <v>319.3114946363287</v>
+        <v>344.8791542406948</v>
       </c>
       <c r="P7" s="3">
-        <v>6.277070487439225</v>
+        <v>6.148588666623284</v>
       </c>
       <c r="Q7" s="4">
         <f>IF(O7=0,0,P7/O7)</f>
@@ -1099,37 +1099,37 @@
         <v>4161.262946589416</v>
       </c>
       <c r="T7" s="3">
-        <v>211.609226067711</v>
+        <v>211.8125045409952</v>
       </c>
       <c r="U7" s="4">
         <f>IF(S7=0,0,T7/S7)</f>
         <v>0</v>
       </c>
       <c r="V7" s="3">
-        <v>118707434.9358999</v>
+        <v>121044503.5745435</v>
       </c>
       <c r="W7" s="3">
-        <v>5528190.844559968</v>
+        <v>5625577.528566912</v>
       </c>
       <c r="X7" s="4">
         <f>IF(V7=0,0,W7/V7)</f>
         <v>0</v>
       </c>
       <c r="Y7" s="3">
-        <v>2254598.791771456</v>
+        <v>2254117.861995054</v>
       </c>
       <c r="Z7" s="3">
-        <v>49247.20910354005</v>
+        <v>45544.04982524691</v>
       </c>
       <c r="AA7" s="4">
         <f>IF(Y7=0,0,Z7/Y7)</f>
         <v>0</v>
       </c>
       <c r="AB7" s="3">
-        <v>144480.0727939743</v>
+        <v>141724.5658578964</v>
       </c>
       <c r="AC7" s="3">
-        <v>577.7277152707975</v>
+        <v>578.2709249557229</v>
       </c>
       <c r="AD7" s="4">
         <f>IF(AB7=0,0,AC7/AB7)</f>
@@ -1156,37 +1156,37 @@
         <v>271.6538476703636</v>
       </c>
       <c r="G8" s="3">
-        <v>12.01171715158402</v>
+        <v>12.01916291244561</v>
       </c>
       <c r="H8" s="4">
         <f>IF(F8=0,0,G8/F8)</f>
         <v>0</v>
       </c>
       <c r="I8" s="3">
-        <v>3783.135075071727</v>
+        <v>3866.44843120562</v>
       </c>
       <c r="J8" s="3">
-        <v>194.7161588536995</v>
+        <v>199.0991080713072</v>
       </c>
       <c r="K8" s="4">
         <f>IF(I8=0,0,J8/I8)</f>
         <v>0</v>
       </c>
       <c r="L8" s="3">
-        <v>11725.45888147103</v>
+        <v>11596.86626484413</v>
       </c>
       <c r="M8" s="3">
-        <v>0.00196340936422348</v>
+        <v>21.67842480659671</v>
       </c>
       <c r="N8" s="4">
         <f>IF(L8=0,0,M8/L8)</f>
         <v>0</v>
       </c>
       <c r="O8" s="3">
-        <v>255.2722093275565</v>
+        <v>277.4788567267415</v>
       </c>
       <c r="P8" s="3">
-        <v>6.028111707371194</v>
+        <v>2.068533699701366</v>
       </c>
       <c r="Q8" s="4">
         <f>IF(O8=0,0,P8/O8)</f>
@@ -1196,37 +1196,37 @@
         <v>3923.86588366907</v>
       </c>
       <c r="T8" s="3">
-        <v>173.5015628881338</v>
+        <v>173.6091121360946</v>
       </c>
       <c r="U8" s="4">
         <f>IF(S8=0,0,T8/S8)</f>
         <v>0</v>
       </c>
       <c r="V8" s="3">
-        <v>112495719.1634136</v>
+        <v>114931674.6513069</v>
       </c>
       <c r="W8" s="3">
-        <v>4763589.916187599</v>
+        <v>4857592.477778837</v>
       </c>
       <c r="X8" s="4">
         <f>IF(V8=0,0,W8/V8)</f>
         <v>0</v>
       </c>
       <c r="Y8" s="3">
-        <v>2008987.954963077</v>
+        <v>2020434.083641439</v>
       </c>
       <c r="Z8" s="3">
-        <v>37127.77873821603</v>
+        <v>41023.30992707051</v>
       </c>
       <c r="AA8" s="4">
         <f>IF(Y8=0,0,Z8/Y8)</f>
         <v>0</v>
       </c>
       <c r="AB8" s="3">
-        <v>130807.1835325652</v>
+        <v>129388.1194588412</v>
       </c>
       <c r="AC8" s="3">
-        <v>0</v>
+        <v>240.9462187315658</v>
       </c>
       <c r="AD8" s="4">
         <f>IF(AB8=0,0,AC8/AB8)</f>
@@ -1253,37 +1253,37 @@
         <v>231.3561787321935</v>
       </c>
       <c r="G9" s="3">
-        <v>4.585401678760419</v>
+        <v>4.583486877183867</v>
       </c>
       <c r="H9" s="4">
         <f>IF(F9=0,0,G9/F9)</f>
         <v>0</v>
       </c>
       <c r="I9" s="3">
-        <v>3283.865109392673</v>
+        <v>3364.438925828685</v>
       </c>
       <c r="J9" s="3">
-        <v>98.62837958013452</v>
+        <v>100.8518174263639</v>
       </c>
       <c r="K9" s="4">
         <f>IF(I9=0,0,J9/I9)</f>
         <v>0</v>
       </c>
       <c r="L9" s="3">
-        <v>11643.22668281579</v>
+        <v>11328.20246422979</v>
       </c>
       <c r="M9" s="3">
-        <v>8.662714833144099</v>
+        <v>8.672433171367272</v>
       </c>
       <c r="N9" s="4">
         <f>IF(L9=0,0,M9/L9)</f>
         <v>0</v>
       </c>
       <c r="O9" s="3">
-        <v>175.1115957679361</v>
+        <v>193.6283842759436</v>
       </c>
       <c r="P9" s="3">
-        <v>0.001510296575113898</v>
+        <v>2.497779431025672</v>
       </c>
       <c r="Q9" s="4">
         <f>IF(O9=0,0,P9/O9)</f>
@@ -1293,37 +1293,37 @@
         <v>3341.791859340324</v>
       </c>
       <c r="T9" s="3">
-        <v>66.2331911162164</v>
+        <v>66.20553303353427</v>
       </c>
       <c r="U9" s="4">
         <f>IF(S9=0,0,T9/S9)</f>
         <v>0</v>
       </c>
       <c r="V9" s="3">
-        <v>104453537.4780618</v>
+        <v>107061599.7071237</v>
       </c>
       <c r="W9" s="3">
-        <v>2623914.142659664</v>
+        <v>2677646.657504544</v>
       </c>
       <c r="X9" s="4">
         <f>IF(V9=0,0,W9/V9)</f>
         <v>0</v>
       </c>
       <c r="Y9" s="3">
-        <v>1264989.590869552</v>
+        <v>1264893.404914272</v>
       </c>
       <c r="Z9" s="3">
-        <v>16063.05453181895</v>
+        <v>14427.89329205267</v>
       </c>
       <c r="AA9" s="4">
         <f>IF(Y9=0,0,Z9/Y9)</f>
         <v>0</v>
       </c>
       <c r="AB9" s="3">
-        <v>129892.4479833864</v>
+        <v>126400.38634657</v>
       </c>
       <c r="AC9" s="3">
-        <v>96.28795254514262</v>
+        <v>96.37848749259138</v>
       </c>
       <c r="AD9" s="4">
         <f>IF(AB9=0,0,AC9/AB9)</f>
@@ -1473,37 +1473,37 @@
         <v>363.2527888669509</v>
       </c>
       <c r="G14" s="3">
-        <v>171.7005339918157</v>
+        <v>171.7832906162409</v>
       </c>
       <c r="H14" s="4">
         <f>IF(F14=0,0,G14/F14)</f>
         <v>0</v>
       </c>
       <c r="I14" s="3">
-        <v>4696.75253329159</v>
+        <v>4771.668377035696</v>
       </c>
       <c r="J14" s="3">
-        <v>308.8367897111615</v>
+        <v>313.5874213735713</v>
       </c>
       <c r="K14" s="4">
         <f>IF(I14=0,0,J14/I14)</f>
         <v>0</v>
       </c>
       <c r="L14" s="3">
-        <v>17149.74236158763</v>
+        <v>17342.74644129576</v>
       </c>
       <c r="M14" s="3">
-        <v>43.31725056460872</v>
+        <v>34.67868384804204</v>
       </c>
       <c r="N14" s="4">
         <f>IF(L14=0,0,M14/L14)</f>
         <v>0</v>
       </c>
       <c r="O14" s="3">
-        <v>422.618887365441</v>
+        <v>419.9952041897751</v>
       </c>
       <c r="P14" s="3">
-        <v>9.181329847155197</v>
+        <v>19.4095228180929</v>
       </c>
       <c r="Q14" s="4">
         <f>IF(O14=0,0,P14/O14)</f>
@@ -1513,37 +1513,37 @@
         <v>5246.953936438476</v>
       </c>
       <c r="T14" s="3">
-        <v>2480.104269886063</v>
+        <v>2481.299636335</v>
       </c>
       <c r="U14" s="4">
         <f>IF(S14=0,0,T14/S14)</f>
         <v>0</v>
       </c>
       <c r="V14" s="3">
-        <v>129715335.2891872</v>
+        <v>131689124.8136304</v>
       </c>
       <c r="W14" s="3">
-        <v>6741067.09856002</v>
+        <v>6832789.946041539</v>
       </c>
       <c r="X14" s="4">
         <f>IF(V14=0,0,W14/V14)</f>
         <v>0</v>
       </c>
       <c r="Y14" s="3">
-        <v>3017209.138211729</v>
+        <v>3021681.785132265</v>
       </c>
       <c r="Z14" s="3">
-        <v>79401.50608393084</v>
+        <v>83056.57238458376</v>
       </c>
       <c r="AA14" s="4">
         <f>IF(Y14=0,0,Z14/Y14)</f>
         <v>0</v>
       </c>
       <c r="AB14" s="3">
-        <v>191324.1617071823</v>
+        <v>193528.0028851792</v>
       </c>
       <c r="AC14" s="3">
-        <v>481.4397627256985</v>
+        <v>385.5139499704819</v>
       </c>
       <c r="AD14" s="4">
         <f>IF(AB14=0,0,AC14/AB14)</f>
@@ -1570,37 +1570,37 @@
         <v>320.8959288091749</v>
       </c>
       <c r="G15" s="3">
-        <v>136.7817413267469</v>
+        <v>136.8384804720325</v>
       </c>
       <c r="H15" s="4">
         <f>IF(F15=0,0,G15/F15)</f>
         <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>4237.11396849146</v>
+        <v>4315.742780998208</v>
       </c>
       <c r="J15" s="3">
-        <v>274.6201343981107</v>
+        <v>279.4333559181248</v>
       </c>
       <c r="K15" s="4">
         <f>IF(I15=0,0,J15/I15)</f>
         <v>0</v>
       </c>
       <c r="L15" s="3">
-        <v>14282.44480906486</v>
+        <v>14283.90029035187</v>
       </c>
       <c r="M15" s="3">
-        <v>-0.001600985677912831</v>
+        <v>30.34748269250803</v>
       </c>
       <c r="N15" s="4">
         <f>IF(L15=0,0,M15/L15)</f>
         <v>0</v>
       </c>
       <c r="O15" s="3">
-        <v>250.7127871641806</v>
+        <v>214.4087795755616</v>
       </c>
       <c r="P15" s="3">
-        <v>5.289893505631073</v>
+        <v>5.588637967688701</v>
       </c>
       <c r="Q15" s="4">
         <f>IF(O15=0,0,P15/O15)</f>
@@ -1610,37 +1610,37 @@
         <v>4635.136214932357</v>
       </c>
       <c r="T15" s="3">
-        <v>1975.724669109567</v>
+        <v>1976.544229731896</v>
       </c>
       <c r="U15" s="4">
         <f>IF(S15=0,0,T15/S15)</f>
         <v>0</v>
       </c>
       <c r="V15" s="3">
-        <v>121193659.6151606</v>
+        <v>123358149.8591988</v>
       </c>
       <c r="W15" s="3">
-        <v>6324800.906607285</v>
+        <v>6427621.054781124</v>
       </c>
       <c r="X15" s="4">
         <f>IF(V15=0,0,W15/V15)</f>
         <v>0</v>
       </c>
       <c r="Y15" s="3">
-        <v>1790068.720744995</v>
+        <v>1781844.821568525</v>
       </c>
       <c r="Z15" s="3">
-        <v>46409.72342276992</v>
+        <v>46313.53746748972</v>
       </c>
       <c r="AA15" s="4">
         <f>IF(Y15=0,0,Z15/Y15)</f>
         <v>0</v>
       </c>
       <c r="AB15" s="3">
-        <v>159404.7054384702</v>
+        <v>159361.8290690457</v>
       </c>
       <c r="AC15" s="3">
-        <v>0</v>
+        <v>337.3247062241426</v>
       </c>
       <c r="AD15" s="4">
         <f>IF(AB15=0,0,AC15/AB15)</f>
@@ -1667,37 +1667,37 @@
         <v>288.0891253989829</v>
       </c>
       <c r="G16" s="3">
-        <v>109.3639574469849</v>
+        <v>109.4384294573394</v>
       </c>
       <c r="H16" s="4">
         <f>IF(F16=0,0,G16/F16)</f>
         <v>0</v>
       </c>
       <c r="I16" s="3">
-        <v>4136.060848493457</v>
+        <v>4219.995713516021</v>
       </c>
       <c r="J16" s="3">
-        <v>238.3348830829528</v>
+        <v>243.0103178216233</v>
       </c>
       <c r="K16" s="4">
         <f>IF(I16=0,0,J16/I16)</f>
         <v>0</v>
       </c>
       <c r="L16" s="3">
-        <v>12947.56214154672</v>
+        <v>12700.07744999716</v>
       </c>
       <c r="M16" s="3">
-        <v>51.97910640976765</v>
+        <v>52.02292426651717</v>
       </c>
       <c r="N16" s="4">
         <f>IF(L16=0,0,M16/L16)</f>
         <v>0</v>
       </c>
       <c r="O16" s="3">
-        <v>319.3114946363287</v>
+        <v>344.8791542406948</v>
       </c>
       <c r="P16" s="3">
-        <v>6.277070487439283</v>
+        <v>6.148588666623284</v>
       </c>
       <c r="Q16" s="4">
         <f>IF(O16=0,0,P16/O16)</f>
@@ -1707,37 +1707,37 @@
         <v>4161.262946589416</v>
       </c>
       <c r="T16" s="3">
-        <v>1579.692337176038</v>
+        <v>1580.768037679544</v>
       </c>
       <c r="U16" s="4">
         <f>IF(S16=0,0,T16/S16)</f>
         <v>0</v>
       </c>
       <c r="V16" s="3">
-        <v>118707434.9358999</v>
+        <v>121044503.5745435</v>
       </c>
       <c r="W16" s="3">
-        <v>5528190.844559968</v>
+        <v>5625577.528566912</v>
       </c>
       <c r="X16" s="4">
         <f>IF(V16=0,0,W16/V16)</f>
         <v>0</v>
       </c>
       <c r="Y16" s="3">
-        <v>2254598.791771456</v>
+        <v>2254117.861995054</v>
       </c>
       <c r="Z16" s="3">
-        <v>49247.20910354005</v>
+        <v>45544.04982524691</v>
       </c>
       <c r="AA16" s="4">
         <f>IF(Y16=0,0,Z16/Y16)</f>
         <v>0</v>
       </c>
       <c r="AB16" s="3">
-        <v>144480.0727939743</v>
+        <v>141724.5658578964</v>
       </c>
       <c r="AC16" s="3">
-        <v>577.7277152707975</v>
+        <v>578.2709249557229</v>
       </c>
       <c r="AD16" s="4">
         <f>IF(AB16=0,0,AC16/AB16)</f>
@@ -1764,37 +1764,37 @@
         <v>271.6538476703636</v>
       </c>
       <c r="G17" s="3">
-        <v>93.19422555617429</v>
+        <v>93.2369079938145</v>
       </c>
       <c r="H17" s="4">
         <f>IF(F17=0,0,G17/F17)</f>
         <v>0</v>
       </c>
       <c r="I17" s="3">
-        <v>3783.135075071727</v>
+        <v>3866.44843120562</v>
       </c>
       <c r="J17" s="3">
-        <v>194.7161588536995</v>
+        <v>199.0991080713072</v>
       </c>
       <c r="K17" s="4">
         <f>IF(I17=0,0,J17/I17)</f>
         <v>0</v>
       </c>
       <c r="L17" s="3">
-        <v>11725.45888147103</v>
+        <v>11596.86626484413</v>
       </c>
       <c r="M17" s="3">
-        <v>0.00196340936422348</v>
+        <v>21.67842480659671</v>
       </c>
       <c r="N17" s="4">
         <f>IF(L17=0,0,M17/L17)</f>
         <v>0</v>
       </c>
       <c r="O17" s="3">
-        <v>255.2722093275565</v>
+        <v>277.4788567267415</v>
       </c>
       <c r="P17" s="3">
-        <v>6.028111707371194</v>
+        <v>2.068533699701366</v>
       </c>
       <c r="Q17" s="4">
         <f>IF(O17=0,0,P17/O17)</f>
@@ -1804,37 +1804,37 @@
         <v>3923.86588366907</v>
       </c>
       <c r="T17" s="3">
-        <v>1346.130913848001</v>
+        <v>1346.747434329211</v>
       </c>
       <c r="U17" s="4">
         <f>IF(S17=0,0,T17/S17)</f>
         <v>0</v>
       </c>
       <c r="V17" s="3">
-        <v>112495719.1634136</v>
+        <v>114931674.6513069</v>
       </c>
       <c r="W17" s="3">
-        <v>4763589.916187599</v>
+        <v>4857592.477778837</v>
       </c>
       <c r="X17" s="4">
         <f>IF(V17=0,0,W17/V17)</f>
         <v>0</v>
       </c>
       <c r="Y17" s="3">
-        <v>2008987.954963077</v>
+        <v>2020434.083641439</v>
       </c>
       <c r="Z17" s="3">
-        <v>37127.77873821603</v>
+        <v>41023.30992707051</v>
       </c>
       <c r="AA17" s="4">
         <f>IF(Y17=0,0,Z17/Y17)</f>
         <v>0</v>
       </c>
       <c r="AB17" s="3">
-        <v>130807.1835325652</v>
+        <v>129388.1194588412</v>
       </c>
       <c r="AC17" s="3">
-        <v>0</v>
+        <v>240.9462187315658</v>
       </c>
       <c r="AD17" s="4">
         <f>IF(AB17=0,0,AC17/AB17)</f>
@@ -1861,37 +1861,37 @@
         <v>231.3561787321935</v>
       </c>
       <c r="G18" s="3">
-        <v>41.46282624707057</v>
+        <v>41.44780297413218</v>
       </c>
       <c r="H18" s="4">
         <f>IF(F18=0,0,G18/F18)</f>
         <v>0</v>
       </c>
       <c r="I18" s="3">
-        <v>3283.865109392673</v>
+        <v>3364.438925828685</v>
       </c>
       <c r="J18" s="3">
-        <v>98.62837958013452</v>
+        <v>100.8518174263639</v>
       </c>
       <c r="K18" s="4">
         <f>IF(I18=0,0,J18/I18)</f>
         <v>0</v>
       </c>
       <c r="L18" s="3">
-        <v>11643.22668281579</v>
+        <v>11328.20246422979</v>
       </c>
       <c r="M18" s="3">
-        <v>8.662714833144099</v>
+        <v>8.672433171365411</v>
       </c>
       <c r="N18" s="4">
         <f>IF(L18=0,0,M18/L18)</f>
         <v>0</v>
       </c>
       <c r="O18" s="3">
-        <v>175.1115957679361</v>
+        <v>193.6283842759436</v>
       </c>
       <c r="P18" s="3">
-        <v>0.001510296575113898</v>
+        <v>2.497779431025672</v>
       </c>
       <c r="Q18" s="4">
         <f>IF(O18=0,0,P18/O18)</f>
@@ -1901,37 +1901,37 @@
         <v>3341.791859340324</v>
       </c>
       <c r="T18" s="3">
-        <v>598.9039755799786</v>
+        <v>598.6869740221155</v>
       </c>
       <c r="U18" s="4">
         <f>IF(S18=0,0,T18/S18)</f>
         <v>0</v>
       </c>
       <c r="V18" s="3">
-        <v>104453537.4780618</v>
+        <v>107061599.7071237</v>
       </c>
       <c r="W18" s="3">
-        <v>2623914.142659664</v>
+        <v>2677646.657504544</v>
       </c>
       <c r="X18" s="4">
         <f>IF(V18=0,0,W18/V18)</f>
         <v>0</v>
       </c>
       <c r="Y18" s="3">
-        <v>1264989.590869552</v>
+        <v>1264893.404914272</v>
       </c>
       <c r="Z18" s="3">
-        <v>16063.05453181895</v>
+        <v>14427.89329205267</v>
       </c>
       <c r="AA18" s="4">
         <f>IF(Y18=0,0,Z18/Y18)</f>
         <v>0</v>
       </c>
       <c r="AB18" s="3">
-        <v>129892.4479833864</v>
+        <v>126400.38634657</v>
       </c>
       <c r="AC18" s="3">
-        <v>96.28795254514262</v>
+        <v>96.37848749259138</v>
       </c>
       <c r="AD18" s="4">
         <f>IF(AB18=0,0,AC18/AB18)</f>
@@ -2078,80 +2078,80 @@
         <v>0</v>
       </c>
       <c r="F23" s="3">
-        <v>414.1174655591563</v>
+        <v>414.1483857332581</v>
       </c>
       <c r="G23" s="3">
-        <v>268.7388335606863</v>
+        <v>268.7588990063936</v>
       </c>
       <c r="H23" s="4">
         <f>IF(F23=0,0,G23/F23)</f>
         <v>0</v>
       </c>
       <c r="I23" s="3">
-        <v>991.8205054212256</v>
+        <v>1108.193378484327</v>
       </c>
       <c r="J23" s="3">
-        <v>137.3802562461348</v>
+        <v>152.6620123236948</v>
       </c>
       <c r="K23" s="4">
         <f>IF(I23=0,0,J23/I23)</f>
         <v>0</v>
       </c>
       <c r="L23" s="3">
-        <v>18248.15090069409</v>
+        <v>16899.69278120454</v>
       </c>
       <c r="M23" s="3">
-        <v>92.70682216655835</v>
+        <v>114.5281090262048</v>
       </c>
       <c r="N23" s="4">
         <f>IF(L23=0,0,M23/L23)</f>
         <v>0</v>
       </c>
       <c r="O23" s="3">
-        <v>476.0481880235133</v>
+        <v>511.5551891389042</v>
       </c>
       <c r="P23" s="3">
-        <v>17.78380361743271</v>
+        <v>29.39199492819834</v>
       </c>
       <c r="Q23" s="4">
         <f>IF(O23=0,0,P23/O23)</f>
         <v>0</v>
       </c>
       <c r="S23" s="3">
-        <v>7595.550633139525</v>
+        <v>7596.11775664314</v>
       </c>
       <c r="T23" s="3">
-        <v>4929.083139840336</v>
+        <v>4929.451170946294</v>
       </c>
       <c r="U23" s="4">
         <f>IF(S23=0,0,T23/S23)</f>
         <v>0</v>
       </c>
       <c r="V23" s="3">
-        <v>25699987.56061059</v>
+        <v>27432336.72224081</v>
       </c>
       <c r="W23" s="3">
-        <v>2724438.198759455</v>
+        <v>2873271.15188776</v>
       </c>
       <c r="X23" s="4">
         <f>IF(V23=0,0,W23/V23)</f>
         <v>0</v>
       </c>
       <c r="Y23" s="3">
-        <v>1959206.361225823</v>
+        <v>2836323.537272255</v>
       </c>
       <c r="Z23" s="3">
-        <v>81685.4768248722</v>
+        <v>110553.4352663648</v>
       </c>
       <c r="AA23" s="4">
         <f>IF(Y23=0,0,Z23/Y23)</f>
         <v>0</v>
       </c>
       <c r="AB23" s="3">
-        <v>205054.6892807224</v>
+        <v>190241.6708006598</v>
       </c>
       <c r="AC23" s="3">
-        <v>1029.360143988684</v>
+        <v>1270.014577409398</v>
       </c>
       <c r="AD23" s="4">
         <f>IF(AB23=0,0,AC23/AB23)</f>
@@ -2175,80 +2175,80 @@
         <v>0</v>
       </c>
       <c r="F24" s="3">
-        <v>423.4608834802265</v>
+        <v>423.4925012827377</v>
       </c>
       <c r="G24" s="3">
-        <v>265.1770602919006</v>
+        <v>265.196859797002</v>
       </c>
       <c r="H24" s="4">
         <f>IF(F24=0,0,G24/F24)</f>
         <v>0</v>
       </c>
       <c r="I24" s="3">
-        <v>847.5293917044748</v>
+        <v>948.9557472002688</v>
       </c>
       <c r="J24" s="3">
-        <v>129.6386109174587</v>
+        <v>143.0812252068468</v>
       </c>
       <c r="K24" s="4">
         <f>IF(I24=0,0,J24/I24)</f>
         <v>0</v>
       </c>
       <c r="L24" s="3">
-        <v>18442.648959675</v>
+        <v>16952.10289749463</v>
       </c>
       <c r="M24" s="3">
-        <v>78.36081872005761</v>
+        <v>82.00023356101661</v>
       </c>
       <c r="N24" s="4">
         <f>IF(L24=0,0,M24/L24)</f>
         <v>0</v>
       </c>
       <c r="O24" s="3">
-        <v>476.5639382629005</v>
+        <v>566.8783011556247</v>
       </c>
       <c r="P24" s="3">
-        <v>20.33018603529909</v>
+        <v>25.30581707247754</v>
       </c>
       <c r="Q24" s="4">
         <f>IF(O24=0,0,P24/O24)</f>
         <v>0</v>
       </c>
       <c r="S24" s="3">
-        <v>7766.92327449926</v>
+        <v>7767.503193579848</v>
       </c>
       <c r="T24" s="3">
-        <v>4863.754745225788</v>
+        <v>4864.117898572401</v>
       </c>
       <c r="U24" s="4">
         <f>IF(S24=0,0,T24/S24)</f>
         <v>0</v>
       </c>
       <c r="V24" s="3">
-        <v>23322467.60095111</v>
+        <v>24925390.04051472</v>
       </c>
       <c r="W24" s="3">
-        <v>2821008.141738795</v>
+        <v>2981250.104581676</v>
       </c>
       <c r="X24" s="4">
         <f>IF(V24=0,0,W24/V24)</f>
         <v>0</v>
       </c>
       <c r="Y24" s="3">
-        <v>2033978.129974804</v>
+        <v>2726453.333948384</v>
       </c>
       <c r="Z24" s="3">
-        <v>83922.17115407297</v>
+        <v>121420.0766374553</v>
       </c>
       <c r="AA24" s="4">
         <f>IF(Y24=0,0,Z24/Y24)</f>
         <v>0</v>
       </c>
       <c r="AB24" s="3">
-        <v>207305.2882361168</v>
+        <v>190795.2668985049</v>
       </c>
       <c r="AC24" s="3">
-        <v>870.3446737535996</v>
+        <v>911.8053376271855</v>
       </c>
       <c r="AD24" s="4">
         <f>IF(AB24=0,0,AC24/AB24)</f>
@@ -2272,80 +2272,80 @@
         <v>0</v>
       </c>
       <c r="F25" s="3">
-        <v>383.3486237845976</v>
+        <v>383.3772465961786</v>
       </c>
       <c r="G25" s="3">
-        <v>207.6706006016967</v>
+        <v>207.6861063739965</v>
       </c>
       <c r="H25" s="4">
         <f>IF(F25=0,0,G25/F25)</f>
         <v>0</v>
       </c>
       <c r="I25" s="3">
-        <v>721.6208038129823</v>
+        <v>812.8022893291875</v>
       </c>
       <c r="J25" s="3">
-        <v>117.9993820939182</v>
+        <v>128.7942138943434</v>
       </c>
       <c r="K25" s="4">
         <f>IF(I25=0,0,J25/I25)</f>
         <v>0</v>
       </c>
       <c r="L25" s="3">
-        <v>15355.96197556525</v>
+        <v>13913.05861415759</v>
       </c>
       <c r="M25" s="3">
-        <v>48.61628105269372</v>
+        <v>64.4541206793096</v>
       </c>
       <c r="N25" s="4">
         <f>IF(L25=0,0,M25/L25)</f>
         <v>0</v>
       </c>
       <c r="O25" s="3">
-        <v>391.5266582641886</v>
+        <v>344.6606313647766</v>
       </c>
       <c r="P25" s="3">
-        <v>16.77983298771235</v>
+        <v>10.42967228277575</v>
       </c>
       <c r="Q25" s="4">
         <f>IF(O25=0,0,P25/O25)</f>
         <v>0</v>
       </c>
       <c r="S25" s="3">
-        <v>7031.20279693764</v>
+        <v>7031.727783282595</v>
       </c>
       <c r="T25" s="3">
-        <v>3808.997912596752</v>
+        <v>3809.282312286219</v>
       </c>
       <c r="U25" s="4">
         <f>IF(S25=0,0,T25/S25)</f>
         <v>0</v>
       </c>
       <c r="V25" s="3">
-        <v>21162807.84637517</v>
+        <v>22582605.07877934</v>
       </c>
       <c r="W25" s="3">
-        <v>2800683.860446602</v>
+        <v>2940602.784735434</v>
       </c>
       <c r="X25" s="4">
         <f>IF(V25=0,0,W25/V25)</f>
         <v>0</v>
       </c>
       <c r="Y25" s="3">
-        <v>1664123.912966297</v>
+        <v>1847101.289104564</v>
       </c>
       <c r="Z25" s="3">
-        <v>70162.63003171934</v>
+        <v>90869.84835166438</v>
       </c>
       <c r="AA25" s="4">
         <f>IF(Y25=0,0,Z25/Y25)</f>
         <v>0</v>
       </c>
       <c r="AB25" s="3">
-        <v>172634.6152091868</v>
+        <v>156700.260166514</v>
       </c>
       <c r="AC25" s="3">
-        <v>539.5924956644885</v>
+        <v>716.4184795642504</v>
       </c>
       <c r="AD25" s="4">
         <f>IF(AB25=0,0,AC25/AB25)</f>
@@ -2369,80 +2369,80 @@
         <v>0</v>
       </c>
       <c r="F26" s="3">
-        <v>339.7997046237476</v>
+        <v>339.8250758454431</v>
       </c>
       <c r="G26" s="3">
-        <v>163.9528075835068</v>
+        <v>163.9650491569163</v>
       </c>
       <c r="H26" s="4">
         <f>IF(F26=0,0,G26/F26)</f>
         <v>0</v>
       </c>
       <c r="I26" s="3">
-        <v>656.2360029629352</v>
+        <v>743.8513994517335</v>
       </c>
       <c r="J26" s="3">
-        <v>111.9114792464019</v>
+        <v>121.7215094544971</v>
       </c>
       <c r="K26" s="4">
         <f>IF(I26=0,0,J26/I26)</f>
         <v>0</v>
       </c>
       <c r="L26" s="3">
-        <v>12320.89391034633</v>
+        <v>11488.16064938751</v>
       </c>
       <c r="M26" s="3">
-        <v>30.92236050494015</v>
+        <v>26.37007743735425</v>
       </c>
       <c r="N26" s="4">
         <f>IF(L26=0,0,M26/L26)</f>
         <v>0</v>
       </c>
       <c r="O26" s="3">
-        <v>305.8977151284149</v>
+        <v>288.1123393639429</v>
       </c>
       <c r="P26" s="3">
-        <v>13.55691215160029</v>
+        <v>9.966017271608406</v>
       </c>
       <c r="Q26" s="4">
         <f>IF(O26=0,0,P26/O26)</f>
         <v>0</v>
       </c>
       <c r="S26" s="3">
-        <v>6232.448704163242</v>
+        <v>6232.914051353447</v>
       </c>
       <c r="T26" s="3">
-        <v>3007.146413794556</v>
+        <v>3007.370943060754</v>
       </c>
       <c r="U26" s="4">
         <f>IF(S26=0,0,T26/S26)</f>
         <v>0</v>
       </c>
       <c r="V26" s="3">
-        <v>20232379.41165718</v>
+        <v>21635078.69522292</v>
       </c>
       <c r="W26" s="3">
-        <v>2815905.181914039</v>
+        <v>2936193.364272114</v>
       </c>
       <c r="X26" s="4">
         <f>IF(V26=0,0,W26/V26)</f>
         <v>0</v>
       </c>
       <c r="Y26" s="3">
-        <v>1291512.272887179</v>
+        <v>1653421.300834798</v>
       </c>
       <c r="Z26" s="3">
-        <v>51650.77630189992</v>
+        <v>69657.12327995477</v>
       </c>
       <c r="AA26" s="4">
         <f>IF(Y26=0,0,Z26/Y26)</f>
         <v>0</v>
       </c>
       <c r="AB26" s="3">
-        <v>138538.5180813732</v>
+        <v>129411.2289903838</v>
       </c>
       <c r="AC26" s="3">
-        <v>343.4734157078783</v>
+        <v>293.0802870944754</v>
       </c>
       <c r="AD26" s="4">
         <f>IF(AB26=0,0,AC26/AB26)</f>
@@ -2466,80 +2466,80 @@
         <v>0</v>
       </c>
       <c r="F27" s="3">
-        <v>298.4523954328049</v>
+        <v>298.4746794483207</v>
       </c>
       <c r="G27" s="3">
-        <v>136.242078071581</v>
+        <v>136.2522506171126</v>
       </c>
       <c r="H27" s="4">
         <f>IF(F27=0,0,G27/F27)</f>
         <v>0</v>
       </c>
       <c r="I27" s="3">
-        <v>465.2285123766713</v>
+        <v>534.6642930986926</v>
       </c>
       <c r="J27" s="3">
-        <v>88.96980408031312</v>
+        <v>94.97364885894879</v>
       </c>
       <c r="K27" s="4">
         <f>IF(I27=0,0,J27/I27)</f>
         <v>0</v>
       </c>
       <c r="L27" s="3">
-        <v>10752.45040482439</v>
+        <v>9796.241413112457</v>
       </c>
       <c r="M27" s="3">
-        <v>19.48994554955885</v>
+        <v>23.29433523116261</v>
       </c>
       <c r="N27" s="4">
         <f>IF(L27=0,0,M27/L27)</f>
         <v>0</v>
       </c>
       <c r="O27" s="3">
-        <v>286.1372571560934</v>
+        <v>239.0687784366582</v>
       </c>
       <c r="P27" s="3">
-        <v>11.8147481515659</v>
+        <v>13.46171006701532</v>
       </c>
       <c r="Q27" s="4">
         <f>IF(O27=0,0,P27/O27)</f>
         <v>0</v>
       </c>
       <c r="S27" s="3">
-        <v>5474.075521134529</v>
+        <v>5474.484244219731</v>
       </c>
       <c r="T27" s="3">
-        <v>2498.889055450901</v>
+        <v>2499.075635566639</v>
       </c>
       <c r="U27" s="4">
         <f>IF(S27=0,0,T27/S27)</f>
         <v>0</v>
       </c>
       <c r="V27" s="3">
-        <v>16252582.50407936</v>
+        <v>17467369.42520155</v>
       </c>
       <c r="W27" s="3">
-        <v>2620057.91268337</v>
+        <v>2696045.26794249</v>
       </c>
       <c r="X27" s="4">
         <f>IF(V27=0,0,W27/V27)</f>
         <v>0</v>
       </c>
       <c r="Y27" s="3">
-        <v>1133183.161267315</v>
+        <v>1100816.798774998</v>
       </c>
       <c r="Z27" s="3">
-        <v>46663.02218609699</v>
+        <v>51990.69733833149</v>
       </c>
       <c r="AA27" s="4">
         <f>IF(Y27=0,0,Z27/Y27)</f>
         <v>0</v>
       </c>
       <c r="AB27" s="3">
-        <v>120916.4236699175</v>
+        <v>110263.3169002113</v>
       </c>
       <c r="AC27" s="3">
-        <v>216.2610395197698</v>
+        <v>260.5158107506577</v>
       </c>
       <c r="AD27" s="4">
         <f>IF(AB27=0,0,AC27/AB27)</f>
@@ -2686,80 +2686,80 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>414.1174655591563</v>
+        <v>414.1483857332581</v>
       </c>
       <c r="G32" s="3">
-        <v>17.33188958193897</v>
+        <v>17.33318367138942</v>
       </c>
       <c r="H32" s="4">
         <f>IF(F32=0,0,G32/F32)</f>
         <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>991.8205054212256</v>
+        <v>1108.193378484327</v>
       </c>
       <c r="J32" s="3">
-        <v>11.67126541163598</v>
+        <v>12.98011290102196</v>
       </c>
       <c r="K32" s="4">
         <f>IF(I32=0,0,J32/I32)</f>
         <v>0</v>
       </c>
       <c r="L32" s="3">
-        <v>18248.15090069409</v>
+        <v>16899.69278120454</v>
       </c>
       <c r="M32" s="3">
-        <v>1.053563024971634</v>
+        <v>5.859440663151443</v>
       </c>
       <c r="N32" s="4">
         <f>IF(L32=0,0,M32/L32)</f>
         <v>0</v>
       </c>
       <c r="O32" s="3">
-        <v>476.0481880235133</v>
+        <v>511.5551891389042</v>
       </c>
       <c r="P32" s="3">
-        <v>1.403611563553917</v>
+        <v>8.079041623072989</v>
       </c>
       <c r="Q32" s="4">
         <f>IF(O32=0,0,P32/O32)</f>
         <v>0</v>
       </c>
       <c r="S32" s="3">
-        <v>7595.550633139525</v>
+        <v>7596.11775664314</v>
       </c>
       <c r="T32" s="3">
-        <v>317.8934863562181</v>
+        <v>317.9172219451793</v>
       </c>
       <c r="U32" s="4">
         <f>IF(S32=0,0,T32/S32)</f>
         <v>0</v>
       </c>
       <c r="V32" s="3">
-        <v>25699987.56061059</v>
+        <v>27432336.72224081</v>
       </c>
       <c r="W32" s="3">
-        <v>227272.752685409</v>
+        <v>239615.7856515162</v>
       </c>
       <c r="X32" s="4">
         <f>IF(V32=0,0,W32/V32)</f>
         <v>0</v>
       </c>
       <c r="Y32" s="3">
-        <v>1959206.361225823</v>
+        <v>2836323.537272255</v>
       </c>
       <c r="Z32" s="3">
-        <v>6013.303388603264</v>
+        <v>8426.527290755883</v>
       </c>
       <c r="AA32" s="4">
         <f>IF(Y32=0,0,Z32/Y32)</f>
         <v>0</v>
       </c>
       <c r="AB32" s="3">
-        <v>205054.6892807224</v>
+        <v>190241.6708006598</v>
       </c>
       <c r="AC32" s="3">
-        <v>11.66113448393298</v>
+        <v>65.12895268769353</v>
       </c>
       <c r="AD32" s="4">
         <f>IF(AB32=0,0,AC32/AB32)</f>
@@ -2783,80 +2783,80 @@
         <v>0</v>
       </c>
       <c r="F33" s="3">
-        <v>423.4608834802265</v>
+        <v>423.4925012827377</v>
       </c>
       <c r="G33" s="3">
-        <v>33.49362841180107</v>
+        <v>33.49612922113162</v>
       </c>
       <c r="H33" s="4">
         <f>IF(F33=0,0,G33/F33)</f>
         <v>0</v>
       </c>
       <c r="I33" s="3">
-        <v>847.5293917044748</v>
+        <v>948.9557472002688</v>
       </c>
       <c r="J33" s="3">
-        <v>14.3231196181163</v>
+        <v>15.82301429034479</v>
       </c>
       <c r="K33" s="4">
         <f>IF(I33=0,0,J33/I33)</f>
         <v>0</v>
       </c>
       <c r="L33" s="3">
-        <v>18442.648959675</v>
+        <v>16952.10289749463</v>
       </c>
       <c r="M33" s="3">
-        <v>1.708336847607046</v>
+        <v>0</v>
       </c>
       <c r="N33" s="4">
         <f>IF(L33=0,0,M33/L33)</f>
         <v>0</v>
       </c>
       <c r="O33" s="3">
-        <v>476.5639382629005</v>
+        <v>566.8783011556247</v>
       </c>
       <c r="P33" s="3">
-        <v>1.674784317461948</v>
+        <v>1.765484009205597</v>
       </c>
       <c r="Q33" s="4">
         <f>IF(O33=0,0,P33/O33)</f>
         <v>0</v>
       </c>
       <c r="S33" s="3">
-        <v>7766.92327449926</v>
+        <v>7767.503193579848</v>
       </c>
       <c r="T33" s="3">
-        <v>614.3246099168791</v>
+        <v>614.3704786026356</v>
       </c>
       <c r="U33" s="4">
         <f>IF(S33=0,0,T33/S33)</f>
         <v>0</v>
       </c>
       <c r="V33" s="3">
-        <v>23322467.60095111</v>
+        <v>24925390.04051472</v>
       </c>
       <c r="W33" s="3">
-        <v>307442.101903148</v>
+        <v>324360.1584538221</v>
       </c>
       <c r="X33" s="4">
         <f>IF(V33=0,0,W33/V33)</f>
         <v>0</v>
       </c>
       <c r="Y33" s="3">
-        <v>2033978.129974804</v>
+        <v>2726453.333948384</v>
       </c>
       <c r="Z33" s="3">
-        <v>8632.855305685196</v>
+        <v>13274.22059702082</v>
       </c>
       <c r="AA33" s="4">
         <f>IF(Y33=0,0,Z33/Y33)</f>
         <v>0</v>
       </c>
       <c r="AB33" s="3">
-        <v>207305.2882361168</v>
+        <v>190795.2668985049</v>
       </c>
       <c r="AC33" s="3">
-        <v>19.08185642829631</v>
+        <v>0</v>
       </c>
       <c r="AD33" s="4">
         <f>IF(AB33=0,0,AC33/AB33)</f>
@@ -2880,80 +2880,80 @@
         <v>0</v>
       </c>
       <c r="F34" s="3">
-        <v>383.3486237845976</v>
+        <v>383.3772465961786</v>
       </c>
       <c r="G34" s="3">
-        <v>41.90672628932121</v>
+        <v>41.90985526450491</v>
       </c>
       <c r="H34" s="4">
         <f>IF(F34=0,0,G34/F34)</f>
         <v>0</v>
       </c>
       <c r="I34" s="3">
-        <v>721.6208038129823</v>
+        <v>812.8022893291875</v>
       </c>
       <c r="J34" s="3">
-        <v>15.78004529479356</v>
+        <v>17.28090339141886</v>
       </c>
       <c r="K34" s="4">
         <f>IF(I34=0,0,J34/I34)</f>
         <v>0</v>
       </c>
       <c r="L34" s="3">
-        <v>15355.96197556525</v>
+        <v>13913.05861415759</v>
       </c>
       <c r="M34" s="3">
-        <v>1.813587757010013</v>
+        <v>-0.000567748699337244</v>
       </c>
       <c r="N34" s="4">
         <f>IF(L34=0,0,M34/L34)</f>
         <v>0</v>
       </c>
       <c r="O34" s="3">
-        <v>391.5266582641886</v>
+        <v>344.6606313647766</v>
       </c>
       <c r="P34" s="3">
-        <v>2.194292167443666</v>
+        <v>2.202265903066785</v>
       </c>
       <c r="Q34" s="4">
         <f>IF(O34=0,0,P34/O34)</f>
         <v>0</v>
       </c>
       <c r="S34" s="3">
-        <v>7031.20279693764</v>
+        <v>7031.727783282595</v>
       </c>
       <c r="T34" s="3">
-        <v>768.6337521888199</v>
+        <v>768.6911424015352</v>
       </c>
       <c r="U34" s="4">
         <f>IF(S34=0,0,T34/S34)</f>
         <v>0</v>
       </c>
       <c r="V34" s="3">
-        <v>21162807.84637517</v>
+        <v>22582605.07877934</v>
       </c>
       <c r="W34" s="3">
-        <v>369371.3976432048</v>
+        <v>388536.1645939276</v>
       </c>
       <c r="X34" s="4">
         <f>IF(V34=0,0,W34/V34)</f>
         <v>0</v>
       </c>
       <c r="Y34" s="3">
-        <v>1664123.912966297</v>
+        <v>1847101.289104564</v>
       </c>
       <c r="Z34" s="3">
-        <v>9278.728632609127</v>
+        <v>12721.1280721447</v>
       </c>
       <c r="AA34" s="4">
         <f>IF(Y34=0,0,Z34/Y34)</f>
         <v>0</v>
       </c>
       <c r="AB34" s="3">
-        <v>172634.6152091868</v>
+        <v>156700.260166514</v>
       </c>
       <c r="AC34" s="3">
-        <v>20.14195956310141</v>
+        <v>0</v>
       </c>
       <c r="AD34" s="4">
         <f>IF(AB34=0,0,AC34/AB34)</f>
@@ -2977,80 +2977,80 @@
         <v>0</v>
       </c>
       <c r="F35" s="3">
-        <v>339.7997046237476</v>
+        <v>339.8250758454431</v>
       </c>
       <c r="G35" s="3">
-        <v>49.15221262038295</v>
+        <v>49.15588258143957</v>
       </c>
       <c r="H35" s="4">
         <f>IF(F35=0,0,G35/F35)</f>
         <v>0</v>
       </c>
       <c r="I35" s="3">
-        <v>656.2360029629352</v>
+        <v>743.8513994517335</v>
       </c>
       <c r="J35" s="3">
-        <v>17.33737326095032</v>
+        <v>18.81659816563327</v>
       </c>
       <c r="K35" s="4">
         <f>IF(I35=0,0,J35/I35)</f>
         <v>0</v>
       </c>
       <c r="L35" s="3">
-        <v>12320.89391034633</v>
+        <v>11488.16064938751</v>
       </c>
       <c r="M35" s="3">
-        <v>0.7611593206617981</v>
+        <v>-2.929739271363244</v>
       </c>
       <c r="N35" s="4">
         <f>IF(L35=0,0,M35/L35)</f>
         <v>0</v>
       </c>
       <c r="O35" s="3">
-        <v>305.8977151284149</v>
+        <v>288.1123393639429</v>
       </c>
       <c r="P35" s="3">
-        <v>2.158408031413972</v>
+        <v>3.669197411940724</v>
       </c>
       <c r="Q35" s="4">
         <f>IF(O35=0,0,P35/O35)</f>
         <v>0</v>
       </c>
       <c r="S35" s="3">
-        <v>6232.448704163242</v>
+        <v>6232.914051353447</v>
       </c>
       <c r="T35" s="3">
-        <v>901.527104597878</v>
+        <v>901.5944173227599</v>
       </c>
       <c r="U35" s="4">
         <f>IF(S35=0,0,T35/S35)</f>
         <v>0</v>
       </c>
       <c r="V35" s="3">
-        <v>20232379.41165718</v>
+        <v>21635078.69522292</v>
       </c>
       <c r="W35" s="3">
-        <v>430534.0067023523</v>
+        <v>448804.1554636247</v>
       </c>
       <c r="X35" s="4">
         <f>IF(V35=0,0,W35/V35)</f>
         <v>0</v>
       </c>
       <c r="Y35" s="3">
-        <v>1291512.272887179</v>
+        <v>1653421.300834798</v>
       </c>
       <c r="Z35" s="3">
-        <v>8071.82576554874</v>
+        <v>10899.17622549506</v>
       </c>
       <c r="AA35" s="4">
         <f>IF(Y35=0,0,Z35/Y35)</f>
         <v>0</v>
       </c>
       <c r="AB35" s="3">
-        <v>138538.5180813732</v>
+        <v>129411.2289903838</v>
       </c>
       <c r="AC35" s="3">
-        <v>8.480825079226634</v>
+        <v>-32.56447634381766</v>
       </c>
       <c r="AD35" s="4">
         <f>IF(AB35=0,0,AC35/AB35)</f>
@@ -3074,80 +3074,80 @@
         <v>0</v>
       </c>
       <c r="F36" s="3">
-        <v>298.4523954328049</v>
+        <v>298.4746794483207</v>
       </c>
       <c r="G36" s="3">
-        <v>47.83864135924927</v>
+        <v>47.84221324221152</v>
       </c>
       <c r="H36" s="4">
         <f>IF(F36=0,0,G36/F36)</f>
         <v>0</v>
       </c>
       <c r="I36" s="3">
-        <v>465.2285123766713</v>
+        <v>534.6642930986926</v>
       </c>
       <c r="J36" s="3">
-        <v>14.87518745130871</v>
+        <v>15.93105861635687</v>
       </c>
       <c r="K36" s="4">
         <f>IF(I36=0,0,J36/I36)</f>
         <v>0</v>
       </c>
       <c r="L36" s="3">
-        <v>10752.45040482439</v>
+        <v>9796.241413112457</v>
       </c>
       <c r="M36" s="3">
-        <v>2.380907366001979</v>
+        <v>11.71944907500595</v>
       </c>
       <c r="N36" s="4">
         <f>IF(L36=0,0,M36/L36)</f>
         <v>0</v>
       </c>
       <c r="O36" s="3">
-        <v>286.1372571560934</v>
+        <v>239.0687784366582</v>
       </c>
       <c r="P36" s="3">
-        <v>1.81975696763437</v>
+        <v>1.726839635706914</v>
       </c>
       <c r="Q36" s="4">
         <f>IF(O36=0,0,P36/O36)</f>
         <v>0</v>
       </c>
       <c r="S36" s="3">
-        <v>5474.075521134529</v>
+        <v>5474.484244219731</v>
       </c>
       <c r="T36" s="3">
-        <v>877.4341892925413</v>
+        <v>877.4997031144685</v>
       </c>
       <c r="U36" s="4">
         <f>IF(S36=0,0,T36/S36)</f>
         <v>0</v>
       </c>
       <c r="V36" s="3">
-        <v>16252582.50407936</v>
+        <v>17467369.42520155</v>
       </c>
       <c r="W36" s="3">
-        <v>432632.1491682045</v>
+        <v>446554.1823121533</v>
       </c>
       <c r="X36" s="4">
         <f>IF(V36=0,0,W36/V36)</f>
         <v>0</v>
       </c>
       <c r="Y36" s="3">
-        <v>1133183.161267315</v>
+        <v>1100816.798774998</v>
       </c>
       <c r="Z36" s="3">
-        <v>7758.964301767992</v>
+        <v>9304.968359676423</v>
       </c>
       <c r="AA36" s="4">
         <f>IF(Y36=0,0,Z36/Y36)</f>
         <v>0</v>
       </c>
       <c r="AB36" s="3">
-        <v>120916.4236699175</v>
+        <v>110263.3169002113</v>
       </c>
       <c r="AC36" s="3">
-        <v>26.50257837252866</v>
+        <v>130.2579053753288</v>
       </c>
       <c r="AD36" s="4">
         <f>IF(AB36=0,0,AC36/AB36)</f>
@@ -3294,20 +3294,20 @@
         <v>0</v>
       </c>
       <c r="F41" s="3">
-        <v>155.693183623828</v>
+        <v>155.6881748268545</v>
       </c>
       <c r="G41" s="3">
-        <v>72.16770895741165</v>
+        <v>72.16538725395763</v>
       </c>
       <c r="H41" s="4">
         <f>IF(F41=0,0,G41/F41)</f>
         <v>0</v>
       </c>
       <c r="I41" s="3">
-        <v>289.9009013946363</v>
+        <v>382.3073643284127</v>
       </c>
       <c r="J41" s="6">
-        <v>2.57749961572641</v>
+        <v>3.356936426061671</v>
       </c>
       <c r="K41" s="7">
         <f>IF(I41=0,0,J41/I41)</f>
@@ -3334,20 +3334,20 @@
         <v>0</v>
       </c>
       <c r="S41" s="3">
-        <v>2076.424364219953</v>
+        <v>2076.357563684252</v>
       </c>
       <c r="T41" s="3">
-        <v>962.4749504201816</v>
+        <v>962.4439866907096</v>
       </c>
       <c r="U41" s="4">
         <f>IF(S41=0,0,T41/S41)</f>
         <v>0</v>
       </c>
       <c r="V41" s="3">
-        <v>7917202.430076606</v>
+        <v>9070418.669545408</v>
       </c>
       <c r="W41" s="6">
-        <v>75888.02632279508</v>
+        <v>78807.32897765189</v>
       </c>
       <c r="X41" s="7">
         <f>IF(V41=0,0,W41/V41)</f>
@@ -3391,20 +3391,20 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>148.099829866749</v>
+        <v>148.0950653551477</v>
       </c>
       <c r="G42" s="3">
-        <v>72.91049047900319</v>
+        <v>72.90814487956493</v>
       </c>
       <c r="H42" s="4">
         <f>IF(F42=0,0,G42/F42)</f>
         <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>172.5102033195305</v>
+        <v>245.090682899663</v>
       </c>
       <c r="J42" s="6">
-        <v>2.092952702855459</v>
+        <v>2.9365686601786</v>
       </c>
       <c r="K42" s="7">
         <f>IF(I42=0,0,J42/I42)</f>
@@ -3431,20 +3431,20 @@
         <v>0</v>
       </c>
       <c r="S42" s="3">
-        <v>1975.154518101098</v>
+        <v>1975.090975512128</v>
       </c>
       <c r="T42" s="3">
-        <v>972.3811621940484</v>
+        <v>972.3498797723723</v>
       </c>
       <c r="U42" s="4">
         <f>IF(S42=0,0,T42/S42)</f>
         <v>0</v>
       </c>
       <c r="V42" s="3">
-        <v>5775458.9344058</v>
+        <v>7100767.677214347</v>
       </c>
       <c r="W42" s="6">
-        <v>81365.06762592774</v>
+        <v>91738.12470871955</v>
       </c>
       <c r="X42" s="7">
         <f>IF(V42=0,0,W42/V42)</f>
@@ -3488,20 +3488,20 @@
         <v>0</v>
       </c>
       <c r="F43" s="3">
-        <v>134.796744990006</v>
+        <v>134.7924084512274</v>
       </c>
       <c r="G43" s="3">
-        <v>72.9484758735861</v>
+        <v>72.9461290521218</v>
       </c>
       <c r="H43" s="4">
         <f>IF(F43=0,0,G43/F43)</f>
         <v>0</v>
       </c>
       <c r="I43" s="3">
-        <v>135.4560554360413</v>
+        <v>200.4130880433794</v>
       </c>
       <c r="J43" s="6">
-        <v>2.287314210165379</v>
+        <v>3.271171722685744</v>
       </c>
       <c r="K43" s="7">
         <f>IF(I43=0,0,J43/I43)</f>
@@ -3528,20 +3528,20 @@
         <v>0</v>
       </c>
       <c r="S43" s="3">
-        <v>1797.736028001397</v>
+        <v>1797.678193133057</v>
       </c>
       <c r="T43" s="3">
-        <v>972.8877598302499</v>
+        <v>972.8564611108482</v>
       </c>
       <c r="U43" s="4">
         <f>IF(S43=0,0,T43/S43)</f>
         <v>0</v>
       </c>
       <c r="V43" s="3">
-        <v>4941006.318926696</v>
+        <v>6292834.208210533</v>
       </c>
       <c r="W43" s="6">
-        <v>93694.98213961534</v>
+        <v>108314.0966329305</v>
       </c>
       <c r="X43" s="7">
         <f>IF(V43=0,0,W43/V43)</f>
@@ -3585,20 +3585,20 @@
         <v>0</v>
       </c>
       <c r="F44" s="3">
-        <v>118.7859525719791</v>
+        <v>118.7821311155358</v>
       </c>
       <c r="G44" s="3">
-        <v>33.21364103058893</v>
+        <v>33.21257251634332</v>
       </c>
       <c r="H44" s="4">
         <f>IF(F44=0,0,G44/F44)</f>
         <v>0</v>
       </c>
       <c r="I44" s="3">
-        <v>131.3138854296834</v>
+        <v>193.9015574705648</v>
       </c>
       <c r="J44" s="6">
-        <v>0.8526697489883809</v>
+        <v>1.247128400560556</v>
       </c>
       <c r="K44" s="7">
         <f>IF(I44=0,0,J44/I44)</f>
@@ -3625,20 +3625,20 @@
         <v>0</v>
       </c>
       <c r="S44" s="3">
-        <v>1584.205809828305</v>
+        <v>1584.154844429043</v>
       </c>
       <c r="T44" s="3">
-        <v>442.958463917078</v>
+        <v>442.9442135243412</v>
       </c>
       <c r="U44" s="4">
         <f>IF(S44=0,0,T44/S44)</f>
         <v>0</v>
       </c>
       <c r="V44" s="3">
-        <v>4714339.930251096</v>
+        <v>6053045.584847068</v>
       </c>
       <c r="W44" s="6">
-        <v>37175.27322141826</v>
+        <v>44071.79961647</v>
       </c>
       <c r="X44" s="7">
         <f>IF(V44=0,0,W44/V44)</f>
@@ -3682,20 +3682,20 @@
         <v>0</v>
       </c>
       <c r="F45" s="3">
-        <v>93.71022621139285</v>
+        <v>93.70721146478344</v>
       </c>
       <c r="G45" s="3">
-        <v>19.08619597135289</v>
+        <v>19.08558195037654</v>
       </c>
       <c r="H45" s="4">
         <f>IF(F45=0,0,G45/F45)</f>
         <v>0</v>
       </c>
       <c r="I45" s="3">
-        <v>85.34930063788899</v>
+        <v>136.6145524202559</v>
       </c>
       <c r="J45" s="6">
-        <v>0.6193965967932891</v>
+        <v>0.9404859014340036</v>
       </c>
       <c r="K45" s="7">
         <f>IF(I45=0,0,J45/I45)</f>
@@ -3722,20 +3722,20 @@
         <v>0</v>
       </c>
       <c r="S45" s="3">
-        <v>1249.779806366036</v>
+        <v>1249.73959976761</v>
       </c>
       <c r="T45" s="3">
-        <v>254.545776589339</v>
+        <v>254.5375876109539</v>
       </c>
       <c r="U45" s="4">
         <f>IF(S45=0,0,T45/S45)</f>
         <v>0</v>
       </c>
       <c r="V45" s="3">
-        <v>3542162.222585884</v>
+        <v>4890905.466101354</v>
       </c>
       <c r="W45" s="6">
-        <v>29337.3724585874</v>
+        <v>36723.80325047113</v>
       </c>
       <c r="X45" s="7">
         <f>IF(V45=0,0,W45/V45)</f>
@@ -3902,20 +3902,20 @@
         <v>0</v>
       </c>
       <c r="F50" s="3">
-        <v>155.693183623828</v>
+        <v>155.6881748268545</v>
       </c>
       <c r="G50" s="3">
-        <v>128.1413608709483</v>
+        <v>128.1372384421717</v>
       </c>
       <c r="H50" s="4">
         <f>IF(F50=0,0,G50/F50)</f>
         <v>0</v>
       </c>
       <c r="I50" s="3">
-        <v>289.9009013946363</v>
+        <v>382.3073643284127</v>
       </c>
       <c r="J50" s="6">
-        <v>9.579560738421627</v>
+        <v>12.60698597415583</v>
       </c>
       <c r="K50" s="7">
         <f>IF(I50=0,0,J50/I50)</f>
@@ -3942,20 +3942,20 @@
         <v>0</v>
       </c>
       <c r="S50" s="3">
-        <v>2076.424364219953</v>
+        <v>2076.357563684252</v>
       </c>
       <c r="T50" s="3">
-        <v>1708.975547828781</v>
+        <v>1708.920568469041</v>
       </c>
       <c r="U50" s="4">
         <f>IF(S50=0,0,T50/S50)</f>
         <v>0</v>
       </c>
       <c r="V50" s="3">
-        <v>7917202.430076606</v>
+        <v>9070418.669545408</v>
       </c>
       <c r="W50" s="6">
-        <v>289948.8097963436</v>
+        <v>304695.9033628255</v>
       </c>
       <c r="X50" s="7">
         <f>IF(V50=0,0,W50/V50)</f>
@@ -3999,20 +3999,20 @@
         <v>0</v>
       </c>
       <c r="F51" s="3">
-        <v>148.099829866749</v>
+        <v>148.0950653551477</v>
       </c>
       <c r="G51" s="3">
-        <v>124.690141566094</v>
+        <v>124.6861301663065</v>
       </c>
       <c r="H51" s="4">
         <f>IF(F51=0,0,G51/F51)</f>
         <v>0</v>
       </c>
       <c r="I51" s="3">
-        <v>172.5102033195305</v>
+        <v>245.090682899663</v>
       </c>
       <c r="J51" s="6">
-        <v>7.55612644698788</v>
+        <v>10.76043447512289</v>
       </c>
       <c r="K51" s="7">
         <f>IF(I51=0,0,J51/I51)</f>
@@ -4039,20 +4039,20 @@
         <v>0</v>
       </c>
       <c r="S51" s="3">
-        <v>1975.154518101098</v>
+        <v>1975.090975512128</v>
       </c>
       <c r="T51" s="3">
-        <v>1662.947869005153</v>
+        <v>1662.894370399373</v>
       </c>
       <c r="U51" s="4">
         <f>IF(S51=0,0,T51/S51)</f>
         <v>0</v>
       </c>
       <c r="V51" s="3">
-        <v>5775458.9344058</v>
+        <v>7100767.677214347</v>
       </c>
       <c r="W51" s="6">
-        <v>301589.2033798397</v>
+        <v>346368.6063864464</v>
       </c>
       <c r="X51" s="7">
         <f>IF(V51=0,0,W51/V51)</f>
@@ -4096,20 +4096,20 @@
         <v>0</v>
       </c>
       <c r="F52" s="3">
-        <v>134.796744990006</v>
+        <v>134.7924084512274</v>
       </c>
       <c r="G52" s="3">
-        <v>117.3169351601271</v>
+        <v>117.3131609633634</v>
       </c>
       <c r="H52" s="4">
         <f>IF(F52=0,0,G52/F52)</f>
         <v>0</v>
       </c>
       <c r="I52" s="3">
-        <v>135.4560554360413</v>
+        <v>200.4130880433794</v>
       </c>
       <c r="J52" s="6">
-        <v>8.085542072412819</v>
+        <v>11.7730736107835</v>
       </c>
       <c r="K52" s="7">
         <f>IF(I52=0,0,J52/I52)</f>
@@ -4136,20 +4136,20 @@
         <v>0</v>
       </c>
       <c r="S52" s="3">
-        <v>1797.736028001397</v>
+        <v>1797.678193133057</v>
       </c>
       <c r="T52" s="3">
-        <v>1564.614049454244</v>
+        <v>1564.563714340444</v>
       </c>
       <c r="U52" s="4">
         <f>IF(S52=0,0,T52/S52)</f>
         <v>0</v>
       </c>
       <c r="V52" s="3">
-        <v>4941006.318926696</v>
+        <v>6292834.208210533</v>
       </c>
       <c r="W52" s="6">
-        <v>340742.8114436772</v>
+        <v>402841.1074284222</v>
       </c>
       <c r="X52" s="7">
         <f>IF(V52=0,0,W52/V52)</f>
@@ -4193,20 +4193,20 @@
         <v>0</v>
       </c>
       <c r="F53" s="3">
-        <v>118.7859525719791</v>
+        <v>118.7821311155358</v>
       </c>
       <c r="G53" s="3">
-        <v>77.0874861199776</v>
+        <v>77.085006142639</v>
       </c>
       <c r="H53" s="4">
         <f>IF(F53=0,0,G53/F53)</f>
         <v>0</v>
       </c>
       <c r="I53" s="3">
-        <v>131.3138854296834</v>
+        <v>193.9015574705648</v>
       </c>
       <c r="J53" s="6">
-        <v>3.240305918559723</v>
+        <v>4.775947591036063</v>
       </c>
       <c r="K53" s="7">
         <f>IF(I53=0,0,J53/I53)</f>
@@ -4233,20 +4233,20 @@
         <v>0</v>
       </c>
       <c r="S53" s="3">
-        <v>1584.205809828305</v>
+        <v>1584.154844429043</v>
       </c>
       <c r="T53" s="3">
-        <v>1028.088260708491</v>
+        <v>1028.055186136768</v>
       </c>
       <c r="U53" s="4">
         <f>IF(S53=0,0,T53/S53)</f>
         <v>0</v>
       </c>
       <c r="V53" s="3">
-        <v>4714339.930251096</v>
+        <v>6053045.584847068</v>
       </c>
       <c r="W53" s="6">
-        <v>142904.1636235043</v>
+        <v>171043.9846910052</v>
       </c>
       <c r="X53" s="7">
         <f>IF(V53=0,0,W53/V53)</f>
@@ -4290,20 +4290,20 @@
         <v>0</v>
       </c>
       <c r="F54" s="3">
-        <v>93.71022621139285</v>
+        <v>93.70721146478344</v>
       </c>
       <c r="G54" s="3">
-        <v>50.34418065239444</v>
+        <v>50.34256103248683</v>
       </c>
       <c r="H54" s="4">
         <f>IF(F54=0,0,G54/F54)</f>
         <v>0</v>
       </c>
       <c r="I54" s="3">
-        <v>85.34930063788899</v>
+        <v>136.6145524202559</v>
       </c>
       <c r="J54" s="6">
-        <v>2.379898399251702</v>
+        <v>3.636206208529707</v>
       </c>
       <c r="K54" s="7">
         <f>IF(I54=0,0,J54/I54)</f>
@@ -4330,20 +4330,20 @@
         <v>0</v>
       </c>
       <c r="S54" s="3">
-        <v>1249.779806366036</v>
+        <v>1249.73959976761</v>
       </c>
       <c r="T54" s="3">
-        <v>671.4223504857664</v>
+        <v>671.4007501937136</v>
       </c>
       <c r="U54" s="4">
         <f>IF(S54=0,0,T54/S54)</f>
         <v>0</v>
       </c>
       <c r="V54" s="3">
-        <v>3542162.222585884</v>
+        <v>4890905.466101354</v>
       </c>
       <c r="W54" s="6">
-        <v>113587.6470628493</v>
+        <v>143249.1869890932</v>
       </c>
       <c r="X54" s="7">
         <f>IF(V54=0,0,W54/V54)</f>

--- a/5000_analyze_results/results_spreadsheet.xlsx
+++ b/5000_analyze_results/results_spreadsheet.xlsx
@@ -872,30 +872,30 @@
         <v>0</v>
       </c>
       <c r="I5" s="3">
-        <v>4771.668377035696</v>
+        <v>4771.172487854658</v>
       </c>
       <c r="J5" s="3">
-        <v>313.5874213735713</v>
+        <v>313.4550641795806</v>
       </c>
       <c r="K5" s="4">
         <f>IF(I5=0,0,J5/I5)</f>
         <v>0</v>
       </c>
       <c r="L5" s="3">
-        <v>17342.74644129576</v>
+        <v>17573.82651946129</v>
       </c>
       <c r="M5" s="3">
-        <v>34.67868384804204</v>
+        <v>52.43127107270062</v>
       </c>
       <c r="N5" s="4">
         <f>IF(L5=0,0,M5/L5)</f>
         <v>0</v>
       </c>
       <c r="O5" s="3">
-        <v>419.9952041897751</v>
+        <v>495.9420392823301</v>
       </c>
       <c r="P5" s="3">
-        <v>19.4095228180929</v>
+        <v>14.94688767936849</v>
       </c>
       <c r="Q5" s="4">
         <f>IF(O5=0,0,P5/O5)</f>
@@ -912,30 +912,30 @@
         <v>0</v>
       </c>
       <c r="V5" s="3">
-        <v>131689124.8136304</v>
+        <v>131693856.602241</v>
       </c>
       <c r="W5" s="3">
-        <v>6832789.946041524</v>
+        <v>6834156.362184763</v>
       </c>
       <c r="X5" s="4">
         <f>IF(V5=0,0,W5/V5)</f>
         <v>0</v>
       </c>
       <c r="Y5" s="3">
-        <v>3021681.785132265</v>
+        <v>3014818.917223012</v>
       </c>
       <c r="Z5" s="3">
-        <v>83056.57238458376</v>
+        <v>82234.18246693723</v>
       </c>
       <c r="AA5" s="4">
         <f>IF(Y5=0,0,Z5/Y5)</f>
         <v>0</v>
       </c>
       <c r="AB5" s="3">
-        <v>193528.0028851792</v>
+        <v>196057.6019358347</v>
       </c>
       <c r="AC5" s="3">
-        <v>385.5139499704819</v>
+        <v>582.7808785878588</v>
       </c>
       <c r="AD5" s="4">
         <f>IF(AB5=0,0,AC5/AB5)</f>
@@ -969,30 +969,30 @@
         <v>0</v>
       </c>
       <c r="I6" s="3">
-        <v>4315.742780998208</v>
+        <v>4315.488605002881</v>
       </c>
       <c r="J6" s="3">
-        <v>279.4333559181248</v>
+        <v>279.5339981601541</v>
       </c>
       <c r="K6" s="4">
         <f>IF(I6=0,0,J6/I6)</f>
         <v>0</v>
       </c>
       <c r="L6" s="3">
-        <v>14283.90029035187</v>
+        <v>14652.1253505373</v>
       </c>
       <c r="M6" s="3">
-        <v>30.34748269250803</v>
+        <v>33.36611404703743</v>
       </c>
       <c r="N6" s="4">
         <f>IF(L6=0,0,M6/L6)</f>
         <v>0</v>
       </c>
       <c r="O6" s="3">
-        <v>214.4087795755616</v>
+        <v>286.4588253328344</v>
       </c>
       <c r="P6" s="3">
-        <v>5.588637967688701</v>
+        <v>8.284407215548388</v>
       </c>
       <c r="Q6" s="4">
         <f>IF(O6=0,0,P6/O6)</f>
@@ -1009,30 +1009,30 @@
         <v>0</v>
       </c>
       <c r="V6" s="3">
-        <v>123358149.8591988</v>
+        <v>123353341.0379582</v>
       </c>
       <c r="W6" s="3">
-        <v>6427621.054781124</v>
+        <v>6428198.322602153</v>
       </c>
       <c r="X6" s="4">
         <f>IF(V6=0,0,W6/V6)</f>
         <v>0</v>
       </c>
       <c r="Y6" s="3">
-        <v>1781844.821568525</v>
+        <v>1787928.583240007</v>
       </c>
       <c r="Z6" s="3">
-        <v>46313.53746748972</v>
+        <v>46645.37901320681</v>
       </c>
       <c r="AA6" s="4">
         <f>IF(Y6=0,0,Z6/Y6)</f>
         <v>0</v>
       </c>
       <c r="AB6" s="3">
-        <v>159361.8290690457</v>
+        <v>163455.5873311974</v>
       </c>
       <c r="AC6" s="3">
-        <v>337.3247062241426</v>
+        <v>370.860559101362</v>
       </c>
       <c r="AD6" s="4">
         <f>IF(AB6=0,0,AC6/AB6)</f>
@@ -1066,30 +1066,30 @@
         <v>0</v>
       </c>
       <c r="I7" s="3">
-        <v>4219.995713516021</v>
+        <v>4219.911362271461</v>
       </c>
       <c r="J7" s="3">
-        <v>243.0103178216233</v>
+        <v>242.9313309619347</v>
       </c>
       <c r="K7" s="4">
         <f>IF(I7=0,0,J7/I7)</f>
         <v>0</v>
       </c>
       <c r="L7" s="3">
-        <v>12700.07744999716</v>
+        <v>12980.21700838298</v>
       </c>
       <c r="M7" s="3">
-        <v>52.02292426651717</v>
+        <v>28.82879728573933</v>
       </c>
       <c r="N7" s="4">
         <f>IF(L7=0,0,M7/L7)</f>
         <v>0</v>
       </c>
       <c r="O7" s="3">
-        <v>344.8791542406948</v>
+        <v>362.0106149542505</v>
       </c>
       <c r="P7" s="3">
-        <v>6.148588666623284</v>
+        <v>7.080686168705637</v>
       </c>
       <c r="Q7" s="4">
         <f>IF(O7=0,0,P7/O7)</f>
@@ -1106,30 +1106,30 @@
         <v>0</v>
       </c>
       <c r="V7" s="3">
-        <v>121044503.5745435</v>
+        <v>121042695.9926408</v>
       </c>
       <c r="W7" s="3">
-        <v>5625577.528566912</v>
+        <v>5624803.04057464</v>
       </c>
       <c r="X7" s="4">
         <f>IF(V7=0,0,W7/V7)</f>
         <v>0</v>
       </c>
       <c r="Y7" s="3">
-        <v>2254117.861995054</v>
+        <v>2262233.551971834</v>
       </c>
       <c r="Z7" s="3">
-        <v>45544.04982524691</v>
+        <v>48143.47526669828</v>
       </c>
       <c r="AA7" s="4">
         <f>IF(Y7=0,0,Z7/Y7)</f>
         <v>0</v>
       </c>
       <c r="AB7" s="3">
-        <v>141724.5658578964</v>
+        <v>144811.4155872839</v>
       </c>
       <c r="AC7" s="3">
-        <v>578.2709249557229</v>
+        <v>320.2886646784609</v>
       </c>
       <c r="AD7" s="4">
         <f>IF(AB7=0,0,AC7/AB7)</f>
@@ -1163,30 +1163,30 @@
         <v>0</v>
       </c>
       <c r="I8" s="3">
-        <v>3866.44843120562</v>
+        <v>3866.404723234419</v>
       </c>
       <c r="J8" s="3">
-        <v>199.0991080713072</v>
+        <v>199.0831212808485</v>
       </c>
       <c r="K8" s="4">
         <f>IF(I8=0,0,J8/I8)</f>
         <v>0</v>
       </c>
       <c r="L8" s="3">
-        <v>11596.86626484413</v>
+        <v>12127.30661114934</v>
       </c>
       <c r="M8" s="3">
-        <v>21.67842480659671</v>
+        <v>26.43375170142017</v>
       </c>
       <c r="N8" s="4">
         <f>IF(L8=0,0,M8/L8)</f>
         <v>0</v>
       </c>
       <c r="O8" s="3">
-        <v>277.4788567267415</v>
+        <v>326.2902544418872</v>
       </c>
       <c r="P8" s="3">
-        <v>2.068533699701366</v>
+        <v>6.173648437333526</v>
       </c>
       <c r="Q8" s="4">
         <f>IF(O8=0,0,P8/O8)</f>
@@ -1203,30 +1203,30 @@
         <v>0</v>
       </c>
       <c r="V8" s="3">
-        <v>114931674.6513069</v>
+        <v>114930948.5074336</v>
       </c>
       <c r="W8" s="3">
-        <v>4857592.477778837</v>
+        <v>4858738.283078313</v>
       </c>
       <c r="X8" s="4">
         <f>IF(V8=0,0,W8/V8)</f>
         <v>0</v>
       </c>
       <c r="Y8" s="3">
-        <v>2020434.083641439</v>
+        <v>2017724.044351414</v>
       </c>
       <c r="Z8" s="3">
-        <v>41023.30992707051</v>
+        <v>39554.06946016243</v>
       </c>
       <c r="AA8" s="4">
         <f>IF(Y8=0,0,Z8/Y8)</f>
         <v>0</v>
       </c>
       <c r="AB8" s="3">
-        <v>129388.1194588412</v>
+        <v>135303.8994357765</v>
       </c>
       <c r="AC8" s="3">
-        <v>240.9462187315658</v>
+        <v>293.7986247426306</v>
       </c>
       <c r="AD8" s="4">
         <f>IF(AB8=0,0,AC8/AB8)</f>
@@ -1260,30 +1260,30 @@
         <v>0</v>
       </c>
       <c r="I9" s="3">
-        <v>3364.438925828685</v>
+        <v>3364.404821554393</v>
       </c>
       <c r="J9" s="3">
-        <v>100.8518174263639</v>
+        <v>100.8406044416442</v>
       </c>
       <c r="K9" s="4">
         <f>IF(I9=0,0,J9/I9)</f>
         <v>0</v>
       </c>
       <c r="L9" s="3">
-        <v>11328.20246422979</v>
+        <v>11639.06744554709</v>
       </c>
       <c r="M9" s="3">
-        <v>8.672433171367272</v>
+        <v>13.65298159589991</v>
       </c>
       <c r="N9" s="4">
         <f>IF(L9=0,0,M9/L9)</f>
         <v>0</v>
       </c>
       <c r="O9" s="3">
-        <v>193.6283842759436</v>
+        <v>210.8368637670372</v>
       </c>
       <c r="P9" s="3">
-        <v>2.497779431025672</v>
+        <v>2.020924868696747</v>
       </c>
       <c r="Q9" s="4">
         <f>IF(O9=0,0,P9/O9)</f>
@@ -1300,30 +1300,30 @@
         <v>0</v>
       </c>
       <c r="V9" s="3">
-        <v>107061599.7071237</v>
+        <v>107057780.7659875</v>
       </c>
       <c r="W9" s="3">
-        <v>2677646.657504544</v>
+        <v>2679796.374648735</v>
       </c>
       <c r="X9" s="4">
         <f>IF(V9=0,0,W9/V9)</f>
         <v>0</v>
       </c>
       <c r="Y9" s="3">
-        <v>1264893.404914272</v>
+        <v>1277885.722823765</v>
       </c>
       <c r="Z9" s="3">
-        <v>14427.89329205267</v>
+        <v>14853.51614416833</v>
       </c>
       <c r="AA9" s="4">
         <f>IF(Y9=0,0,Z9/Y9)</f>
         <v>0</v>
       </c>
       <c r="AB9" s="3">
-        <v>126400.38634657</v>
+        <v>129863.8085071404</v>
       </c>
       <c r="AC9" s="3">
-        <v>96.37848749259138</v>
+        <v>151.7156832687178</v>
       </c>
       <c r="AD9" s="4">
         <f>IF(AB9=0,0,AC9/AB9)</f>
@@ -1480,30 +1480,30 @@
         <v>0</v>
       </c>
       <c r="I14" s="3">
-        <v>4771.668377035696</v>
+        <v>4771.172487854658</v>
       </c>
       <c r="J14" s="3">
-        <v>313.5874213735713</v>
+        <v>313.4550641795806</v>
       </c>
       <c r="K14" s="4">
         <f>IF(I14=0,0,J14/I14)</f>
         <v>0</v>
       </c>
       <c r="L14" s="3">
-        <v>17342.74644129576</v>
+        <v>17573.82651946129</v>
       </c>
       <c r="M14" s="3">
-        <v>34.67868384804204</v>
+        <v>52.43127107270062</v>
       </c>
       <c r="N14" s="4">
         <f>IF(L14=0,0,M14/L14)</f>
         <v>0</v>
       </c>
       <c r="O14" s="3">
-        <v>419.9952041897751</v>
+        <v>495.9420392823301</v>
       </c>
       <c r="P14" s="3">
-        <v>19.4095228180929</v>
+        <v>14.94688767936849</v>
       </c>
       <c r="Q14" s="4">
         <f>IF(O14=0,0,P14/O14)</f>
@@ -1520,30 +1520,30 @@
         <v>0</v>
       </c>
       <c r="V14" s="3">
-        <v>131689124.8136304</v>
+        <v>131693856.602241</v>
       </c>
       <c r="W14" s="3">
-        <v>6832789.946041539</v>
+        <v>6834156.362184763</v>
       </c>
       <c r="X14" s="4">
         <f>IF(V14=0,0,W14/V14)</f>
         <v>0</v>
       </c>
       <c r="Y14" s="3">
-        <v>3021681.785132265</v>
+        <v>3014818.917223012</v>
       </c>
       <c r="Z14" s="3">
-        <v>83056.57238458376</v>
+        <v>82234.18246693723</v>
       </c>
       <c r="AA14" s="4">
         <f>IF(Y14=0,0,Z14/Y14)</f>
         <v>0</v>
       </c>
       <c r="AB14" s="3">
-        <v>193528.0028851792</v>
+        <v>196057.6019358347</v>
       </c>
       <c r="AC14" s="3">
-        <v>385.5139499704819</v>
+        <v>582.7808785878588</v>
       </c>
       <c r="AD14" s="4">
         <f>IF(AB14=0,0,AC14/AB14)</f>
@@ -1577,30 +1577,30 @@
         <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>4315.742780998208</v>
+        <v>4315.488605002881</v>
       </c>
       <c r="J15" s="3">
-        <v>279.4333559181248</v>
+        <v>279.5339981601541</v>
       </c>
       <c r="K15" s="4">
         <f>IF(I15=0,0,J15/I15)</f>
         <v>0</v>
       </c>
       <c r="L15" s="3">
-        <v>14283.90029035187</v>
+        <v>14652.1253505373</v>
       </c>
       <c r="M15" s="3">
-        <v>30.34748269250803</v>
+        <v>33.36611404703743</v>
       </c>
       <c r="N15" s="4">
         <f>IF(L15=0,0,M15/L15)</f>
         <v>0</v>
       </c>
       <c r="O15" s="3">
-        <v>214.4087795755616</v>
+        <v>286.4588253328344</v>
       </c>
       <c r="P15" s="3">
-        <v>5.588637967688701</v>
+        <v>8.284407215548388</v>
       </c>
       <c r="Q15" s="4">
         <f>IF(O15=0,0,P15/O15)</f>
@@ -1617,30 +1617,30 @@
         <v>0</v>
       </c>
       <c r="V15" s="3">
-        <v>123358149.8591988</v>
+        <v>123353341.0379582</v>
       </c>
       <c r="W15" s="3">
-        <v>6427621.054781124</v>
+        <v>6428198.322602153</v>
       </c>
       <c r="X15" s="4">
         <f>IF(V15=0,0,W15/V15)</f>
         <v>0</v>
       </c>
       <c r="Y15" s="3">
-        <v>1781844.821568525</v>
+        <v>1787928.583240007</v>
       </c>
       <c r="Z15" s="3">
-        <v>46313.53746748972</v>
+        <v>46645.37901320681</v>
       </c>
       <c r="AA15" s="4">
         <f>IF(Y15=0,0,Z15/Y15)</f>
         <v>0</v>
       </c>
       <c r="AB15" s="3">
-        <v>159361.8290690457</v>
+        <v>163455.5873311974</v>
       </c>
       <c r="AC15" s="3">
-        <v>337.3247062241426</v>
+        <v>370.860559101362</v>
       </c>
       <c r="AD15" s="4">
         <f>IF(AB15=0,0,AC15/AB15)</f>
@@ -1674,30 +1674,30 @@
         <v>0</v>
       </c>
       <c r="I16" s="3">
-        <v>4219.995713516021</v>
+        <v>4219.911362271461</v>
       </c>
       <c r="J16" s="3">
-        <v>243.0103178216233</v>
+        <v>242.9313309619347</v>
       </c>
       <c r="K16" s="4">
         <f>IF(I16=0,0,J16/I16)</f>
         <v>0</v>
       </c>
       <c r="L16" s="3">
-        <v>12700.07744999716</v>
+        <v>12980.21700838298</v>
       </c>
       <c r="M16" s="3">
-        <v>52.02292426651717</v>
+        <v>28.82879728573933</v>
       </c>
       <c r="N16" s="4">
         <f>IF(L16=0,0,M16/L16)</f>
         <v>0</v>
       </c>
       <c r="O16" s="3">
-        <v>344.8791542406948</v>
+        <v>362.0106149542505</v>
       </c>
       <c r="P16" s="3">
-        <v>6.148588666623284</v>
+        <v>7.080686168705637</v>
       </c>
       <c r="Q16" s="4">
         <f>IF(O16=0,0,P16/O16)</f>
@@ -1714,30 +1714,30 @@
         <v>0</v>
       </c>
       <c r="V16" s="3">
-        <v>121044503.5745435</v>
+        <v>121042695.9926408</v>
       </c>
       <c r="W16" s="3">
-        <v>5625577.528566912</v>
+        <v>5624803.04057464</v>
       </c>
       <c r="X16" s="4">
         <f>IF(V16=0,0,W16/V16)</f>
         <v>0</v>
       </c>
       <c r="Y16" s="3">
-        <v>2254117.861995054</v>
+        <v>2262233.551971834</v>
       </c>
       <c r="Z16" s="3">
-        <v>45544.04982524691</v>
+        <v>48143.47526669828</v>
       </c>
       <c r="AA16" s="4">
         <f>IF(Y16=0,0,Z16/Y16)</f>
         <v>0</v>
       </c>
       <c r="AB16" s="3">
-        <v>141724.5658578964</v>
+        <v>144811.4155872839</v>
       </c>
       <c r="AC16" s="3">
-        <v>578.2709249557229</v>
+        <v>320.2886646784609</v>
       </c>
       <c r="AD16" s="4">
         <f>IF(AB16=0,0,AC16/AB16)</f>
@@ -1771,30 +1771,30 @@
         <v>0</v>
       </c>
       <c r="I17" s="3">
-        <v>3866.44843120562</v>
+        <v>3866.404723234419</v>
       </c>
       <c r="J17" s="3">
-        <v>199.0991080713072</v>
+        <v>199.0831212808485</v>
       </c>
       <c r="K17" s="4">
         <f>IF(I17=0,0,J17/I17)</f>
         <v>0</v>
       </c>
       <c r="L17" s="3">
-        <v>11596.86626484413</v>
+        <v>12127.30661114934</v>
       </c>
       <c r="M17" s="3">
-        <v>21.67842480659671</v>
+        <v>26.43375170142017</v>
       </c>
       <c r="N17" s="4">
         <f>IF(L17=0,0,M17/L17)</f>
         <v>0</v>
       </c>
       <c r="O17" s="3">
-        <v>277.4788567267415</v>
+        <v>326.2902544418872</v>
       </c>
       <c r="P17" s="3">
-        <v>2.068533699701366</v>
+        <v>6.173648437333526</v>
       </c>
       <c r="Q17" s="4">
         <f>IF(O17=0,0,P17/O17)</f>
@@ -1811,30 +1811,30 @@
         <v>0</v>
       </c>
       <c r="V17" s="3">
-        <v>114931674.6513069</v>
+        <v>114930948.5074336</v>
       </c>
       <c r="W17" s="3">
-        <v>4857592.477778837</v>
+        <v>4858738.283078313</v>
       </c>
       <c r="X17" s="4">
         <f>IF(V17=0,0,W17/V17)</f>
         <v>0</v>
       </c>
       <c r="Y17" s="3">
-        <v>2020434.083641439</v>
+        <v>2017724.044351414</v>
       </c>
       <c r="Z17" s="3">
-        <v>41023.30992707051</v>
+        <v>39554.06946016243</v>
       </c>
       <c r="AA17" s="4">
         <f>IF(Y17=0,0,Z17/Y17)</f>
         <v>0</v>
       </c>
       <c r="AB17" s="3">
-        <v>129388.1194588412</v>
+        <v>135303.8994357765</v>
       </c>
       <c r="AC17" s="3">
-        <v>240.9462187315658</v>
+        <v>293.7986247426306</v>
       </c>
       <c r="AD17" s="4">
         <f>IF(AB17=0,0,AC17/AB17)</f>
@@ -1868,30 +1868,30 @@
         <v>0</v>
       </c>
       <c r="I18" s="3">
-        <v>3364.438925828685</v>
+        <v>3364.404821554393</v>
       </c>
       <c r="J18" s="3">
-        <v>100.8518174263639</v>
+        <v>100.8406044416442</v>
       </c>
       <c r="K18" s="4">
         <f>IF(I18=0,0,J18/I18)</f>
         <v>0</v>
       </c>
       <c r="L18" s="3">
-        <v>11328.20246422979</v>
+        <v>11639.06744554709</v>
       </c>
       <c r="M18" s="3">
-        <v>8.672433171365411</v>
+        <v>13.65298159589991</v>
       </c>
       <c r="N18" s="4">
         <f>IF(L18=0,0,M18/L18)</f>
         <v>0</v>
       </c>
       <c r="O18" s="3">
-        <v>193.6283842759436</v>
+        <v>210.8368637670372</v>
       </c>
       <c r="P18" s="3">
-        <v>2.497779431025672</v>
+        <v>2.020924868696747</v>
       </c>
       <c r="Q18" s="4">
         <f>IF(O18=0,0,P18/O18)</f>
@@ -1908,30 +1908,30 @@
         <v>0</v>
       </c>
       <c r="V18" s="3">
-        <v>107061599.7071237</v>
+        <v>107057780.7659875</v>
       </c>
       <c r="W18" s="3">
-        <v>2677646.657504544</v>
+        <v>2679796.374648735</v>
       </c>
       <c r="X18" s="4">
         <f>IF(V18=0,0,W18/V18)</f>
         <v>0</v>
       </c>
       <c r="Y18" s="3">
-        <v>1264893.404914272</v>
+        <v>1277885.722823765</v>
       </c>
       <c r="Z18" s="3">
-        <v>14427.89329205267</v>
+        <v>14853.51614416833</v>
       </c>
       <c r="AA18" s="4">
         <f>IF(Y18=0,0,Z18/Y18)</f>
         <v>0</v>
       </c>
       <c r="AB18" s="3">
-        <v>126400.38634657</v>
+        <v>129863.8085071404</v>
       </c>
       <c r="AC18" s="3">
-        <v>96.37848749259138</v>
+        <v>151.7156832687178</v>
       </c>
       <c r="AD18" s="4">
         <f>IF(AB18=0,0,AC18/AB18)</f>
@@ -2088,30 +2088,30 @@
         <v>0</v>
       </c>
       <c r="I23" s="3">
-        <v>1108.193378484327</v>
+        <v>1108.055716585262</v>
       </c>
       <c r="J23" s="3">
-        <v>152.6620123236948</v>
+        <v>152.8113304434048</v>
       </c>
       <c r="K23" s="4">
         <f>IF(I23=0,0,J23/I23)</f>
         <v>0</v>
       </c>
       <c r="L23" s="3">
-        <v>16899.69278120454</v>
+        <v>17011.801165714</v>
       </c>
       <c r="M23" s="3">
-        <v>114.5281090262048</v>
+        <v>89.60077630843968</v>
       </c>
       <c r="N23" s="4">
         <f>IF(L23=0,0,M23/L23)</f>
         <v>0</v>
       </c>
       <c r="O23" s="3">
-        <v>511.5551891389042</v>
+        <v>549.9985622454193</v>
       </c>
       <c r="P23" s="3">
-        <v>29.39199492819834</v>
+        <v>22.28616294577986</v>
       </c>
       <c r="Q23" s="4">
         <f>IF(O23=0,0,P23/O23)</f>
@@ -2128,30 +2128,30 @@
         <v>0</v>
       </c>
       <c r="V23" s="3">
-        <v>27432336.72224081</v>
+        <v>27431637.53707126</v>
       </c>
       <c r="W23" s="3">
-        <v>2873271.15188776</v>
+        <v>2871705.046079703</v>
       </c>
       <c r="X23" s="4">
         <f>IF(V23=0,0,W23/V23)</f>
         <v>0</v>
       </c>
       <c r="Y23" s="3">
-        <v>2836323.537272255</v>
+        <v>2838841.735003161</v>
       </c>
       <c r="Z23" s="3">
-        <v>110553.4352663648</v>
+        <v>112549.4485840783</v>
       </c>
       <c r="AA23" s="4">
         <f>IF(Y23=0,0,Z23/Y23)</f>
         <v>0</v>
       </c>
       <c r="AB23" s="3">
-        <v>190241.6708006598</v>
+        <v>191414.3297679779</v>
       </c>
       <c r="AC23" s="3">
-        <v>1270.014577409398</v>
+        <v>995.015786015254</v>
       </c>
       <c r="AD23" s="4">
         <f>IF(AB23=0,0,AC23/AB23)</f>
@@ -2185,30 +2185,30 @@
         <v>0</v>
       </c>
       <c r="I24" s="3">
-        <v>948.9557472002688</v>
+        <v>949.118316777312</v>
       </c>
       <c r="J24" s="3">
-        <v>143.0812252068468</v>
+        <v>143.1138573807727</v>
       </c>
       <c r="K24" s="4">
         <f>IF(I24=0,0,J24/I24)</f>
         <v>0</v>
       </c>
       <c r="L24" s="3">
-        <v>16952.10289749463</v>
+        <v>17262.12457025323</v>
       </c>
       <c r="M24" s="3">
-        <v>82.00023356101661</v>
+        <v>83.62756285276636</v>
       </c>
       <c r="N24" s="4">
         <f>IF(L24=0,0,M24/L24)</f>
         <v>0</v>
       </c>
       <c r="O24" s="3">
-        <v>566.8783011556247</v>
+        <v>546.7455795701167</v>
       </c>
       <c r="P24" s="3">
-        <v>25.30581707247754</v>
+        <v>23.62213058602001</v>
       </c>
       <c r="Q24" s="4">
         <f>IF(O24=0,0,P24/O24)</f>
@@ -2225,30 +2225,30 @@
         <v>0</v>
       </c>
       <c r="V24" s="3">
-        <v>24925390.04051472</v>
+        <v>24926729.65305717</v>
       </c>
       <c r="W24" s="3">
-        <v>2981250.104581676</v>
+        <v>2981714.140268512</v>
       </c>
       <c r="X24" s="4">
         <f>IF(V24=0,0,W24/V24)</f>
         <v>0</v>
       </c>
       <c r="Y24" s="3">
-        <v>2726453.333948384</v>
+        <v>2728058.929013245</v>
       </c>
       <c r="Z24" s="3">
-        <v>121420.0766374553</v>
+        <v>120382.214781953</v>
       </c>
       <c r="AA24" s="4">
         <f>IF(Y24=0,0,Z24/Y24)</f>
         <v>0</v>
       </c>
       <c r="AB24" s="3">
-        <v>190795.2668985049</v>
+        <v>194285.3818641235</v>
       </c>
       <c r="AC24" s="3">
-        <v>911.8053376271855</v>
+        <v>928.2471326165542</v>
       </c>
       <c r="AD24" s="4">
         <f>IF(AB24=0,0,AC24/AB24)</f>
@@ -2282,30 +2282,30 @@
         <v>0</v>
       </c>
       <c r="I25" s="3">
-        <v>812.8022893291875</v>
+        <v>812.8399148483488</v>
       </c>
       <c r="J25" s="3">
-        <v>128.7942138943434</v>
+        <v>128.7957158822644</v>
       </c>
       <c r="K25" s="4">
         <f>IF(I25=0,0,J25/I25)</f>
         <v>0</v>
       </c>
       <c r="L25" s="3">
-        <v>13913.05861415759</v>
+        <v>14358.06173102218</v>
       </c>
       <c r="M25" s="3">
-        <v>64.4541206793096</v>
+        <v>47.82929256691225</v>
       </c>
       <c r="N25" s="4">
         <f>IF(L25=0,0,M25/L25)</f>
         <v>0</v>
       </c>
       <c r="O25" s="3">
-        <v>344.6606313647766</v>
+        <v>368.6755302231475</v>
       </c>
       <c r="P25" s="3">
-        <v>10.42967228277575</v>
+        <v>17.95913611626596</v>
       </c>
       <c r="Q25" s="4">
         <f>IF(O25=0,0,P25/O25)</f>
@@ -2322,30 +2322,30 @@
         <v>0</v>
       </c>
       <c r="V25" s="3">
-        <v>22582605.07877934</v>
+        <v>22587787.7184066</v>
       </c>
       <c r="W25" s="3">
-        <v>2940602.784735434</v>
+        <v>2940867.548315275</v>
       </c>
       <c r="X25" s="4">
         <f>IF(V25=0,0,W25/V25)</f>
         <v>0</v>
       </c>
       <c r="Y25" s="3">
-        <v>1847101.289104564</v>
+        <v>1833771.759255057</v>
       </c>
       <c r="Z25" s="3">
-        <v>90869.84835166438</v>
+        <v>90350.91742391349</v>
       </c>
       <c r="AA25" s="4">
         <f>IF(Y25=0,0,Z25/Y25)</f>
         <v>0</v>
       </c>
       <c r="AB25" s="3">
-        <v>156700.260166514</v>
+        <v>161615.9683072457</v>
       </c>
       <c r="AC25" s="3">
-        <v>716.4184795642504</v>
+        <v>530.8922197069915</v>
       </c>
       <c r="AD25" s="4">
         <f>IF(AB25=0,0,AC25/AB25)</f>
@@ -2379,30 +2379,30 @@
         <v>0</v>
       </c>
       <c r="I26" s="3">
-        <v>743.8513994517335</v>
+        <v>743.9010935936449</v>
       </c>
       <c r="J26" s="3">
-        <v>121.7215094544971</v>
+        <v>121.8135940932956</v>
       </c>
       <c r="K26" s="4">
         <f>IF(I26=0,0,J26/I26)</f>
         <v>0</v>
       </c>
       <c r="L26" s="3">
-        <v>11488.16064938751</v>
+        <v>11515.87046614333</v>
       </c>
       <c r="M26" s="3">
-        <v>26.37007743735425</v>
+        <v>29.4853726437483</v>
       </c>
       <c r="N26" s="4">
         <f>IF(L26=0,0,M26/L26)</f>
         <v>0</v>
       </c>
       <c r="O26" s="3">
-        <v>288.1123393639429</v>
+        <v>322.3352502269547</v>
       </c>
       <c r="P26" s="3">
-        <v>9.966017271608406</v>
+        <v>15.34015562439407</v>
       </c>
       <c r="Q26" s="4">
         <f>IF(O26=0,0,P26/O26)</f>
@@ -2419,30 +2419,30 @@
         <v>0</v>
       </c>
       <c r="V26" s="3">
-        <v>21635078.69522292</v>
+        <v>21637527.93050475</v>
       </c>
       <c r="W26" s="3">
-        <v>2936193.364272114</v>
+        <v>2939331.981051177</v>
       </c>
       <c r="X26" s="4">
         <f>IF(V26=0,0,W26/V26)</f>
         <v>0</v>
       </c>
       <c r="Y26" s="3">
-        <v>1653421.300834798</v>
+        <v>1639385.764644713</v>
       </c>
       <c r="Z26" s="3">
-        <v>69657.12327995477</v>
+        <v>70324.08779524639</v>
       </c>
       <c r="AA26" s="4">
         <f>IF(Y26=0,0,Z26/Y26)</f>
         <v>0</v>
       </c>
       <c r="AB26" s="3">
-        <v>129411.2289903838</v>
+        <v>129654.9538778912</v>
       </c>
       <c r="AC26" s="3">
-        <v>293.0802870944754</v>
+        <v>327.3292520279356</v>
       </c>
       <c r="AD26" s="4">
         <f>IF(AB26=0,0,AC26/AB26)</f>
@@ -2476,30 +2476,30 @@
         <v>0</v>
       </c>
       <c r="I27" s="3">
-        <v>534.6642930986926</v>
+        <v>534.7276074530099</v>
       </c>
       <c r="J27" s="3">
-        <v>94.97364885894879</v>
+        <v>94.97372757948976</v>
       </c>
       <c r="K27" s="4">
         <f>IF(I27=0,0,J27/I27)</f>
         <v>0</v>
       </c>
       <c r="L27" s="3">
-        <v>9796.241413112457</v>
+        <v>10051.0537036804</v>
       </c>
       <c r="M27" s="3">
-        <v>23.29433523116261</v>
+        <v>26.25223764907569</v>
       </c>
       <c r="N27" s="4">
         <f>IF(L27=0,0,M27/L27)</f>
         <v>0</v>
       </c>
       <c r="O27" s="3">
-        <v>239.0687784366582</v>
+        <v>226.6668752752476</v>
       </c>
       <c r="P27" s="3">
-        <v>13.46171006701532</v>
+        <v>9.975083572365314</v>
       </c>
       <c r="Q27" s="4">
         <f>IF(O27=0,0,P27/O27)</f>
@@ -2516,30 +2516,30 @@
         <v>0</v>
       </c>
       <c r="V27" s="3">
-        <v>17467369.42520155</v>
+        <v>17469072.97061635</v>
       </c>
       <c r="W27" s="3">
-        <v>2696045.26794249</v>
+        <v>2697278.525443047</v>
       </c>
       <c r="X27" s="4">
         <f>IF(V27=0,0,W27/V27)</f>
         <v>0</v>
       </c>
       <c r="Y27" s="3">
-        <v>1100816.798774998</v>
+        <v>1102531.385602113</v>
       </c>
       <c r="Z27" s="3">
-        <v>51990.69733833149</v>
+        <v>52826.84309652611</v>
       </c>
       <c r="AA27" s="4">
         <f>IF(Y27=0,0,Z27/Y27)</f>
         <v>0</v>
       </c>
       <c r="AB27" s="3">
-        <v>110263.3169002113</v>
+        <v>113172.8675108527</v>
       </c>
       <c r="AC27" s="3">
-        <v>260.5158107506577</v>
+        <v>291.5021697164193</v>
       </c>
       <c r="AD27" s="4">
         <f>IF(AB27=0,0,AC27/AB27)</f>
@@ -2696,30 +2696,30 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>1108.193378484327</v>
+        <v>1108.055716585262</v>
       </c>
       <c r="J32" s="3">
-        <v>12.98011290102196</v>
+        <v>12.96842238628073</v>
       </c>
       <c r="K32" s="4">
         <f>IF(I32=0,0,J32/I32)</f>
         <v>0</v>
       </c>
       <c r="L32" s="3">
-        <v>16899.69278120454</v>
+        <v>17011.801165714</v>
       </c>
       <c r="M32" s="3">
-        <v>5.859440663151443</v>
+        <v>1.612388412721455</v>
       </c>
       <c r="N32" s="4">
         <f>IF(L32=0,0,M32/L32)</f>
         <v>0</v>
       </c>
       <c r="O32" s="3">
-        <v>511.5551891389042</v>
+        <v>549.9985622454193</v>
       </c>
       <c r="P32" s="3">
-        <v>8.079041623072989</v>
+        <v>1.850068818195141</v>
       </c>
       <c r="Q32" s="4">
         <f>IF(O32=0,0,P32/O32)</f>
@@ -2736,30 +2736,30 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
-        <v>27432336.72224081</v>
+        <v>27431637.53707126</v>
       </c>
       <c r="W32" s="3">
-        <v>239615.7856515162</v>
+        <v>238834.02248694</v>
       </c>
       <c r="X32" s="4">
         <f>IF(V32=0,0,W32/V32)</f>
         <v>0</v>
       </c>
       <c r="Y32" s="3">
-        <v>2836323.537272255</v>
+        <v>2838841.735003161</v>
       </c>
       <c r="Z32" s="3">
-        <v>8426.527290755883</v>
+        <v>8224.811193448491</v>
       </c>
       <c r="AA32" s="4">
         <f>IF(Y32=0,0,Z32/Y32)</f>
         <v>0</v>
       </c>
       <c r="AB32" s="3">
-        <v>190241.6708006598</v>
+        <v>191414.3297679779</v>
       </c>
       <c r="AC32" s="3">
-        <v>65.12895268769353</v>
+        <v>17.91354115575086</v>
       </c>
       <c r="AD32" s="4">
         <f>IF(AB32=0,0,AC32/AB32)</f>
@@ -2793,30 +2793,30 @@
         <v>0</v>
       </c>
       <c r="I33" s="3">
-        <v>948.9557472002688</v>
+        <v>949.118316777312</v>
       </c>
       <c r="J33" s="3">
-        <v>15.82301429034479</v>
+        <v>15.83439497350773</v>
       </c>
       <c r="K33" s="4">
         <f>IF(I33=0,0,J33/I33)</f>
         <v>0</v>
       </c>
       <c r="L33" s="3">
-        <v>16952.10289749463</v>
+        <v>17262.12457025323</v>
       </c>
       <c r="M33" s="3">
-        <v>0</v>
+        <v>3.088071183532477</v>
       </c>
       <c r="N33" s="4">
         <f>IF(L33=0,0,M33/L33)</f>
         <v>0</v>
       </c>
       <c r="O33" s="3">
-        <v>566.8783011556247</v>
+        <v>546.7455795701167</v>
       </c>
       <c r="P33" s="3">
-        <v>1.765484009205597</v>
+        <v>2.163429498037091</v>
       </c>
       <c r="Q33" s="4">
         <f>IF(O33=0,0,P33/O33)</f>
@@ -2833,30 +2833,30 @@
         <v>0</v>
       </c>
       <c r="V33" s="3">
-        <v>24925390.04051472</v>
+        <v>24926729.65305717</v>
       </c>
       <c r="W33" s="3">
-        <v>324360.1584538221</v>
+        <v>324457.6168491468</v>
       </c>
       <c r="X33" s="4">
         <f>IF(V33=0,0,W33/V33)</f>
         <v>0</v>
       </c>
       <c r="Y33" s="3">
-        <v>2726453.333948384</v>
+        <v>2728058.929013245</v>
       </c>
       <c r="Z33" s="3">
-        <v>13274.22059702082</v>
+        <v>12538.93288748013</v>
       </c>
       <c r="AA33" s="4">
         <f>IF(Y33=0,0,Z33/Y33)</f>
         <v>0</v>
       </c>
       <c r="AB33" s="3">
-        <v>190795.2668985049</v>
+        <v>194285.3818641235</v>
       </c>
       <c r="AC33" s="3">
-        <v>0</v>
+        <v>34.19857857009629</v>
       </c>
       <c r="AD33" s="4">
         <f>IF(AB33=0,0,AC33/AB33)</f>
@@ -2890,30 +2890,30 @@
         <v>0</v>
       </c>
       <c r="I34" s="3">
-        <v>812.8022893291875</v>
+        <v>812.8399148483488</v>
       </c>
       <c r="J34" s="3">
-        <v>17.28090339141886</v>
+        <v>17.2345983792363</v>
       </c>
       <c r="K34" s="4">
         <f>IF(I34=0,0,J34/I34)</f>
         <v>0</v>
       </c>
       <c r="L34" s="3">
-        <v>13913.05861415759</v>
+        <v>14358.06173102218</v>
       </c>
       <c r="M34" s="3">
-        <v>-0.000567748699337244</v>
+        <v>2.197665334034711</v>
       </c>
       <c r="N34" s="4">
         <f>IF(L34=0,0,M34/L34)</f>
         <v>0</v>
       </c>
       <c r="O34" s="3">
-        <v>344.6606313647766</v>
+        <v>368.6755302231475</v>
       </c>
       <c r="P34" s="3">
-        <v>2.202265903066785</v>
+        <v>1.927282700260461</v>
       </c>
       <c r="Q34" s="4">
         <f>IF(O34=0,0,P34/O34)</f>
@@ -2930,30 +2930,30 @@
         <v>0</v>
       </c>
       <c r="V34" s="3">
-        <v>22582605.07877934</v>
+        <v>22587787.7184066</v>
       </c>
       <c r="W34" s="3">
-        <v>388536.1645939276</v>
+        <v>388017.1677994356</v>
       </c>
       <c r="X34" s="4">
         <f>IF(V34=0,0,W34/V34)</f>
         <v>0</v>
       </c>
       <c r="Y34" s="3">
-        <v>1847101.289104564</v>
+        <v>1833771.759255057</v>
       </c>
       <c r="Z34" s="3">
-        <v>12721.1280721447</v>
+        <v>12224.97154247691</v>
       </c>
       <c r="AA34" s="4">
         <f>IF(Y34=0,0,Z34/Y34)</f>
         <v>0</v>
       </c>
       <c r="AB34" s="3">
-        <v>156700.260166514</v>
+        <v>161615.9683072457</v>
       </c>
       <c r="AC34" s="3">
-        <v>0</v>
+        <v>24.42755612148903</v>
       </c>
       <c r="AD34" s="4">
         <f>IF(AB34=0,0,AC34/AB34)</f>
@@ -2987,30 +2987,30 @@
         <v>0</v>
       </c>
       <c r="I35" s="3">
-        <v>743.8513994517335</v>
+        <v>743.9010935936449</v>
       </c>
       <c r="J35" s="3">
-        <v>18.81659816563327</v>
+        <v>18.88886539927812</v>
       </c>
       <c r="K35" s="4">
         <f>IF(I35=0,0,J35/I35)</f>
         <v>0</v>
       </c>
       <c r="L35" s="3">
-        <v>11488.16064938751</v>
+        <v>11515.87046614333</v>
       </c>
       <c r="M35" s="3">
-        <v>-2.929739271363244</v>
+        <v>2.638893344042823</v>
       </c>
       <c r="N35" s="4">
         <f>IF(L35=0,0,M35/L35)</f>
         <v>0</v>
       </c>
       <c r="O35" s="3">
-        <v>288.1123393639429</v>
+        <v>322.3352502269547</v>
       </c>
       <c r="P35" s="3">
-        <v>3.669197411940724</v>
+        <v>2.3030336125826</v>
       </c>
       <c r="Q35" s="4">
         <f>IF(O35=0,0,P35/O35)</f>
@@ -3027,30 +3027,30 @@
         <v>0</v>
       </c>
       <c r="V35" s="3">
-        <v>21635078.69522292</v>
+        <v>21637527.93050475</v>
       </c>
       <c r="W35" s="3">
-        <v>448804.1554636247</v>
+        <v>449735.9740116</v>
       </c>
       <c r="X35" s="4">
         <f>IF(V35=0,0,W35/V35)</f>
         <v>0</v>
       </c>
       <c r="Y35" s="3">
-        <v>1653421.300834798</v>
+        <v>1639385.764644713</v>
       </c>
       <c r="Z35" s="3">
-        <v>10899.17622549506</v>
+        <v>10788.55772052007</v>
       </c>
       <c r="AA35" s="4">
         <f>IF(Y35=0,0,Z35/Y35)</f>
         <v>0</v>
       </c>
       <c r="AB35" s="3">
-        <v>129411.2289903838</v>
+        <v>129654.9538778912</v>
       </c>
       <c r="AC35" s="3">
-        <v>-32.56447634381766</v>
+        <v>29.31306734577811</v>
       </c>
       <c r="AD35" s="4">
         <f>IF(AB35=0,0,AC35/AB35)</f>
@@ -3084,30 +3084,30 @@
         <v>0</v>
       </c>
       <c r="I36" s="3">
-        <v>534.6642930986926</v>
+        <v>534.7276074530099</v>
       </c>
       <c r="J36" s="3">
-        <v>15.93105861635687</v>
+        <v>15.8855046137232</v>
       </c>
       <c r="K36" s="4">
         <f>IF(I36=0,0,J36/I36)</f>
         <v>0</v>
       </c>
       <c r="L36" s="3">
-        <v>9796.241413112457</v>
+        <v>10051.0537036804</v>
       </c>
       <c r="M36" s="3">
-        <v>11.71944907500595</v>
+        <v>2.796754232564941</v>
       </c>
       <c r="N36" s="4">
         <f>IF(L36=0,0,M36/L36)</f>
         <v>0</v>
       </c>
       <c r="O36" s="3">
-        <v>239.0687784366582</v>
+        <v>226.6668752752476</v>
       </c>
       <c r="P36" s="3">
-        <v>1.726839635706914</v>
+        <v>1.474631430243928</v>
       </c>
       <c r="Q36" s="4">
         <f>IF(O36=0,0,P36/O36)</f>
@@ -3124,30 +3124,30 @@
         <v>0</v>
       </c>
       <c r="V36" s="3">
-        <v>17467369.42520155</v>
+        <v>17469072.97061635</v>
       </c>
       <c r="W36" s="3">
-        <v>446554.1823121533</v>
+        <v>445666.0981375836</v>
       </c>
       <c r="X36" s="4">
         <f>IF(V36=0,0,W36/V36)</f>
         <v>0</v>
       </c>
       <c r="Y36" s="3">
-        <v>1100816.798774998</v>
+        <v>1102531.385602113</v>
       </c>
       <c r="Z36" s="3">
-        <v>9304.968359676423</v>
+        <v>8784.410689204931</v>
       </c>
       <c r="AA36" s="4">
         <f>IF(Y36=0,0,Z36/Y36)</f>
         <v>0</v>
       </c>
       <c r="AB36" s="3">
-        <v>110263.3169002113</v>
+        <v>113172.8675108527</v>
       </c>
       <c r="AC36" s="3">
-        <v>130.2579053753288</v>
+        <v>30.94157108721265</v>
       </c>
       <c r="AD36" s="4">
         <f>IF(AB36=0,0,AC36/AB36)</f>
@@ -3307,7 +3307,7 @@
         <v>382.3073643284127</v>
       </c>
       <c r="J41" s="6">
-        <v>3.356936426061671</v>
+        <v>6.931603770051908</v>
       </c>
       <c r="K41" s="7">
         <f>IF(I41=0,0,J41/I41)</f>
@@ -3347,7 +3347,7 @@
         <v>9070418.669545408</v>
       </c>
       <c r="W41" s="6">
-        <v>78807.32897765189</v>
+        <v>164538.3844167478</v>
       </c>
       <c r="X41" s="7">
         <f>IF(V41=0,0,W41/V41)</f>
@@ -3404,7 +3404,7 @@
         <v>245.090682899663</v>
       </c>
       <c r="J42" s="6">
-        <v>2.9365686601786</v>
+        <v>6.008397319649958</v>
       </c>
       <c r="K42" s="7">
         <f>IF(I42=0,0,J42/I42)</f>
@@ -3444,7 +3444,7 @@
         <v>7100767.677214347</v>
       </c>
       <c r="W42" s="6">
-        <v>91738.12470871955</v>
+        <v>189877.8700925186</v>
       </c>
       <c r="X42" s="7">
         <f>IF(V42=0,0,W42/V42)</f>
@@ -3501,7 +3501,7 @@
         <v>200.4130880433794</v>
       </c>
       <c r="J43" s="6">
-        <v>3.271171722685744</v>
+        <v>6.648335109332984</v>
       </c>
       <c r="K43" s="7">
         <f>IF(I43=0,0,J43/I43)</f>
@@ -3541,7 +3541,7 @@
         <v>6292834.208210533</v>
       </c>
       <c r="W43" s="6">
-        <v>108314.0966329305</v>
+        <v>222967.1563095488</v>
       </c>
       <c r="X43" s="7">
         <f>IF(V43=0,0,W43/V43)</f>
@@ -3598,7 +3598,7 @@
         <v>193.9015574705648</v>
       </c>
       <c r="J44" s="6">
-        <v>1.247128400560556</v>
+        <v>2.593667459385906</v>
       </c>
       <c r="K44" s="7">
         <f>IF(I44=0,0,J44/I44)</f>
@@ -3638,7 +3638,7 @@
         <v>6053045.584847068</v>
       </c>
       <c r="W44" s="6">
-        <v>44071.79961647</v>
+        <v>92120.66669745091</v>
       </c>
       <c r="X44" s="7">
         <f>IF(V44=0,0,W44/V44)</f>
@@ -3695,7 +3695,7 @@
         <v>136.6145524202559</v>
       </c>
       <c r="J45" s="6">
-        <v>0.9404859014340036</v>
+        <v>1.96286239209451</v>
       </c>
       <c r="K45" s="7">
         <f>IF(I45=0,0,J45/I45)</f>
@@ -3735,7 +3735,7 @@
         <v>4890905.466101354</v>
       </c>
       <c r="W45" s="6">
-        <v>36723.80325047113</v>
+        <v>76901.85631352663</v>
       </c>
       <c r="X45" s="7">
         <f>IF(V45=0,0,W45/V45)</f>
@@ -3915,7 +3915,7 @@
         <v>382.3073643284127</v>
       </c>
       <c r="J50" s="6">
-        <v>12.60698597415583</v>
+        <v>24.23689331551536</v>
       </c>
       <c r="K50" s="7">
         <f>IF(I50=0,0,J50/I50)</f>
@@ -3955,7 +3955,7 @@
         <v>9070418.669545408</v>
       </c>
       <c r="W50" s="6">
-        <v>304695.9033628255</v>
+        <v>608963.1786537524</v>
       </c>
       <c r="X50" s="7">
         <f>IF(V50=0,0,W50/V50)</f>
@@ -4012,7 +4012,7 @@
         <v>245.090682899663</v>
       </c>
       <c r="J51" s="6">
-        <v>10.76043447512289</v>
+        <v>19.96254009473606</v>
       </c>
       <c r="K51" s="7">
         <f>IF(I51=0,0,J51/I51)</f>
@@ -4052,7 +4052,7 @@
         <v>7100767.677214347</v>
       </c>
       <c r="W51" s="6">
-        <v>346368.6063864464</v>
+        <v>667327.7781731561</v>
       </c>
       <c r="X51" s="7">
         <f>IF(V51=0,0,W51/V51)</f>
@@ -4109,7 +4109,7 @@
         <v>200.4130880433794</v>
       </c>
       <c r="J52" s="6">
-        <v>11.7730736107835</v>
+        <v>21.28849801111122</v>
       </c>
       <c r="K52" s="7">
         <f>IF(I52=0,0,J52/I52)</f>
@@ -4149,7 +4149,7 @@
         <v>6292834.208210533</v>
       </c>
       <c r="W52" s="6">
-        <v>402841.1074284222</v>
+        <v>757796.3406777447</v>
       </c>
       <c r="X52" s="7">
         <f>IF(V52=0,0,W52/V52)</f>
@@ -4206,7 +4206,7 @@
         <v>193.9015574705648</v>
       </c>
       <c r="J53" s="6">
-        <v>4.775947591036063</v>
+        <v>9.462193079037592</v>
       </c>
       <c r="K53" s="7">
         <f>IF(I53=0,0,J53/I53)</f>
@@ -4246,7 +4246,7 @@
         <v>6053045.584847068</v>
       </c>
       <c r="W53" s="6">
-        <v>171043.9846910052</v>
+        <v>345144.5598841952</v>
       </c>
       <c r="X53" s="7">
         <f>IF(V53=0,0,W53/V53)</f>
@@ -4303,7 +4303,7 @@
         <v>136.6145524202559</v>
       </c>
       <c r="J54" s="6">
-        <v>3.636206208529707</v>
+        <v>7.307984633459724</v>
       </c>
       <c r="K54" s="7">
         <f>IF(I54=0,0,J54/I54)</f>
@@ -4343,7 +4343,7 @@
         <v>4890905.466101354</v>
       </c>
       <c r="W54" s="6">
-        <v>143249.1869890932</v>
+        <v>291466.352394985</v>
       </c>
       <c r="X54" s="7">
         <f>IF(V54=0,0,W54/V54)</f>

--- a/5000_analyze_results/results_spreadsheet.xlsx
+++ b/5000_analyze_results/results_spreadsheet.xlsx
@@ -882,10 +882,10 @@
         <v>0</v>
       </c>
       <c r="L5" s="3">
-        <v>17573.82651946129</v>
+        <v>17935.27995420955</v>
       </c>
       <c r="M5" s="3">
-        <v>52.43127107270062</v>
+        <v>51.79140364386141</v>
       </c>
       <c r="N5" s="4">
         <f>IF(L5=0,0,M5/L5)</f>
@@ -932,10 +932,10 @@
         <v>0</v>
       </c>
       <c r="AB5" s="3">
-        <v>196057.6019358347</v>
+        <v>200072.0470788344</v>
       </c>
       <c r="AC5" s="3">
-        <v>582.7808785878588</v>
+        <v>575.5563222417259</v>
       </c>
       <c r="AD5" s="4">
         <f>IF(AB5=0,0,AC5/AB5)</f>
@@ -979,10 +979,10 @@
         <v>0</v>
       </c>
       <c r="L6" s="3">
-        <v>14652.1253505373</v>
+        <v>14938.0946218137</v>
       </c>
       <c r="M6" s="3">
-        <v>33.36611404703743</v>
+        <v>39.87119663484022</v>
       </c>
       <c r="N6" s="4">
         <f>IF(L6=0,0,M6/L6)</f>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="AB6" s="3">
-        <v>163455.5873311974</v>
+        <v>166631.983938046</v>
       </c>
       <c r="AC6" s="3">
-        <v>370.860559101362</v>
+        <v>443.1061225626618</v>
       </c>
       <c r="AD6" s="4">
         <f>IF(AB6=0,0,AC6/AB6)</f>
@@ -1076,10 +1076,10 @@
         <v>0</v>
       </c>
       <c r="L7" s="3">
-        <v>12980.21700838298</v>
+        <v>13234.92997176094</v>
       </c>
       <c r="M7" s="3">
-        <v>28.82879728573933</v>
+        <v>30.1158939311821</v>
       </c>
       <c r="N7" s="4">
         <f>IF(L7=0,0,M7/L7)</f>
@@ -1126,10 +1126,10 @@
         <v>0</v>
       </c>
       <c r="AB7" s="3">
-        <v>144811.4155872839</v>
+        <v>147641.0334895182</v>
       </c>
       <c r="AC7" s="3">
-        <v>320.2886646784609</v>
+        <v>334.7377773706976</v>
       </c>
       <c r="AD7" s="4">
         <f>IF(AB7=0,0,AC7/AB7)</f>
@@ -1173,10 +1173,10 @@
         <v>0</v>
       </c>
       <c r="L8" s="3">
-        <v>12127.30661114934</v>
+        <v>12362.34693163964</v>
       </c>
       <c r="M8" s="3">
-        <v>26.43375170142017</v>
+        <v>21.66686408916116</v>
       </c>
       <c r="N8" s="4">
         <f>IF(L8=0,0,M8/L8)</f>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="AB8" s="3">
-        <v>135303.8994357765</v>
+        <v>137914.3724621782</v>
       </c>
       <c r="AC8" s="3">
-        <v>293.7986247426306</v>
+        <v>240.8185448710283</v>
       </c>
       <c r="AD8" s="4">
         <f>IF(AB8=0,0,AC8/AB8)</f>
@@ -1270,10 +1270,10 @@
         <v>0</v>
       </c>
       <c r="L9" s="3">
-        <v>11639.06744554709</v>
+        <v>11834.18418972814</v>
       </c>
       <c r="M9" s="3">
-        <v>13.65298159589991</v>
+        <v>9.966248810512946</v>
       </c>
       <c r="N9" s="4">
         <f>IF(L9=0,0,M9/L9)</f>
@@ -1320,10 +1320,10 @@
         <v>0</v>
       </c>
       <c r="AB9" s="3">
-        <v>129863.8085071404</v>
+        <v>132031.1754109795</v>
       </c>
       <c r="AC9" s="3">
-        <v>151.7156832687178</v>
+        <v>110.7765306406654</v>
       </c>
       <c r="AD9" s="4">
         <f>IF(AB9=0,0,AC9/AB9)</f>
@@ -1490,10 +1490,10 @@
         <v>0</v>
       </c>
       <c r="L14" s="3">
-        <v>17573.82651946129</v>
+        <v>17935.27995420955</v>
       </c>
       <c r="M14" s="3">
-        <v>52.43127107270062</v>
+        <v>51.79140364386141</v>
       </c>
       <c r="N14" s="4">
         <f>IF(L14=0,0,M14/L14)</f>
@@ -1540,10 +1540,10 @@
         <v>0</v>
       </c>
       <c r="AB14" s="3">
-        <v>196057.6019358347</v>
+        <v>200072.0470788344</v>
       </c>
       <c r="AC14" s="3">
-        <v>582.7808785878588</v>
+        <v>575.5563222417259</v>
       </c>
       <c r="AD14" s="4">
         <f>IF(AB14=0,0,AC14/AB14)</f>
@@ -1587,10 +1587,10 @@
         <v>0</v>
       </c>
       <c r="L15" s="3">
-        <v>14652.1253505373</v>
+        <v>14938.0946218137</v>
       </c>
       <c r="M15" s="3">
-        <v>33.36611404703743</v>
+        <v>39.87119663484022</v>
       </c>
       <c r="N15" s="4">
         <f>IF(L15=0,0,M15/L15)</f>
@@ -1637,10 +1637,10 @@
         <v>0</v>
       </c>
       <c r="AB15" s="3">
-        <v>163455.5873311974</v>
+        <v>166631.983938046</v>
       </c>
       <c r="AC15" s="3">
-        <v>370.860559101362</v>
+        <v>443.1061225626618</v>
       </c>
       <c r="AD15" s="4">
         <f>IF(AB15=0,0,AC15/AB15)</f>
@@ -1684,10 +1684,10 @@
         <v>0</v>
       </c>
       <c r="L16" s="3">
-        <v>12980.21700838298</v>
+        <v>13234.92997176094</v>
       </c>
       <c r="M16" s="3">
-        <v>28.82879728573933</v>
+        <v>30.1158939311821</v>
       </c>
       <c r="N16" s="4">
         <f>IF(L16=0,0,M16/L16)</f>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="AB16" s="3">
-        <v>144811.4155872839</v>
+        <v>147641.0334895182</v>
       </c>
       <c r="AC16" s="3">
-        <v>320.2886646784609</v>
+        <v>334.7377773706976</v>
       </c>
       <c r="AD16" s="4">
         <f>IF(AB16=0,0,AC16/AB16)</f>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="L17" s="3">
-        <v>12127.30661114934</v>
+        <v>12362.34693163964</v>
       </c>
       <c r="M17" s="3">
-        <v>26.43375170142017</v>
+        <v>21.66686408916116</v>
       </c>
       <c r="N17" s="4">
         <f>IF(L17=0,0,M17/L17)</f>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AB17" s="3">
-        <v>135303.8994357765</v>
+        <v>137914.3724621782</v>
       </c>
       <c r="AC17" s="3">
-        <v>293.7986247426306</v>
+        <v>240.8185448710283</v>
       </c>
       <c r="AD17" s="4">
         <f>IF(AB17=0,0,AC17/AB17)</f>
@@ -1878,10 +1878,10 @@
         <v>0</v>
       </c>
       <c r="L18" s="3">
-        <v>11639.06744554709</v>
+        <v>11834.18418972814</v>
       </c>
       <c r="M18" s="3">
-        <v>13.65298159589991</v>
+        <v>9.966248810512946</v>
       </c>
       <c r="N18" s="4">
         <f>IF(L18=0,0,M18/L18)</f>
@@ -1928,10 +1928,10 @@
         <v>0</v>
       </c>
       <c r="AB18" s="3">
-        <v>129863.8085071404</v>
+        <v>132031.1754109795</v>
       </c>
       <c r="AC18" s="3">
-        <v>151.7156832687178</v>
+        <v>110.7765306406654</v>
       </c>
       <c r="AD18" s="4">
         <f>IF(AB18=0,0,AC18/AB18)</f>
@@ -2088,30 +2088,30 @@
         <v>0</v>
       </c>
       <c r="I23" s="3">
-        <v>1108.055716585262</v>
+        <v>1006.030531365336</v>
       </c>
       <c r="J23" s="3">
-        <v>152.8113304434048</v>
+        <v>137.7016734290448</v>
       </c>
       <c r="K23" s="4">
         <f>IF(I23=0,0,J23/I23)</f>
         <v>0</v>
       </c>
       <c r="L23" s="3">
-        <v>17011.801165714</v>
+        <v>15508.35321860747</v>
       </c>
       <c r="M23" s="3">
-        <v>89.60077630843968</v>
+        <v>69.41307935650087</v>
       </c>
       <c r="N23" s="4">
         <f>IF(L23=0,0,M23/L23)</f>
         <v>0</v>
       </c>
       <c r="O23" s="3">
-        <v>549.9985622454193</v>
+        <v>489.4651924619991</v>
       </c>
       <c r="P23" s="3">
-        <v>22.28616294577986</v>
+        <v>17.50721234002186</v>
       </c>
       <c r="Q23" s="4">
         <f>IF(O23=0,0,P23/O23)</f>
@@ -2128,30 +2128,30 @@
         <v>0</v>
       </c>
       <c r="V23" s="3">
-        <v>27431637.53707126</v>
+        <v>24943983.83125177</v>
       </c>
       <c r="W23" s="3">
-        <v>2871705.046079703</v>
+        <v>2711534.335743245</v>
       </c>
       <c r="X23" s="4">
         <f>IF(V23=0,0,W23/V23)</f>
         <v>0</v>
       </c>
       <c r="Y23" s="3">
-        <v>2838841.735003161</v>
+        <v>2560969.677248245</v>
       </c>
       <c r="Z23" s="3">
-        <v>112549.4485840783</v>
+        <v>106489.8319512471</v>
       </c>
       <c r="AA23" s="4">
         <f>IF(Y23=0,0,Z23/Y23)</f>
         <v>0</v>
       </c>
       <c r="AB23" s="3">
-        <v>191414.3297679779</v>
+        <v>174653.7692611545</v>
       </c>
       <c r="AC23" s="3">
-        <v>995.015786015254</v>
+        <v>770.2822696975782</v>
       </c>
       <c r="AD23" s="4">
         <f>IF(AB23=0,0,AC23/AB23)</f>
@@ -2185,30 +2185,30 @@
         <v>0</v>
       </c>
       <c r="I24" s="3">
-        <v>949.118316777312</v>
+        <v>964.635763828982</v>
       </c>
       <c r="J24" s="3">
-        <v>143.1138573807727</v>
+        <v>140.6393015231089</v>
       </c>
       <c r="K24" s="4">
         <f>IF(I24=0,0,J24/I24)</f>
         <v>0</v>
       </c>
       <c r="L24" s="3">
-        <v>17262.12457025323</v>
+        <v>16011.09974104909</v>
       </c>
       <c r="M24" s="3">
-        <v>83.62756285276636</v>
+        <v>65.18596044688859</v>
       </c>
       <c r="N24" s="4">
         <f>IF(L24=0,0,M24/L24)</f>
         <v>0</v>
       </c>
       <c r="O24" s="3">
-        <v>546.7455795701167</v>
+        <v>434.0130658424808</v>
       </c>
       <c r="P24" s="3">
-        <v>23.62213058602001</v>
+        <v>23.55264100846788</v>
       </c>
       <c r="Q24" s="4">
         <f>IF(O24=0,0,P24/O24)</f>
@@ -2225,30 +2225,30 @@
         <v>0</v>
       </c>
       <c r="V24" s="3">
-        <v>24926729.65305717</v>
+        <v>24664123.92119449</v>
       </c>
       <c r="W24" s="3">
-        <v>2981714.140268512</v>
+        <v>2871099.152244043</v>
       </c>
       <c r="X24" s="4">
         <f>IF(V24=0,0,W24/V24)</f>
         <v>0</v>
       </c>
       <c r="Y24" s="3">
-        <v>2728058.929013245</v>
+        <v>2158754.286187634</v>
       </c>
       <c r="Z24" s="3">
-        <v>120382.214781953</v>
+        <v>104503.5790898548</v>
       </c>
       <c r="AA24" s="4">
         <f>IF(Y24=0,0,Z24/Y24)</f>
         <v>0</v>
       </c>
       <c r="AB24" s="3">
-        <v>194285.3818641235</v>
+        <v>180322.590785081</v>
       </c>
       <c r="AC24" s="3">
-        <v>928.2471326165542</v>
+        <v>723.0556611960346</v>
       </c>
       <c r="AD24" s="4">
         <f>IF(AB24=0,0,AC24/AB24)</f>
@@ -2282,30 +2282,30 @@
         <v>0</v>
       </c>
       <c r="I25" s="3">
-        <v>812.8399148483488</v>
+        <v>794.0335099241948</v>
       </c>
       <c r="J25" s="3">
-        <v>128.7957158822644</v>
+        <v>130.4479592776196</v>
       </c>
       <c r="K25" s="4">
         <f>IF(I25=0,0,J25/I25)</f>
         <v>0</v>
       </c>
       <c r="L25" s="3">
-        <v>14358.06173102218</v>
+        <v>14053.45528341239</v>
       </c>
       <c r="M25" s="3">
-        <v>47.82929256691225</v>
+        <v>41.82331183696166</v>
       </c>
       <c r="N25" s="4">
         <f>IF(L25=0,0,M25/L25)</f>
         <v>0</v>
       </c>
       <c r="O25" s="3">
-        <v>368.6755302231475</v>
+        <v>416.2346518831183</v>
       </c>
       <c r="P25" s="3">
-        <v>17.95913611626596</v>
+        <v>18.87297791093762</v>
       </c>
       <c r="Q25" s="4">
         <f>IF(O25=0,0,P25/O25)</f>
@@ -2322,30 +2322,30 @@
         <v>0</v>
       </c>
       <c r="V25" s="3">
-        <v>22587787.7184066</v>
+        <v>22724255.81598294</v>
       </c>
       <c r="W25" s="3">
-        <v>2940867.548315275</v>
+        <v>3049970.807713103</v>
       </c>
       <c r="X25" s="4">
         <f>IF(V25=0,0,W25/V25)</f>
         <v>0</v>
       </c>
       <c r="Y25" s="3">
-        <v>1833771.759255057</v>
+        <v>2072058.659656062</v>
       </c>
       <c r="Z25" s="3">
-        <v>90350.91742391349</v>
+        <v>98196.69756354927</v>
       </c>
       <c r="AA25" s="4">
         <f>IF(Y25=0,0,Z25/Y25)</f>
         <v>0</v>
       </c>
       <c r="AB25" s="3">
-        <v>161615.9683072457</v>
+        <v>158254.736584929</v>
       </c>
       <c r="AC25" s="3">
-        <v>530.8922197069915</v>
+        <v>464.1235663082625</v>
       </c>
       <c r="AD25" s="4">
         <f>IF(AB25=0,0,AC25/AB25)</f>
@@ -2379,30 +2379,30 @@
         <v>0</v>
       </c>
       <c r="I26" s="3">
-        <v>743.9010935936449</v>
+        <v>721.6901097134873</v>
       </c>
       <c r="J26" s="3">
-        <v>121.8135940932956</v>
+        <v>122.2583434718093</v>
       </c>
       <c r="K26" s="4">
         <f>IF(I26=0,0,J26/I26)</f>
         <v>0</v>
       </c>
       <c r="L26" s="3">
-        <v>11515.87046614333</v>
+        <v>12426.67038256435</v>
       </c>
       <c r="M26" s="3">
-        <v>29.4853726437483</v>
+        <v>31.56021921042912</v>
       </c>
       <c r="N26" s="4">
         <f>IF(L26=0,0,M26/L26)</f>
         <v>0</v>
       </c>
       <c r="O26" s="3">
-        <v>322.3352502269547</v>
+        <v>408.4416891589786</v>
       </c>
       <c r="P26" s="3">
-        <v>15.34015562439407</v>
+        <v>17.98217159471451</v>
       </c>
       <c r="Q26" s="4">
         <f>IF(O26=0,0,P26/O26)</f>
@@ -2419,30 +2419,30 @@
         <v>0</v>
       </c>
       <c r="V26" s="3">
-        <v>21637527.93050475</v>
+        <v>21494889.54934806</v>
       </c>
       <c r="W26" s="3">
-        <v>2939331.981051177</v>
+        <v>3023372.087489758</v>
       </c>
       <c r="X26" s="4">
         <f>IF(V26=0,0,W26/V26)</f>
         <v>0</v>
       </c>
       <c r="Y26" s="3">
-        <v>1639385.764644713</v>
+        <v>2032784.210161714</v>
       </c>
       <c r="Z26" s="3">
-        <v>70324.08779524639</v>
+        <v>81138.67339928937</v>
       </c>
       <c r="AA26" s="4">
         <f>IF(Y26=0,0,Z26/Y26)</f>
         <v>0</v>
       </c>
       <c r="AB26" s="3">
-        <v>129654.9538778912</v>
+        <v>139955.2400424519</v>
       </c>
       <c r="AC26" s="3">
-        <v>327.3292520279356</v>
+        <v>350.1283044079901</v>
       </c>
       <c r="AD26" s="4">
         <f>IF(AB26=0,0,AC26/AB26)</f>
@@ -2476,30 +2476,30 @@
         <v>0</v>
       </c>
       <c r="I27" s="3">
-        <v>534.7276074530099</v>
+        <v>613.5011676610787</v>
       </c>
       <c r="J27" s="3">
-        <v>94.97372757948976</v>
+        <v>110.1809203461102</v>
       </c>
       <c r="K27" s="4">
         <f>IF(I27=0,0,J27/I27)</f>
         <v>0</v>
       </c>
       <c r="L27" s="3">
-        <v>10051.0537036804</v>
+        <v>9448.065592686806</v>
       </c>
       <c r="M27" s="3">
-        <v>26.25223764907569</v>
+        <v>21.28188721634261</v>
       </c>
       <c r="N27" s="4">
         <f>IF(L27=0,0,M27/L27)</f>
         <v>0</v>
       </c>
       <c r="O27" s="3">
-        <v>226.6668752752476</v>
+        <v>284.4883780056052</v>
       </c>
       <c r="P27" s="3">
-        <v>9.975083572365314</v>
+        <v>14.14908918231103</v>
       </c>
       <c r="Q27" s="4">
         <f>IF(O27=0,0,P27/O27)</f>
@@ -2516,30 +2516,30 @@
         <v>0</v>
       </c>
       <c r="V27" s="3">
-        <v>17469072.97061635</v>
+        <v>20021735.0102083</v>
       </c>
       <c r="W27" s="3">
-        <v>2697278.525443047</v>
+        <v>3026591.775948588</v>
       </c>
       <c r="X27" s="4">
         <f>IF(V27=0,0,W27/V27)</f>
         <v>0</v>
       </c>
       <c r="Y27" s="3">
-        <v>1102531.385602113</v>
+        <v>1396693.644957343</v>
       </c>
       <c r="Z27" s="3">
-        <v>52826.84309652611</v>
+        <v>67914.88182659587</v>
       </c>
       <c r="AA27" s="4">
         <f>IF(Y27=0,0,Z27/Y27)</f>
         <v>0</v>
       </c>
       <c r="AB27" s="3">
-        <v>113172.8675108527</v>
+        <v>106414.5769839078</v>
       </c>
       <c r="AC27" s="3">
-        <v>291.5021697164193</v>
+        <v>236.1330425077176</v>
       </c>
       <c r="AD27" s="4">
         <f>IF(AB27=0,0,AC27/AB27)</f>
@@ -2696,30 +2696,30 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>1108.055716585262</v>
+        <v>1006.030531365336</v>
       </c>
       <c r="J32" s="3">
-        <v>12.96842238628073</v>
+        <v>11.68607680639857</v>
       </c>
       <c r="K32" s="4">
         <f>IF(I32=0,0,J32/I32)</f>
         <v>0</v>
       </c>
       <c r="L32" s="3">
-        <v>17011.801165714</v>
+        <v>15508.35321860747</v>
       </c>
       <c r="M32" s="3">
-        <v>1.612388412721455</v>
+        <v>1.175133258519694</v>
       </c>
       <c r="N32" s="4">
         <f>IF(L32=0,0,M32/L32)</f>
         <v>0</v>
       </c>
       <c r="O32" s="3">
-        <v>549.9985622454193</v>
+        <v>489.4651924619991</v>
       </c>
       <c r="P32" s="3">
-        <v>1.850068818195141</v>
+        <v>1.322742544303008</v>
       </c>
       <c r="Q32" s="4">
         <f>IF(O32=0,0,P32/O32)</f>
@@ -2736,30 +2736,30 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
-        <v>27431637.53707126</v>
+        <v>24943983.83125177</v>
       </c>
       <c r="W32" s="3">
-        <v>238834.02248694</v>
+        <v>226783.7306828722</v>
       </c>
       <c r="X32" s="4">
         <f>IF(V32=0,0,W32/V32)</f>
         <v>0</v>
       </c>
       <c r="Y32" s="3">
-        <v>2838841.735003161</v>
+        <v>2560969.677248245</v>
       </c>
       <c r="Z32" s="3">
-        <v>8224.811193448491</v>
+        <v>7736.78837738093</v>
       </c>
       <c r="AA32" s="4">
         <f>IF(Y32=0,0,Z32/Y32)</f>
         <v>0</v>
       </c>
       <c r="AB32" s="3">
-        <v>191414.3297679779</v>
+        <v>174653.7692611545</v>
       </c>
       <c r="AC32" s="3">
-        <v>17.91354115575086</v>
+        <v>13.02802993147634</v>
       </c>
       <c r="AD32" s="4">
         <f>IF(AB32=0,0,AC32/AB32)</f>
@@ -2793,30 +2793,30 @@
         <v>0</v>
       </c>
       <c r="I33" s="3">
-        <v>949.118316777312</v>
+        <v>964.635763828982</v>
       </c>
       <c r="J33" s="3">
-        <v>15.83439497350773</v>
+        <v>15.53968362151366</v>
       </c>
       <c r="K33" s="4">
         <f>IF(I33=0,0,J33/I33)</f>
         <v>0</v>
       </c>
       <c r="L33" s="3">
-        <v>17262.12457025323</v>
+        <v>16011.09974104909</v>
       </c>
       <c r="M33" s="3">
-        <v>3.088071183532477</v>
+        <v>1.781353609535843</v>
       </c>
       <c r="N33" s="4">
         <f>IF(L33=0,0,M33/L33)</f>
         <v>0</v>
       </c>
       <c r="O33" s="3">
-        <v>546.7455795701167</v>
+        <v>434.0130658424808</v>
       </c>
       <c r="P33" s="3">
-        <v>2.163429498037091</v>
+        <v>1.743656035621534</v>
       </c>
       <c r="Q33" s="4">
         <f>IF(O33=0,0,P33/O33)</f>
@@ -2833,30 +2833,30 @@
         <v>0</v>
       </c>
       <c r="V33" s="3">
-        <v>24926729.65305717</v>
+        <v>24664123.92119449</v>
       </c>
       <c r="W33" s="3">
-        <v>324457.6168491468</v>
+        <v>312466.3625391275</v>
       </c>
       <c r="X33" s="4">
         <f>IF(V33=0,0,W33/V33)</f>
         <v>0</v>
       </c>
       <c r="Y33" s="3">
-        <v>2728058.929013245</v>
+        <v>2158754.286187634</v>
       </c>
       <c r="Z33" s="3">
-        <v>12538.93288748013</v>
+        <v>10969.12616246473</v>
       </c>
       <c r="AA33" s="4">
         <f>IF(Y33=0,0,Z33/Y33)</f>
         <v>0</v>
       </c>
       <c r="AB33" s="3">
-        <v>194285.3818641235</v>
+        <v>180322.590785081</v>
       </c>
       <c r="AC33" s="3">
-        <v>34.19857857009629</v>
+        <v>19.54204489718541</v>
       </c>
       <c r="AD33" s="4">
         <f>IF(AB33=0,0,AC33/AB33)</f>
@@ -2890,30 +2890,30 @@
         <v>0</v>
       </c>
       <c r="I34" s="3">
-        <v>812.8399148483488</v>
+        <v>794.0335099241948</v>
       </c>
       <c r="J34" s="3">
-        <v>17.2345983792363</v>
+        <v>17.47400642631936</v>
       </c>
       <c r="K34" s="4">
         <f>IF(I34=0,0,J34/I34)</f>
         <v>0</v>
       </c>
       <c r="L34" s="3">
-        <v>14358.06173102218</v>
+        <v>14053.45528341239</v>
       </c>
       <c r="M34" s="3">
-        <v>2.197665334034711</v>
+        <v>2.34422612186335</v>
       </c>
       <c r="N34" s="4">
         <f>IF(L34=0,0,M34/L34)</f>
         <v>0</v>
       </c>
       <c r="O34" s="3">
-        <v>368.6755302231475</v>
+        <v>416.2346518831183</v>
       </c>
       <c r="P34" s="3">
-        <v>1.927282700260461</v>
+        <v>2.377086763853033</v>
       </c>
       <c r="Q34" s="4">
         <f>IF(O34=0,0,P34/O34)</f>
@@ -2930,30 +2930,30 @@
         <v>0</v>
       </c>
       <c r="V34" s="3">
-        <v>22587787.7184066</v>
+        <v>22724255.81598294</v>
       </c>
       <c r="W34" s="3">
-        <v>388017.1677994356</v>
+        <v>402460.4812298082</v>
       </c>
       <c r="X34" s="4">
         <f>IF(V34=0,0,W34/V34)</f>
         <v>0</v>
       </c>
       <c r="Y34" s="3">
-        <v>1833771.759255057</v>
+        <v>2072058.659656062</v>
       </c>
       <c r="Z34" s="3">
-        <v>12224.97154247691</v>
+        <v>13201.0171746104</v>
       </c>
       <c r="AA34" s="4">
         <f>IF(Y34=0,0,Z34/Y34)</f>
         <v>0</v>
       </c>
       <c r="AB34" s="3">
-        <v>161615.9683072457</v>
+        <v>158254.736584929</v>
       </c>
       <c r="AC34" s="3">
-        <v>24.42755612148903</v>
+        <v>26.05605986292358</v>
       </c>
       <c r="AD34" s="4">
         <f>IF(AB34=0,0,AC34/AB34)</f>
@@ -2987,30 +2987,30 @@
         <v>0</v>
       </c>
       <c r="I35" s="3">
-        <v>743.9010935936449</v>
+        <v>721.6901097134873</v>
       </c>
       <c r="J35" s="3">
-        <v>18.88886539927812</v>
+        <v>18.98792808560363</v>
       </c>
       <c r="K35" s="4">
         <f>IF(I35=0,0,J35/I35)</f>
         <v>0</v>
       </c>
       <c r="L35" s="3">
-        <v>11515.87046614333</v>
+        <v>12426.67038256435</v>
       </c>
       <c r="M35" s="3">
-        <v>2.638893344042823</v>
+        <v>2.490720905642957</v>
       </c>
       <c r="N35" s="4">
         <f>IF(L35=0,0,M35/L35)</f>
         <v>0</v>
       </c>
       <c r="O35" s="3">
-        <v>322.3352502269547</v>
+        <v>408.4416891589786</v>
       </c>
       <c r="P35" s="3">
-        <v>2.3030336125826</v>
+        <v>3.220887604453601</v>
       </c>
       <c r="Q35" s="4">
         <f>IF(O35=0,0,P35/O35)</f>
@@ -3027,30 +3027,30 @@
         <v>0</v>
       </c>
       <c r="V35" s="3">
-        <v>21637527.93050475</v>
+        <v>21494889.54934806</v>
       </c>
       <c r="W35" s="3">
-        <v>449735.9740116</v>
+        <v>462770.4463554397</v>
       </c>
       <c r="X35" s="4">
         <f>IF(V35=0,0,W35/V35)</f>
         <v>0</v>
       </c>
       <c r="Y35" s="3">
-        <v>1639385.764644713</v>
+        <v>2032784.210161714</v>
       </c>
       <c r="Z35" s="3">
-        <v>10788.55772052007</v>
+        <v>12594.24213996739</v>
       </c>
       <c r="AA35" s="4">
         <f>IF(Y35=0,0,Z35/Y35)</f>
         <v>0</v>
       </c>
       <c r="AB35" s="3">
-        <v>129654.9538778912</v>
+        <v>139955.2400424519</v>
       </c>
       <c r="AC35" s="3">
-        <v>29.31306734577811</v>
+        <v>27.68456360435812</v>
       </c>
       <c r="AD35" s="4">
         <f>IF(AB35=0,0,AC35/AB35)</f>
@@ -3084,30 +3084,30 @@
         <v>0</v>
       </c>
       <c r="I36" s="3">
-        <v>534.7276074530099</v>
+        <v>613.5011676610787</v>
       </c>
       <c r="J36" s="3">
-        <v>15.8855046137232</v>
+        <v>18.4046604282771</v>
       </c>
       <c r="K36" s="4">
         <f>IF(I36=0,0,J36/I36)</f>
         <v>0</v>
       </c>
       <c r="L36" s="3">
-        <v>10051.0537036804</v>
+        <v>9448.065592686806</v>
       </c>
       <c r="M36" s="3">
-        <v>2.796754232564941</v>
+        <v>1.760577471522614</v>
       </c>
       <c r="N36" s="4">
         <f>IF(L36=0,0,M36/L36)</f>
         <v>0</v>
       </c>
       <c r="O36" s="3">
-        <v>226.6668752752476</v>
+        <v>284.4883780056052</v>
       </c>
       <c r="P36" s="3">
-        <v>1.474631430243928</v>
+        <v>2.601356038767728</v>
       </c>
       <c r="Q36" s="4">
         <f>IF(O36=0,0,P36/O36)</f>
@@ -3124,30 +3124,30 @@
         <v>0</v>
       </c>
       <c r="V36" s="3">
-        <v>17469072.97061635</v>
+        <v>20021735.0102083</v>
       </c>
       <c r="W36" s="3">
-        <v>445666.0981375836</v>
+        <v>498447.049526915</v>
       </c>
       <c r="X36" s="4">
         <f>IF(V36=0,0,W36/V36)</f>
         <v>0</v>
       </c>
       <c r="Y36" s="3">
-        <v>1102531.385602113</v>
+        <v>1396693.644957343</v>
       </c>
       <c r="Z36" s="3">
-        <v>8784.410689204931</v>
+        <v>11029.31564311287</v>
       </c>
       <c r="AA36" s="4">
         <f>IF(Y36=0,0,Z36/Y36)</f>
         <v>0</v>
       </c>
       <c r="AB36" s="3">
-        <v>113172.8675108527</v>
+        <v>106414.5769839078</v>
       </c>
       <c r="AC36" s="3">
-        <v>30.94157108721265</v>
+        <v>19.54204489719996</v>
       </c>
       <c r="AD36" s="4">
         <f>IF(AB36=0,0,AC36/AB36)</f>
@@ -3290,7 +3290,7 @@
         <v>0</v>
       </c>
       <c r="E41" s="3">
-        <f>P41+M41</f>
+        <f>M41+P41</f>
         <v>0</v>
       </c>
       <c r="F41" s="3">
@@ -3387,7 +3387,7 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <f>P42+M42</f>
+        <f>M42+P42</f>
         <v>0</v>
       </c>
       <c r="F42" s="3">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="E43" s="3">
-        <f>P43+M43</f>
+        <f>M43+P43</f>
         <v>0</v>
       </c>
       <c r="F43" s="3">
@@ -3581,7 +3581,7 @@
         <v>0</v>
       </c>
       <c r="E44" s="3">
-        <f>P44+M44</f>
+        <f>M44+P44</f>
         <v>0</v>
       </c>
       <c r="F44" s="3">
@@ -3678,7 +3678,7 @@
         <v>0</v>
       </c>
       <c r="E45" s="3">
-        <f>P45+M45</f>
+        <f>M45+P45</f>
         <v>0</v>
       </c>
       <c r="F45" s="3">
@@ -3898,7 +3898,7 @@
         <v>0</v>
       </c>
       <c r="E50" s="3">
-        <f>P50+M50</f>
+        <f>M50+P50</f>
         <v>0</v>
       </c>
       <c r="F50" s="3">
@@ -3995,7 +3995,7 @@
         <v>0</v>
       </c>
       <c r="E51" s="3">
-        <f>P51+M51</f>
+        <f>M51+P51</f>
         <v>0</v>
       </c>
       <c r="F51" s="3">
@@ -4092,7 +4092,7 @@
         <v>0</v>
       </c>
       <c r="E52" s="3">
-        <f>P52+M52</f>
+        <f>M52+P52</f>
         <v>0</v>
       </c>
       <c r="F52" s="3">
@@ -4189,7 +4189,7 @@
         <v>0</v>
       </c>
       <c r="E53" s="3">
-        <f>P53+M53</f>
+        <f>M53+P53</f>
         <v>0</v>
       </c>
       <c r="F53" s="3">
@@ -4286,7 +4286,7 @@
         <v>0</v>
       </c>
       <c r="E54" s="3">
-        <f>P54+M54</f>
+        <f>M54+P54</f>
         <v>0</v>
       </c>
       <c r="F54" s="3">

--- a/5000_analyze_results/results_spreadsheet.xlsx
+++ b/5000_analyze_results/results_spreadsheet.xlsx
@@ -2088,10 +2088,10 @@
         <v>0</v>
       </c>
       <c r="I23" s="3">
-        <v>1006.030531365336</v>
+        <v>1006.03050891829</v>
       </c>
       <c r="J23" s="3">
-        <v>137.7016734290448</v>
+        <v>137.7016614572871</v>
       </c>
       <c r="K23" s="4">
         <f>IF(I23=0,0,J23/I23)</f>
@@ -2108,10 +2108,10 @@
         <v>0</v>
       </c>
       <c r="O23" s="3">
-        <v>489.4651924619991</v>
+        <v>490.4767894259087</v>
       </c>
       <c r="P23" s="3">
-        <v>17.50721234002186</v>
+        <v>18.30659451972903</v>
       </c>
       <c r="Q23" s="4">
         <f>IF(O23=0,0,P23/O23)</f>
@@ -2128,20 +2128,20 @@
         <v>0</v>
       </c>
       <c r="V23" s="3">
-        <v>24943983.83125177</v>
+        <v>24943983.79121354</v>
       </c>
       <c r="W23" s="3">
-        <v>2711534.335743245</v>
+        <v>2711534.522799071</v>
       </c>
       <c r="X23" s="4">
         <f>IF(V23=0,0,W23/V23)</f>
         <v>0</v>
       </c>
       <c r="Y23" s="3">
-        <v>2560969.677248245</v>
+        <v>2562179.973832092</v>
       </c>
       <c r="Z23" s="3">
-        <v>106489.8319512471</v>
+        <v>106463.8040677239</v>
       </c>
       <c r="AA23" s="4">
         <f>IF(Y23=0,0,Z23/Y23)</f>
@@ -2185,10 +2185,10 @@
         <v>0</v>
       </c>
       <c r="I24" s="3">
-        <v>964.635763828982</v>
+        <v>964.6353829774464</v>
       </c>
       <c r="J24" s="3">
-        <v>140.6393015231089</v>
+        <v>140.6392386713823</v>
       </c>
       <c r="K24" s="4">
         <f>IF(I24=0,0,J24/I24)</f>
@@ -2205,10 +2205,10 @@
         <v>0</v>
       </c>
       <c r="O24" s="3">
-        <v>434.0130658424808</v>
+        <v>445.5228835589704</v>
       </c>
       <c r="P24" s="3">
-        <v>23.55264100846788</v>
+        <v>23.2267178141388</v>
       </c>
       <c r="Q24" s="4">
         <f>IF(O24=0,0,P24/O24)</f>
@@ -2225,20 +2225,20 @@
         <v>0</v>
       </c>
       <c r="V24" s="3">
-        <v>24664123.92119449</v>
+        <v>24664122.16385399</v>
       </c>
       <c r="W24" s="3">
-        <v>2871099.152244043</v>
+        <v>2871097.97539036</v>
       </c>
       <c r="X24" s="4">
         <f>IF(V24=0,0,W24/V24)</f>
         <v>0</v>
       </c>
       <c r="Y24" s="3">
-        <v>2158754.286187634</v>
+        <v>2215774.872016895</v>
       </c>
       <c r="Z24" s="3">
-        <v>104503.5790898548</v>
+        <v>105761.0512125869</v>
       </c>
       <c r="AA24" s="4">
         <f>IF(Y24=0,0,Z24/Y24)</f>
@@ -2282,10 +2282,10 @@
         <v>0</v>
       </c>
       <c r="I25" s="3">
-        <v>794.0335099241948</v>
+        <v>794.0332832090369</v>
       </c>
       <c r="J25" s="3">
-        <v>130.4479592776196</v>
+        <v>130.447879964726</v>
       </c>
       <c r="K25" s="4">
         <f>IF(I25=0,0,J25/I25)</f>
@@ -2302,10 +2302,10 @@
         <v>0</v>
       </c>
       <c r="O25" s="3">
-        <v>416.2346518831183</v>
+        <v>423.2626485083759</v>
       </c>
       <c r="P25" s="3">
-        <v>18.87297791093762</v>
+        <v>18.88101471107895</v>
       </c>
       <c r="Q25" s="4">
         <f>IF(O25=0,0,P25/O25)</f>
@@ -2322,20 +2322,20 @@
         <v>0</v>
       </c>
       <c r="V25" s="3">
-        <v>22724255.81598294</v>
+        <v>22724254.79066634</v>
       </c>
       <c r="W25" s="3">
-        <v>3049970.807713103</v>
+        <v>3049970.033541534</v>
       </c>
       <c r="X25" s="4">
         <f>IF(V25=0,0,W25/V25)</f>
         <v>0</v>
       </c>
       <c r="Y25" s="3">
-        <v>2072058.659656062</v>
+        <v>2110361.943746436</v>
       </c>
       <c r="Z25" s="3">
-        <v>98196.69756354927</v>
+        <v>98500.89845223143</v>
       </c>
       <c r="AA25" s="4">
         <f>IF(Y25=0,0,Z25/Y25)</f>
@@ -2379,10 +2379,10 @@
         <v>0</v>
       </c>
       <c r="I26" s="3">
-        <v>721.6901097134873</v>
+        <v>721.6906170167119</v>
       </c>
       <c r="J26" s="3">
-        <v>122.2583434718093</v>
+        <v>122.258392855309</v>
       </c>
       <c r="K26" s="4">
         <f>IF(I26=0,0,J26/I26)</f>
@@ -2399,10 +2399,10 @@
         <v>0</v>
       </c>
       <c r="O26" s="3">
-        <v>408.4416891589786</v>
+        <v>386.7499979717133</v>
       </c>
       <c r="P26" s="3">
-        <v>17.98217159471451</v>
+        <v>18.98683480456413</v>
       </c>
       <c r="Q26" s="4">
         <f>IF(O26=0,0,P26/O26)</f>
@@ -2419,20 +2419,20 @@
         <v>0</v>
       </c>
       <c r="V26" s="3">
-        <v>21494889.54934806</v>
+        <v>21494888.75936157</v>
       </c>
       <c r="W26" s="3">
-        <v>3023372.087489758</v>
+        <v>3023371.617128544</v>
       </c>
       <c r="X26" s="4">
         <f>IF(V26=0,0,W26/V26)</f>
         <v>0</v>
       </c>
       <c r="Y26" s="3">
-        <v>2032784.210161714</v>
+        <v>1927070.334488014</v>
       </c>
       <c r="Z26" s="3">
-        <v>81138.67339928937</v>
+        <v>82220.45730823791</v>
       </c>
       <c r="AA26" s="4">
         <f>IF(Y26=0,0,Z26/Y26)</f>
@@ -2476,10 +2476,10 @@
         <v>0</v>
       </c>
       <c r="I27" s="3">
-        <v>613.5011676610787</v>
+        <v>613.5010816140716</v>
       </c>
       <c r="J27" s="3">
-        <v>110.1809203461102</v>
+        <v>110.1809181014056</v>
       </c>
       <c r="K27" s="4">
         <f>IF(I27=0,0,J27/I27)</f>
@@ -2496,10 +2496,10 @@
         <v>0</v>
       </c>
       <c r="O27" s="3">
-        <v>284.4883780056052</v>
+        <v>287.6064386127327</v>
       </c>
       <c r="P27" s="3">
-        <v>14.14908918231103</v>
+        <v>14.57451940548077</v>
       </c>
       <c r="Q27" s="4">
         <f>IF(O27=0,0,P27/O27)</f>
@@ -2516,20 +2516,20 @@
         <v>0</v>
       </c>
       <c r="V27" s="3">
-        <v>20021735.0102083</v>
+        <v>20021733.97656191</v>
       </c>
       <c r="W27" s="3">
-        <v>3026591.775948588</v>
+        <v>3026592.02297743</v>
       </c>
       <c r="X27" s="4">
         <f>IF(V27=0,0,W27/V27)</f>
         <v>0</v>
       </c>
       <c r="Y27" s="3">
-        <v>1396693.644957343</v>
+        <v>1405956.318006293</v>
       </c>
       <c r="Z27" s="3">
-        <v>67914.88182659587</v>
+        <v>68241.85711336066</v>
       </c>
       <c r="AA27" s="4">
         <f>IF(Y27=0,0,Z27/Y27)</f>
@@ -2696,10 +2696,10 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>1006.030531365336</v>
+        <v>1006.03050891829</v>
       </c>
       <c r="J32" s="3">
-        <v>11.68607680639857</v>
+        <v>11.68607605816354</v>
       </c>
       <c r="K32" s="4">
         <f>IF(I32=0,0,J32/I32)</f>
@@ -2716,10 +2716,10 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
-        <v>489.4651924619991</v>
+        <v>490.4767894259087</v>
       </c>
       <c r="P32" s="3">
-        <v>1.322742544303008</v>
+        <v>1.324936358721752</v>
       </c>
       <c r="Q32" s="4">
         <f>IF(O32=0,0,P32/O32)</f>
@@ -2736,20 +2736,20 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
-        <v>24943983.83125177</v>
+        <v>24943983.79121354</v>
       </c>
       <c r="W32" s="3">
-        <v>226783.7306828722</v>
+        <v>226783.5345008299</v>
       </c>
       <c r="X32" s="4">
         <f>IF(V32=0,0,W32/V32)</f>
         <v>0</v>
       </c>
       <c r="Y32" s="3">
-        <v>2560969.677248245</v>
+        <v>2562179.973832092</v>
       </c>
       <c r="Z32" s="3">
-        <v>7736.78837738093</v>
+        <v>7749.802319143433</v>
       </c>
       <c r="AA32" s="4">
         <f>IF(Y32=0,0,Z32/Y32)</f>
@@ -2793,10 +2793,10 @@
         <v>0</v>
       </c>
       <c r="I33" s="3">
-        <v>964.635763828982</v>
+        <v>964.6353829774464</v>
       </c>
       <c r="J33" s="3">
-        <v>15.53968362151366</v>
+        <v>15.53966267093841</v>
       </c>
       <c r="K33" s="4">
         <f>IF(I33=0,0,J33/I33)</f>
@@ -2813,10 +2813,10 @@
         <v>0</v>
       </c>
       <c r="O33" s="3">
-        <v>434.0130658424808</v>
+        <v>445.5228835589704</v>
       </c>
       <c r="P33" s="3">
-        <v>1.743656035621534</v>
+        <v>2.013518356469227</v>
       </c>
       <c r="Q33" s="4">
         <f>IF(O33=0,0,P33/O33)</f>
@@ -2833,20 +2833,20 @@
         <v>0</v>
       </c>
       <c r="V33" s="3">
-        <v>24664123.92119449</v>
+        <v>24664122.16385399</v>
       </c>
       <c r="W33" s="3">
-        <v>312466.3625391275</v>
+        <v>312466.0118141025</v>
       </c>
       <c r="X33" s="4">
         <f>IF(V33=0,0,W33/V33)</f>
         <v>0</v>
       </c>
       <c r="Y33" s="3">
-        <v>2158754.286187634</v>
+        <v>2215774.872016895</v>
       </c>
       <c r="Z33" s="3">
-        <v>10969.12616246473</v>
+        <v>10960.99244886357</v>
       </c>
       <c r="AA33" s="4">
         <f>IF(Y33=0,0,Z33/Y33)</f>
@@ -2890,10 +2890,10 @@
         <v>0</v>
       </c>
       <c r="I34" s="3">
-        <v>794.0335099241948</v>
+        <v>794.0332832090369</v>
       </c>
       <c r="J34" s="3">
-        <v>17.47400642631936</v>
+        <v>17.47401316043292</v>
       </c>
       <c r="K34" s="4">
         <f>IF(I34=0,0,J34/I34)</f>
@@ -2910,10 +2910,10 @@
         <v>0</v>
       </c>
       <c r="O34" s="3">
-        <v>416.2346518831183</v>
+        <v>423.2626485083759</v>
       </c>
       <c r="P34" s="3">
-        <v>2.377086763853033</v>
+        <v>2.302160093775892</v>
       </c>
       <c r="Q34" s="4">
         <f>IF(O34=0,0,P34/O34)</f>
@@ -2930,20 +2930,20 @@
         <v>0</v>
       </c>
       <c r="V34" s="3">
-        <v>22724255.81598294</v>
+        <v>22724254.79066634</v>
       </c>
       <c r="W34" s="3">
-        <v>402460.4812298082</v>
+        <v>402460.020815663</v>
       </c>
       <c r="X34" s="4">
         <f>IF(V34=0,0,W34/V34)</f>
         <v>0</v>
       </c>
       <c r="Y34" s="3">
-        <v>2072058.659656062</v>
+        <v>2110361.943746436</v>
       </c>
       <c r="Z34" s="3">
-        <v>13201.0171746104</v>
+        <v>13274.22059702082</v>
       </c>
       <c r="AA34" s="4">
         <f>IF(Y34=0,0,Z34/Y34)</f>
@@ -2987,10 +2987,10 @@
         <v>0</v>
       </c>
       <c r="I35" s="3">
-        <v>721.6901097134873</v>
+        <v>721.6906170167119</v>
       </c>
       <c r="J35" s="3">
-        <v>18.98792808560363</v>
+        <v>18.98791012796736</v>
       </c>
       <c r="K35" s="4">
         <f>IF(I35=0,0,J35/I35)</f>
@@ -3007,10 +3007,10 @@
         <v>0</v>
       </c>
       <c r="O35" s="3">
-        <v>408.4416891589786</v>
+        <v>386.7499979717133</v>
       </c>
       <c r="P35" s="3">
-        <v>3.220887604453601</v>
+        <v>3.202118789545784</v>
       </c>
       <c r="Q35" s="4">
         <f>IF(O35=0,0,P35/O35)</f>
@@ -3027,20 +3027,20 @@
         <v>0</v>
       </c>
       <c r="V35" s="3">
-        <v>21494889.54934806</v>
+        <v>21494888.75936157</v>
       </c>
       <c r="W35" s="3">
-        <v>462770.4463554397</v>
+        <v>462770.0523576438</v>
       </c>
       <c r="X35" s="4">
         <f>IF(V35=0,0,W35/V35)</f>
         <v>0</v>
       </c>
       <c r="Y35" s="3">
-        <v>2032784.210161714</v>
+        <v>1927070.334488014</v>
       </c>
       <c r="Z35" s="3">
-        <v>12594.24213996739</v>
+        <v>12821.98612079886</v>
       </c>
       <c r="AA35" s="4">
         <f>IF(Y35=0,0,Z35/Y35)</f>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="I36" s="3">
-        <v>613.5011676610787</v>
+        <v>613.5010816140716</v>
       </c>
       <c r="J36" s="3">
-        <v>18.4046604282771</v>
+        <v>18.4046589318075</v>
       </c>
       <c r="K36" s="4">
         <f>IF(I36=0,0,J36/I36)</f>
@@ -3104,10 +3104,10 @@
         <v>0</v>
       </c>
       <c r="O36" s="3">
-        <v>284.4883780056052</v>
+        <v>287.6064386127327</v>
       </c>
       <c r="P36" s="3">
-        <v>2.601356038767728</v>
+        <v>2.951383382774657</v>
       </c>
       <c r="Q36" s="4">
         <f>IF(O36=0,0,P36/O36)</f>
@@ -3124,20 +3124,20 @@
         <v>0</v>
       </c>
       <c r="V36" s="3">
-        <v>20021735.0102083</v>
+        <v>20021733.97656191</v>
       </c>
       <c r="W36" s="3">
-        <v>498447.049526915</v>
+        <v>498447.0926206037</v>
       </c>
       <c r="X36" s="4">
         <f>IF(V36=0,0,W36/V36)</f>
         <v>0</v>
       </c>
       <c r="Y36" s="3">
-        <v>1396693.644957343</v>
+        <v>1405956.318006293</v>
       </c>
       <c r="Z36" s="3">
-        <v>11029.31564311287</v>
+        <v>11174.0957452131</v>
       </c>
       <c r="AA36" s="4">
         <f>IF(Y36=0,0,Z36/Y36)</f>

--- a/5000_analyze_results/results_spreadsheet.xlsx
+++ b/5000_analyze_results/results_spreadsheet.xlsx
@@ -882,10 +882,10 @@
         <v>0</v>
       </c>
       <c r="L5" s="3">
-        <v>17573.82651946129</v>
+        <v>17935.27995420955</v>
       </c>
       <c r="M5" s="3">
-        <v>52.43127107270062</v>
+        <v>51.79140364386141</v>
       </c>
       <c r="N5" s="4">
         <f>IF(L5=0,0,M5/L5)</f>
@@ -932,10 +932,10 @@
         <v>0</v>
       </c>
       <c r="AB5" s="3">
-        <v>196057.6019358347</v>
+        <v>200072.0470788344</v>
       </c>
       <c r="AC5" s="3">
-        <v>582.7808785878588</v>
+        <v>575.5563222417259</v>
       </c>
       <c r="AD5" s="4">
         <f>IF(AB5=0,0,AC5/AB5)</f>
@@ -979,10 +979,10 @@
         <v>0</v>
       </c>
       <c r="L6" s="3">
-        <v>14652.1253505373</v>
+        <v>14938.0946218137</v>
       </c>
       <c r="M6" s="3">
-        <v>33.36611404703743</v>
+        <v>39.87119663484022</v>
       </c>
       <c r="N6" s="4">
         <f>IF(L6=0,0,M6/L6)</f>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="AB6" s="3">
-        <v>163455.5873311974</v>
+        <v>166631.983938046</v>
       </c>
       <c r="AC6" s="3">
-        <v>370.860559101362</v>
+        <v>443.1061225626618</v>
       </c>
       <c r="AD6" s="4">
         <f>IF(AB6=0,0,AC6/AB6)</f>
@@ -1076,10 +1076,10 @@
         <v>0</v>
       </c>
       <c r="L7" s="3">
-        <v>12980.21700838298</v>
+        <v>13234.92997176094</v>
       </c>
       <c r="M7" s="3">
-        <v>28.82879728573933</v>
+        <v>30.1158939311821</v>
       </c>
       <c r="N7" s="4">
         <f>IF(L7=0,0,M7/L7)</f>
@@ -1126,10 +1126,10 @@
         <v>0</v>
       </c>
       <c r="AB7" s="3">
-        <v>144811.4155872839</v>
+        <v>147641.0334895182</v>
       </c>
       <c r="AC7" s="3">
-        <v>320.2886646784609</v>
+        <v>334.7377773706976</v>
       </c>
       <c r="AD7" s="4">
         <f>IF(AB7=0,0,AC7/AB7)</f>
@@ -1173,10 +1173,10 @@
         <v>0</v>
       </c>
       <c r="L8" s="3">
-        <v>12127.30661114934</v>
+        <v>12362.34693163964</v>
       </c>
       <c r="M8" s="3">
-        <v>26.43375170142017</v>
+        <v>21.66686408916116</v>
       </c>
       <c r="N8" s="4">
         <f>IF(L8=0,0,M8/L8)</f>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="AB8" s="3">
-        <v>135303.8994357765</v>
+        <v>137914.3724621782</v>
       </c>
       <c r="AC8" s="3">
-        <v>293.7986247426306</v>
+        <v>240.8185448710283</v>
       </c>
       <c r="AD8" s="4">
         <f>IF(AB8=0,0,AC8/AB8)</f>
@@ -1270,10 +1270,10 @@
         <v>0</v>
       </c>
       <c r="L9" s="3">
-        <v>11639.06744554709</v>
+        <v>11834.18418972814</v>
       </c>
       <c r="M9" s="3">
-        <v>13.65298159589991</v>
+        <v>9.966248810512946</v>
       </c>
       <c r="N9" s="4">
         <f>IF(L9=0,0,M9/L9)</f>
@@ -1320,10 +1320,10 @@
         <v>0</v>
       </c>
       <c r="AB9" s="3">
-        <v>129863.8085071404</v>
+        <v>132031.1754109795</v>
       </c>
       <c r="AC9" s="3">
-        <v>151.7156832687178</v>
+        <v>110.7765306406654</v>
       </c>
       <c r="AD9" s="4">
         <f>IF(AB9=0,0,AC9/AB9)</f>
@@ -1490,10 +1490,10 @@
         <v>0</v>
       </c>
       <c r="L14" s="3">
-        <v>17573.82651946129</v>
+        <v>17935.27995420955</v>
       </c>
       <c r="M14" s="3">
-        <v>52.43127107270062</v>
+        <v>51.79140364386141</v>
       </c>
       <c r="N14" s="4">
         <f>IF(L14=0,0,M14/L14)</f>
@@ -1540,10 +1540,10 @@
         <v>0</v>
       </c>
       <c r="AB14" s="3">
-        <v>196057.6019358347</v>
+        <v>200072.0470788344</v>
       </c>
       <c r="AC14" s="3">
-        <v>582.7808785878588</v>
+        <v>575.5563222417259</v>
       </c>
       <c r="AD14" s="4">
         <f>IF(AB14=0,0,AC14/AB14)</f>
@@ -1587,10 +1587,10 @@
         <v>0</v>
       </c>
       <c r="L15" s="3">
-        <v>14652.1253505373</v>
+        <v>14938.0946218137</v>
       </c>
       <c r="M15" s="3">
-        <v>33.36611404703743</v>
+        <v>39.87119663484022</v>
       </c>
       <c r="N15" s="4">
         <f>IF(L15=0,0,M15/L15)</f>
@@ -1637,10 +1637,10 @@
         <v>0</v>
       </c>
       <c r="AB15" s="3">
-        <v>163455.5873311974</v>
+        <v>166631.983938046</v>
       </c>
       <c r="AC15" s="3">
-        <v>370.860559101362</v>
+        <v>443.1061225626618</v>
       </c>
       <c r="AD15" s="4">
         <f>IF(AB15=0,0,AC15/AB15)</f>
@@ -1684,10 +1684,10 @@
         <v>0</v>
       </c>
       <c r="L16" s="3">
-        <v>12980.21700838298</v>
+        <v>13234.92997176094</v>
       </c>
       <c r="M16" s="3">
-        <v>28.82879728573933</v>
+        <v>30.1158939311821</v>
       </c>
       <c r="N16" s="4">
         <f>IF(L16=0,0,M16/L16)</f>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="AB16" s="3">
-        <v>144811.4155872839</v>
+        <v>147641.0334895182</v>
       </c>
       <c r="AC16" s="3">
-        <v>320.2886646784609</v>
+        <v>334.7377773706976</v>
       </c>
       <c r="AD16" s="4">
         <f>IF(AB16=0,0,AC16/AB16)</f>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="L17" s="3">
-        <v>12127.30661114934</v>
+        <v>12362.34693163964</v>
       </c>
       <c r="M17" s="3">
-        <v>26.43375170142017</v>
+        <v>21.66686408916116</v>
       </c>
       <c r="N17" s="4">
         <f>IF(L17=0,0,M17/L17)</f>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AB17" s="3">
-        <v>135303.8994357765</v>
+        <v>137914.3724621782</v>
       </c>
       <c r="AC17" s="3">
-        <v>293.7986247426306</v>
+        <v>240.8185448710283</v>
       </c>
       <c r="AD17" s="4">
         <f>IF(AB17=0,0,AC17/AB17)</f>
@@ -1878,10 +1878,10 @@
         <v>0</v>
       </c>
       <c r="L18" s="3">
-        <v>11639.06744554709</v>
+        <v>11834.18418972814</v>
       </c>
       <c r="M18" s="3">
-        <v>13.65298159589991</v>
+        <v>9.966248810512946</v>
       </c>
       <c r="N18" s="4">
         <f>IF(L18=0,0,M18/L18)</f>
@@ -1928,10 +1928,10 @@
         <v>0</v>
       </c>
       <c r="AB18" s="3">
-        <v>129863.8085071404</v>
+        <v>132031.1754109795</v>
       </c>
       <c r="AC18" s="3">
-        <v>151.7156832687178</v>
+        <v>110.7765306406654</v>
       </c>
       <c r="AD18" s="4">
         <f>IF(AB18=0,0,AC18/AB18)</f>
@@ -2088,30 +2088,30 @@
         <v>0</v>
       </c>
       <c r="I23" s="3">
-        <v>1108.055716585262</v>
+        <v>1006.03050891829</v>
       </c>
       <c r="J23" s="3">
-        <v>152.8113304434048</v>
+        <v>137.7016614572871</v>
       </c>
       <c r="K23" s="4">
         <f>IF(I23=0,0,J23/I23)</f>
         <v>0</v>
       </c>
       <c r="L23" s="3">
-        <v>17011.801165714</v>
+        <v>15508.35321860747</v>
       </c>
       <c r="M23" s="3">
-        <v>89.60077630843968</v>
+        <v>69.41307935650087</v>
       </c>
       <c r="N23" s="4">
         <f>IF(L23=0,0,M23/L23)</f>
         <v>0</v>
       </c>
       <c r="O23" s="3">
-        <v>549.9985622454193</v>
+        <v>490.4767894259087</v>
       </c>
       <c r="P23" s="3">
-        <v>22.28616294577986</v>
+        <v>18.30659451972903</v>
       </c>
       <c r="Q23" s="4">
         <f>IF(O23=0,0,P23/O23)</f>
@@ -2128,30 +2128,30 @@
         <v>0</v>
       </c>
       <c r="V23" s="3">
-        <v>27431637.53707126</v>
+        <v>24943983.79121354</v>
       </c>
       <c r="W23" s="3">
-        <v>2871705.046079703</v>
+        <v>2711534.522799071</v>
       </c>
       <c r="X23" s="4">
         <f>IF(V23=0,0,W23/V23)</f>
         <v>0</v>
       </c>
       <c r="Y23" s="3">
-        <v>2838841.735003161</v>
+        <v>2562179.973832092</v>
       </c>
       <c r="Z23" s="3">
-        <v>112549.4485840783</v>
+        <v>106463.8040677239</v>
       </c>
       <c r="AA23" s="4">
         <f>IF(Y23=0,0,Z23/Y23)</f>
         <v>0</v>
       </c>
       <c r="AB23" s="3">
-        <v>191414.3297679779</v>
+        <v>174653.7692611545</v>
       </c>
       <c r="AC23" s="3">
-        <v>995.015786015254</v>
+        <v>770.2822696975782</v>
       </c>
       <c r="AD23" s="4">
         <f>IF(AB23=0,0,AC23/AB23)</f>
@@ -2185,30 +2185,30 @@
         <v>0</v>
       </c>
       <c r="I24" s="3">
-        <v>949.118316777312</v>
+        <v>964.6353829774464</v>
       </c>
       <c r="J24" s="3">
-        <v>143.1138573807727</v>
+        <v>140.6392386713823</v>
       </c>
       <c r="K24" s="4">
         <f>IF(I24=0,0,J24/I24)</f>
         <v>0</v>
       </c>
       <c r="L24" s="3">
-        <v>17262.12457025323</v>
+        <v>16011.09974104909</v>
       </c>
       <c r="M24" s="3">
-        <v>83.62756285276636</v>
+        <v>65.18596044688859</v>
       </c>
       <c r="N24" s="4">
         <f>IF(L24=0,0,M24/L24)</f>
         <v>0</v>
       </c>
       <c r="O24" s="3">
-        <v>546.7455795701167</v>
+        <v>445.5228835589704</v>
       </c>
       <c r="P24" s="3">
-        <v>23.62213058602001</v>
+        <v>23.2267178141388</v>
       </c>
       <c r="Q24" s="4">
         <f>IF(O24=0,0,P24/O24)</f>
@@ -2225,30 +2225,30 @@
         <v>0</v>
       </c>
       <c r="V24" s="3">
-        <v>24926729.65305717</v>
+        <v>24664122.16385399</v>
       </c>
       <c r="W24" s="3">
-        <v>2981714.140268512</v>
+        <v>2871097.97539036</v>
       </c>
       <c r="X24" s="4">
         <f>IF(V24=0,0,W24/V24)</f>
         <v>0</v>
       </c>
       <c r="Y24" s="3">
-        <v>2728058.929013245</v>
+        <v>2215774.872016895</v>
       </c>
       <c r="Z24" s="3">
-        <v>120382.214781953</v>
+        <v>105761.0512125869</v>
       </c>
       <c r="AA24" s="4">
         <f>IF(Y24=0,0,Z24/Y24)</f>
         <v>0</v>
       </c>
       <c r="AB24" s="3">
-        <v>194285.3818641235</v>
+        <v>180322.590785081</v>
       </c>
       <c r="AC24" s="3">
-        <v>928.2471326165542</v>
+        <v>723.0556611960346</v>
       </c>
       <c r="AD24" s="4">
         <f>IF(AB24=0,0,AC24/AB24)</f>
@@ -2282,30 +2282,30 @@
         <v>0</v>
       </c>
       <c r="I25" s="3">
-        <v>812.8399148483488</v>
+        <v>794.0332832090369</v>
       </c>
       <c r="J25" s="3">
-        <v>128.7957158822644</v>
+        <v>130.447879964726</v>
       </c>
       <c r="K25" s="4">
         <f>IF(I25=0,0,J25/I25)</f>
         <v>0</v>
       </c>
       <c r="L25" s="3">
-        <v>14358.06173102218</v>
+        <v>14053.45528341239</v>
       </c>
       <c r="M25" s="3">
-        <v>47.82929256691225</v>
+        <v>41.82331183696166</v>
       </c>
       <c r="N25" s="4">
         <f>IF(L25=0,0,M25/L25)</f>
         <v>0</v>
       </c>
       <c r="O25" s="3">
-        <v>368.6755302231475</v>
+        <v>423.2626485083759</v>
       </c>
       <c r="P25" s="3">
-        <v>17.95913611626596</v>
+        <v>18.88101471107895</v>
       </c>
       <c r="Q25" s="4">
         <f>IF(O25=0,0,P25/O25)</f>
@@ -2322,30 +2322,30 @@
         <v>0</v>
       </c>
       <c r="V25" s="3">
-        <v>22587787.7184066</v>
+        <v>22724254.79066634</v>
       </c>
       <c r="W25" s="3">
-        <v>2940867.548315275</v>
+        <v>3049970.033541534</v>
       </c>
       <c r="X25" s="4">
         <f>IF(V25=0,0,W25/V25)</f>
         <v>0</v>
       </c>
       <c r="Y25" s="3">
-        <v>1833771.759255057</v>
+        <v>2110361.943746436</v>
       </c>
       <c r="Z25" s="3">
-        <v>90350.91742391349</v>
+        <v>98500.89845223143</v>
       </c>
       <c r="AA25" s="4">
         <f>IF(Y25=0,0,Z25/Y25)</f>
         <v>0</v>
       </c>
       <c r="AB25" s="3">
-        <v>161615.9683072457</v>
+        <v>158254.736584929</v>
       </c>
       <c r="AC25" s="3">
-        <v>530.8922197069915</v>
+        <v>464.1235663082625</v>
       </c>
       <c r="AD25" s="4">
         <f>IF(AB25=0,0,AC25/AB25)</f>
@@ -2379,30 +2379,30 @@
         <v>0</v>
       </c>
       <c r="I26" s="3">
-        <v>743.9010935936449</v>
+        <v>721.6906170167119</v>
       </c>
       <c r="J26" s="3">
-        <v>121.8135940932956</v>
+        <v>122.258392855309</v>
       </c>
       <c r="K26" s="4">
         <f>IF(I26=0,0,J26/I26)</f>
         <v>0</v>
       </c>
       <c r="L26" s="3">
-        <v>11515.87046614333</v>
+        <v>12426.67038256435</v>
       </c>
       <c r="M26" s="3">
-        <v>29.4853726437483</v>
+        <v>31.56021921042912</v>
       </c>
       <c r="N26" s="4">
         <f>IF(L26=0,0,M26/L26)</f>
         <v>0</v>
       </c>
       <c r="O26" s="3">
-        <v>322.3352502269547</v>
+        <v>386.7499979717133</v>
       </c>
       <c r="P26" s="3">
-        <v>15.34015562439407</v>
+        <v>18.98683480456413</v>
       </c>
       <c r="Q26" s="4">
         <f>IF(O26=0,0,P26/O26)</f>
@@ -2419,30 +2419,30 @@
         <v>0</v>
       </c>
       <c r="V26" s="3">
-        <v>21637527.93050475</v>
+        <v>21494888.75936157</v>
       </c>
       <c r="W26" s="3">
-        <v>2939331.981051177</v>
+        <v>3023371.617128544</v>
       </c>
       <c r="X26" s="4">
         <f>IF(V26=0,0,W26/V26)</f>
         <v>0</v>
       </c>
       <c r="Y26" s="3">
-        <v>1639385.764644713</v>
+        <v>1927070.334488014</v>
       </c>
       <c r="Z26" s="3">
-        <v>70324.08779524639</v>
+        <v>82220.45730823791</v>
       </c>
       <c r="AA26" s="4">
         <f>IF(Y26=0,0,Z26/Y26)</f>
         <v>0</v>
       </c>
       <c r="AB26" s="3">
-        <v>129654.9538778912</v>
+        <v>139955.2400424519</v>
       </c>
       <c r="AC26" s="3">
-        <v>327.3292520279356</v>
+        <v>350.1283044079901</v>
       </c>
       <c r="AD26" s="4">
         <f>IF(AB26=0,0,AC26/AB26)</f>
@@ -2476,30 +2476,30 @@
         <v>0</v>
       </c>
       <c r="I27" s="3">
-        <v>534.7276074530099</v>
+        <v>613.5010816140716</v>
       </c>
       <c r="J27" s="3">
-        <v>94.97372757948976</v>
+        <v>110.1809181014056</v>
       </c>
       <c r="K27" s="4">
         <f>IF(I27=0,0,J27/I27)</f>
         <v>0</v>
       </c>
       <c r="L27" s="3">
-        <v>10051.0537036804</v>
+        <v>9448.065592686806</v>
       </c>
       <c r="M27" s="3">
-        <v>26.25223764907569</v>
+        <v>21.28188721634261</v>
       </c>
       <c r="N27" s="4">
         <f>IF(L27=0,0,M27/L27)</f>
         <v>0</v>
       </c>
       <c r="O27" s="3">
-        <v>226.6668752752476</v>
+        <v>287.6064386127327</v>
       </c>
       <c r="P27" s="3">
-        <v>9.975083572365314</v>
+        <v>14.57451940548077</v>
       </c>
       <c r="Q27" s="4">
         <f>IF(O27=0,0,P27/O27)</f>
@@ -2516,30 +2516,30 @@
         <v>0</v>
       </c>
       <c r="V27" s="3">
-        <v>17469072.97061635</v>
+        <v>20021733.97656191</v>
       </c>
       <c r="W27" s="3">
-        <v>2697278.525443047</v>
+        <v>3026592.02297743</v>
       </c>
       <c r="X27" s="4">
         <f>IF(V27=0,0,W27/V27)</f>
         <v>0</v>
       </c>
       <c r="Y27" s="3">
-        <v>1102531.385602113</v>
+        <v>1405956.318006293</v>
       </c>
       <c r="Z27" s="3">
-        <v>52826.84309652611</v>
+        <v>68241.85711336066</v>
       </c>
       <c r="AA27" s="4">
         <f>IF(Y27=0,0,Z27/Y27)</f>
         <v>0</v>
       </c>
       <c r="AB27" s="3">
-        <v>113172.8675108527</v>
+        <v>106414.5769839078</v>
       </c>
       <c r="AC27" s="3">
-        <v>291.5021697164193</v>
+        <v>236.1330425077176</v>
       </c>
       <c r="AD27" s="4">
         <f>IF(AB27=0,0,AC27/AB27)</f>
@@ -2696,30 +2696,30 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>1108.055716585262</v>
+        <v>1006.03050891829</v>
       </c>
       <c r="J32" s="3">
-        <v>12.96842238628073</v>
+        <v>11.68607605816354</v>
       </c>
       <c r="K32" s="4">
         <f>IF(I32=0,0,J32/I32)</f>
         <v>0</v>
       </c>
       <c r="L32" s="3">
-        <v>17011.801165714</v>
+        <v>15508.35321860747</v>
       </c>
       <c r="M32" s="3">
-        <v>1.612388412721455</v>
+        <v>1.175133258519694</v>
       </c>
       <c r="N32" s="4">
         <f>IF(L32=0,0,M32/L32)</f>
         <v>0</v>
       </c>
       <c r="O32" s="3">
-        <v>549.9985622454193</v>
+        <v>490.4767894259087</v>
       </c>
       <c r="P32" s="3">
-        <v>1.850068818195141</v>
+        <v>1.324936358721752</v>
       </c>
       <c r="Q32" s="4">
         <f>IF(O32=0,0,P32/O32)</f>
@@ -2736,30 +2736,30 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
-        <v>27431637.53707126</v>
+        <v>24943983.79121354</v>
       </c>
       <c r="W32" s="3">
-        <v>238834.02248694</v>
+        <v>226783.5345008299</v>
       </c>
       <c r="X32" s="4">
         <f>IF(V32=0,0,W32/V32)</f>
         <v>0</v>
       </c>
       <c r="Y32" s="3">
-        <v>2838841.735003161</v>
+        <v>2562179.973832092</v>
       </c>
       <c r="Z32" s="3">
-        <v>8224.811193448491</v>
+        <v>7749.802319143433</v>
       </c>
       <c r="AA32" s="4">
         <f>IF(Y32=0,0,Z32/Y32)</f>
         <v>0</v>
       </c>
       <c r="AB32" s="3">
-        <v>191414.3297679779</v>
+        <v>174653.7692611545</v>
       </c>
       <c r="AC32" s="3">
-        <v>17.91354115575086</v>
+        <v>13.02802993147634</v>
       </c>
       <c r="AD32" s="4">
         <f>IF(AB32=0,0,AC32/AB32)</f>
@@ -2793,30 +2793,30 @@
         <v>0</v>
       </c>
       <c r="I33" s="3">
-        <v>949.118316777312</v>
+        <v>964.6353829774464</v>
       </c>
       <c r="J33" s="3">
-        <v>15.83439497350773</v>
+        <v>15.53966267093841</v>
       </c>
       <c r="K33" s="4">
         <f>IF(I33=0,0,J33/I33)</f>
         <v>0</v>
       </c>
       <c r="L33" s="3">
-        <v>17262.12457025323</v>
+        <v>16011.09974104909</v>
       </c>
       <c r="M33" s="3">
-        <v>3.088071183532477</v>
+        <v>1.781353609535843</v>
       </c>
       <c r="N33" s="4">
         <f>IF(L33=0,0,M33/L33)</f>
         <v>0</v>
       </c>
       <c r="O33" s="3">
-        <v>546.7455795701167</v>
+        <v>445.5228835589704</v>
       </c>
       <c r="P33" s="3">
-        <v>2.163429498037091</v>
+        <v>2.013518356469227</v>
       </c>
       <c r="Q33" s="4">
         <f>IF(O33=0,0,P33/O33)</f>
@@ -2833,30 +2833,30 @@
         <v>0</v>
       </c>
       <c r="V33" s="3">
-        <v>24926729.65305717</v>
+        <v>24664122.16385399</v>
       </c>
       <c r="W33" s="3">
-        <v>324457.6168491468</v>
+        <v>312466.0118141025</v>
       </c>
       <c r="X33" s="4">
         <f>IF(V33=0,0,W33/V33)</f>
         <v>0</v>
       </c>
       <c r="Y33" s="3">
-        <v>2728058.929013245</v>
+        <v>2215774.872016895</v>
       </c>
       <c r="Z33" s="3">
-        <v>12538.93288748013</v>
+        <v>10960.99244886357</v>
       </c>
       <c r="AA33" s="4">
         <f>IF(Y33=0,0,Z33/Y33)</f>
         <v>0</v>
       </c>
       <c r="AB33" s="3">
-        <v>194285.3818641235</v>
+        <v>180322.590785081</v>
       </c>
       <c r="AC33" s="3">
-        <v>34.19857857009629</v>
+        <v>19.54204489718541</v>
       </c>
       <c r="AD33" s="4">
         <f>IF(AB33=0,0,AC33/AB33)</f>
@@ -2890,30 +2890,30 @@
         <v>0</v>
       </c>
       <c r="I34" s="3">
-        <v>812.8399148483488</v>
+        <v>794.0332832090369</v>
       </c>
       <c r="J34" s="3">
-        <v>17.2345983792363</v>
+        <v>17.47401316043292</v>
       </c>
       <c r="K34" s="4">
         <f>IF(I34=0,0,J34/I34)</f>
         <v>0</v>
       </c>
       <c r="L34" s="3">
-        <v>14358.06173102218</v>
+        <v>14053.45528341239</v>
       </c>
       <c r="M34" s="3">
-        <v>2.197665334034711</v>
+        <v>2.34422612186335</v>
       </c>
       <c r="N34" s="4">
         <f>IF(L34=0,0,M34/L34)</f>
         <v>0</v>
       </c>
       <c r="O34" s="3">
-        <v>368.6755302231475</v>
+        <v>423.2626485083759</v>
       </c>
       <c r="P34" s="3">
-        <v>1.927282700260461</v>
+        <v>2.302160093775892</v>
       </c>
       <c r="Q34" s="4">
         <f>IF(O34=0,0,P34/O34)</f>
@@ -2930,30 +2930,30 @@
         <v>0</v>
       </c>
       <c r="V34" s="3">
-        <v>22587787.7184066</v>
+        <v>22724254.79066634</v>
       </c>
       <c r="W34" s="3">
-        <v>388017.1677994356</v>
+        <v>402460.020815663</v>
       </c>
       <c r="X34" s="4">
         <f>IF(V34=0,0,W34/V34)</f>
         <v>0</v>
       </c>
       <c r="Y34" s="3">
-        <v>1833771.759255057</v>
+        <v>2110361.943746436</v>
       </c>
       <c r="Z34" s="3">
-        <v>12224.97154247691</v>
+        <v>13274.22059702082</v>
       </c>
       <c r="AA34" s="4">
         <f>IF(Y34=0,0,Z34/Y34)</f>
         <v>0</v>
       </c>
       <c r="AB34" s="3">
-        <v>161615.9683072457</v>
+        <v>158254.736584929</v>
       </c>
       <c r="AC34" s="3">
-        <v>24.42755612148903</v>
+        <v>26.05605986292358</v>
       </c>
       <c r="AD34" s="4">
         <f>IF(AB34=0,0,AC34/AB34)</f>
@@ -2987,30 +2987,30 @@
         <v>0</v>
       </c>
       <c r="I35" s="3">
-        <v>743.9010935936449</v>
+        <v>721.6906170167119</v>
       </c>
       <c r="J35" s="3">
-        <v>18.88886539927812</v>
+        <v>18.98791012796736</v>
       </c>
       <c r="K35" s="4">
         <f>IF(I35=0,0,J35/I35)</f>
         <v>0</v>
       </c>
       <c r="L35" s="3">
-        <v>11515.87046614333</v>
+        <v>12426.67038256435</v>
       </c>
       <c r="M35" s="3">
-        <v>2.638893344042823</v>
+        <v>2.490720905642957</v>
       </c>
       <c r="N35" s="4">
         <f>IF(L35=0,0,M35/L35)</f>
         <v>0</v>
       </c>
       <c r="O35" s="3">
-        <v>322.3352502269547</v>
+        <v>386.7499979717133</v>
       </c>
       <c r="P35" s="3">
-        <v>2.3030336125826</v>
+        <v>3.202118789545784</v>
       </c>
       <c r="Q35" s="4">
         <f>IF(O35=0,0,P35/O35)</f>
@@ -3027,30 +3027,30 @@
         <v>0</v>
       </c>
       <c r="V35" s="3">
-        <v>21637527.93050475</v>
+        <v>21494888.75936157</v>
       </c>
       <c r="W35" s="3">
-        <v>449735.9740116</v>
+        <v>462770.0523576438</v>
       </c>
       <c r="X35" s="4">
         <f>IF(V35=0,0,W35/V35)</f>
         <v>0</v>
       </c>
       <c r="Y35" s="3">
-        <v>1639385.764644713</v>
+        <v>1927070.334488014</v>
       </c>
       <c r="Z35" s="3">
-        <v>10788.55772052007</v>
+        <v>12821.98612079886</v>
       </c>
       <c r="AA35" s="4">
         <f>IF(Y35=0,0,Z35/Y35)</f>
         <v>0</v>
       </c>
       <c r="AB35" s="3">
-        <v>129654.9538778912</v>
+        <v>139955.2400424519</v>
       </c>
       <c r="AC35" s="3">
-        <v>29.31306734577811</v>
+        <v>27.68456360435812</v>
       </c>
       <c r="AD35" s="4">
         <f>IF(AB35=0,0,AC35/AB35)</f>
@@ -3084,30 +3084,30 @@
         <v>0</v>
       </c>
       <c r="I36" s="3">
-        <v>534.7276074530099</v>
+        <v>613.5010816140716</v>
       </c>
       <c r="J36" s="3">
-        <v>15.8855046137232</v>
+        <v>18.4046589318075</v>
       </c>
       <c r="K36" s="4">
         <f>IF(I36=0,0,J36/I36)</f>
         <v>0</v>
       </c>
       <c r="L36" s="3">
-        <v>10051.0537036804</v>
+        <v>9448.065592686806</v>
       </c>
       <c r="M36" s="3">
-        <v>2.796754232564941</v>
+        <v>1.760577471522614</v>
       </c>
       <c r="N36" s="4">
         <f>IF(L36=0,0,M36/L36)</f>
         <v>0</v>
       </c>
       <c r="O36" s="3">
-        <v>226.6668752752476</v>
+        <v>287.6064386127327</v>
       </c>
       <c r="P36" s="3">
-        <v>1.474631430243928</v>
+        <v>2.951383382774657</v>
       </c>
       <c r="Q36" s="4">
         <f>IF(O36=0,0,P36/O36)</f>
@@ -3124,30 +3124,30 @@
         <v>0</v>
       </c>
       <c r="V36" s="3">
-        <v>17469072.97061635</v>
+        <v>20021733.97656191</v>
       </c>
       <c r="W36" s="3">
-        <v>445666.0981375836</v>
+        <v>498447.0926206037</v>
       </c>
       <c r="X36" s="4">
         <f>IF(V36=0,0,W36/V36)</f>
         <v>0</v>
       </c>
       <c r="Y36" s="3">
-        <v>1102531.385602113</v>
+        <v>1405956.318006293</v>
       </c>
       <c r="Z36" s="3">
-        <v>8784.410689204931</v>
+        <v>11174.0957452131</v>
       </c>
       <c r="AA36" s="4">
         <f>IF(Y36=0,0,Z36/Y36)</f>
         <v>0</v>
       </c>
       <c r="AB36" s="3">
-        <v>113172.8675108527</v>
+        <v>106414.5769839078</v>
       </c>
       <c r="AC36" s="3">
-        <v>30.94157108721265</v>
+        <v>19.54204489719996</v>
       </c>
       <c r="AD36" s="4">
         <f>IF(AB36=0,0,AC36/AB36)</f>
@@ -3290,7 +3290,7 @@
         <v>0</v>
       </c>
       <c r="E41" s="3">
-        <f>P41+M41</f>
+        <f>M41+P41</f>
         <v>0</v>
       </c>
       <c r="F41" s="3">
@@ -3387,7 +3387,7 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <f>P42+M42</f>
+        <f>M42+P42</f>
         <v>0</v>
       </c>
       <c r="F42" s="3">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="E43" s="3">
-        <f>P43+M43</f>
+        <f>M43+P43</f>
         <v>0</v>
       </c>
       <c r="F43" s="3">
@@ -3581,7 +3581,7 @@
         <v>0</v>
       </c>
       <c r="E44" s="3">
-        <f>P44+M44</f>
+        <f>M44+P44</f>
         <v>0</v>
       </c>
       <c r="F44" s="3">
@@ -3678,7 +3678,7 @@
         <v>0</v>
       </c>
       <c r="E45" s="3">
-        <f>P45+M45</f>
+        <f>M45+P45</f>
         <v>0</v>
       </c>
       <c r="F45" s="3">
@@ -3898,7 +3898,7 @@
         <v>0</v>
       </c>
       <c r="E50" s="3">
-        <f>P50+M50</f>
+        <f>M50+P50</f>
         <v>0</v>
       </c>
       <c r="F50" s="3">
@@ -3995,7 +3995,7 @@
         <v>0</v>
       </c>
       <c r="E51" s="3">
-        <f>P51+M51</f>
+        <f>M51+P51</f>
         <v>0</v>
       </c>
       <c r="F51" s="3">
@@ -4092,7 +4092,7 @@
         <v>0</v>
       </c>
       <c r="E52" s="3">
-        <f>P52+M52</f>
+        <f>M52+P52</f>
         <v>0</v>
       </c>
       <c r="F52" s="3">
@@ -4189,7 +4189,7 @@
         <v>0</v>
       </c>
       <c r="E53" s="3">
-        <f>P53+M53</f>
+        <f>M53+P53</f>
         <v>0</v>
       </c>
       <c r="F53" s="3">
@@ -4286,7 +4286,7 @@
         <v>0</v>
       </c>
       <c r="E54" s="3">
-        <f>P54+M54</f>
+        <f>M54+P54</f>
         <v>0</v>
       </c>
       <c r="F54" s="3">

--- a/5000_analyze_results/results_spreadsheet.xlsx
+++ b/5000_analyze_results/results_spreadsheet.xlsx
@@ -872,30 +872,30 @@
         <v>0</v>
       </c>
       <c r="I5" s="3">
-        <v>4771.172487854658</v>
+        <v>4771.261231090824</v>
       </c>
       <c r="J5" s="3">
-        <v>313.4550641795806</v>
+        <v>313.4364668127587</v>
       </c>
       <c r="K5" s="4">
         <f>IF(I5=0,0,J5/I5)</f>
         <v>0</v>
       </c>
       <c r="L5" s="3">
-        <v>17935.27995420955</v>
+        <v>16522.03201076821</v>
       </c>
       <c r="M5" s="3">
-        <v>51.79140364386141</v>
+        <v>47.24953973846883</v>
       </c>
       <c r="N5" s="4">
         <f>IF(L5=0,0,M5/L5)</f>
         <v>0</v>
       </c>
       <c r="O5" s="3">
-        <v>495.9420392823301</v>
+        <v>506.7963637284521</v>
       </c>
       <c r="P5" s="3">
-        <v>14.94688767936849</v>
+        <v>15.01370971237042</v>
       </c>
       <c r="Q5" s="4">
         <f>IF(O5=0,0,P5/O5)</f>
@@ -912,30 +912,30 @@
         <v>0</v>
       </c>
       <c r="V5" s="3">
-        <v>131693856.602241</v>
+        <v>131696392.1412486</v>
       </c>
       <c r="W5" s="3">
-        <v>6834156.362184763</v>
+        <v>6833090.704050109</v>
       </c>
       <c r="X5" s="4">
         <f>IF(V5=0,0,W5/V5)</f>
         <v>0</v>
       </c>
       <c r="Y5" s="3">
-        <v>3014818.917223012</v>
+        <v>3016543.050471412</v>
       </c>
       <c r="Z5" s="3">
-        <v>82234.18246693723</v>
+        <v>83335.51165489713</v>
       </c>
       <c r="AA5" s="4">
         <f>IF(Y5=0,0,Z5/Y5)</f>
         <v>0</v>
       </c>
       <c r="AB5" s="3">
-        <v>200072.0470788344</v>
+        <v>184370.0487466397</v>
       </c>
       <c r="AC5" s="3">
-        <v>575.5563222417259</v>
+        <v>525.1747063550574</v>
       </c>
       <c r="AD5" s="4">
         <f>IF(AB5=0,0,AC5/AB5)</f>
@@ -969,30 +969,30 @@
         <v>0</v>
       </c>
       <c r="I6" s="3">
-        <v>4315.488605002881</v>
+        <v>4315.21265961095</v>
       </c>
       <c r="J6" s="3">
-        <v>279.5339981601541</v>
+        <v>279.4920962596657</v>
       </c>
       <c r="K6" s="4">
         <f>IF(I6=0,0,J6/I6)</f>
         <v>0</v>
       </c>
       <c r="L6" s="3">
-        <v>14938.0946218137</v>
+        <v>13642.46320366066</v>
       </c>
       <c r="M6" s="3">
-        <v>39.87119663484022</v>
+        <v>33.80926878551207</v>
       </c>
       <c r="N6" s="4">
         <f>IF(L6=0,0,M6/L6)</f>
         <v>0</v>
       </c>
       <c r="O6" s="3">
-        <v>286.4588253328344</v>
+        <v>297.573370209569</v>
       </c>
       <c r="P6" s="3">
-        <v>8.284407215548388</v>
+        <v>8.344677452836709</v>
       </c>
       <c r="Q6" s="4">
         <f>IF(O6=0,0,P6/O6)</f>
@@ -1009,30 +1009,30 @@
         <v>0</v>
       </c>
       <c r="V6" s="3">
-        <v>123353341.0379582</v>
+        <v>123352422.8520256</v>
       </c>
       <c r="W6" s="3">
-        <v>6428198.322602153</v>
+        <v>6427646.223230928</v>
       </c>
       <c r="X6" s="4">
         <f>IF(V6=0,0,W6/V6)</f>
         <v>0</v>
       </c>
       <c r="Y6" s="3">
-        <v>1787928.583240007</v>
+        <v>1788522.531513863</v>
       </c>
       <c r="Z6" s="3">
-        <v>46645.37901320681</v>
+        <v>46989.24380333396</v>
       </c>
       <c r="AA6" s="4">
         <f>IF(Y6=0,0,Z6/Y6)</f>
         <v>0</v>
       </c>
       <c r="AB6" s="3">
-        <v>166631.983938046</v>
+        <v>152242.8474441103</v>
       </c>
       <c r="AC6" s="3">
-        <v>443.1061225626618</v>
+        <v>375.8130926210724</v>
       </c>
       <c r="AD6" s="4">
         <f>IF(AB6=0,0,AC6/AB6)</f>
@@ -1066,30 +1066,30 @@
         <v>0</v>
       </c>
       <c r="I7" s="3">
-        <v>4219.911362271461</v>
+        <v>4220.065012527612</v>
       </c>
       <c r="J7" s="3">
-        <v>242.9313309619347</v>
+        <v>242.9326465501119</v>
       </c>
       <c r="K7" s="4">
         <f>IF(I7=0,0,J7/I7)</f>
         <v>0</v>
       </c>
       <c r="L7" s="3">
-        <v>13234.92997176094</v>
+        <v>12108.71669338748</v>
       </c>
       <c r="M7" s="3">
-        <v>30.1158939311821</v>
+        <v>21.03499195626378</v>
       </c>
       <c r="N7" s="4">
         <f>IF(L7=0,0,M7/L7)</f>
         <v>0</v>
       </c>
       <c r="O7" s="3">
-        <v>362.0106149542505</v>
+        <v>350.6722046220511</v>
       </c>
       <c r="P7" s="3">
-        <v>7.080686168705637</v>
+        <v>7.230571189964132</v>
       </c>
       <c r="Q7" s="4">
         <f>IF(O7=0,0,P7/O7)</f>
@@ -1106,30 +1106,30 @@
         <v>0</v>
       </c>
       <c r="V7" s="3">
-        <v>121042695.9926408</v>
+        <v>121045766.1486471</v>
       </c>
       <c r="W7" s="3">
-        <v>5624803.04057464</v>
+        <v>5624078.184110358</v>
       </c>
       <c r="X7" s="4">
         <f>IF(V7=0,0,W7/V7)</f>
         <v>0</v>
       </c>
       <c r="Y7" s="3">
-        <v>2262233.551971834</v>
+        <v>2261372.687672075</v>
       </c>
       <c r="Z7" s="3">
-        <v>48143.47526669828</v>
+        <v>48881.70247347467</v>
       </c>
       <c r="AA7" s="4">
         <f>IF(Y7=0,0,Z7/Y7)</f>
         <v>0</v>
       </c>
       <c r="AB7" s="3">
-        <v>147641.0334895182</v>
+        <v>135116.8520887052</v>
       </c>
       <c r="AC7" s="3">
-        <v>334.7377773706976</v>
+        <v>233.6786537451553</v>
       </c>
       <c r="AD7" s="4">
         <f>IF(AB7=0,0,AC7/AB7)</f>
@@ -1163,30 +1163,30 @@
         <v>0</v>
       </c>
       <c r="I8" s="3">
-        <v>3866.404723234419</v>
+        <v>3866.462901477351</v>
       </c>
       <c r="J8" s="3">
-        <v>199.0831212808485</v>
+        <v>199.0834636001452</v>
       </c>
       <c r="K8" s="4">
         <f>IF(I8=0,0,J8/I8)</f>
         <v>0</v>
       </c>
       <c r="L8" s="3">
-        <v>12362.34693163964</v>
+        <v>11547.79616860948</v>
       </c>
       <c r="M8" s="3">
-        <v>21.66686408916116</v>
+        <v>23.62541006216407</v>
       </c>
       <c r="N8" s="4">
         <f>IF(L8=0,0,M8/L8)</f>
         <v>0</v>
       </c>
       <c r="O8" s="3">
-        <v>326.2902544418872</v>
+        <v>341.4996444598856</v>
       </c>
       <c r="P8" s="3">
-        <v>6.173648437333526</v>
+        <v>8.565760149411567</v>
       </c>
       <c r="Q8" s="4">
         <f>IF(O8=0,0,P8/O8)</f>
@@ -1203,30 +1203,30 @@
         <v>0</v>
       </c>
       <c r="V8" s="3">
-        <v>114930948.5074336</v>
+        <v>114934295.1461658</v>
       </c>
       <c r="W8" s="3">
-        <v>4858738.283078313</v>
+        <v>4858362.349655852</v>
       </c>
       <c r="X8" s="4">
         <f>IF(V8=0,0,W8/V8)</f>
         <v>0</v>
       </c>
       <c r="Y8" s="3">
-        <v>2017724.044351414</v>
+        <v>2020070.981660255</v>
       </c>
       <c r="Z8" s="3">
-        <v>39554.06946016243</v>
+        <v>39029.85600388492</v>
       </c>
       <c r="AA8" s="4">
         <f>IF(Y8=0,0,Z8/Y8)</f>
         <v>0</v>
       </c>
       <c r="AB8" s="3">
-        <v>137914.3724621782</v>
+        <v>128855.7096033067</v>
       </c>
       <c r="AC8" s="3">
-        <v>240.8185448710283</v>
+        <v>262.5873531775433</v>
       </c>
       <c r="AD8" s="4">
         <f>IF(AB8=0,0,AC8/AB8)</f>
@@ -1260,30 +1260,30 @@
         <v>0</v>
       </c>
       <c r="I9" s="3">
-        <v>3364.404821554393</v>
+        <v>3364.297008165505</v>
       </c>
       <c r="J9" s="3">
-        <v>100.8406044416442</v>
+        <v>100.8268812075821</v>
       </c>
       <c r="K9" s="4">
         <f>IF(I9=0,0,J9/I9)</f>
         <v>0</v>
       </c>
       <c r="L9" s="3">
-        <v>11834.18418972814</v>
+        <v>10928.70618227773</v>
       </c>
       <c r="M9" s="3">
-        <v>9.966248810512946</v>
+        <v>6.068353288041428</v>
       </c>
       <c r="N9" s="4">
         <f>IF(L9=0,0,M9/L9)</f>
         <v>0</v>
       </c>
       <c r="O9" s="3">
-        <v>210.8368637670372</v>
+        <v>209.6942036708812</v>
       </c>
       <c r="P9" s="3">
-        <v>2.020924868696747</v>
+        <v>2.195864039865555</v>
       </c>
       <c r="Q9" s="4">
         <f>IF(O9=0,0,P9/O9)</f>
@@ -1300,30 +1300,30 @@
         <v>0</v>
       </c>
       <c r="V9" s="3">
-        <v>107057780.7659875</v>
+        <v>107056308.1865083</v>
       </c>
       <c r="W9" s="3">
-        <v>2679796.374648735</v>
+        <v>2679940.421917364</v>
       </c>
       <c r="X9" s="4">
         <f>IF(V9=0,0,W9/V9)</f>
         <v>0</v>
       </c>
       <c r="Y9" s="3">
-        <v>1277885.722823765</v>
+        <v>1277060.928257236</v>
       </c>
       <c r="Z9" s="3">
-        <v>14853.51614416833</v>
+        <v>14533.69784286129</v>
       </c>
       <c r="AA9" s="4">
         <f>IF(Y9=0,0,Z9/Y9)</f>
         <v>0</v>
       </c>
       <c r="AB9" s="3">
-        <v>132031.1754109795</v>
+        <v>121958.5757303956</v>
       </c>
       <c r="AC9" s="3">
-        <v>110.7765306406654</v>
+        <v>67.45363200891006</v>
       </c>
       <c r="AD9" s="4">
         <f>IF(AB9=0,0,AC9/AB9)</f>
@@ -1480,30 +1480,30 @@
         <v>0</v>
       </c>
       <c r="I14" s="3">
-        <v>4771.172487854658</v>
+        <v>4771.261231090824</v>
       </c>
       <c r="J14" s="3">
-        <v>313.4550641795806</v>
+        <v>313.4364668127587</v>
       </c>
       <c r="K14" s="4">
         <f>IF(I14=0,0,J14/I14)</f>
         <v>0</v>
       </c>
       <c r="L14" s="3">
-        <v>17935.27995420955</v>
+        <v>16522.03201076821</v>
       </c>
       <c r="M14" s="3">
-        <v>51.79140364386141</v>
+        <v>47.24953973846883</v>
       </c>
       <c r="N14" s="4">
         <f>IF(L14=0,0,M14/L14)</f>
         <v>0</v>
       </c>
       <c r="O14" s="3">
-        <v>495.9420392823301</v>
+        <v>506.7963637284521</v>
       </c>
       <c r="P14" s="3">
-        <v>14.94688767936849</v>
+        <v>15.01370971237042</v>
       </c>
       <c r="Q14" s="4">
         <f>IF(O14=0,0,P14/O14)</f>
@@ -1520,30 +1520,30 @@
         <v>0</v>
       </c>
       <c r="V14" s="3">
-        <v>131693856.602241</v>
+        <v>131696392.1412486</v>
       </c>
       <c r="W14" s="3">
-        <v>6834156.362184763</v>
+        <v>6833090.704050109</v>
       </c>
       <c r="X14" s="4">
         <f>IF(V14=0,0,W14/V14)</f>
         <v>0</v>
       </c>
       <c r="Y14" s="3">
-        <v>3014818.917223012</v>
+        <v>3016543.050471412</v>
       </c>
       <c r="Z14" s="3">
-        <v>82234.18246693723</v>
+        <v>83335.51165489713</v>
       </c>
       <c r="AA14" s="4">
         <f>IF(Y14=0,0,Z14/Y14)</f>
         <v>0</v>
       </c>
       <c r="AB14" s="3">
-        <v>200072.0470788344</v>
+        <v>184370.0487466397</v>
       </c>
       <c r="AC14" s="3">
-        <v>575.5563222417259</v>
+        <v>525.1747063550574</v>
       </c>
       <c r="AD14" s="4">
         <f>IF(AB14=0,0,AC14/AB14)</f>
@@ -1577,30 +1577,30 @@
         <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>4315.488605002881</v>
+        <v>4315.21265961095</v>
       </c>
       <c r="J15" s="3">
-        <v>279.5339981601541</v>
+        <v>279.4920962596657</v>
       </c>
       <c r="K15" s="4">
         <f>IF(I15=0,0,J15/I15)</f>
         <v>0</v>
       </c>
       <c r="L15" s="3">
-        <v>14938.0946218137</v>
+        <v>13642.46320366066</v>
       </c>
       <c r="M15" s="3">
-        <v>39.87119663484022</v>
+        <v>33.80926878551207</v>
       </c>
       <c r="N15" s="4">
         <f>IF(L15=0,0,M15/L15)</f>
         <v>0</v>
       </c>
       <c r="O15" s="3">
-        <v>286.4588253328344</v>
+        <v>297.573370209569</v>
       </c>
       <c r="P15" s="3">
-        <v>8.284407215548388</v>
+        <v>8.344677452836709</v>
       </c>
       <c r="Q15" s="4">
         <f>IF(O15=0,0,P15/O15)</f>
@@ -1617,30 +1617,30 @@
         <v>0</v>
       </c>
       <c r="V15" s="3">
-        <v>123353341.0379582</v>
+        <v>123352422.8520256</v>
       </c>
       <c r="W15" s="3">
-        <v>6428198.322602153</v>
+        <v>6427646.223230928</v>
       </c>
       <c r="X15" s="4">
         <f>IF(V15=0,0,W15/V15)</f>
         <v>0</v>
       </c>
       <c r="Y15" s="3">
-        <v>1787928.583240007</v>
+        <v>1788522.531513863</v>
       </c>
       <c r="Z15" s="3">
-        <v>46645.37901320681</v>
+        <v>46989.24380333396</v>
       </c>
       <c r="AA15" s="4">
         <f>IF(Y15=0,0,Z15/Y15)</f>
         <v>0</v>
       </c>
       <c r="AB15" s="3">
-        <v>166631.983938046</v>
+        <v>152242.8474441103</v>
       </c>
       <c r="AC15" s="3">
-        <v>443.1061225626618</v>
+        <v>375.8130926210724</v>
       </c>
       <c r="AD15" s="4">
         <f>IF(AB15=0,0,AC15/AB15)</f>
@@ -1674,30 +1674,30 @@
         <v>0</v>
       </c>
       <c r="I16" s="3">
-        <v>4219.911362271461</v>
+        <v>4220.065012527612</v>
       </c>
       <c r="J16" s="3">
-        <v>242.9313309619347</v>
+        <v>242.9326465501119</v>
       </c>
       <c r="K16" s="4">
         <f>IF(I16=0,0,J16/I16)</f>
         <v>0</v>
       </c>
       <c r="L16" s="3">
-        <v>13234.92997176094</v>
+        <v>12108.71669338748</v>
       </c>
       <c r="M16" s="3">
-        <v>30.1158939311821</v>
+        <v>21.03499195626378</v>
       </c>
       <c r="N16" s="4">
         <f>IF(L16=0,0,M16/L16)</f>
         <v>0</v>
       </c>
       <c r="O16" s="3">
-        <v>362.0106149542505</v>
+        <v>350.6722046220511</v>
       </c>
       <c r="P16" s="3">
-        <v>7.080686168705637</v>
+        <v>7.230571189964132</v>
       </c>
       <c r="Q16" s="4">
         <f>IF(O16=0,0,P16/O16)</f>
@@ -1714,30 +1714,30 @@
         <v>0</v>
       </c>
       <c r="V16" s="3">
-        <v>121042695.9926408</v>
+        <v>121045766.1486471</v>
       </c>
       <c r="W16" s="3">
-        <v>5624803.04057464</v>
+        <v>5624078.184110358</v>
       </c>
       <c r="X16" s="4">
         <f>IF(V16=0,0,W16/V16)</f>
         <v>0</v>
       </c>
       <c r="Y16" s="3">
-        <v>2262233.551971834</v>
+        <v>2261372.687672075</v>
       </c>
       <c r="Z16" s="3">
-        <v>48143.47526669828</v>
+        <v>48881.70247347467</v>
       </c>
       <c r="AA16" s="4">
         <f>IF(Y16=0,0,Z16/Y16)</f>
         <v>0</v>
       </c>
       <c r="AB16" s="3">
-        <v>147641.0334895182</v>
+        <v>135116.8520887052</v>
       </c>
       <c r="AC16" s="3">
-        <v>334.7377773706976</v>
+        <v>233.6786537451553</v>
       </c>
       <c r="AD16" s="4">
         <f>IF(AB16=0,0,AC16/AB16)</f>
@@ -1771,30 +1771,30 @@
         <v>0</v>
       </c>
       <c r="I17" s="3">
-        <v>3866.404723234419</v>
+        <v>3866.462901477351</v>
       </c>
       <c r="J17" s="3">
-        <v>199.0831212808485</v>
+        <v>199.0834636001452</v>
       </c>
       <c r="K17" s="4">
         <f>IF(I17=0,0,J17/I17)</f>
         <v>0</v>
       </c>
       <c r="L17" s="3">
-        <v>12362.34693163964</v>
+        <v>11547.79616860948</v>
       </c>
       <c r="M17" s="3">
-        <v>21.66686408916116</v>
+        <v>23.62541006216407</v>
       </c>
       <c r="N17" s="4">
         <f>IF(L17=0,0,M17/L17)</f>
         <v>0</v>
       </c>
       <c r="O17" s="3">
-        <v>326.2902544418872</v>
+        <v>341.4996444598856</v>
       </c>
       <c r="P17" s="3">
-        <v>6.173648437333526</v>
+        <v>8.565760149411567</v>
       </c>
       <c r="Q17" s="4">
         <f>IF(O17=0,0,P17/O17)</f>
@@ -1811,30 +1811,30 @@
         <v>0</v>
       </c>
       <c r="V17" s="3">
-        <v>114930948.5074336</v>
+        <v>114934295.1461658</v>
       </c>
       <c r="W17" s="3">
-        <v>4858738.283078313</v>
+        <v>4858362.349655852</v>
       </c>
       <c r="X17" s="4">
         <f>IF(V17=0,0,W17/V17)</f>
         <v>0</v>
       </c>
       <c r="Y17" s="3">
-        <v>2017724.044351414</v>
+        <v>2020070.981660255</v>
       </c>
       <c r="Z17" s="3">
-        <v>39554.06946016243</v>
+        <v>39029.85600388492</v>
       </c>
       <c r="AA17" s="4">
         <f>IF(Y17=0,0,Z17/Y17)</f>
         <v>0</v>
       </c>
       <c r="AB17" s="3">
-        <v>137914.3724621782</v>
+        <v>128855.7096033067</v>
       </c>
       <c r="AC17" s="3">
-        <v>240.8185448710283</v>
+        <v>262.5873531775433</v>
       </c>
       <c r="AD17" s="4">
         <f>IF(AB17=0,0,AC17/AB17)</f>
@@ -1868,30 +1868,30 @@
         <v>0</v>
       </c>
       <c r="I18" s="3">
-        <v>3364.404821554393</v>
+        <v>3364.297008165505</v>
       </c>
       <c r="J18" s="3">
-        <v>100.8406044416442</v>
+        <v>100.8268812075821</v>
       </c>
       <c r="K18" s="4">
         <f>IF(I18=0,0,J18/I18)</f>
         <v>0</v>
       </c>
       <c r="L18" s="3">
-        <v>11834.18418972814</v>
+        <v>10928.70618227773</v>
       </c>
       <c r="M18" s="3">
-        <v>9.966248810512946</v>
+        <v>6.068353288041428</v>
       </c>
       <c r="N18" s="4">
         <f>IF(L18=0,0,M18/L18)</f>
         <v>0</v>
       </c>
       <c r="O18" s="3">
-        <v>210.8368637670372</v>
+        <v>209.6942036708812</v>
       </c>
       <c r="P18" s="3">
-        <v>2.020924868696747</v>
+        <v>2.195864039865555</v>
       </c>
       <c r="Q18" s="4">
         <f>IF(O18=0,0,P18/O18)</f>
@@ -1908,30 +1908,30 @@
         <v>0</v>
       </c>
       <c r="V18" s="3">
-        <v>107057780.7659875</v>
+        <v>107056308.1865083</v>
       </c>
       <c r="W18" s="3">
-        <v>2679796.374648735</v>
+        <v>2679940.421917364</v>
       </c>
       <c r="X18" s="4">
         <f>IF(V18=0,0,W18/V18)</f>
         <v>0</v>
       </c>
       <c r="Y18" s="3">
-        <v>1277885.722823765</v>
+        <v>1277060.928257236</v>
       </c>
       <c r="Z18" s="3">
-        <v>14853.51614416833</v>
+        <v>14533.69784286129</v>
       </c>
       <c r="AA18" s="4">
         <f>IF(Y18=0,0,Z18/Y18)</f>
         <v>0</v>
       </c>
       <c r="AB18" s="3">
-        <v>132031.1754109795</v>
+        <v>121958.5757303956</v>
       </c>
       <c r="AC18" s="3">
-        <v>110.7765306406654</v>
+        <v>67.45363200891006</v>
       </c>
       <c r="AD18" s="4">
         <f>IF(AB18=0,0,AC18/AB18)</f>
@@ -2088,30 +2088,30 @@
         <v>0</v>
       </c>
       <c r="I23" s="3">
-        <v>1006.03050891829</v>
+        <v>1006.030840012209</v>
       </c>
       <c r="J23" s="3">
-        <v>137.7016614572871</v>
+        <v>137.6545265903092</v>
       </c>
       <c r="K23" s="4">
         <f>IF(I23=0,0,J23/I23)</f>
         <v>0</v>
       </c>
       <c r="L23" s="3">
-        <v>15508.35321860747</v>
+        <v>14879.51549115505</v>
       </c>
       <c r="M23" s="3">
-        <v>69.41307935650087</v>
+        <v>56.06812795555219</v>
       </c>
       <c r="N23" s="4">
         <f>IF(L23=0,0,M23/L23)</f>
         <v>0</v>
       </c>
       <c r="O23" s="3">
-        <v>490.4767894259087</v>
+        <v>503.5634310516943</v>
       </c>
       <c r="P23" s="3">
-        <v>18.30659451972903</v>
+        <v>18.84933287622535</v>
       </c>
       <c r="Q23" s="4">
         <f>IF(O23=0,0,P23/O23)</f>
@@ -2128,30 +2128,30 @@
         <v>0</v>
       </c>
       <c r="V23" s="3">
-        <v>24943983.79121354</v>
+        <v>24943823.20853924</v>
       </c>
       <c r="W23" s="3">
-        <v>2711534.522799071</v>
+        <v>2711281.827288892</v>
       </c>
       <c r="X23" s="4">
         <f>IF(V23=0,0,W23/V23)</f>
         <v>0</v>
       </c>
       <c r="Y23" s="3">
-        <v>2562179.973832092</v>
+        <v>2561085.175981381</v>
       </c>
       <c r="Z23" s="3">
-        <v>106463.8040677239</v>
+        <v>107277.175427835</v>
       </c>
       <c r="AA23" s="4">
         <f>IF(Y23=0,0,Z23/Y23)</f>
         <v>0</v>
       </c>
       <c r="AB23" s="3">
-        <v>174653.7692611545</v>
+        <v>167649.5308066797</v>
       </c>
       <c r="AC23" s="3">
-        <v>770.2822696975782</v>
+        <v>622.3663595898252</v>
       </c>
       <c r="AD23" s="4">
         <f>IF(AB23=0,0,AC23/AB23)</f>
@@ -2185,30 +2185,30 @@
         <v>0</v>
       </c>
       <c r="I24" s="3">
-        <v>964.6353829774464</v>
+        <v>964.5986558077452</v>
       </c>
       <c r="J24" s="3">
-        <v>140.6392386713823</v>
+        <v>140.6009727878995</v>
       </c>
       <c r="K24" s="4">
         <f>IF(I24=0,0,J24/I24)</f>
         <v>0</v>
       </c>
       <c r="L24" s="3">
-        <v>16011.09974104909</v>
+        <v>15413.09139410279</v>
       </c>
       <c r="M24" s="3">
-        <v>65.18596044688859</v>
+        <v>54.75217633925006</v>
       </c>
       <c r="N24" s="4">
         <f>IF(L24=0,0,M24/L24)</f>
         <v>0</v>
       </c>
       <c r="O24" s="3">
-        <v>445.5228835589704</v>
+        <v>427.6878840211459</v>
       </c>
       <c r="P24" s="3">
-        <v>23.2267178141388</v>
+        <v>20.50220103713742</v>
       </c>
       <c r="Q24" s="4">
         <f>IF(O24=0,0,P24/O24)</f>
@@ -2225,30 +2225,30 @@
         <v>0</v>
       </c>
       <c r="V24" s="3">
-        <v>24664122.16385399</v>
+        <v>24665300.63578367</v>
       </c>
       <c r="W24" s="3">
-        <v>2871097.97539036</v>
+        <v>2871454.841513783</v>
       </c>
       <c r="X24" s="4">
         <f>IF(V24=0,0,W24/V24)</f>
         <v>0</v>
       </c>
       <c r="Y24" s="3">
-        <v>2215774.872016895</v>
+        <v>2216806.226901517</v>
       </c>
       <c r="Z24" s="3">
-        <v>105761.0512125869</v>
+        <v>105930.2324554906</v>
       </c>
       <c r="AA24" s="4">
         <f>IF(Y24=0,0,Z24/Y24)</f>
         <v>0</v>
       </c>
       <c r="AB24" s="3">
-        <v>180322.590785081</v>
+        <v>173674.428183023</v>
       </c>
       <c r="AC24" s="3">
-        <v>723.0556611960346</v>
+        <v>607.7032778193534</v>
       </c>
       <c r="AD24" s="4">
         <f>IF(AB24=0,0,AC24/AB24)</f>
@@ -2282,30 +2282,30 @@
         <v>0</v>
       </c>
       <c r="I25" s="3">
-        <v>794.0332832090369</v>
+        <v>794.1006249062289</v>
       </c>
       <c r="J25" s="3">
-        <v>130.447879964726</v>
+        <v>130.4419380447662</v>
       </c>
       <c r="K25" s="4">
         <f>IF(I25=0,0,J25/I25)</f>
         <v>0</v>
       </c>
       <c r="L25" s="3">
-        <v>14053.45528341239</v>
+        <v>13666.60844459826</v>
       </c>
       <c r="M25" s="3">
-        <v>41.82331183696166</v>
+        <v>39.80089049636759</v>
       </c>
       <c r="N25" s="4">
         <f>IF(L25=0,0,M25/L25)</f>
         <v>0</v>
       </c>
       <c r="O25" s="3">
-        <v>423.2626485083759</v>
+        <v>410.8336896551561</v>
       </c>
       <c r="P25" s="3">
-        <v>18.88101471107895</v>
+        <v>18.67755932054459</v>
       </c>
       <c r="Q25" s="4">
         <f>IF(O25=0,0,P25/O25)</f>
@@ -2322,30 +2322,30 @@
         <v>0</v>
       </c>
       <c r="V25" s="3">
-        <v>22724254.79066634</v>
+        <v>22725958.89165936</v>
       </c>
       <c r="W25" s="3">
-        <v>3049970.033541534</v>
+        <v>3050344.148597278</v>
       </c>
       <c r="X25" s="4">
         <f>IF(V25=0,0,W25/V25)</f>
         <v>0</v>
       </c>
       <c r="Y25" s="3">
-        <v>2110361.943746436</v>
+        <v>2114085.557833027</v>
       </c>
       <c r="Z25" s="3">
-        <v>98500.89845223143</v>
+        <v>98409.80085989856</v>
       </c>
       <c r="AA25" s="4">
         <f>IF(Y25=0,0,Z25/Y25)</f>
         <v>0</v>
       </c>
       <c r="AB25" s="3">
-        <v>158254.736584929</v>
+        <v>153960.7293583194</v>
       </c>
       <c r="AC25" s="3">
-        <v>464.1235663082625</v>
+        <v>441.5216844210227</v>
       </c>
       <c r="AD25" s="4">
         <f>IF(AB25=0,0,AC25/AB25)</f>
@@ -2379,30 +2379,30 @@
         <v>0</v>
       </c>
       <c r="I26" s="3">
-        <v>721.6906170167119</v>
+        <v>721.6494802184835</v>
       </c>
       <c r="J26" s="3">
-        <v>122.258392855309</v>
+        <v>122.2476639782248</v>
       </c>
       <c r="K26" s="4">
         <f>IF(I26=0,0,J26/I26)</f>
         <v>0</v>
       </c>
       <c r="L26" s="3">
-        <v>12426.67038256435</v>
+        <v>12078.7457080966</v>
       </c>
       <c r="M26" s="3">
-        <v>31.56021921042912</v>
+        <v>28.4645291917026</v>
       </c>
       <c r="N26" s="4">
         <f>IF(L26=0,0,M26/L26)</f>
         <v>0</v>
       </c>
       <c r="O26" s="3">
-        <v>386.7499979717133</v>
+        <v>388.5202631627004</v>
       </c>
       <c r="P26" s="3">
-        <v>18.98683480456413</v>
+        <v>15.74235513104481</v>
       </c>
       <c r="Q26" s="4">
         <f>IF(O26=0,0,P26/O26)</f>
@@ -2419,30 +2419,30 @@
         <v>0</v>
       </c>
       <c r="V26" s="3">
-        <v>21494888.75936157</v>
+        <v>21493332.04664342</v>
       </c>
       <c r="W26" s="3">
-        <v>3023371.617128544</v>
+        <v>3023273.37047838</v>
       </c>
       <c r="X26" s="4">
         <f>IF(V26=0,0,W26/V26)</f>
         <v>0</v>
       </c>
       <c r="Y26" s="3">
-        <v>1927070.334488014</v>
+        <v>1925897.452986733</v>
       </c>
       <c r="Z26" s="3">
-        <v>82220.45730823791</v>
+        <v>82371.74438121915</v>
       </c>
       <c r="AA26" s="4">
         <f>IF(Y26=0,0,Z26/Y26)</f>
         <v>0</v>
       </c>
       <c r="AB26" s="3">
-        <v>139955.2400424519</v>
+        <v>136092.9496053835</v>
       </c>
       <c r="AC26" s="3">
-        <v>350.1283044079901</v>
+        <v>316.0708737183886</v>
       </c>
       <c r="AD26" s="4">
         <f>IF(AB26=0,0,AC26/AB26)</f>
@@ -2476,30 +2476,30 @@
         <v>0</v>
       </c>
       <c r="I27" s="3">
-        <v>613.5010816140716</v>
+        <v>613.496298429298</v>
       </c>
       <c r="J27" s="3">
-        <v>110.1809181014056</v>
+        <v>110.1680808232352</v>
       </c>
       <c r="K27" s="4">
         <f>IF(I27=0,0,J27/I27)</f>
         <v>0</v>
       </c>
       <c r="L27" s="3">
-        <v>9448.065592686806</v>
+        <v>9193.681247525743</v>
       </c>
       <c r="M27" s="3">
-        <v>21.28188721634261</v>
+        <v>21.72556047260389</v>
       </c>
       <c r="N27" s="4">
         <f>IF(L27=0,0,M27/L27)</f>
         <v>0</v>
       </c>
       <c r="O27" s="3">
-        <v>287.6064386127327</v>
+        <v>285.742923347472</v>
       </c>
       <c r="P27" s="3">
-        <v>14.57451940548077</v>
+        <v>13.57646327128552</v>
       </c>
       <c r="Q27" s="4">
         <f>IF(O27=0,0,P27/O27)</f>
@@ -2516,30 +2516,30 @@
         <v>0</v>
       </c>
       <c r="V27" s="3">
-        <v>20021733.97656191</v>
+        <v>20021798.10615849</v>
       </c>
       <c r="W27" s="3">
-        <v>3026592.02297743</v>
+        <v>3027627.545589577</v>
       </c>
       <c r="X27" s="4">
         <f>IF(V27=0,0,W27/V27)</f>
         <v>0</v>
       </c>
       <c r="Y27" s="3">
-        <v>1405956.318006293</v>
+        <v>1405792.016991551</v>
       </c>
       <c r="Z27" s="3">
-        <v>68241.85711336066</v>
+        <v>68362.23607465718</v>
       </c>
       <c r="AA27" s="4">
         <f>IF(Y27=0,0,Z27/Y27)</f>
         <v>0</v>
       </c>
       <c r="AB27" s="3">
-        <v>106414.5769839078</v>
+        <v>103604.4480960104</v>
       </c>
       <c r="AC27" s="3">
-        <v>236.1330425077176</v>
+        <v>241.1262335583597</v>
       </c>
       <c r="AD27" s="4">
         <f>IF(AB27=0,0,AC27/AB27)</f>
@@ -2696,30 +2696,30 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>1006.03050891829</v>
+        <v>1006.030840012209</v>
       </c>
       <c r="J32" s="3">
-        <v>11.68607605816354</v>
+        <v>11.68040300392487</v>
       </c>
       <c r="K32" s="4">
         <f>IF(I32=0,0,J32/I32)</f>
         <v>0</v>
       </c>
       <c r="L32" s="3">
-        <v>15508.35321860747</v>
+        <v>14879.51549115505</v>
       </c>
       <c r="M32" s="3">
-        <v>1.175133258519694</v>
+        <v>0.8794182835407555</v>
       </c>
       <c r="N32" s="4">
         <f>IF(L32=0,0,M32/L32)</f>
         <v>0</v>
       </c>
       <c r="O32" s="3">
-        <v>490.4767894259087</v>
+        <v>503.5634310516943</v>
       </c>
       <c r="P32" s="3">
-        <v>1.324936358721752</v>
+        <v>0.9890495645757182</v>
       </c>
       <c r="Q32" s="4">
         <f>IF(O32=0,0,P32/O32)</f>
@@ -2736,30 +2736,30 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
-        <v>24943983.79121354</v>
+        <v>24943823.20853924</v>
       </c>
       <c r="W32" s="3">
-        <v>226783.5345008299</v>
+        <v>226849.3098196089</v>
       </c>
       <c r="X32" s="4">
         <f>IF(V32=0,0,W32/V32)</f>
         <v>0</v>
       </c>
       <c r="Y32" s="3">
-        <v>2562179.973832092</v>
+        <v>2561085.175981381</v>
       </c>
       <c r="Z32" s="3">
-        <v>7749.802319143433</v>
+        <v>8042.616008783225</v>
       </c>
       <c r="AA32" s="4">
         <f>IF(Y32=0,0,Z32/Y32)</f>
         <v>0</v>
       </c>
       <c r="AB32" s="3">
-        <v>174653.7692611545</v>
+        <v>167649.5308066797</v>
       </c>
       <c r="AC32" s="3">
-        <v>13.02802993147634</v>
+        <v>9.775387846952071</v>
       </c>
       <c r="AD32" s="4">
         <f>IF(AB32=0,0,AC32/AB32)</f>
@@ -2793,30 +2793,30 @@
         <v>0</v>
       </c>
       <c r="I33" s="3">
-        <v>964.6353829774464</v>
+        <v>964.5986558077452</v>
       </c>
       <c r="J33" s="3">
-        <v>15.53966267093841</v>
+        <v>15.53238761472038</v>
       </c>
       <c r="K33" s="4">
         <f>IF(I33=0,0,J33/I33)</f>
         <v>0</v>
       </c>
       <c r="L33" s="3">
-        <v>16011.09974104909</v>
+        <v>15413.09139410279</v>
       </c>
       <c r="M33" s="3">
-        <v>1.781353609535843</v>
+        <v>2.345310499604791</v>
       </c>
       <c r="N33" s="4">
         <f>IF(L33=0,0,M33/L33)</f>
         <v>0</v>
       </c>
       <c r="O33" s="3">
-        <v>445.5228835589704</v>
+        <v>427.6878840211459</v>
       </c>
       <c r="P33" s="3">
-        <v>2.013518356469227</v>
+        <v>2.086115786817216</v>
       </c>
       <c r="Q33" s="4">
         <f>IF(O33=0,0,P33/O33)</f>
@@ -2833,30 +2833,30 @@
         <v>0</v>
       </c>
       <c r="V33" s="3">
-        <v>24664122.16385399</v>
+        <v>24665300.63578367</v>
       </c>
       <c r="W33" s="3">
-        <v>312466.0118141025</v>
+        <v>312647.3967796117</v>
       </c>
       <c r="X33" s="4">
         <f>IF(V33=0,0,W33/V33)</f>
         <v>0</v>
       </c>
       <c r="Y33" s="3">
-        <v>2215774.872016895</v>
+        <v>2216806.226901517</v>
       </c>
       <c r="Z33" s="3">
-        <v>10960.99244886357</v>
+        <v>11335.14327451494</v>
       </c>
       <c r="AA33" s="4">
         <f>IF(Y33=0,0,Z33/Y33)</f>
         <v>0</v>
       </c>
       <c r="AB33" s="3">
-        <v>180322.590785081</v>
+        <v>173674.428183023</v>
       </c>
       <c r="AC33" s="3">
-        <v>19.54204489718541</v>
+        <v>26.06770092522493</v>
       </c>
       <c r="AD33" s="4">
         <f>IF(AB33=0,0,AC33/AB33)</f>
@@ -2890,30 +2890,30 @@
         <v>0</v>
       </c>
       <c r="I34" s="3">
-        <v>794.0332832090369</v>
+        <v>794.1006249062289</v>
       </c>
       <c r="J34" s="3">
-        <v>17.47401316043292</v>
+        <v>17.47281985056156</v>
       </c>
       <c r="K34" s="4">
         <f>IF(I34=0,0,J34/I34)</f>
         <v>0</v>
       </c>
       <c r="L34" s="3">
-        <v>14053.45528341239</v>
+        <v>13666.60844459826</v>
       </c>
       <c r="M34" s="3">
-        <v>2.34422612186335</v>
+        <v>2.347127422653139</v>
       </c>
       <c r="N34" s="4">
         <f>IF(L34=0,0,M34/L34)</f>
         <v>0</v>
       </c>
       <c r="O34" s="3">
-        <v>423.2626485083759</v>
+        <v>410.8336896551561</v>
       </c>
       <c r="P34" s="3">
-        <v>2.302160093775892</v>
+        <v>2.356564286178851</v>
       </c>
       <c r="Q34" s="4">
         <f>IF(O34=0,0,P34/O34)</f>
@@ -2930,30 +2930,30 @@
         <v>0</v>
       </c>
       <c r="V34" s="3">
-        <v>22724254.79066634</v>
+        <v>22725958.89165936</v>
       </c>
       <c r="W34" s="3">
-        <v>402460.020815663</v>
+        <v>402664.4387529455</v>
       </c>
       <c r="X34" s="4">
         <f>IF(V34=0,0,W34/V34)</f>
         <v>0</v>
       </c>
       <c r="Y34" s="3">
-        <v>2110361.943746436</v>
+        <v>2114085.557833027</v>
       </c>
       <c r="Z34" s="3">
-        <v>13274.22059702082</v>
+        <v>13360.4379611928</v>
       </c>
       <c r="AA34" s="4">
         <f>IF(Y34=0,0,Z34/Y34)</f>
         <v>0</v>
       </c>
       <c r="AB34" s="3">
-        <v>158254.736584929</v>
+        <v>153960.7293583194</v>
       </c>
       <c r="AC34" s="3">
-        <v>26.05605986292358</v>
+        <v>26.06770092522493</v>
       </c>
       <c r="AD34" s="4">
         <f>IF(AB34=0,0,AC34/AB34)</f>
@@ -2987,30 +2987,30 @@
         <v>0</v>
       </c>
       <c r="I35" s="3">
-        <v>721.6906170167119</v>
+        <v>721.6494802184835</v>
       </c>
       <c r="J35" s="3">
-        <v>18.98791012796736</v>
+        <v>18.98855847346026</v>
       </c>
       <c r="K35" s="4">
         <f>IF(I35=0,0,J35/I35)</f>
         <v>0</v>
       </c>
       <c r="L35" s="3">
-        <v>12426.67038256435</v>
+        <v>12078.7457080966</v>
       </c>
       <c r="M35" s="3">
-        <v>2.490720905642957</v>
+        <v>2.345336273258552</v>
       </c>
       <c r="N35" s="4">
         <f>IF(L35=0,0,M35/L35)</f>
         <v>0</v>
       </c>
       <c r="O35" s="3">
-        <v>386.7499979717133</v>
+        <v>388.5202631627004</v>
       </c>
       <c r="P35" s="3">
-        <v>3.202118789545784</v>
+        <v>1.884715648668061</v>
       </c>
       <c r="Q35" s="4">
         <f>IF(O35=0,0,P35/O35)</f>
@@ -3027,30 +3027,30 @@
         <v>0</v>
       </c>
       <c r="V35" s="3">
-        <v>21494888.75936157</v>
+        <v>21493332.04664342</v>
       </c>
       <c r="W35" s="3">
-        <v>462770.0523576438</v>
+        <v>462697.4952477962</v>
       </c>
       <c r="X35" s="4">
         <f>IF(V35=0,0,W35/V35)</f>
         <v>0</v>
       </c>
       <c r="Y35" s="3">
-        <v>1927070.334488014</v>
+        <v>1925897.452986733</v>
       </c>
       <c r="Z35" s="3">
-        <v>12821.98612079886</v>
+        <v>12870.78840240557</v>
       </c>
       <c r="AA35" s="4">
         <f>IF(Y35=0,0,Z35/Y35)</f>
         <v>0</v>
       </c>
       <c r="AB35" s="3">
-        <v>139955.2400424519</v>
+        <v>136092.9496053835</v>
       </c>
       <c r="AC35" s="3">
-        <v>27.68456360435812</v>
+        <v>26.06770092522493</v>
       </c>
       <c r="AD35" s="4">
         <f>IF(AB35=0,0,AC35/AB35)</f>
@@ -3084,30 +3084,30 @@
         <v>0</v>
       </c>
       <c r="I36" s="3">
-        <v>613.5010816140716</v>
+        <v>613.496298429298</v>
       </c>
       <c r="J36" s="3">
-        <v>18.4046589318075</v>
+        <v>18.40218963211437</v>
       </c>
       <c r="K36" s="4">
         <f>IF(I36=0,0,J36/I36)</f>
         <v>0</v>
       </c>
       <c r="L36" s="3">
-        <v>9448.065592686806</v>
+        <v>9193.681247525743</v>
       </c>
       <c r="M36" s="3">
-        <v>1.760577471522614</v>
+        <v>2.498986293654889</v>
       </c>
       <c r="N36" s="4">
         <f>IF(L36=0,0,M36/L36)</f>
         <v>0</v>
       </c>
       <c r="O36" s="3">
-        <v>287.6064386127327</v>
+        <v>285.742923347472</v>
       </c>
       <c r="P36" s="3">
-        <v>2.951383382774657</v>
+        <v>2.324883436981007</v>
       </c>
       <c r="Q36" s="4">
         <f>IF(O36=0,0,P36/O36)</f>
@@ -3124,30 +3124,30 @@
         <v>0</v>
       </c>
       <c r="V36" s="3">
-        <v>20021733.97656191</v>
+        <v>20021798.10615849</v>
       </c>
       <c r="W36" s="3">
-        <v>498447.0926206037</v>
+        <v>498757.7532412633</v>
       </c>
       <c r="X36" s="4">
         <f>IF(V36=0,0,W36/V36)</f>
         <v>0</v>
       </c>
       <c r="Y36" s="3">
-        <v>1405956.318006293</v>
+        <v>1405792.016991551</v>
       </c>
       <c r="Z36" s="3">
-        <v>11174.0957452131</v>
+        <v>11273.32705114642</v>
       </c>
       <c r="AA36" s="4">
         <f>IF(Y36=0,0,Z36/Y36)</f>
         <v>0</v>
       </c>
       <c r="AB36" s="3">
-        <v>106414.5769839078</v>
+        <v>103604.4480960104</v>
       </c>
       <c r="AC36" s="3">
-        <v>19.54204489719996</v>
+        <v>27.69693223308423</v>
       </c>
       <c r="AD36" s="4">
         <f>IF(AB36=0,0,AC36/AB36)</f>
@@ -3290,7 +3290,7 @@
         <v>0</v>
       </c>
       <c r="E41" s="3">
-        <f>M41+P41</f>
+        <f>P41+M41</f>
         <v>0</v>
       </c>
       <c r="F41" s="3">
@@ -3387,7 +3387,7 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <f>M42+P42</f>
+        <f>P42+M42</f>
         <v>0</v>
       </c>
       <c r="F42" s="3">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="E43" s="3">
-        <f>M43+P43</f>
+        <f>P43+M43</f>
         <v>0</v>
       </c>
       <c r="F43" s="3">
@@ -3581,7 +3581,7 @@
         <v>0</v>
       </c>
       <c r="E44" s="3">
-        <f>M44+P44</f>
+        <f>P44+M44</f>
         <v>0</v>
       </c>
       <c r="F44" s="3">
@@ -3678,7 +3678,7 @@
         <v>0</v>
       </c>
       <c r="E45" s="3">
-        <f>M45+P45</f>
+        <f>P45+M45</f>
         <v>0</v>
       </c>
       <c r="F45" s="3">
@@ -3898,7 +3898,7 @@
         <v>0</v>
       </c>
       <c r="E50" s="3">
-        <f>M50+P50</f>
+        <f>P50+M50</f>
         <v>0</v>
       </c>
       <c r="F50" s="3">
@@ -3995,7 +3995,7 @@
         <v>0</v>
       </c>
       <c r="E51" s="3">
-        <f>M51+P51</f>
+        <f>P51+M51</f>
         <v>0</v>
       </c>
       <c r="F51" s="3">
@@ -4092,7 +4092,7 @@
         <v>0</v>
       </c>
       <c r="E52" s="3">
-        <f>M52+P52</f>
+        <f>P52+M52</f>
         <v>0</v>
       </c>
       <c r="F52" s="3">
@@ -4189,7 +4189,7 @@
         <v>0</v>
       </c>
       <c r="E53" s="3">
-        <f>M53+P53</f>
+        <f>P53+M53</f>
         <v>0</v>
       </c>
       <c r="F53" s="3">
@@ -4286,7 +4286,7 @@
         <v>0</v>
       </c>
       <c r="E54" s="3">
-        <f>M54+P54</f>
+        <f>P54+M54</f>
         <v>0</v>
       </c>
       <c r="F54" s="3">

--- a/5000_analyze_results/results_spreadsheet.xlsx
+++ b/5000_analyze_results/results_spreadsheet.xlsx
@@ -123,12 +123,64 @@
         </r>
       </text>
     </comment>
+    <comment ref="J57" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Based on correlation between serum folate and hemoglobin</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K57" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Based on correlation between serum folate and hemoglobin</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W57" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Based on correlation between serum folate and hemoglobin</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X57" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Based on correlation between serum folate and hemoglobin</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="41">
   <si>
     <t>DALYs Averted by Fortification (1000s)</t>
   </si>
@@ -248,6 +300,9 @@
   </si>
   <si>
     <t>Ethiopia -- Salt-- 100% NRV per average intake</t>
+  </si>
+  <si>
+    <t>Ethiopia -- Salt-- DFS-IoFA preliminary standard 45 ppm</t>
   </si>
 </sst>
 </file>
@@ -628,7 +683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD54"/>
+  <dimension ref="A1:AD63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="1.7109375" customWidth="1"/>
@@ -862,10 +917,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="3">
-        <v>363.2527888669509</v>
+        <v>362.8529849538489</v>
       </c>
       <c r="G5" s="3">
-        <v>25.63269042834587</v>
+        <v>25.58090999587317</v>
       </c>
       <c r="H5" s="4">
         <f>IF(F5=0,0,G5/F5)</f>
@@ -902,10 +957,10 @@
         <v>0</v>
       </c>
       <c r="S5" s="3">
-        <v>5246.953936438476</v>
+        <v>4684.597214204819</v>
       </c>
       <c r="T5" s="3">
-        <v>370.2478000623951</v>
+        <v>330.261193024865</v>
       </c>
       <c r="U5" s="4">
         <f>IF(S5=0,0,T5/S5)</f>
@@ -959,10 +1014,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="3">
-        <v>320.8959288091749</v>
+        <v>320.5427437766894</v>
       </c>
       <c r="G6" s="3">
-        <v>19.3141818814585</v>
+        <v>19.27496735575946</v>
       </c>
       <c r="H6" s="4">
         <f>IF(F6=0,0,G6/F6)</f>
@@ -999,10 +1054,10 @@
         <v>0</v>
       </c>
       <c r="S6" s="3">
-        <v>4635.136214932357</v>
+        <v>4138.352740079671</v>
       </c>
       <c r="T6" s="3">
-        <v>278.980989982505</v>
+        <v>248.8486029408423</v>
       </c>
       <c r="U6" s="4">
         <f>IF(S6=0,0,T6/S6)</f>
@@ -1056,10 +1111,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="3">
-        <v>288.0891253989829</v>
+        <v>287.7720482472399</v>
       </c>
       <c r="G7" s="3">
-        <v>14.66402867711027</v>
+        <v>14.63412098323711</v>
       </c>
       <c r="H7" s="4">
         <f>IF(F7=0,0,G7/F7)</f>
@@ -1096,10 +1151,10 @@
         <v>0</v>
       </c>
       <c r="S7" s="3">
-        <v>4161.262946589416</v>
+        <v>3715.268142871963</v>
       </c>
       <c r="T7" s="3">
-        <v>211.8125045409952</v>
+        <v>188.9331636589077</v>
       </c>
       <c r="U7" s="4">
         <f>IF(S7=0,0,T7/S7)</f>
@@ -1153,10 +1208,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="3">
-        <v>271.6538476703636</v>
+        <v>271.3548595424364</v>
       </c>
       <c r="G8" s="3">
-        <v>12.01916291244561</v>
+        <v>11.99457042306478</v>
       </c>
       <c r="H8" s="4">
         <f>IF(F8=0,0,G8/F8)</f>
@@ -1193,10 +1248,10 @@
         <v>0</v>
       </c>
       <c r="S8" s="3">
-        <v>3923.86588366907</v>
+        <v>3503.314763237015</v>
       </c>
       <c r="T8" s="3">
-        <v>173.6091121360946</v>
+        <v>154.8553643471328</v>
       </c>
       <c r="U8" s="4">
         <f>IF(S8=0,0,T8/S8)</f>
@@ -1250,10 +1305,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="3">
-        <v>231.3561787321935</v>
+        <v>231.1015430943892</v>
       </c>
       <c r="G9" s="3">
-        <v>4.583486877183867</v>
+        <v>4.573997896683897</v>
       </c>
       <c r="H9" s="4">
         <f>IF(F9=0,0,G9/F9)</f>
@@ -1290,10 +1345,10 @@
         <v>0</v>
       </c>
       <c r="S9" s="3">
-        <v>3341.791859340324</v>
+        <v>2983.6261237209</v>
       </c>
       <c r="T9" s="3">
-        <v>66.20553303353427</v>
+        <v>59.05239502799986</v>
       </c>
       <c r="U9" s="4">
         <f>IF(S9=0,0,T9/S9)</f>
@@ -1470,10 +1525,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>363.2527888669509</v>
+        <v>362.8529849538489</v>
       </c>
       <c r="G14" s="3">
-        <v>171.7832906162409</v>
+        <v>236.1367268275891</v>
       </c>
       <c r="H14" s="4">
         <f>IF(F14=0,0,G14/F14)</f>
@@ -1483,7 +1538,7 @@
         <v>4771.261231090824</v>
       </c>
       <c r="J14" s="3">
-        <v>313.4364668127587</v>
+        <v>574.7557064126702</v>
       </c>
       <c r="K14" s="4">
         <f>IF(I14=0,0,J14/I14)</f>
@@ -1493,7 +1548,7 @@
         <v>16522.03201076821</v>
       </c>
       <c r="M14" s="3">
-        <v>47.24953973846883</v>
+        <v>86.04892678987235</v>
       </c>
       <c r="N14" s="4">
         <f>IF(L14=0,0,M14/L14)</f>
@@ -1503,17 +1558,17 @@
         <v>506.7963637284521</v>
       </c>
       <c r="P14" s="3">
-        <v>15.01370971237042</v>
+        <v>22.007135649256</v>
       </c>
       <c r="Q14" s="4">
         <f>IF(O14=0,0,P14/O14)</f>
         <v>0</v>
       </c>
       <c r="S14" s="3">
-        <v>5246.953936438476</v>
+        <v>4684.597214204819</v>
       </c>
       <c r="T14" s="3">
-        <v>2481.299636335</v>
+        <v>3048.632637839994</v>
       </c>
       <c r="U14" s="4">
         <f>IF(S14=0,0,T14/S14)</f>
@@ -1523,7 +1578,7 @@
         <v>131696392.1412486</v>
       </c>
       <c r="W14" s="3">
-        <v>6833090.704050109</v>
+        <v>12551111.5207074</v>
       </c>
       <c r="X14" s="4">
         <f>IF(V14=0,0,W14/V14)</f>
@@ -1533,7 +1588,7 @@
         <v>3016543.050471412</v>
       </c>
       <c r="Z14" s="3">
-        <v>83335.51165489713</v>
+        <v>119816.4398438525</v>
       </c>
       <c r="AA14" s="4">
         <f>IF(Y14=0,0,Z14/Y14)</f>
@@ -1543,7 +1598,7 @@
         <v>184370.0487466397</v>
       </c>
       <c r="AC14" s="3">
-        <v>525.1747063550574</v>
+        <v>956.396139554854</v>
       </c>
       <c r="AD14" s="4">
         <f>IF(AB14=0,0,AC14/AB14)</f>
@@ -1567,10 +1622,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="3">
-        <v>320.8959288091749</v>
+        <v>320.5427437766894</v>
       </c>
       <c r="G15" s="3">
-        <v>136.8384804720325</v>
+        <v>192.7207779040032</v>
       </c>
       <c r="H15" s="4">
         <f>IF(F15=0,0,G15/F15)</f>
@@ -1580,7 +1635,7 @@
         <v>4315.21265961095</v>
       </c>
       <c r="J15" s="3">
-        <v>279.4920962596657</v>
+        <v>513.5291981071886</v>
       </c>
       <c r="K15" s="4">
         <f>IF(I15=0,0,J15/I15)</f>
@@ -1590,7 +1645,7 @@
         <v>13642.46320366066</v>
       </c>
       <c r="M15" s="3">
-        <v>33.80926878551207</v>
+        <v>63.50293867536261</v>
       </c>
       <c r="N15" s="4">
         <f>IF(L15=0,0,M15/L15)</f>
@@ -1600,17 +1655,17 @@
         <v>297.573370209569</v>
       </c>
       <c r="P15" s="3">
-        <v>8.344677452836709</v>
+        <v>10.47285401756043</v>
       </c>
       <c r="Q15" s="4">
         <f>IF(O15=0,0,P15/O15)</f>
         <v>0</v>
       </c>
       <c r="S15" s="3">
-        <v>4635.136214932357</v>
+        <v>4138.352740079671</v>
       </c>
       <c r="T15" s="3">
-        <v>1976.544229731896</v>
+        <v>2488.112973366633</v>
       </c>
       <c r="U15" s="4">
         <f>IF(S15=0,0,T15/S15)</f>
@@ -1620,7 +1675,7 @@
         <v>123352422.8520256</v>
       </c>
       <c r="W15" s="3">
-        <v>6427646.223230928</v>
+        <v>11833860.56680924</v>
       </c>
       <c r="X15" s="4">
         <f>IF(V15=0,0,W15/V15)</f>
@@ -1630,7 +1685,7 @@
         <v>1788522.531513863</v>
       </c>
       <c r="Z15" s="3">
-        <v>46989.24380333396</v>
+        <v>68972.54388265847</v>
       </c>
       <c r="AA15" s="4">
         <f>IF(Y15=0,0,Z15/Y15)</f>
@@ -1640,7 +1695,7 @@
         <v>152242.8474441103</v>
       </c>
       <c r="AC15" s="3">
-        <v>375.8130926210724</v>
+        <v>705.8540778075403</v>
       </c>
       <c r="AD15" s="4">
         <f>IF(AB15=0,0,AC15/AB15)</f>
@@ -1664,10 +1719,10 @@
         <v>0</v>
       </c>
       <c r="F16" s="3">
-        <v>288.0891253989829</v>
+        <v>287.7720482472399</v>
       </c>
       <c r="G16" s="3">
-        <v>109.4384294573394</v>
+        <v>161.6901662622983</v>
       </c>
       <c r="H16" s="4">
         <f>IF(F16=0,0,G16/F16)</f>
@@ -1677,7 +1732,7 @@
         <v>4220.065012527612</v>
       </c>
       <c r="J16" s="3">
-        <v>242.9326465501119</v>
+        <v>463.6088522818093</v>
       </c>
       <c r="K16" s="4">
         <f>IF(I16=0,0,J16/I16)</f>
@@ -1687,7 +1742,7 @@
         <v>12108.71669338748</v>
       </c>
       <c r="M16" s="3">
-        <v>21.03499195626378</v>
+        <v>39.67505093289166</v>
       </c>
       <c r="N16" s="4">
         <f>IF(L16=0,0,M16/L16)</f>
@@ -1697,17 +1752,17 @@
         <v>350.6722046220511</v>
       </c>
       <c r="P16" s="3">
-        <v>7.230571189964132</v>
+        <v>12.10934546388395</v>
       </c>
       <c r="Q16" s="4">
         <f>IF(O16=0,0,P16/O16)</f>
         <v>0</v>
       </c>
       <c r="S16" s="3">
-        <v>4161.262946589416</v>
+        <v>3715.268142871963</v>
       </c>
       <c r="T16" s="3">
-        <v>1580.768037679544</v>
+        <v>2087.493651273165</v>
       </c>
       <c r="U16" s="4">
         <f>IF(S16=0,0,T16/S16)</f>
@@ -1717,7 +1772,7 @@
         <v>121045766.1486471</v>
       </c>
       <c r="W16" s="3">
-        <v>5624078.184110358</v>
+        <v>10757671.65764305</v>
       </c>
       <c r="X16" s="4">
         <f>IF(V16=0,0,W16/V16)</f>
@@ -1727,7 +1782,7 @@
         <v>2261372.687672075</v>
       </c>
       <c r="Z16" s="3">
-        <v>48881.70247347467</v>
+        <v>74873.55223910837</v>
       </c>
       <c r="AA16" s="4">
         <f>IF(Y16=0,0,Z16/Y16)</f>
@@ -1737,7 +1792,7 @@
         <v>135116.8520887052</v>
       </c>
       <c r="AC16" s="3">
-        <v>233.6786537451553</v>
+        <v>440.8576663439744</v>
       </c>
       <c r="AD16" s="4">
         <f>IF(AB16=0,0,AC16/AB16)</f>
@@ -1761,10 +1816,10 @@
         <v>0</v>
       </c>
       <c r="F17" s="3">
-        <v>271.6538476703636</v>
+        <v>271.3548595424364</v>
       </c>
       <c r="G17" s="3">
-        <v>93.2369079938145</v>
+        <v>144.676134576367</v>
       </c>
       <c r="H17" s="4">
         <f>IF(F17=0,0,G17/F17)</f>
@@ -1774,7 +1829,7 @@
         <v>3866.462901477351</v>
       </c>
       <c r="J17" s="3">
-        <v>199.0834636001452</v>
+        <v>398.1802336081071</v>
       </c>
       <c r="K17" s="4">
         <f>IF(I17=0,0,J17/I17)</f>
@@ -1784,7 +1839,7 @@
         <v>11547.79616860948</v>
       </c>
       <c r="M17" s="3">
-        <v>23.62541006216407</v>
+        <v>43.56478136807494</v>
       </c>
       <c r="N17" s="4">
         <f>IF(L17=0,0,M17/L17)</f>
@@ -1794,17 +1849,17 @@
         <v>341.4996444598856</v>
       </c>
       <c r="P17" s="3">
-        <v>8.565760149411567</v>
+        <v>11.67196939960052</v>
       </c>
       <c r="Q17" s="4">
         <f>IF(O17=0,0,P17/O17)</f>
         <v>0</v>
       </c>
       <c r="S17" s="3">
-        <v>3923.86588366907</v>
+        <v>3503.314763237015</v>
       </c>
       <c r="T17" s="3">
-        <v>1346.747434329211</v>
+        <v>1867.834757056148</v>
       </c>
       <c r="U17" s="4">
         <f>IF(S17=0,0,T17/S17)</f>
@@ -1814,7 +1869,7 @@
         <v>114934295.1461658</v>
       </c>
       <c r="W17" s="3">
-        <v>4858362.349655852</v>
+        <v>9734869.333226398</v>
       </c>
       <c r="X17" s="4">
         <f>IF(V17=0,0,W17/V17)</f>
@@ -1824,7 +1879,7 @@
         <v>2020070.981660255</v>
       </c>
       <c r="Z17" s="3">
-        <v>39029.85600388492</v>
+        <v>61669.62522799801</v>
       </c>
       <c r="AA17" s="4">
         <f>IF(Y17=0,0,Z17/Y17)</f>
@@ -1834,7 +1889,7 @@
         <v>128855.7096033067</v>
       </c>
       <c r="AC17" s="3">
-        <v>262.5873531775433</v>
+        <v>484.2207154925272</v>
       </c>
       <c r="AD17" s="4">
         <f>IF(AB17=0,0,AC17/AB17)</f>
@@ -1858,10 +1913,10 @@
         <v>0</v>
       </c>
       <c r="F18" s="3">
-        <v>231.3561787321935</v>
+        <v>231.1015430943892</v>
       </c>
       <c r="G18" s="3">
-        <v>41.44780297413218</v>
+        <v>78.90054096724134</v>
       </c>
       <c r="H18" s="4">
         <f>IF(F18=0,0,G18/F18)</f>
@@ -1871,7 +1926,7 @@
         <v>3364.297008165505</v>
       </c>
       <c r="J18" s="3">
-        <v>100.8268812075821</v>
+        <v>227.1775098421918</v>
       </c>
       <c r="K18" s="4">
         <f>IF(I18=0,0,J18/I18)</f>
@@ -1881,7 +1936,7 @@
         <v>10928.70618227773</v>
       </c>
       <c r="M18" s="3">
-        <v>6.068353288041428</v>
+        <v>16.47360831031948</v>
       </c>
       <c r="N18" s="4">
         <f>IF(L18=0,0,M18/L18)</f>
@@ -1891,17 +1946,17 @@
         <v>209.6942036708812</v>
       </c>
       <c r="P18" s="3">
-        <v>2.195864039865555</v>
+        <v>3.993387343400682</v>
       </c>
       <c r="Q18" s="4">
         <f>IF(O18=0,0,P18/O18)</f>
         <v>0</v>
       </c>
       <c r="S18" s="3">
-        <v>3341.791859340324</v>
+        <v>2983.6261237209</v>
       </c>
       <c r="T18" s="3">
-        <v>598.6869740221155</v>
+        <v>1018.641901103288</v>
       </c>
       <c r="U18" s="4">
         <f>IF(S18=0,0,T18/S18)</f>
@@ -1911,7 +1966,7 @@
         <v>107056308.1865083</v>
       </c>
       <c r="W18" s="3">
-        <v>2679940.421917364</v>
+        <v>6047039.221417382</v>
       </c>
       <c r="X18" s="4">
         <f>IF(V18=0,0,W18/V18)</f>
@@ -1921,7 +1976,7 @@
         <v>1277060.928257236</v>
       </c>
       <c r="Z18" s="3">
-        <v>14533.69784286129</v>
+        <v>25179.07844351418</v>
       </c>
       <c r="AA18" s="4">
         <f>IF(Y18=0,0,Z18/Y18)</f>
@@ -1931,7 +1986,7 @@
         <v>121958.5757303956</v>
       </c>
       <c r="AC18" s="3">
-        <v>67.45363200891006</v>
+        <v>183.0884297384764</v>
       </c>
       <c r="AD18" s="4">
         <f>IF(AB18=0,0,AC18/AB18)</f>
@@ -2078,10 +2133,10 @@
         <v>0</v>
       </c>
       <c r="F23" s="3">
-        <v>414.1483857332581</v>
+        <v>412.7408750394843</v>
       </c>
       <c r="G23" s="3">
-        <v>268.7588990063936</v>
+        <v>213.4118382061803</v>
       </c>
       <c r="H23" s="4">
         <f>IF(F23=0,0,G23/F23)</f>
@@ -2091,7 +2146,7 @@
         <v>1006.030840012209</v>
       </c>
       <c r="J23" s="3">
-        <v>137.6545265903092</v>
+        <v>86.86733689510881</v>
       </c>
       <c r="K23" s="4">
         <f>IF(I23=0,0,J23/I23)</f>
@@ -2101,7 +2156,7 @@
         <v>14879.51549115505</v>
       </c>
       <c r="M23" s="3">
-        <v>56.06812795555219</v>
+        <v>37.13764736627601</v>
       </c>
       <c r="N23" s="4">
         <f>IF(L23=0,0,M23/L23)</f>
@@ -2111,17 +2166,17 @@
         <v>503.5634310516943</v>
       </c>
       <c r="P23" s="3">
-        <v>18.84933287622535</v>
+        <v>12.79226160240127</v>
       </c>
       <c r="Q23" s="4">
         <f>IF(O23=0,0,P23/O23)</f>
         <v>0</v>
       </c>
       <c r="S23" s="3">
-        <v>7596.11775664314</v>
+        <v>12734.95565684622</v>
       </c>
       <c r="T23" s="3">
-        <v>4929.451170946294</v>
+        <v>6584.73744802172</v>
       </c>
       <c r="U23" s="4">
         <f>IF(S23=0,0,T23/S23)</f>
@@ -2131,7 +2186,7 @@
         <v>24943823.20853924</v>
       </c>
       <c r="W23" s="3">
-        <v>2711281.827288892</v>
+        <v>1711094.158100959</v>
       </c>
       <c r="X23" s="4">
         <f>IF(V23=0,0,W23/V23)</f>
@@ -2141,7 +2196,7 @@
         <v>2561085.175981381</v>
       </c>
       <c r="Z23" s="3">
-        <v>107277.175427835</v>
+        <v>67792.87612257898</v>
       </c>
       <c r="AA23" s="4">
         <f>IF(Y23=0,0,Z23/Y23)</f>
@@ -2151,7 +2206,7 @@
         <v>167649.5308066797</v>
       </c>
       <c r="AC23" s="3">
-        <v>622.3663595898252</v>
+        <v>412.1955208801664</v>
       </c>
       <c r="AD23" s="4">
         <f>IF(AB23=0,0,AC23/AB23)</f>
@@ -2175,10 +2230,10 @@
         <v>0</v>
       </c>
       <c r="F24" s="3">
-        <v>423.4925012827377</v>
+        <v>422.0532339939541</v>
       </c>
       <c r="G24" s="3">
-        <v>265.196859797002</v>
+        <v>208.3471500632799</v>
       </c>
       <c r="H24" s="4">
         <f>IF(F24=0,0,G24/F24)</f>
@@ -2188,7 +2243,7 @@
         <v>964.5986558077452</v>
       </c>
       <c r="J24" s="3">
-        <v>140.6009727878995</v>
+        <v>88.73307073881558</v>
       </c>
       <c r="K24" s="4">
         <f>IF(I24=0,0,J24/I24)</f>
@@ -2198,7 +2253,7 @@
         <v>15413.09139410279</v>
       </c>
       <c r="M24" s="3">
-        <v>54.75217633925006</v>
+        <v>31.57339394500479</v>
       </c>
       <c r="N24" s="4">
         <f>IF(L24=0,0,M24/L24)</f>
@@ -2208,17 +2263,17 @@
         <v>427.6878840211459</v>
       </c>
       <c r="P24" s="3">
-        <v>20.50220103713742</v>
+        <v>13.53889125172485</v>
       </c>
       <c r="Q24" s="4">
         <f>IF(O24=0,0,P24/O24)</f>
         <v>0</v>
       </c>
       <c r="S24" s="3">
-        <v>7767.503193579848</v>
+        <v>13022.28479122008</v>
       </c>
       <c r="T24" s="3">
-        <v>4864.117898572401</v>
+        <v>6428.468508316091</v>
       </c>
       <c r="U24" s="4">
         <f>IF(S24=0,0,T24/S24)</f>
@@ -2228,7 +2283,7 @@
         <v>24665300.63578367</v>
       </c>
       <c r="W24" s="3">
-        <v>2871454.841513783</v>
+        <v>1812415.629343331</v>
       </c>
       <c r="X24" s="4">
         <f>IF(V24=0,0,W24/V24)</f>
@@ -2238,7 +2293,7 @@
         <v>2216806.226901517</v>
       </c>
       <c r="Z24" s="3">
-        <v>105930.2324554906</v>
+        <v>66880.27345653391</v>
       </c>
       <c r="AA24" s="4">
         <f>IF(Y24=0,0,Z24/Y24)</f>
@@ -2248,7 +2303,7 @@
         <v>173674.428183023</v>
       </c>
       <c r="AC24" s="3">
-        <v>607.7032778193534</v>
+        <v>350.2847311827354</v>
       </c>
       <c r="AD24" s="4">
         <f>IF(AB24=0,0,AC24/AB24)</f>
@@ -2272,10 +2327,10 @@
         <v>0</v>
       </c>
       <c r="F25" s="3">
-        <v>383.3772465961786</v>
+        <v>382.0743136549376</v>
       </c>
       <c r="G25" s="3">
-        <v>207.6861063739965</v>
+        <v>157.1453841591108</v>
       </c>
       <c r="H25" s="4">
         <f>IF(F25=0,0,G25/F25)</f>
@@ -2285,7 +2340,7 @@
         <v>794.1006249062289</v>
       </c>
       <c r="J25" s="3">
-        <v>130.4419380447662</v>
+        <v>82.29511533396365</v>
       </c>
       <c r="K25" s="4">
         <f>IF(I25=0,0,J25/I25)</f>
@@ -2295,7 +2350,7 @@
         <v>13666.60844459826</v>
       </c>
       <c r="M25" s="3">
-        <v>39.80089049636759</v>
+        <v>25.40226683093235</v>
       </c>
       <c r="N25" s="4">
         <f>IF(L25=0,0,M25/L25)</f>
@@ -2305,17 +2360,17 @@
         <v>410.8336896551561</v>
       </c>
       <c r="P25" s="3">
-        <v>18.67755932054459</v>
+        <v>11.78005736867187</v>
       </c>
       <c r="Q25" s="4">
         <f>IF(O25=0,0,P25/O25)</f>
         <v>0</v>
       </c>
       <c r="S25" s="3">
-        <v>7031.727783282595</v>
+        <v>11788.75109364953</v>
       </c>
       <c r="T25" s="3">
-        <v>3809.282312286219</v>
+        <v>4848.658371315645</v>
       </c>
       <c r="U25" s="4">
         <f>IF(S25=0,0,T25/S25)</f>
@@ -2325,7 +2380,7 @@
         <v>22725958.89165936</v>
       </c>
       <c r="W25" s="3">
-        <v>3050344.148597278</v>
+        <v>1925420.011185676</v>
       </c>
       <c r="X25" s="4">
         <f>IF(V25=0,0,W25/V25)</f>
@@ -2335,7 +2390,7 @@
         <v>2114085.557833027</v>
       </c>
       <c r="Z25" s="3">
-        <v>98409.80085989856</v>
+        <v>62043.96734931064</v>
       </c>
       <c r="AA25" s="4">
         <f>IF(Y25=0,0,Z25/Y25)</f>
@@ -2345,7 +2400,7 @@
         <v>153960.7293583194</v>
       </c>
       <c r="AC25" s="3">
-        <v>441.5216844210227</v>
+        <v>281.8570162540418</v>
       </c>
       <c r="AD25" s="4">
         <f>IF(AB25=0,0,AC25/AB25)</f>
@@ -2369,10 +2424,10 @@
         <v>0</v>
       </c>
       <c r="F26" s="3">
-        <v>339.8250758454431</v>
+        <v>338.6701578384149</v>
       </c>
       <c r="G26" s="3">
-        <v>163.9650491569163</v>
+        <v>121.0430906924064</v>
       </c>
       <c r="H26" s="4">
         <f>IF(F26=0,0,G26/F26)</f>
@@ -2382,7 +2437,7 @@
         <v>721.6494802184835</v>
       </c>
       <c r="J26" s="3">
-        <v>122.2476639782248</v>
+        <v>77.17266564486199</v>
       </c>
       <c r="K26" s="4">
         <f>IF(I26=0,0,J26/I26)</f>
@@ -2392,7 +2447,7 @@
         <v>12078.7457080966</v>
       </c>
       <c r="M26" s="3">
-        <v>28.4645291917026</v>
+        <v>18.92579680037685</v>
       </c>
       <c r="N26" s="4">
         <f>IF(L26=0,0,M26/L26)</f>
@@ -2402,17 +2457,17 @@
         <v>388.5202631627004</v>
       </c>
       <c r="P26" s="3">
-        <v>15.74235513104481</v>
+        <v>9.65561708555062</v>
       </c>
       <c r="Q26" s="4">
         <f>IF(O26=0,0,P26/O26)</f>
         <v>0</v>
       </c>
       <c r="S26" s="3">
-        <v>6232.914051353447</v>
+        <v>10449.53311676904</v>
       </c>
       <c r="T26" s="3">
-        <v>3007.370943060754</v>
+        <v>3734.736455137735</v>
       </c>
       <c r="U26" s="4">
         <f>IF(S26=0,0,T26/S26)</f>
@@ -2422,7 +2477,7 @@
         <v>21493332.04664342</v>
       </c>
       <c r="W26" s="3">
-        <v>3023273.37047838</v>
+        <v>1908378.392676797</v>
       </c>
       <c r="X26" s="4">
         <f>IF(V26=0,0,W26/V26)</f>
@@ -2432,7 +2487,7 @@
         <v>1925897.452986733</v>
       </c>
       <c r="Z26" s="3">
-        <v>82371.74438121915</v>
+        <v>52002.08453737316</v>
       </c>
       <c r="AA26" s="4">
         <f>IF(Y26=0,0,Z26/Y26)</f>
@@ -2442,7 +2497,7 @@
         <v>136092.9496053835</v>
       </c>
       <c r="AC26" s="3">
-        <v>316.0708737183886</v>
+        <v>210.1708387096587</v>
       </c>
       <c r="AD26" s="4">
         <f>IF(AB26=0,0,AC26/AB26)</f>
@@ -2466,10 +2521,10 @@
         <v>0</v>
       </c>
       <c r="F27" s="3">
-        <v>298.4746794483207</v>
+        <v>297.4602934996698</v>
       </c>
       <c r="G27" s="3">
-        <v>136.2522506171126</v>
+        <v>99.54060524581827</v>
       </c>
       <c r="H27" s="4">
         <f>IF(F27=0,0,G27/F27)</f>
@@ -2479,7 +2534,7 @@
         <v>613.496298429298</v>
       </c>
       <c r="J27" s="3">
-        <v>110.1680808232352</v>
+        <v>69.54268932890368</v>
       </c>
       <c r="K27" s="4">
         <f>IF(I27=0,0,J27/I27)</f>
@@ -2489,7 +2544,7 @@
         <v>9193.681247525743</v>
       </c>
       <c r="M27" s="3">
-        <v>21.72556047260389</v>
+        <v>14.23950953404792</v>
       </c>
       <c r="N27" s="4">
         <f>IF(L27=0,0,M27/L27)</f>
@@ -2499,17 +2554,17 @@
         <v>285.742923347472</v>
       </c>
       <c r="P27" s="3">
-        <v>13.57646327128552</v>
+        <v>8.734878812706157</v>
       </c>
       <c r="Q27" s="4">
         <f>IF(O27=0,0,P27/O27)</f>
         <v>0</v>
       </c>
       <c r="S27" s="3">
-        <v>5474.484244219731</v>
+        <v>9178.019131321482</v>
       </c>
       <c r="T27" s="3">
-        <v>2499.075635566639</v>
+        <v>3071.285812775053</v>
       </c>
       <c r="U27" s="4">
         <f>IF(S27=0,0,T27/S27)</f>
@@ -2519,7 +2574,7 @@
         <v>20021798.10615849</v>
       </c>
       <c r="W27" s="3">
-        <v>3027627.545589577</v>
+        <v>1911129.785046071</v>
       </c>
       <c r="X27" s="4">
         <f>IF(V27=0,0,W27/V27)</f>
@@ -2529,7 +2584,7 @@
         <v>1405792.016991551</v>
       </c>
       <c r="Z27" s="3">
-        <v>68362.23607465718</v>
+        <v>42911.84621676616</v>
       </c>
       <c r="AA27" s="4">
         <f>IF(Y27=0,0,Z27/Y27)</f>
@@ -2539,7 +2594,7 @@
         <v>103604.4480960104</v>
       </c>
       <c r="AC27" s="3">
-        <v>241.1262335583597</v>
+        <v>158.0354368591943</v>
       </c>
       <c r="AD27" s="4">
         <f>IF(AB27=0,0,AC27/AB27)</f>
@@ -2686,10 +2741,10 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>414.1483857332581</v>
+        <v>412.7408750394843</v>
       </c>
       <c r="G32" s="3">
-        <v>17.33318367138942</v>
+        <v>44.60952190125041</v>
       </c>
       <c r="H32" s="4">
         <f>IF(F32=0,0,G32/F32)</f>
@@ -2699,7 +2754,7 @@
         <v>1006.030840012209</v>
       </c>
       <c r="J32" s="3">
-        <v>11.68040300392487</v>
+        <v>32.09737479080761</v>
       </c>
       <c r="K32" s="4">
         <f>IF(I32=0,0,J32/I32)</f>
@@ -2709,7 +2764,7 @@
         <v>14879.51549115505</v>
       </c>
       <c r="M32" s="3">
-        <v>0.8794182835407555</v>
+        <v>3.229242778953165</v>
       </c>
       <c r="N32" s="4">
         <f>IF(L32=0,0,M32/L32)</f>
@@ -2719,17 +2774,17 @@
         <v>503.5634310516943</v>
       </c>
       <c r="P32" s="3">
-        <v>0.9890495645757182</v>
+        <v>3.068391177042213</v>
       </c>
       <c r="Q32" s="4">
         <f>IF(O32=0,0,P32/O32)</f>
         <v>0</v>
       </c>
       <c r="S32" s="3">
-        <v>7596.11775664314</v>
+        <v>12734.95565684622</v>
       </c>
       <c r="T32" s="3">
-        <v>317.9172219451793</v>
+        <v>1376.409068355992</v>
       </c>
       <c r="U32" s="4">
         <f>IF(S32=0,0,T32/S32)</f>
@@ -2739,7 +2794,7 @@
         <v>24943823.20853924</v>
       </c>
       <c r="W32" s="3">
-        <v>226849.3098196089</v>
+        <v>623654.2003708966</v>
       </c>
       <c r="X32" s="4">
         <f>IF(V32=0,0,W32/V32)</f>
@@ -2749,7 +2804,7 @@
         <v>2561085.175981381</v>
       </c>
       <c r="Z32" s="3">
-        <v>8042.616008783225</v>
+        <v>21651.94560616976</v>
       </c>
       <c r="AA32" s="4">
         <f>IF(Y32=0,0,Z32/Y32)</f>
@@ -2759,7 +2814,7 @@
         <v>167649.5308066797</v>
       </c>
       <c r="AC32" s="3">
-        <v>9.775387846952071</v>
+        <v>35.843088772177</v>
       </c>
       <c r="AD32" s="4">
         <f>IF(AB32=0,0,AC32/AB32)</f>
@@ -2783,10 +2838,10 @@
         <v>0</v>
       </c>
       <c r="F33" s="3">
-        <v>423.4925012827377</v>
+        <v>422.0532339939541</v>
       </c>
       <c r="G33" s="3">
-        <v>33.49612922113162</v>
+        <v>82.11660802380734</v>
       </c>
       <c r="H33" s="4">
         <f>IF(F33=0,0,G33/F33)</f>
@@ -2796,7 +2851,7 @@
         <v>964.5986558077452</v>
       </c>
       <c r="J33" s="3">
-        <v>15.53238761472038</v>
+        <v>42.69060008609377</v>
       </c>
       <c r="K33" s="4">
         <f>IF(I33=0,0,J33/I33)</f>
@@ -2806,7 +2861,7 @@
         <v>15413.09139410279</v>
       </c>
       <c r="M33" s="3">
-        <v>2.345310499604791</v>
+        <v>4.543952167578041</v>
       </c>
       <c r="N33" s="4">
         <f>IF(L33=0,0,M33/L33)</f>
@@ -2816,17 +2871,17 @@
         <v>427.6878840211459</v>
       </c>
       <c r="P33" s="3">
-        <v>2.086115786817216</v>
+        <v>5.825039412285958</v>
       </c>
       <c r="Q33" s="4">
         <f>IF(O33=0,0,P33/O33)</f>
         <v>0</v>
       </c>
       <c r="S33" s="3">
-        <v>7767.503193579848</v>
+        <v>13022.28479122008</v>
       </c>
       <c r="T33" s="3">
-        <v>614.3704786026356</v>
+        <v>2533.675303600032</v>
       </c>
       <c r="U33" s="4">
         <f>IF(S33=0,0,T33/S33)</f>
@@ -2836,7 +2891,7 @@
         <v>24665300.63578367</v>
       </c>
       <c r="W33" s="3">
-        <v>312647.3967796117</v>
+        <v>859445.1501166448</v>
       </c>
       <c r="X33" s="4">
         <f>IF(V33=0,0,W33/V33)</f>
@@ -2846,7 +2901,7 @@
         <v>2216806.226901517</v>
       </c>
       <c r="Z33" s="3">
-        <v>11335.14327451494</v>
+        <v>30576.25616931403</v>
       </c>
       <c r="AA33" s="4">
         <f>IF(Y33=0,0,Z33/Y33)</f>
@@ -2856,7 +2911,7 @@
         <v>173674.428183023</v>
       </c>
       <c r="AC33" s="3">
-        <v>26.06770092522493</v>
+        <v>50.50617054261966</v>
       </c>
       <c r="AD33" s="4">
         <f>IF(AB33=0,0,AC33/AB33)</f>
@@ -2880,10 +2935,10 @@
         <v>0</v>
       </c>
       <c r="F34" s="3">
-        <v>383.3772465961786</v>
+        <v>382.0743136549376</v>
       </c>
       <c r="G34" s="3">
-        <v>41.90985526450491</v>
+        <v>98.872168911535</v>
       </c>
       <c r="H34" s="4">
         <f>IF(F34=0,0,G34/F34)</f>
@@ -2893,7 +2948,7 @@
         <v>794.1006249062289</v>
       </c>
       <c r="J34" s="3">
-        <v>17.47281985056156</v>
+        <v>48.03179086984182</v>
       </c>
       <c r="K34" s="4">
         <f>IF(I34=0,0,J34/I34)</f>
@@ -2903,7 +2958,7 @@
         <v>13666.60844459826</v>
       </c>
       <c r="M34" s="3">
-        <v>2.347127422653139</v>
+        <v>7.04667079638131</v>
       </c>
       <c r="N34" s="4">
         <f>IF(L34=0,0,M34/L34)</f>
@@ -2913,17 +2968,17 @@
         <v>410.8336896551561</v>
       </c>
       <c r="P34" s="3">
-        <v>2.356564286178851</v>
+        <v>6.801262350148347</v>
       </c>
       <c r="Q34" s="4">
         <f>IF(O34=0,0,P34/O34)</f>
         <v>0</v>
       </c>
       <c r="S34" s="3">
-        <v>7031.727783282595</v>
+        <v>11788.75109364953</v>
       </c>
       <c r="T34" s="3">
-        <v>768.6911424015352</v>
+        <v>3050.661475348556</v>
       </c>
       <c r="U34" s="4">
         <f>IF(S34=0,0,T34/S34)</f>
@@ -2933,7 +2988,7 @@
         <v>22725958.89165936</v>
       </c>
       <c r="W34" s="3">
-        <v>402664.4387529455</v>
+        <v>1106195.733125906</v>
       </c>
       <c r="X34" s="4">
         <f>IF(V34=0,0,W34/V34)</f>
@@ -2943,7 +2998,7 @@
         <v>2114085.557833027</v>
       </c>
       <c r="Z34" s="3">
-        <v>13360.4379611928</v>
+        <v>36476.45201556338</v>
       </c>
       <c r="AA34" s="4">
         <f>IF(Y34=0,0,Z34/Y34)</f>
@@ -2953,7 +3008,7 @@
         <v>153960.7293583194</v>
       </c>
       <c r="AC34" s="3">
-        <v>26.06770092522493</v>
+        <v>78.20310277567478</v>
       </c>
       <c r="AD34" s="4">
         <f>IF(AB34=0,0,AC34/AB34)</f>
@@ -2977,10 +3032,10 @@
         <v>0</v>
       </c>
       <c r="F35" s="3">
-        <v>339.8250758454431</v>
+        <v>338.6701578384149</v>
       </c>
       <c r="G35" s="3">
-        <v>49.15588258143957</v>
+        <v>111.0000684404046</v>
       </c>
       <c r="H35" s="4">
         <f>IF(F35=0,0,G35/F35)</f>
@@ -2990,7 +3045,7 @@
         <v>721.6494802184835</v>
       </c>
       <c r="J35" s="3">
-        <v>18.98855847346026</v>
+        <v>52.18241248611535</v>
       </c>
       <c r="K35" s="4">
         <f>IF(I35=0,0,J35/I35)</f>
@@ -3000,7 +3055,7 @@
         <v>12078.7457080966</v>
       </c>
       <c r="M35" s="3">
-        <v>2.345336273258552</v>
+        <v>5.727335256190971</v>
       </c>
       <c r="N35" s="4">
         <f>IF(L35=0,0,M35/L35)</f>
@@ -3010,17 +3065,17 @@
         <v>388.5202631627004</v>
       </c>
       <c r="P35" s="3">
-        <v>1.884715648668061</v>
+        <v>6.425640266744071</v>
       </c>
       <c r="Q35" s="4">
         <f>IF(O35=0,0,P35/O35)</f>
         <v>0</v>
       </c>
       <c r="S35" s="3">
-        <v>6232.914051353447</v>
+        <v>10449.53311676904</v>
       </c>
       <c r="T35" s="3">
-        <v>901.5944173227599</v>
+        <v>3424.862995118233</v>
       </c>
       <c r="U35" s="4">
         <f>IF(S35=0,0,T35/S35)</f>
@@ -3030,7 +3085,7 @@
         <v>21493332.04664342</v>
       </c>
       <c r="W35" s="3">
-        <v>462697.4952477962</v>
+        <v>1271558.913595185</v>
       </c>
       <c r="X35" s="4">
         <f>IF(V35=0,0,W35/V35)</f>
@@ -3040,7 +3095,7 @@
         <v>1925897.452986733</v>
       </c>
       <c r="Z35" s="3">
-        <v>12870.78840240557</v>
+        <v>35243.3810336343</v>
       </c>
       <c r="AA35" s="4">
         <f>IF(Y35=0,0,Z35/Y35)</f>
@@ -3050,7 +3105,7 @@
         <v>136092.9496053835</v>
       </c>
       <c r="AC35" s="3">
-        <v>26.06770092522493</v>
+        <v>63.54002100523212</v>
       </c>
       <c r="AD35" s="4">
         <f>IF(AB35=0,0,AC35/AB35)</f>
@@ -3074,10 +3129,10 @@
         <v>0</v>
       </c>
       <c r="F36" s="3">
-        <v>298.4746794483207</v>
+        <v>297.4602934996698</v>
       </c>
       <c r="G36" s="3">
-        <v>47.84221324221152</v>
+        <v>106.0000459180257</v>
       </c>
       <c r="H36" s="4">
         <f>IF(F36=0,0,G36/F36)</f>
@@ -3087,7 +3142,7 @@
         <v>613.496298429298</v>
       </c>
       <c r="J36" s="3">
-        <v>18.40218963211437</v>
+        <v>50.59624545245489</v>
       </c>
       <c r="K36" s="4">
         <f>IF(I36=0,0,J36/I36)</f>
@@ -3097,7 +3152,7 @@
         <v>9193.681247525743</v>
       </c>
       <c r="M36" s="3">
-        <v>2.498986293654889</v>
+        <v>7.336046989347786</v>
       </c>
       <c r="N36" s="4">
         <f>IF(L36=0,0,M36/L36)</f>
@@ -3107,17 +3162,17 @@
         <v>285.742923347472</v>
       </c>
       <c r="P36" s="3">
-        <v>2.324883436981007</v>
+        <v>6.236481271973287</v>
       </c>
       <c r="Q36" s="4">
         <f>IF(O36=0,0,P36/O36)</f>
         <v>0</v>
       </c>
       <c r="S36" s="3">
-        <v>5474.484244219731</v>
+        <v>9178.019131321482</v>
       </c>
       <c r="T36" s="3">
-        <v>877.4997031144685</v>
+        <v>3270.58928743266</v>
       </c>
       <c r="U36" s="4">
         <f>IF(S36=0,0,T36/S36)</f>
@@ -3127,7 +3182,7 @@
         <v>20021798.10615849</v>
       </c>
       <c r="W36" s="3">
-        <v>498757.7532412633</v>
+        <v>1370173.648558669</v>
       </c>
       <c r="X36" s="4">
         <f>IF(V36=0,0,W36/V36)</f>
@@ -3137,7 +3192,7 @@
         <v>1405792.016991551</v>
       </c>
       <c r="Z36" s="3">
-        <v>11273.32705114642</v>
+        <v>30795.86643654411</v>
       </c>
       <c r="AA36" s="4">
         <f>IF(Y36=0,0,Z36/Y36)</f>
@@ -3147,7 +3202,7 @@
         <v>103604.4480960104</v>
       </c>
       <c r="AC36" s="3">
-        <v>27.69693223308423</v>
+        <v>81.46156539136427</v>
       </c>
       <c r="AD36" s="4">
         <f>IF(AB36=0,0,AC36/AB36)</f>
@@ -3286,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="D41" s="3">
-        <f>G41+J41</f>
+        <f>J41+G41</f>
         <v>0</v>
       </c>
       <c r="E41" s="3">
@@ -3294,10 +3349,10 @@
         <v>0</v>
       </c>
       <c r="F41" s="3">
-        <v>155.6881748268545</v>
+        <v>155.3366697637048</v>
       </c>
       <c r="G41" s="3">
-        <v>72.16538725395763</v>
+        <v>81.86999988549339</v>
       </c>
       <c r="H41" s="4">
         <f>IF(F41=0,0,G41/F41)</f>
@@ -3307,7 +3362,7 @@
         <v>382.3073643284127</v>
       </c>
       <c r="J41" s="6">
-        <v>6.931603770051908</v>
+        <v>8.688572781210882</v>
       </c>
       <c r="K41" s="7">
         <f>IF(I41=0,0,J41/I41)</f>
@@ -3334,10 +3389,10 @@
         <v>0</v>
       </c>
       <c r="S41" s="3">
-        <v>2076.357563684252</v>
+        <v>2198.402026122217</v>
       </c>
       <c r="T41" s="3">
-        <v>962.4439866907096</v>
+        <v>1158.665071812607</v>
       </c>
       <c r="U41" s="4">
         <f>IF(S41=0,0,T41/S41)</f>
@@ -3347,7 +3402,7 @@
         <v>9070418.669545408</v>
       </c>
       <c r="W41" s="6">
-        <v>164538.3844167478</v>
+        <v>206244.2943557166</v>
       </c>
       <c r="X41" s="7">
         <f>IF(V41=0,0,W41/V41)</f>
@@ -3383,7 +3438,7 @@
         <v>0</v>
       </c>
       <c r="D42" s="3">
-        <f>G42+J42</f>
+        <f>J42+G42</f>
         <v>0</v>
       </c>
       <c r="E42" s="3">
@@ -3391,10 +3446,10 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>148.0950653551477</v>
+        <v>147.7607036391234</v>
       </c>
       <c r="G42" s="3">
-        <v>72.90814487956493</v>
+        <v>82.20269740785589</v>
       </c>
       <c r="H42" s="4">
         <f>IF(F42=0,0,G42/F42)</f>
@@ -3404,7 +3459,7 @@
         <v>245.090682899663</v>
       </c>
       <c r="J42" s="6">
-        <v>6.008397319649958</v>
+        <v>7.531359140255663</v>
       </c>
       <c r="K42" s="7">
         <f>IF(I42=0,0,J42/I42)</f>
@@ -3431,10 +3486,10 @@
         <v>0</v>
       </c>
       <c r="S42" s="3">
-        <v>1975.090975512128</v>
+        <v>2091.183174942721</v>
       </c>
       <c r="T42" s="3">
-        <v>972.3498797723723</v>
+        <v>1163.373573085103</v>
       </c>
       <c r="U42" s="4">
         <f>IF(S42=0,0,T42/S42)</f>
@@ -3444,7 +3499,7 @@
         <v>7100767.677214347</v>
       </c>
       <c r="W42" s="6">
-        <v>189877.8700925186</v>
+        <v>238006.6357756918</v>
       </c>
       <c r="X42" s="7">
         <f>IF(V42=0,0,W42/V42)</f>
@@ -3480,7 +3535,7 @@
         <v>0</v>
       </c>
       <c r="D43" s="3">
-        <f>G43+J43</f>
+        <f>J43+G43</f>
         <v>0</v>
       </c>
       <c r="E43" s="3">
@@ -3488,10 +3543,10 @@
         <v>0</v>
       </c>
       <c r="F43" s="3">
-        <v>134.7924084512274</v>
+        <v>134.4880808162132</v>
       </c>
       <c r="G43" s="3">
-        <v>72.9461290521218</v>
+        <v>81.3780121199603</v>
       </c>
       <c r="H43" s="4">
         <f>IF(F43=0,0,G43/F43)</f>
@@ -3501,7 +3556,7 @@
         <v>200.4130880433794</v>
       </c>
       <c r="J43" s="6">
-        <v>6.648335109332984</v>
+        <v>8.333503383573669</v>
       </c>
       <c r="K43" s="7">
         <f>IF(I43=0,0,J43/I43)</f>
@@ -3528,10 +3583,10 @@
         <v>0</v>
       </c>
       <c r="S43" s="3">
-        <v>1797.678193133057</v>
+        <v>1903.342396907326</v>
       </c>
       <c r="T43" s="3">
-        <v>972.8564611108482</v>
+        <v>1151.702215571254</v>
       </c>
       <c r="U43" s="4">
         <f>IF(S43=0,0,T43/S43)</f>
@@ -3541,7 +3596,7 @@
         <v>6292834.208210533</v>
       </c>
       <c r="W43" s="6">
-        <v>222967.1563095488</v>
+        <v>279483.1369019002</v>
       </c>
       <c r="X43" s="7">
         <f>IF(V43=0,0,W43/V43)</f>
@@ -3577,7 +3632,7 @@
         <v>0</v>
       </c>
       <c r="D44" s="3">
-        <f>G44+J44</f>
+        <f>J44+G44</f>
         <v>0</v>
       </c>
       <c r="E44" s="3">
@@ -3585,10 +3640,10 @@
         <v>0</v>
       </c>
       <c r="F44" s="3">
-        <v>118.7821311155358</v>
+        <v>118.5139506930648</v>
       </c>
       <c r="G44" s="3">
-        <v>33.21257251634332</v>
+        <v>39.16266033894262</v>
       </c>
       <c r="H44" s="4">
         <f>IF(F44=0,0,G44/F44)</f>
@@ -3598,7 +3653,7 @@
         <v>193.9015574705648</v>
       </c>
       <c r="J44" s="6">
-        <v>2.593667459385906</v>
+        <v>3.251090114021907</v>
       </c>
       <c r="K44" s="7">
         <f>IF(I44=0,0,J44/I44)</f>
@@ -3625,10 +3680,10 @@
         <v>0</v>
       </c>
       <c r="S44" s="3">
-        <v>1584.154844429043</v>
+        <v>1677.268540156761</v>
       </c>
       <c r="T44" s="3">
-        <v>442.9442135243412</v>
+        <v>554.2495018622074</v>
       </c>
       <c r="U44" s="4">
         <f>IF(S44=0,0,T44/S44)</f>
@@ -3638,7 +3693,7 @@
         <v>6053045.584847068</v>
       </c>
       <c r="W44" s="6">
-        <v>92120.66669745091</v>
+        <v>115470.6967978468</v>
       </c>
       <c r="X44" s="7">
         <f>IF(V44=0,0,W44/V44)</f>
@@ -3674,7 +3729,7 @@
         <v>0</v>
       </c>
       <c r="D45" s="3">
-        <f>G45+J45</f>
+        <f>J45+G45</f>
         <v>0</v>
       </c>
       <c r="E45" s="3">
@@ -3682,10 +3737,10 @@
         <v>0</v>
       </c>
       <c r="F45" s="3">
-        <v>93.70721146478344</v>
+        <v>93.49564395607489</v>
       </c>
       <c r="G45" s="3">
-        <v>19.08558195037654</v>
+        <v>22.85792253853465</v>
       </c>
       <c r="H45" s="4">
         <f>IF(F45=0,0,G45/F45)</f>
@@ -3695,7 +3750,7 @@
         <v>136.6145524202559</v>
       </c>
       <c r="J45" s="6">
-        <v>1.96286239209451</v>
+        <v>2.460393484535132</v>
       </c>
       <c r="K45" s="7">
         <f>IF(I45=0,0,J45/I45)</f>
@@ -3722,10 +3777,10 @@
         <v>0</v>
       </c>
       <c r="S45" s="3">
-        <v>1249.73959976761</v>
+        <v>1323.196985098892</v>
       </c>
       <c r="T45" s="3">
-        <v>254.5375876109539</v>
+        <v>323.4967203693753</v>
       </c>
       <c r="U45" s="4">
         <f>IF(S45=0,0,T45/S45)</f>
@@ -3735,7 +3790,7 @@
         <v>4890905.466101354</v>
       </c>
       <c r="W45" s="6">
-        <v>76901.85631352663</v>
+        <v>96394.34072632995</v>
       </c>
       <c r="X45" s="7">
         <f>IF(V45=0,0,W45/V45)</f>
@@ -3894,7 +3949,7 @@
         <v>0</v>
       </c>
       <c r="D50" s="3">
-        <f>G50+J50</f>
+        <f>J50+G50</f>
         <v>0</v>
       </c>
       <c r="E50" s="3">
@@ -3902,10 +3957,10 @@
         <v>0</v>
       </c>
       <c r="F50" s="3">
-        <v>155.6881748268545</v>
+        <v>155.3366697637048</v>
       </c>
       <c r="G50" s="3">
-        <v>128.1372384421717</v>
+        <v>133.9952818442369</v>
       </c>
       <c r="H50" s="4">
         <f>IF(F50=0,0,G50/F50)</f>
@@ -3915,7 +3970,7 @@
         <v>382.3073643284127</v>
       </c>
       <c r="J50" s="6">
-        <v>24.23689331551536</v>
+        <v>30.38027252396196</v>
       </c>
       <c r="K50" s="7">
         <f>IF(I50=0,0,J50/I50)</f>
@@ -3942,10 +3997,10 @@
         <v>0</v>
       </c>
       <c r="S50" s="3">
-        <v>2076.357563684252</v>
+        <v>2198.402026122217</v>
       </c>
       <c r="T50" s="3">
-        <v>1708.920568469041</v>
+        <v>1896.36806006779</v>
       </c>
       <c r="U50" s="4">
         <f>IF(S50=0,0,T50/S50)</f>
@@ -3955,7 +4010,7 @@
         <v>9070418.669545408</v>
       </c>
       <c r="W50" s="6">
-        <v>608963.1786537524</v>
+        <v>763318.428798628</v>
       </c>
       <c r="X50" s="7">
         <f>IF(V50=0,0,W50/V50)</f>
@@ -3991,7 +4046,7 @@
         <v>0</v>
       </c>
       <c r="D51" s="3">
-        <f>G51+J51</f>
+        <f>J51+G51</f>
         <v>0</v>
       </c>
       <c r="E51" s="3">
@@ -3999,10 +4054,10 @@
         <v>0</v>
       </c>
       <c r="F51" s="3">
-        <v>148.0950653551477</v>
+        <v>147.7607036391234</v>
       </c>
       <c r="G51" s="3">
-        <v>124.6861301663065</v>
+        <v>129.7820746858701</v>
       </c>
       <c r="H51" s="4">
         <f>IF(F51=0,0,G51/F51)</f>
@@ -4012,7 +4067,7 @@
         <v>245.090682899663</v>
       </c>
       <c r="J51" s="6">
-        <v>19.96254009473606</v>
+        <v>25.02248949374902</v>
       </c>
       <c r="K51" s="7">
         <f>IF(I51=0,0,J51/I51)</f>
@@ -4039,10 +4094,10 @@
         <v>0</v>
       </c>
       <c r="S51" s="3">
-        <v>1975.090975512128</v>
+        <v>2091.183174942721</v>
       </c>
       <c r="T51" s="3">
-        <v>1662.894370399373</v>
+        <v>1836.740650985853</v>
       </c>
       <c r="U51" s="4">
         <f>IF(S51=0,0,T51/S51)</f>
@@ -4052,7 +4107,7 @@
         <v>7100767.677214347</v>
       </c>
       <c r="W51" s="6">
-        <v>667327.7781731561</v>
+        <v>836476.8330573235</v>
       </c>
       <c r="X51" s="7">
         <f>IF(V51=0,0,W51/V51)</f>
@@ -4088,7 +4143,7 @@
         <v>0</v>
       </c>
       <c r="D52" s="3">
-        <f>G52+J52</f>
+        <f>J52+G52</f>
         <v>0</v>
       </c>
       <c r="E52" s="3">
@@ -4096,10 +4151,10 @@
         <v>0</v>
       </c>
       <c r="F52" s="3">
-        <v>134.7924084512274</v>
+        <v>134.4880808162132</v>
       </c>
       <c r="G52" s="3">
-        <v>117.3131609633634</v>
+        <v>121.2448620347747</v>
       </c>
       <c r="H52" s="4">
         <f>IF(F52=0,0,G52/F52)</f>
@@ -4109,7 +4164,7 @@
         <v>200.4130880433794</v>
       </c>
       <c r="J52" s="6">
-        <v>21.28849801111122</v>
+        <v>26.68454090976095</v>
       </c>
       <c r="K52" s="7">
         <f>IF(I52=0,0,J52/I52)</f>
@@ -4136,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="S52" s="3">
-        <v>1797.678193133057</v>
+        <v>1903.342396907326</v>
       </c>
       <c r="T52" s="3">
-        <v>1564.563714340444</v>
+        <v>1715.917759532378</v>
       </c>
       <c r="U52" s="4">
         <f>IF(S52=0,0,T52/S52)</f>
@@ -4149,7 +4204,7 @@
         <v>6292834.208210533</v>
       </c>
       <c r="W52" s="6">
-        <v>757796.3406777447</v>
+        <v>949876.6631412003</v>
       </c>
       <c r="X52" s="7">
         <f>IF(V52=0,0,W52/V52)</f>
@@ -4185,7 +4240,7 @@
         <v>0</v>
       </c>
       <c r="D53" s="3">
-        <f>G53+J53</f>
+        <f>J53+G53</f>
         <v>0</v>
       </c>
       <c r="E53" s="3">
@@ -4193,10 +4248,10 @@
         <v>0</v>
       </c>
       <c r="F53" s="3">
-        <v>118.7821311155358</v>
+        <v>118.5139506930648</v>
       </c>
       <c r="G53" s="3">
-        <v>77.085006142639</v>
+        <v>83.96254109871973</v>
       </c>
       <c r="H53" s="4">
         <f>IF(F53=0,0,G53/F53)</f>
@@ -4206,7 +4261,7 @@
         <v>193.9015574705648</v>
       </c>
       <c r="J53" s="6">
-        <v>9.462193079037592</v>
+        <v>11.86059618587699</v>
       </c>
       <c r="K53" s="7">
         <f>IF(I53=0,0,J53/I53)</f>
@@ -4233,10 +4288,10 @@
         <v>0</v>
       </c>
       <c r="S53" s="3">
-        <v>1584.154844429043</v>
+        <v>1677.268540156761</v>
       </c>
       <c r="T53" s="3">
-        <v>1028.055186136768</v>
+        <v>1188.279758736814</v>
       </c>
       <c r="U53" s="4">
         <f>IF(S53=0,0,T53/S53)</f>
@@ -4246,7 +4301,7 @@
         <v>6053045.584847068</v>
       </c>
       <c r="W53" s="6">
-        <v>345144.5598841952</v>
+        <v>432629.1184659526</v>
       </c>
       <c r="X53" s="7">
         <f>IF(V53=0,0,W53/V53)</f>
@@ -4282,7 +4337,7 @@
         <v>0</v>
       </c>
       <c r="D54" s="3">
-        <f>G54+J54</f>
+        <f>J54+G54</f>
         <v>0</v>
       </c>
       <c r="E54" s="3">
@@ -4290,10 +4345,10 @@
         <v>0</v>
       </c>
       <c r="F54" s="3">
-        <v>93.70721146478344</v>
+        <v>93.49564395607489</v>
       </c>
       <c r="G54" s="3">
-        <v>50.34256103248683</v>
+        <v>56.21002423112071</v>
       </c>
       <c r="H54" s="4">
         <f>IF(F54=0,0,G54/F54)</f>
@@ -4303,7 +4358,7 @@
         <v>136.6145524202559</v>
       </c>
       <c r="J54" s="6">
-        <v>7.307984633459724</v>
+        <v>9.160355738468628</v>
       </c>
       <c r="K54" s="7">
         <f>IF(I54=0,0,J54/I54)</f>
@@ -4330,10 +4385,10 @@
         <v>0</v>
       </c>
       <c r="S54" s="3">
-        <v>1249.73959976761</v>
+        <v>1323.196985098892</v>
       </c>
       <c r="T54" s="3">
-        <v>671.4007501937136</v>
+        <v>795.512298197524</v>
       </c>
       <c r="U54" s="4">
         <f>IF(S54=0,0,T54/S54)</f>
@@ -4343,7 +4398,7 @@
         <v>4890905.466101354</v>
       </c>
       <c r="W54" s="6">
-        <v>291466.352394985</v>
+        <v>365344.9764395468</v>
       </c>
       <c r="X54" s="7">
         <f>IF(V54=0,0,W54/V54)</f>
@@ -4367,6 +4422,614 @@
       </c>
       <c r="AD54" s="4">
         <f>IF(AB54=0,0,AC54/AB54)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:30">
+      <c r="A56" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="57" spans="1:30">
+      <c r="B57" t="s">
+        <v>28</v>
+      </c>
+      <c r="C57" s="3">
+        <f>C59+C60+C61+C62+C63</f>
+        <v>0</v>
+      </c>
+      <c r="D57" s="3">
+        <f>D59+D60+D61+D62+D63</f>
+        <v>0</v>
+      </c>
+      <c r="E57" s="3">
+        <f>E59+E60+E61+E62+E63</f>
+        <v>0</v>
+      </c>
+      <c r="F57" s="3">
+        <f>F59+F60+F61+F62+F63</f>
+        <v>0</v>
+      </c>
+      <c r="G57" s="3">
+        <f>G59+G60+G61+G62+G63</f>
+        <v>0</v>
+      </c>
+      <c r="H57" s="4">
+        <f>IF(F57=0,0,G57/F57)</f>
+        <v>0</v>
+      </c>
+      <c r="I57" s="3">
+        <f>I59+I60+I61+I62+I63</f>
+        <v>0</v>
+      </c>
+      <c r="J57" s="6">
+        <f>J59+J60+J61+J62+J63</f>
+        <v>0</v>
+      </c>
+      <c r="K57" s="7">
+        <f>IF(I57=0,0,J57/I57)</f>
+        <v>0</v>
+      </c>
+      <c r="L57" s="3">
+        <f>L59+L60+L61+L62+L63</f>
+        <v>0</v>
+      </c>
+      <c r="M57" s="3">
+        <f>M59+M60+M61+M62+M63</f>
+        <v>0</v>
+      </c>
+      <c r="N57" s="4">
+        <f>IF(L57=0,0,M57/L57)</f>
+        <v>0</v>
+      </c>
+      <c r="O57" s="3">
+        <f>O59+O60+O61+O62+O63</f>
+        <v>0</v>
+      </c>
+      <c r="P57" s="3">
+        <f>P59+P60+P61+P62+P63</f>
+        <v>0</v>
+      </c>
+      <c r="Q57" s="4">
+        <f>IF(O57=0,0,P57/O57)</f>
+        <v>0</v>
+      </c>
+      <c r="S57" s="3">
+        <f>S59+S60+S61+S62+S63</f>
+        <v>0</v>
+      </c>
+      <c r="T57" s="3">
+        <f>T59+T60+T61+T62+T63</f>
+        <v>0</v>
+      </c>
+      <c r="U57" s="4">
+        <f>IF(S57=0,0,T57/S57)</f>
+        <v>0</v>
+      </c>
+      <c r="V57" s="3">
+        <f>V59+V60+V61+V62+V63</f>
+        <v>0</v>
+      </c>
+      <c r="W57" s="6">
+        <f>W59+W60+W61+W62+W63</f>
+        <v>0</v>
+      </c>
+      <c r="X57" s="7">
+        <f>IF(V57=0,0,W57/V57)</f>
+        <v>0</v>
+      </c>
+      <c r="Y57" s="3">
+        <f>Y59+Y60+Y61+Y62+Y63</f>
+        <v>0</v>
+      </c>
+      <c r="Z57" s="3">
+        <f>Z59+Z60+Z61+Z62+Z63</f>
+        <v>0</v>
+      </c>
+      <c r="AA57" s="4">
+        <f>IF(Y57=0,0,Z57/Y57)</f>
+        <v>0</v>
+      </c>
+      <c r="AB57" s="3">
+        <f>AB59+AB60+AB61+AB62+AB63</f>
+        <v>0</v>
+      </c>
+      <c r="AC57" s="3">
+        <f>AC59+AC60+AC61+AC62+AC63</f>
+        <v>0</v>
+      </c>
+      <c r="AD57" s="4">
+        <f>IF(AB57=0,0,AC57/AB57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:30">
+      <c r="A58" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="59" spans="1:30">
+      <c r="B59" t="s">
+        <v>30</v>
+      </c>
+      <c r="C59" s="3">
+        <f>J59+M59+G59+P59</f>
+        <v>0</v>
+      </c>
+      <c r="D59" s="3">
+        <f>J59+G59</f>
+        <v>0</v>
+      </c>
+      <c r="E59" s="3">
+        <f>P59+M59</f>
+        <v>0</v>
+      </c>
+      <c r="F59" s="3">
+        <v>155.3366697637048</v>
+      </c>
+      <c r="G59" s="3">
+        <v>127.8303805653116</v>
+      </c>
+      <c r="H59" s="4">
+        <f>IF(F59=0,0,G59/F59)</f>
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
+        <v>382.3073643284127</v>
+      </c>
+      <c r="J59" s="6">
+        <v>25.16365196989442</v>
+      </c>
+      <c r="K59" s="7">
+        <f>IF(I59=0,0,J59/I59)</f>
+        <v>0</v>
+      </c>
+      <c r="L59" s="3">
+        <v>0</v>
+      </c>
+      <c r="M59" s="3">
+        <v>0</v>
+      </c>
+      <c r="N59" s="4">
+        <f>IF(L59=0,0,M59/L59)</f>
+        <v>0</v>
+      </c>
+      <c r="O59" s="3">
+        <v>0</v>
+      </c>
+      <c r="P59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="4">
+        <f>IF(O59=0,0,P59/O59)</f>
+        <v>0</v>
+      </c>
+      <c r="S59" s="3">
+        <v>2198.402026122217</v>
+      </c>
+      <c r="T59" s="3">
+        <v>1809.119302365895</v>
+      </c>
+      <c r="U59" s="4">
+        <f>IF(S59=0,0,T59/S59)</f>
+        <v>0</v>
+      </c>
+      <c r="V59" s="3">
+        <v>9070418.669545408</v>
+      </c>
+      <c r="W59" s="6">
+        <v>623324.3944149893</v>
+      </c>
+      <c r="X59" s="7">
+        <f>IF(V59=0,0,W59/V59)</f>
+        <v>0</v>
+      </c>
+      <c r="Y59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="4">
+        <f>IF(Y59=0,0,Z59/Y59)</f>
+        <v>0</v>
+      </c>
+      <c r="AB59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD59" s="4">
+        <f>IF(AB59=0,0,AC59/AB59)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:30">
+      <c r="B60" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="3">
+        <f>J60+M60+G60+P60</f>
+        <v>0</v>
+      </c>
+      <c r="D60" s="3">
+        <f>J60+G60</f>
+        <v>0</v>
+      </c>
+      <c r="E60" s="3">
+        <f>P60+M60</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="3">
+        <v>147.7607036391234</v>
+      </c>
+      <c r="G60" s="3">
+        <v>124.3897710242896</v>
+      </c>
+      <c r="H60" s="4">
+        <f>IF(F60=0,0,G60/F60)</f>
+        <v>0</v>
+      </c>
+      <c r="I60" s="3">
+        <v>245.090682899663</v>
+      </c>
+      <c r="J60" s="6">
+        <v>21.00591395392729</v>
+      </c>
+      <c r="K60" s="7">
+        <f>IF(I60=0,0,J60/I60)</f>
+        <v>0</v>
+      </c>
+      <c r="L60" s="3">
+        <v>0</v>
+      </c>
+      <c r="M60" s="3">
+        <v>0</v>
+      </c>
+      <c r="N60" s="4">
+        <f>IF(L60=0,0,M60/L60)</f>
+        <v>0</v>
+      </c>
+      <c r="O60" s="3">
+        <v>0</v>
+      </c>
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="4">
+        <f>IF(O60=0,0,P60/O60)</f>
+        <v>0</v>
+      </c>
+      <c r="S60" s="3">
+        <v>2091.183174942721</v>
+      </c>
+      <c r="T60" s="3">
+        <v>1760.426080104955</v>
+      </c>
+      <c r="U60" s="4">
+        <f>IF(S60=0,0,T60/S60)</f>
+        <v>0</v>
+      </c>
+      <c r="V60" s="3">
+        <v>7100767.677214347</v>
+      </c>
+      <c r="W60" s="6">
+        <v>692794.20388046</v>
+      </c>
+      <c r="X60" s="7">
+        <f>IF(V60=0,0,W60/V60)</f>
+        <v>0</v>
+      </c>
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="4">
+        <f>IF(Y60=0,0,Z60/Y60)</f>
+        <v>0</v>
+      </c>
+      <c r="AB60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD60" s="4">
+        <f>IF(AB60=0,0,AC60/AB60)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:30">
+      <c r="B61" t="s">
+        <v>32</v>
+      </c>
+      <c r="C61" s="3">
+        <f>J61+M61+G61+P61</f>
+        <v>0</v>
+      </c>
+      <c r="D61" s="3">
+        <f>J61+G61</f>
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
+        <f>P61+M61</f>
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
+        <v>134.4880808162132</v>
+      </c>
+      <c r="G61" s="3">
+        <v>117.0373671682523</v>
+      </c>
+      <c r="H61" s="4">
+        <f>IF(F61=0,0,G61/F61)</f>
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
+        <v>200.4130880433794</v>
+      </c>
+      <c r="J61" s="6">
+        <v>22.61656617855845</v>
+      </c>
+      <c r="K61" s="7">
+        <f>IF(I61=0,0,J61/I61)</f>
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="4">
+        <f>IF(L61=0,0,M61/L61)</f>
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="4">
+        <f>IF(O61=0,0,P61/O61)</f>
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
+        <v>1903.342396907326</v>
+      </c>
+      <c r="T61" s="3">
+        <v>1656.371193653684</v>
+      </c>
+      <c r="U61" s="4">
+        <f>IF(S61=0,0,T61/S61)</f>
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
+        <v>6292834.208210533</v>
+      </c>
+      <c r="W61" s="6">
+        <v>794041.0575617198</v>
+      </c>
+      <c r="X61" s="7">
+        <f>IF(V61=0,0,W61/V61)</f>
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="4">
+        <f>IF(Y61=0,0,Z61/Y61)</f>
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="4">
+        <f>IF(AB61=0,0,AC61/AB61)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:30">
+      <c r="B62" t="s">
+        <v>33</v>
+      </c>
+      <c r="C62" s="3">
+        <f>J62+M62+G62+P62</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="3">
+        <f>J62+G62</f>
+        <v>0</v>
+      </c>
+      <c r="E62" s="3">
+        <f>P62+M62</f>
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
+        <v>118.5139506930648</v>
+      </c>
+      <c r="G62" s="3">
+        <v>76.88625128893909</v>
+      </c>
+      <c r="H62" s="4">
+        <f>IF(F62=0,0,G62/F62)</f>
+        <v>0</v>
+      </c>
+      <c r="I62" s="3">
+        <v>193.9015574705648</v>
+      </c>
+      <c r="J62" s="6">
+        <v>9.710502579285967</v>
+      </c>
+      <c r="K62" s="7">
+        <f>IF(I62=0,0,J62/I62)</f>
+        <v>0</v>
+      </c>
+      <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3">
+        <v>0</v>
+      </c>
+      <c r="N62" s="4">
+        <f>IF(L62=0,0,M62/L62)</f>
+        <v>0</v>
+      </c>
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="4">
+        <f>IF(O62=0,0,P62/O62)</f>
+        <v>0</v>
+      </c>
+      <c r="S62" s="3">
+        <v>1677.268540156761</v>
+      </c>
+      <c r="T62" s="3">
+        <v>1088.132575982645</v>
+      </c>
+      <c r="U62" s="4">
+        <f>IF(S62=0,0,T62/S62)</f>
+        <v>0</v>
+      </c>
+      <c r="V62" s="3">
+        <v>6053045.584847068</v>
+      </c>
+      <c r="W62" s="6">
+        <v>351805.066879469</v>
+      </c>
+      <c r="X62" s="7">
+        <f>IF(V62=0,0,W62/V62)</f>
+        <v>0</v>
+      </c>
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="4">
+        <f>IF(Y62=0,0,Z62/Y62)</f>
+        <v>0</v>
+      </c>
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="4">
+        <f>IF(AB62=0,0,AC62/AB62)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:30">
+      <c r="B63" t="s">
+        <v>34</v>
+      </c>
+      <c r="C63" s="3">
+        <f>J63+M63+G63+P63</f>
+        <v>0</v>
+      </c>
+      <c r="D63" s="3">
+        <f>J63+G63</f>
+        <v>0</v>
+      </c>
+      <c r="E63" s="3">
+        <f>P63+M63</f>
+        <v>0</v>
+      </c>
+      <c r="F63" s="3">
+        <v>93.49564395607489</v>
+      </c>
+      <c r="G63" s="3">
+        <v>50.20618165273297</v>
+      </c>
+      <c r="H63" s="4">
+        <f>IF(F63=0,0,G63/F63)</f>
+        <v>0</v>
+      </c>
+      <c r="I63" s="3">
+        <v>136.6145524202559</v>
+      </c>
+      <c r="J63" s="6">
+        <v>7.458779051449644</v>
+      </c>
+      <c r="K63" s="7">
+        <f>IF(I63=0,0,J63/I63)</f>
+        <v>0</v>
+      </c>
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="4">
+        <f>IF(L63=0,0,M63/L63)</f>
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="4">
+        <f>IF(O63=0,0,P63/O63)</f>
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>1323.196985098892</v>
+      </c>
+      <c r="T63" s="3">
+        <v>710.5429235551791</v>
+      </c>
+      <c r="U63" s="4">
+        <f>IF(S63=0,0,T63/S63)</f>
+        <v>0</v>
+      </c>
+      <c r="V63" s="3">
+        <v>4890905.466101354</v>
+      </c>
+      <c r="W63" s="6">
+        <v>296120.1093025655</v>
+      </c>
+      <c r="X63" s="7">
+        <f>IF(V63=0,0,W63/V63)</f>
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="4">
+        <f>IF(Y63=0,0,Z63/Y63)</f>
+        <v>0</v>
+      </c>
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD63" s="4">
+        <f>IF(AB63=0,0,AC63/AB63)</f>
         <v>0</v>
       </c>
     </row>

--- a/5000_analyze_results/results_spreadsheet.xlsx
+++ b/5000_analyze_results/results_spreadsheet.xlsx
@@ -123,12 +123,64 @@
         </r>
       </text>
     </comment>
+    <comment ref="J57" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Based on correlation between serum folate and hemoglobin</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K57" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Based on correlation between serum folate and hemoglobin</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W57" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Based on correlation between serum folate and hemoglobin</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X57" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Based on correlation between serum folate and hemoglobin</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="41">
   <si>
     <t>DALYs Averted by Fortification (1000s)</t>
   </si>
@@ -248,6 +300,9 @@
   </si>
   <si>
     <t>Ethiopia -- Salt-- 100% NRV per average intake</t>
+  </si>
+  <si>
+    <t>Ethiopia -- Salt-- DFS-IoFA preliminary standard 45 ppm</t>
   </si>
 </sst>
 </file>
@@ -628,7 +683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD54"/>
+  <dimension ref="A1:AD63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="1.7109375" customWidth="1"/>
@@ -862,80 +917,80 @@
         <v>0</v>
       </c>
       <c r="F5" s="3">
-        <v>363.2527888669509</v>
+        <v>362.8529849538489</v>
       </c>
       <c r="G5" s="3">
-        <v>25.63269042834587</v>
+        <v>25.58090999587317</v>
       </c>
       <c r="H5" s="4">
         <f>IF(F5=0,0,G5/F5)</f>
         <v>0</v>
       </c>
       <c r="I5" s="3">
-        <v>4771.172487854658</v>
+        <v>4771.261231090824</v>
       </c>
       <c r="J5" s="3">
-        <v>313.4550641795806</v>
+        <v>313.4364668127587</v>
       </c>
       <c r="K5" s="4">
         <f>IF(I5=0,0,J5/I5)</f>
         <v>0</v>
       </c>
       <c r="L5" s="3">
-        <v>17935.27995420955</v>
+        <v>17957.14040242062</v>
       </c>
       <c r="M5" s="3">
-        <v>51.79140364386141</v>
+        <v>52.45177887492255</v>
       </c>
       <c r="N5" s="4">
         <f>IF(L5=0,0,M5/L5)</f>
         <v>0</v>
       </c>
       <c r="O5" s="3">
-        <v>495.9420392823301</v>
+        <v>506.7963637284521</v>
       </c>
       <c r="P5" s="3">
-        <v>14.94688767936849</v>
+        <v>15.01370971237042</v>
       </c>
       <c r="Q5" s="4">
         <f>IF(O5=0,0,P5/O5)</f>
         <v>0</v>
       </c>
       <c r="S5" s="3">
-        <v>5246.953936438476</v>
+        <v>4684.597214204819</v>
       </c>
       <c r="T5" s="3">
-        <v>370.2478000623951</v>
+        <v>330.261193024865</v>
       </c>
       <c r="U5" s="4">
         <f>IF(S5=0,0,T5/S5)</f>
         <v>0</v>
       </c>
       <c r="V5" s="3">
-        <v>131693856.602241</v>
+        <v>131696392.1412486</v>
       </c>
       <c r="W5" s="3">
-        <v>6834156.362184763</v>
+        <v>6833090.704050109</v>
       </c>
       <c r="X5" s="4">
         <f>IF(V5=0,0,W5/V5)</f>
         <v>0</v>
       </c>
       <c r="Y5" s="3">
-        <v>3014818.917223012</v>
+        <v>3016543.050471412</v>
       </c>
       <c r="Z5" s="3">
-        <v>82234.18246693723</v>
+        <v>83335.51165489713</v>
       </c>
       <c r="AA5" s="4">
         <f>IF(Y5=0,0,Z5/Y5)</f>
         <v>0</v>
       </c>
       <c r="AB5" s="3">
-        <v>200072.0470788344</v>
+        <v>200318.014600175</v>
       </c>
       <c r="AC5" s="3">
-        <v>575.5563222417259</v>
+        <v>582.9921052198624</v>
       </c>
       <c r="AD5" s="4">
         <f>IF(AB5=0,0,AC5/AB5)</f>
@@ -959,80 +1014,80 @@
         <v>0</v>
       </c>
       <c r="F6" s="3">
-        <v>320.8959288091749</v>
+        <v>320.5427437766894</v>
       </c>
       <c r="G6" s="3">
-        <v>19.3141818814585</v>
+        <v>19.27496735575946</v>
       </c>
       <c r="H6" s="4">
         <f>IF(F6=0,0,G6/F6)</f>
         <v>0</v>
       </c>
       <c r="I6" s="3">
-        <v>4315.488605002881</v>
+        <v>4315.21265961095</v>
       </c>
       <c r="J6" s="3">
-        <v>279.5339981601541</v>
+        <v>279.4920962596657</v>
       </c>
       <c r="K6" s="4">
         <f>IF(I6=0,0,J6/I6)</f>
         <v>0</v>
       </c>
       <c r="L6" s="3">
-        <v>14938.0946218137</v>
+        <v>14810.98291993852</v>
       </c>
       <c r="M6" s="3">
-        <v>39.87119663484022</v>
+        <v>35.10980211630091</v>
       </c>
       <c r="N6" s="4">
         <f>IF(L6=0,0,M6/L6)</f>
         <v>0</v>
       </c>
       <c r="O6" s="3">
-        <v>286.4588253328344</v>
+        <v>297.573370209569</v>
       </c>
       <c r="P6" s="3">
-        <v>8.284407215548388</v>
+        <v>8.344677452836709</v>
       </c>
       <c r="Q6" s="4">
         <f>IF(O6=0,0,P6/O6)</f>
         <v>0</v>
       </c>
       <c r="S6" s="3">
-        <v>4635.136214932357</v>
+        <v>4138.352740079671</v>
       </c>
       <c r="T6" s="3">
-        <v>278.980989982505</v>
+        <v>248.8486029408423</v>
       </c>
       <c r="U6" s="4">
         <f>IF(S6=0,0,T6/S6)</f>
         <v>0</v>
       </c>
       <c r="V6" s="3">
-        <v>123353341.0379582</v>
+        <v>123352422.8520256</v>
       </c>
       <c r="W6" s="3">
-        <v>6428198.322602153</v>
+        <v>6427646.223230928</v>
       </c>
       <c r="X6" s="4">
         <f>IF(V6=0,0,W6/V6)</f>
         <v>0</v>
       </c>
       <c r="Y6" s="3">
-        <v>1787928.583240007</v>
+        <v>1788522.531513863</v>
       </c>
       <c r="Z6" s="3">
-        <v>46645.37901320681</v>
+        <v>46989.24380333396</v>
       </c>
       <c r="AA6" s="4">
         <f>IF(Y6=0,0,Z6/Y6)</f>
         <v>0</v>
       </c>
       <c r="AB6" s="3">
-        <v>166631.983938046</v>
+        <v>165227.6716058255</v>
       </c>
       <c r="AC6" s="3">
-        <v>443.1061225626618</v>
+        <v>390.2674423372664</v>
       </c>
       <c r="AD6" s="4">
         <f>IF(AB6=0,0,AC6/AB6)</f>
@@ -1056,80 +1111,80 @@
         <v>0</v>
       </c>
       <c r="F7" s="3">
-        <v>288.0891253989829</v>
+        <v>287.7720482472399</v>
       </c>
       <c r="G7" s="3">
-        <v>14.66402867711027</v>
+        <v>14.63412098323711</v>
       </c>
       <c r="H7" s="4">
         <f>IF(F7=0,0,G7/F7)</f>
         <v>0</v>
       </c>
       <c r="I7" s="3">
-        <v>4219.911362271461</v>
+        <v>4220.065012527612</v>
       </c>
       <c r="J7" s="3">
-        <v>242.9313309619347</v>
+        <v>242.9326465501119</v>
       </c>
       <c r="K7" s="4">
         <f>IF(I7=0,0,J7/I7)</f>
         <v>0</v>
       </c>
       <c r="L7" s="3">
-        <v>13234.92997176094</v>
+        <v>13140.17641177926</v>
       </c>
       <c r="M7" s="3">
-        <v>30.1158939311821</v>
+        <v>24.07275763035007</v>
       </c>
       <c r="N7" s="4">
         <f>IF(L7=0,0,M7/L7)</f>
         <v>0</v>
       </c>
       <c r="O7" s="3">
-        <v>362.0106149542505</v>
+        <v>350.6722046220511</v>
       </c>
       <c r="P7" s="3">
-        <v>7.080686168705637</v>
+        <v>7.230571189964132</v>
       </c>
       <c r="Q7" s="4">
         <f>IF(O7=0,0,P7/O7)</f>
         <v>0</v>
       </c>
       <c r="S7" s="3">
-        <v>4161.262946589416</v>
+        <v>3715.268142871963</v>
       </c>
       <c r="T7" s="3">
-        <v>211.8125045409952</v>
+        <v>188.9331636589077</v>
       </c>
       <c r="U7" s="4">
         <f>IF(S7=0,0,T7/S7)</f>
         <v>0</v>
       </c>
       <c r="V7" s="3">
-        <v>121042695.9926408</v>
+        <v>121045766.1486471</v>
       </c>
       <c r="W7" s="3">
-        <v>5624803.04057464</v>
+        <v>5624078.184110358</v>
       </c>
       <c r="X7" s="4">
         <f>IF(V7=0,0,W7/V7)</f>
         <v>0</v>
       </c>
       <c r="Y7" s="3">
-        <v>2262233.551971834</v>
+        <v>2261372.687672075</v>
       </c>
       <c r="Z7" s="3">
-        <v>48143.47526669828</v>
+        <v>48881.70247347467</v>
       </c>
       <c r="AA7" s="4">
         <f>IF(Y7=0,0,Z7/Y7)</f>
         <v>0</v>
       </c>
       <c r="AB7" s="3">
-        <v>147641.0334895182</v>
+        <v>146579.1514136479</v>
       </c>
       <c r="AC7" s="3">
-        <v>334.7377773706976</v>
+        <v>267.4054697496467</v>
       </c>
       <c r="AD7" s="4">
         <f>IF(AB7=0,0,AC7/AB7)</f>
@@ -1153,80 +1208,80 @@
         <v>0</v>
       </c>
       <c r="F8" s="3">
-        <v>271.6538476703636</v>
+        <v>271.3548595424364</v>
       </c>
       <c r="G8" s="3">
-        <v>12.01916291244561</v>
+        <v>11.99457042306478</v>
       </c>
       <c r="H8" s="4">
         <f>IF(F8=0,0,G8/F8)</f>
         <v>0</v>
       </c>
       <c r="I8" s="3">
-        <v>3866.404723234419</v>
+        <v>3866.462901477351</v>
       </c>
       <c r="J8" s="3">
-        <v>199.0831212808485</v>
+        <v>199.0834636001452</v>
       </c>
       <c r="K8" s="4">
         <f>IF(I8=0,0,J8/I8)</f>
         <v>0</v>
       </c>
       <c r="L8" s="3">
-        <v>12362.34693163964</v>
+        <v>12529.63951354596</v>
       </c>
       <c r="M8" s="3">
-        <v>21.66686408916116</v>
+        <v>26.4433246140331</v>
       </c>
       <c r="N8" s="4">
         <f>IF(L8=0,0,M8/L8)</f>
         <v>0</v>
       </c>
       <c r="O8" s="3">
-        <v>326.2902544418872</v>
+        <v>341.4996444598856</v>
       </c>
       <c r="P8" s="3">
-        <v>6.173648437333526</v>
+        <v>8.565760149411567</v>
       </c>
       <c r="Q8" s="4">
         <f>IF(O8=0,0,P8/O8)</f>
         <v>0</v>
       </c>
       <c r="S8" s="3">
-        <v>3923.86588366907</v>
+        <v>3503.314763237015</v>
       </c>
       <c r="T8" s="3">
-        <v>173.6091121360946</v>
+        <v>154.8553643471328</v>
       </c>
       <c r="U8" s="4">
         <f>IF(S8=0,0,T8/S8)</f>
         <v>0</v>
       </c>
       <c r="V8" s="3">
-        <v>114930948.5074336</v>
+        <v>114934295.1461658</v>
       </c>
       <c r="W8" s="3">
-        <v>4858738.283078313</v>
+        <v>4858362.349655852</v>
       </c>
       <c r="X8" s="4">
         <f>IF(V8=0,0,W8/V8)</f>
         <v>0</v>
       </c>
       <c r="Y8" s="3">
-        <v>2017724.044351414</v>
+        <v>2020070.981660255</v>
       </c>
       <c r="Z8" s="3">
-        <v>39554.06946016243</v>
+        <v>39029.85600388492</v>
       </c>
       <c r="AA8" s="4">
         <f>IF(Y8=0,0,Z8/Y8)</f>
         <v>0</v>
       </c>
       <c r="AB8" s="3">
-        <v>137914.3724621782</v>
+        <v>139766.3345807479</v>
       </c>
       <c r="AC8" s="3">
-        <v>240.8185448710283</v>
+        <v>293.9051108959829</v>
       </c>
       <c r="AD8" s="4">
         <f>IF(AB8=0,0,AC8/AB8)</f>
@@ -1250,80 +1305,80 @@
         <v>0</v>
       </c>
       <c r="F9" s="3">
-        <v>231.3561787321935</v>
+        <v>231.1015430943892</v>
       </c>
       <c r="G9" s="3">
-        <v>4.583486877183867</v>
+        <v>4.573997896683897</v>
       </c>
       <c r="H9" s="4">
         <f>IF(F9=0,0,G9/F9)</f>
         <v>0</v>
       </c>
       <c r="I9" s="3">
-        <v>3364.404821554393</v>
+        <v>3364.297008165505</v>
       </c>
       <c r="J9" s="3">
-        <v>100.8406044416442</v>
+        <v>100.8268812075821</v>
       </c>
       <c r="K9" s="4">
         <f>IF(I9=0,0,J9/I9)</f>
         <v>0</v>
       </c>
       <c r="L9" s="3">
-        <v>11834.18418972814</v>
+        <v>11856.76378900309</v>
       </c>
       <c r="M9" s="3">
-        <v>9.966248810512946</v>
+        <v>10.18657588824816</v>
       </c>
       <c r="N9" s="4">
         <f>IF(L9=0,0,M9/L9)</f>
         <v>0</v>
       </c>
       <c r="O9" s="3">
-        <v>210.8368637670372</v>
+        <v>209.6942036708812</v>
       </c>
       <c r="P9" s="3">
-        <v>2.020924868696747</v>
+        <v>2.195864039865555</v>
       </c>
       <c r="Q9" s="4">
         <f>IF(O9=0,0,P9/O9)</f>
         <v>0</v>
       </c>
       <c r="S9" s="3">
-        <v>3341.791859340324</v>
+        <v>2983.6261237209</v>
       </c>
       <c r="T9" s="3">
-        <v>66.20553303353427</v>
+        <v>59.05239502799986</v>
       </c>
       <c r="U9" s="4">
         <f>IF(S9=0,0,T9/S9)</f>
         <v>0</v>
       </c>
       <c r="V9" s="3">
-        <v>107057780.7659875</v>
+        <v>107056308.1865083</v>
       </c>
       <c r="W9" s="3">
-        <v>2679796.374648735</v>
+        <v>2679940.421917364</v>
       </c>
       <c r="X9" s="4">
         <f>IF(V9=0,0,W9/V9)</f>
         <v>0</v>
       </c>
       <c r="Y9" s="3">
-        <v>1277885.722823765</v>
+        <v>1277060.928257236</v>
       </c>
       <c r="Z9" s="3">
-        <v>14853.51614416833</v>
+        <v>14533.69784286129</v>
       </c>
       <c r="AA9" s="4">
         <f>IF(Y9=0,0,Z9/Y9)</f>
         <v>0</v>
       </c>
       <c r="AB9" s="3">
-        <v>132031.1754109795</v>
+        <v>132271.7542529008</v>
       </c>
       <c r="AC9" s="3">
-        <v>110.7765306406654</v>
+        <v>113.2257394435292</v>
       </c>
       <c r="AD9" s="4">
         <f>IF(AB9=0,0,AC9/AB9)</f>
@@ -1470,80 +1525,80 @@
         <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>363.2527888669509</v>
+        <v>362.8529849538489</v>
       </c>
       <c r="G14" s="3">
-        <v>171.7832906162409</v>
+        <v>236.1367268275891</v>
       </c>
       <c r="H14" s="4">
         <f>IF(F14=0,0,G14/F14)</f>
         <v>0</v>
       </c>
       <c r="I14" s="3">
-        <v>4771.172487854658</v>
+        <v>4771.261231090824</v>
       </c>
       <c r="J14" s="3">
-        <v>313.4550641795806</v>
+        <v>574.7557064126702</v>
       </c>
       <c r="K14" s="4">
         <f>IF(I14=0,0,J14/I14)</f>
         <v>0</v>
       </c>
       <c r="L14" s="3">
-        <v>17935.27995420955</v>
+        <v>17957.14040242062</v>
       </c>
       <c r="M14" s="3">
-        <v>51.79140364386141</v>
+        <v>100.1389094884172</v>
       </c>
       <c r="N14" s="4">
         <f>IF(L14=0,0,M14/L14)</f>
         <v>0</v>
       </c>
       <c r="O14" s="3">
-        <v>495.9420392823301</v>
+        <v>506.7963637284521</v>
       </c>
       <c r="P14" s="3">
-        <v>14.94688767936849</v>
+        <v>22.007135649256</v>
       </c>
       <c r="Q14" s="4">
         <f>IF(O14=0,0,P14/O14)</f>
         <v>0</v>
       </c>
       <c r="S14" s="3">
-        <v>5246.953936438476</v>
+        <v>4684.597214204819</v>
       </c>
       <c r="T14" s="3">
-        <v>2481.299636335</v>
+        <v>3048.632637839994</v>
       </c>
       <c r="U14" s="4">
         <f>IF(S14=0,0,T14/S14)</f>
         <v>0</v>
       </c>
       <c r="V14" s="3">
-        <v>131693856.602241</v>
+        <v>131696392.1412486</v>
       </c>
       <c r="W14" s="3">
-        <v>6834156.362184763</v>
+        <v>12551111.5207074</v>
       </c>
       <c r="X14" s="4">
         <f>IF(V14=0,0,W14/V14)</f>
         <v>0</v>
       </c>
       <c r="Y14" s="3">
-        <v>3014818.917223012</v>
+        <v>3016543.050471412</v>
       </c>
       <c r="Z14" s="3">
-        <v>82234.18246693723</v>
+        <v>119816.4398438525</v>
       </c>
       <c r="AA14" s="4">
         <f>IF(Y14=0,0,Z14/Y14)</f>
         <v>0</v>
       </c>
       <c r="AB14" s="3">
-        <v>200072.0470788344</v>
+        <v>200318.014600175</v>
       </c>
       <c r="AC14" s="3">
-        <v>575.5563222417259</v>
+        <v>1112.984928146965</v>
       </c>
       <c r="AD14" s="4">
         <f>IF(AB14=0,0,AC14/AB14)</f>
@@ -1567,80 +1622,80 @@
         <v>0</v>
       </c>
       <c r="F15" s="3">
-        <v>320.8959288091749</v>
+        <v>320.5427437766894</v>
       </c>
       <c r="G15" s="3">
-        <v>136.8384804720325</v>
+        <v>192.7207779040032</v>
       </c>
       <c r="H15" s="4">
         <f>IF(F15=0,0,G15/F15)</f>
         <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>4315.488605002881</v>
+        <v>4315.21265961095</v>
       </c>
       <c r="J15" s="3">
-        <v>279.5339981601541</v>
+        <v>513.5291981071886</v>
       </c>
       <c r="K15" s="4">
         <f>IF(I15=0,0,J15/I15)</f>
         <v>0</v>
       </c>
       <c r="L15" s="3">
-        <v>14938.0946218137</v>
+        <v>14810.98291993852</v>
       </c>
       <c r="M15" s="3">
-        <v>39.87119663484022</v>
+        <v>66.97132194078527</v>
       </c>
       <c r="N15" s="4">
         <f>IF(L15=0,0,M15/L15)</f>
         <v>0</v>
       </c>
       <c r="O15" s="3">
-        <v>286.4588253328344</v>
+        <v>297.573370209569</v>
       </c>
       <c r="P15" s="3">
-        <v>8.284407215548388</v>
+        <v>10.47285401756043</v>
       </c>
       <c r="Q15" s="4">
         <f>IF(O15=0,0,P15/O15)</f>
         <v>0</v>
       </c>
       <c r="S15" s="3">
-        <v>4635.136214932357</v>
+        <v>4138.352740079671</v>
       </c>
       <c r="T15" s="3">
-        <v>1976.544229731896</v>
+        <v>2488.112973366633</v>
       </c>
       <c r="U15" s="4">
         <f>IF(S15=0,0,T15/S15)</f>
         <v>0</v>
       </c>
       <c r="V15" s="3">
-        <v>123353341.0379582</v>
+        <v>123352422.8520256</v>
       </c>
       <c r="W15" s="3">
-        <v>6428198.322602153</v>
+        <v>11833860.56680924</v>
       </c>
       <c r="X15" s="4">
         <f>IF(V15=0,0,W15/V15)</f>
         <v>0</v>
       </c>
       <c r="Y15" s="3">
-        <v>1787928.583240007</v>
+        <v>1788522.531513863</v>
       </c>
       <c r="Z15" s="3">
-        <v>46645.37901320681</v>
+        <v>68972.54388265847</v>
       </c>
       <c r="AA15" s="4">
         <f>IF(Y15=0,0,Z15/Y15)</f>
         <v>0</v>
       </c>
       <c r="AB15" s="3">
-        <v>166631.983938046</v>
+        <v>165227.6716058255</v>
       </c>
       <c r="AC15" s="3">
-        <v>443.1061225626618</v>
+        <v>744.3990103840479</v>
       </c>
       <c r="AD15" s="4">
         <f>IF(AB15=0,0,AC15/AB15)</f>
@@ -1664,80 +1719,80 @@
         <v>0</v>
       </c>
       <c r="F16" s="3">
-        <v>288.0891253989829</v>
+        <v>287.7720482472399</v>
       </c>
       <c r="G16" s="3">
-        <v>109.4384294573394</v>
+        <v>161.6901662622983</v>
       </c>
       <c r="H16" s="4">
         <f>IF(F16=0,0,G16/F16)</f>
         <v>0</v>
       </c>
       <c r="I16" s="3">
-        <v>4219.911362271461</v>
+        <v>4220.065012527612</v>
       </c>
       <c r="J16" s="3">
-        <v>242.9313309619347</v>
+        <v>463.6088522818093</v>
       </c>
       <c r="K16" s="4">
         <f>IF(I16=0,0,J16/I16)</f>
         <v>0</v>
       </c>
       <c r="L16" s="3">
-        <v>13234.92997176094</v>
+        <v>13140.17641177926</v>
       </c>
       <c r="M16" s="3">
-        <v>30.1158939311821</v>
+        <v>45.31403995645046</v>
       </c>
       <c r="N16" s="4">
         <f>IF(L16=0,0,M16/L16)</f>
         <v>0</v>
       </c>
       <c r="O16" s="3">
-        <v>362.0106149542505</v>
+        <v>350.6722046220511</v>
       </c>
       <c r="P16" s="3">
-        <v>7.080686168705637</v>
+        <v>12.10934546388395</v>
       </c>
       <c r="Q16" s="4">
         <f>IF(O16=0,0,P16/O16)</f>
         <v>0</v>
       </c>
       <c r="S16" s="3">
-        <v>4161.262946589416</v>
+        <v>3715.268142871963</v>
       </c>
       <c r="T16" s="3">
-        <v>1580.768037679544</v>
+        <v>2087.493651273165</v>
       </c>
       <c r="U16" s="4">
         <f>IF(S16=0,0,T16/S16)</f>
         <v>0</v>
       </c>
       <c r="V16" s="3">
-        <v>121042695.9926408</v>
+        <v>121045766.1486471</v>
       </c>
       <c r="W16" s="3">
-        <v>5624803.04057464</v>
+        <v>10757671.65764305</v>
       </c>
       <c r="X16" s="4">
         <f>IF(V16=0,0,W16/V16)</f>
         <v>0</v>
       </c>
       <c r="Y16" s="3">
-        <v>2262233.551971834</v>
+        <v>2261372.687672075</v>
       </c>
       <c r="Z16" s="3">
-        <v>48143.47526669828</v>
+        <v>74873.55223910837</v>
       </c>
       <c r="AA16" s="4">
         <f>IF(Y16=0,0,Z16/Y16)</f>
         <v>0</v>
       </c>
       <c r="AB16" s="3">
-        <v>147641.0334895182</v>
+        <v>146579.1514136479</v>
       </c>
       <c r="AC16" s="3">
-        <v>334.7377773706976</v>
+        <v>503.4931817808247</v>
       </c>
       <c r="AD16" s="4">
         <f>IF(AB16=0,0,AC16/AB16)</f>
@@ -1761,80 +1816,80 @@
         <v>0</v>
       </c>
       <c r="F17" s="3">
-        <v>271.6538476703636</v>
+        <v>271.3548595424364</v>
       </c>
       <c r="G17" s="3">
-        <v>93.2369079938145</v>
+        <v>144.676134576367</v>
       </c>
       <c r="H17" s="4">
         <f>IF(F17=0,0,G17/F17)</f>
         <v>0</v>
       </c>
       <c r="I17" s="3">
-        <v>3866.404723234419</v>
+        <v>3866.462901477351</v>
       </c>
       <c r="J17" s="3">
-        <v>199.0831212808485</v>
+        <v>398.1802336081071</v>
       </c>
       <c r="K17" s="4">
         <f>IF(I17=0,0,J17/I17)</f>
         <v>0</v>
       </c>
       <c r="L17" s="3">
-        <v>12362.34693163964</v>
+        <v>12529.63951354596</v>
       </c>
       <c r="M17" s="3">
-        <v>21.66686408916116</v>
+        <v>50.28439562279545</v>
       </c>
       <c r="N17" s="4">
         <f>IF(L17=0,0,M17/L17)</f>
         <v>0</v>
       </c>
       <c r="O17" s="3">
-        <v>326.2902544418872</v>
+        <v>341.4996444598856</v>
       </c>
       <c r="P17" s="3">
-        <v>6.173648437333526</v>
+        <v>11.67196939960052</v>
       </c>
       <c r="Q17" s="4">
         <f>IF(O17=0,0,P17/O17)</f>
         <v>0</v>
       </c>
       <c r="S17" s="3">
-        <v>3923.86588366907</v>
+        <v>3503.314763237015</v>
       </c>
       <c r="T17" s="3">
-        <v>1346.747434329211</v>
+        <v>1867.834757056148</v>
       </c>
       <c r="U17" s="4">
         <f>IF(S17=0,0,T17/S17)</f>
         <v>0</v>
       </c>
       <c r="V17" s="3">
-        <v>114930948.5074336</v>
+        <v>114934295.1461658</v>
       </c>
       <c r="W17" s="3">
-        <v>4858738.283078313</v>
+        <v>9734869.333226398</v>
       </c>
       <c r="X17" s="4">
         <f>IF(V17=0,0,W17/V17)</f>
         <v>0</v>
       </c>
       <c r="Y17" s="3">
-        <v>2017724.044351414</v>
+        <v>2020070.981660255</v>
       </c>
       <c r="Z17" s="3">
-        <v>39554.06946016243</v>
+        <v>61669.62522799801</v>
       </c>
       <c r="AA17" s="4">
         <f>IF(Y17=0,0,Z17/Y17)</f>
         <v>0</v>
       </c>
       <c r="AB17" s="3">
-        <v>137914.3724621782</v>
+        <v>139766.3345807479</v>
       </c>
       <c r="AC17" s="3">
-        <v>240.8185448710283</v>
+        <v>558.9015223595488</v>
       </c>
       <c r="AD17" s="4">
         <f>IF(AB17=0,0,AC17/AB17)</f>
@@ -1858,80 +1913,80 @@
         <v>0</v>
       </c>
       <c r="F18" s="3">
-        <v>231.3561787321935</v>
+        <v>231.1015430943892</v>
       </c>
       <c r="G18" s="3">
-        <v>41.44780297413218</v>
+        <v>78.90054096724134</v>
       </c>
       <c r="H18" s="4">
         <f>IF(F18=0,0,G18/F18)</f>
         <v>0</v>
       </c>
       <c r="I18" s="3">
-        <v>3364.404821554393</v>
+        <v>3364.297008165505</v>
       </c>
       <c r="J18" s="3">
-        <v>100.8406044416442</v>
+        <v>227.1775098421918</v>
       </c>
       <c r="K18" s="4">
         <f>IF(I18=0,0,J18/I18)</f>
         <v>0</v>
       </c>
       <c r="L18" s="3">
-        <v>11834.18418972814</v>
+        <v>11856.76378900309</v>
       </c>
       <c r="M18" s="3">
-        <v>9.966248810512946</v>
+        <v>21.89240697437897</v>
       </c>
       <c r="N18" s="4">
         <f>IF(L18=0,0,M18/L18)</f>
         <v>0</v>
       </c>
       <c r="O18" s="3">
-        <v>210.8368637670372</v>
+        <v>209.6942036708812</v>
       </c>
       <c r="P18" s="3">
-        <v>2.020924868696747</v>
+        <v>3.993387343400682</v>
       </c>
       <c r="Q18" s="4">
         <f>IF(O18=0,0,P18/O18)</f>
         <v>0</v>
       </c>
       <c r="S18" s="3">
-        <v>3341.791859340324</v>
+        <v>2983.6261237209</v>
       </c>
       <c r="T18" s="3">
-        <v>598.6869740221155</v>
+        <v>1018.641901103288</v>
       </c>
       <c r="U18" s="4">
         <f>IF(S18=0,0,T18/S18)</f>
         <v>0</v>
       </c>
       <c r="V18" s="3">
-        <v>107057780.7659875</v>
+        <v>107056308.1865083</v>
       </c>
       <c r="W18" s="3">
-        <v>2679796.374648735</v>
+        <v>6047039.221417382</v>
       </c>
       <c r="X18" s="4">
         <f>IF(V18=0,0,W18/V18)</f>
         <v>0</v>
       </c>
       <c r="Y18" s="3">
-        <v>1277885.722823765</v>
+        <v>1277060.928257236</v>
       </c>
       <c r="Z18" s="3">
-        <v>14853.51614416833</v>
+        <v>25179.07844351418</v>
       </c>
       <c r="AA18" s="4">
         <f>IF(Y18=0,0,Z18/Y18)</f>
         <v>0</v>
       </c>
       <c r="AB18" s="3">
-        <v>132031.1754109795</v>
+        <v>132271.7542529008</v>
       </c>
       <c r="AC18" s="3">
-        <v>110.7765306406654</v>
+        <v>243.3148868892749</v>
       </c>
       <c r="AD18" s="4">
         <f>IF(AB18=0,0,AC18/AB18)</f>
@@ -2078,80 +2133,80 @@
         <v>0</v>
       </c>
       <c r="F23" s="3">
-        <v>414.1483857332581</v>
+        <v>412.7408750394843</v>
       </c>
       <c r="G23" s="3">
-        <v>268.7588990063936</v>
+        <v>213.4118382061803</v>
       </c>
       <c r="H23" s="4">
         <f>IF(F23=0,0,G23/F23)</f>
         <v>0</v>
       </c>
       <c r="I23" s="3">
-        <v>1006.03050891829</v>
+        <v>1006.030840012209</v>
       </c>
       <c r="J23" s="3">
-        <v>137.7016614572871</v>
+        <v>86.86733689510881</v>
       </c>
       <c r="K23" s="4">
         <f>IF(I23=0,0,J23/I23)</f>
         <v>0</v>
       </c>
       <c r="L23" s="3">
-        <v>15508.35321860747</v>
+        <v>15352.83741703859</v>
       </c>
       <c r="M23" s="3">
-        <v>69.41307935650087</v>
+        <v>39.63639084755815</v>
       </c>
       <c r="N23" s="4">
         <f>IF(L23=0,0,M23/L23)</f>
         <v>0</v>
       </c>
       <c r="O23" s="3">
-        <v>490.4767894259087</v>
+        <v>503.5634310516943</v>
       </c>
       <c r="P23" s="3">
-        <v>18.30659451972903</v>
+        <v>12.79226160240127</v>
       </c>
       <c r="Q23" s="4">
         <f>IF(O23=0,0,P23/O23)</f>
         <v>0</v>
       </c>
       <c r="S23" s="3">
-        <v>7596.11775664314</v>
+        <v>12734.95565684622</v>
       </c>
       <c r="T23" s="3">
-        <v>4929.451170946294</v>
+        <v>6584.73744802172</v>
       </c>
       <c r="U23" s="4">
         <f>IF(S23=0,0,T23/S23)</f>
         <v>0</v>
       </c>
       <c r="V23" s="3">
-        <v>24943983.79121354</v>
+        <v>24943823.20853924</v>
       </c>
       <c r="W23" s="3">
-        <v>2711534.522799071</v>
+        <v>1711094.158100959</v>
       </c>
       <c r="X23" s="4">
         <f>IF(V23=0,0,W23/V23)</f>
         <v>0</v>
       </c>
       <c r="Y23" s="3">
-        <v>2562179.973832092</v>
+        <v>2561085.175981381</v>
       </c>
       <c r="Z23" s="3">
-        <v>106463.8040677239</v>
+        <v>67792.87612257898</v>
       </c>
       <c r="AA23" s="4">
         <f>IF(Y23=0,0,Z23/Y23)</f>
         <v>0</v>
       </c>
       <c r="AB23" s="3">
-        <v>174653.7692611545</v>
+        <v>172903.801774421</v>
       </c>
       <c r="AC23" s="3">
-        <v>770.2822696975782</v>
+        <v>439.8924531132216</v>
       </c>
       <c r="AD23" s="4">
         <f>IF(AB23=0,0,AC23/AB23)</f>
@@ -2175,80 +2230,80 @@
         <v>0</v>
       </c>
       <c r="F24" s="3">
-        <v>423.4925012827377</v>
+        <v>422.0532339939541</v>
       </c>
       <c r="G24" s="3">
-        <v>265.196859797002</v>
+        <v>208.3471500632799</v>
       </c>
       <c r="H24" s="4">
         <f>IF(F24=0,0,G24/F24)</f>
         <v>0</v>
       </c>
       <c r="I24" s="3">
-        <v>964.6353829774464</v>
+        <v>964.5986558077452</v>
       </c>
       <c r="J24" s="3">
-        <v>140.6392386713823</v>
+        <v>88.73307073881558</v>
       </c>
       <c r="K24" s="4">
         <f>IF(I24=0,0,J24/I24)</f>
         <v>0</v>
       </c>
       <c r="L24" s="3">
-        <v>16011.09974104909</v>
+        <v>15897.14811387405</v>
       </c>
       <c r="M24" s="3">
-        <v>65.18596044688859</v>
+        <v>35.37980973197706</v>
       </c>
       <c r="N24" s="4">
         <f>IF(L24=0,0,M24/L24)</f>
         <v>0</v>
       </c>
       <c r="O24" s="3">
-        <v>445.5228835589704</v>
+        <v>427.6878840211459</v>
       </c>
       <c r="P24" s="3">
-        <v>23.2267178141388</v>
+        <v>13.53889125172485</v>
       </c>
       <c r="Q24" s="4">
         <f>IF(O24=0,0,P24/O24)</f>
         <v>0</v>
       </c>
       <c r="S24" s="3">
-        <v>7767.503193579848</v>
+        <v>13022.28479122008</v>
       </c>
       <c r="T24" s="3">
-        <v>4864.117898572401</v>
+        <v>6428.468508316091</v>
       </c>
       <c r="U24" s="4">
         <f>IF(S24=0,0,T24/S24)</f>
         <v>0</v>
       </c>
       <c r="V24" s="3">
-        <v>24664122.16385399</v>
+        <v>24665300.63578367</v>
       </c>
       <c r="W24" s="3">
-        <v>2871097.97539036</v>
+        <v>1812415.629343331</v>
       </c>
       <c r="X24" s="4">
         <f>IF(V24=0,0,W24/V24)</f>
         <v>0</v>
       </c>
       <c r="Y24" s="3">
-        <v>2215774.872016895</v>
+        <v>2216806.226901517</v>
       </c>
       <c r="Z24" s="3">
-        <v>105761.0512125869</v>
+        <v>66880.27345653391</v>
       </c>
       <c r="AA24" s="4">
         <f>IF(Y24=0,0,Z24/Y24)</f>
         <v>0</v>
       </c>
       <c r="AB24" s="3">
-        <v>180322.590785081</v>
+        <v>179047.6330362356</v>
       </c>
       <c r="AC24" s="3">
-        <v>723.0556611960346</v>
+        <v>392.6447451862332</v>
       </c>
       <c r="AD24" s="4">
         <f>IF(AB24=0,0,AC24/AB24)</f>
@@ -2272,80 +2327,80 @@
         <v>0</v>
       </c>
       <c r="F25" s="3">
-        <v>383.3772465961786</v>
+        <v>382.0743136549376</v>
       </c>
       <c r="G25" s="3">
-        <v>207.6861063739965</v>
+        <v>157.1453841591108</v>
       </c>
       <c r="H25" s="4">
         <f>IF(F25=0,0,G25/F25)</f>
         <v>0</v>
       </c>
       <c r="I25" s="3">
-        <v>794.0332832090369</v>
+        <v>794.1006249062289</v>
       </c>
       <c r="J25" s="3">
-        <v>130.447879964726</v>
+        <v>82.29511533396365</v>
       </c>
       <c r="K25" s="4">
         <f>IF(I25=0,0,J25/I25)</f>
         <v>0</v>
       </c>
       <c r="L25" s="3">
-        <v>14053.45528341239</v>
+        <v>14099.36149543928</v>
       </c>
       <c r="M25" s="3">
-        <v>41.82331183696166</v>
+        <v>27.60176385746338</v>
       </c>
       <c r="N25" s="4">
         <f>IF(L25=0,0,M25/L25)</f>
         <v>0</v>
       </c>
       <c r="O25" s="3">
-        <v>423.2626485083759</v>
+        <v>410.8336896551561</v>
       </c>
       <c r="P25" s="3">
-        <v>18.88101471107895</v>
+        <v>11.78005736867187</v>
       </c>
       <c r="Q25" s="4">
         <f>IF(O25=0,0,P25/O25)</f>
         <v>0</v>
       </c>
       <c r="S25" s="3">
-        <v>7031.727783282595</v>
+        <v>11788.75109364953</v>
       </c>
       <c r="T25" s="3">
-        <v>3809.282312286219</v>
+        <v>4848.658371315645</v>
       </c>
       <c r="U25" s="4">
         <f>IF(S25=0,0,T25/S25)</f>
         <v>0</v>
       </c>
       <c r="V25" s="3">
-        <v>22724254.79066634</v>
+        <v>22725958.89165936</v>
       </c>
       <c r="W25" s="3">
-        <v>3049970.033541534</v>
+        <v>1925420.011185676</v>
       </c>
       <c r="X25" s="4">
         <f>IF(V25=0,0,W25/V25)</f>
         <v>0</v>
       </c>
       <c r="Y25" s="3">
-        <v>2110361.943746436</v>
+        <v>2114085.557833027</v>
       </c>
       <c r="Z25" s="3">
-        <v>98500.89845223143</v>
+        <v>62043.96734931064</v>
       </c>
       <c r="AA25" s="4">
         <f>IF(Y25=0,0,Z25/Y25)</f>
         <v>0</v>
       </c>
       <c r="AB25" s="3">
-        <v>158254.736584929</v>
+        <v>158763.7032537926</v>
       </c>
       <c r="AC25" s="3">
-        <v>464.1235663082625</v>
+        <v>306.2954858714365</v>
       </c>
       <c r="AD25" s="4">
         <f>IF(AB25=0,0,AC25/AB25)</f>
@@ -2369,80 +2424,80 @@
         <v>0</v>
       </c>
       <c r="F26" s="3">
-        <v>339.8250758454431</v>
+        <v>338.6701578384149</v>
       </c>
       <c r="G26" s="3">
-        <v>163.9650491569163</v>
+        <v>121.0430906924064</v>
       </c>
       <c r="H26" s="4">
         <f>IF(F26=0,0,G26/F26)</f>
         <v>0</v>
       </c>
       <c r="I26" s="3">
-        <v>721.6906170167119</v>
+        <v>721.6494802184835</v>
       </c>
       <c r="J26" s="3">
-        <v>122.258392855309</v>
+        <v>77.17266564486199</v>
       </c>
       <c r="K26" s="4">
         <f>IF(I26=0,0,J26/I26)</f>
         <v>0</v>
       </c>
       <c r="L26" s="3">
-        <v>12426.67038256435</v>
+        <v>12459.036398116</v>
       </c>
       <c r="M26" s="3">
-        <v>31.56021921042912</v>
+        <v>20.68435130110197</v>
       </c>
       <c r="N26" s="4">
         <f>IF(L26=0,0,M26/L26)</f>
         <v>0</v>
       </c>
       <c r="O26" s="3">
-        <v>386.7499979717133</v>
+        <v>388.5202631627004</v>
       </c>
       <c r="P26" s="3">
-        <v>18.98683480456413</v>
+        <v>9.65561708555062</v>
       </c>
       <c r="Q26" s="4">
         <f>IF(O26=0,0,P26/O26)</f>
         <v>0</v>
       </c>
       <c r="S26" s="3">
-        <v>6232.914051353447</v>
+        <v>10449.53311676904</v>
       </c>
       <c r="T26" s="3">
-        <v>3007.370943060754</v>
+        <v>3734.736455137735</v>
       </c>
       <c r="U26" s="4">
         <f>IF(S26=0,0,T26/S26)</f>
         <v>0</v>
       </c>
       <c r="V26" s="3">
-        <v>21494888.75936157</v>
+        <v>21493332.04664342</v>
       </c>
       <c r="W26" s="3">
-        <v>3023371.617128544</v>
+        <v>1908378.392676797</v>
       </c>
       <c r="X26" s="4">
         <f>IF(V26=0,0,W26/V26)</f>
         <v>0</v>
       </c>
       <c r="Y26" s="3">
-        <v>1927070.334488014</v>
+        <v>1925897.452986733</v>
       </c>
       <c r="Z26" s="3">
-        <v>82220.45730823791</v>
+        <v>52002.08453737316</v>
       </c>
       <c r="AA26" s="4">
         <f>IF(Y26=0,0,Z26/Y26)</f>
         <v>0</v>
       </c>
       <c r="AB26" s="3">
-        <v>139955.2400424519</v>
+        <v>140314.2879239626</v>
       </c>
       <c r="AC26" s="3">
-        <v>350.1283044079901</v>
+        <v>229.721614403592</v>
       </c>
       <c r="AD26" s="4">
         <f>IF(AB26=0,0,AC26/AB26)</f>
@@ -2466,80 +2521,80 @@
         <v>0</v>
       </c>
       <c r="F27" s="3">
-        <v>298.4746794483207</v>
+        <v>297.4602934996698</v>
       </c>
       <c r="G27" s="3">
-        <v>136.2522506171126</v>
+        <v>99.54060524581827</v>
       </c>
       <c r="H27" s="4">
         <f>IF(F27=0,0,G27/F27)</f>
         <v>0</v>
       </c>
       <c r="I27" s="3">
-        <v>613.5010816140716</v>
+        <v>613.496298429298</v>
       </c>
       <c r="J27" s="3">
-        <v>110.1809181014056</v>
+        <v>69.54268932890368</v>
       </c>
       <c r="K27" s="4">
         <f>IF(I27=0,0,J27/I27)</f>
         <v>0</v>
       </c>
       <c r="L27" s="3">
-        <v>9448.065592686806</v>
+        <v>9475.405513778041</v>
       </c>
       <c r="M27" s="3">
-        <v>21.28188721634261</v>
+        <v>16.14096631298959</v>
       </c>
       <c r="N27" s="4">
         <f>IF(L27=0,0,M27/L27)</f>
         <v>0</v>
       </c>
       <c r="O27" s="3">
-        <v>287.6064386127327</v>
+        <v>285.742923347472</v>
       </c>
       <c r="P27" s="3">
-        <v>14.57451940548077</v>
+        <v>8.734878812706157</v>
       </c>
       <c r="Q27" s="4">
         <f>IF(O27=0,0,P27/O27)</f>
         <v>0</v>
       </c>
       <c r="S27" s="3">
-        <v>5474.484244219731</v>
+        <v>9178.019131321482</v>
       </c>
       <c r="T27" s="3">
-        <v>2499.075635566639</v>
+        <v>3071.285812775053</v>
       </c>
       <c r="U27" s="4">
         <f>IF(S27=0,0,T27/S27)</f>
         <v>0</v>
       </c>
       <c r="V27" s="3">
-        <v>20021733.97656191</v>
+        <v>20021798.10615849</v>
       </c>
       <c r="W27" s="3">
-        <v>3026592.02297743</v>
+        <v>1911129.785046071</v>
       </c>
       <c r="X27" s="4">
         <f>IF(V27=0,0,W27/V27)</f>
         <v>0</v>
       </c>
       <c r="Y27" s="3">
-        <v>1405956.318006293</v>
+        <v>1405792.016991551</v>
       </c>
       <c r="Z27" s="3">
-        <v>68241.85711336066</v>
+        <v>42911.84621676616</v>
       </c>
       <c r="AA27" s="4">
         <f>IF(Y27=0,0,Z27/Y27)</f>
         <v>0</v>
       </c>
       <c r="AB27" s="3">
-        <v>106414.5769839078</v>
+        <v>106730.9429757299</v>
       </c>
       <c r="AC27" s="3">
-        <v>236.1330425077176</v>
+        <v>179.2154438609432</v>
       </c>
       <c r="AD27" s="4">
         <f>IF(AB27=0,0,AC27/AB27)</f>
@@ -2686,80 +2741,80 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>414.1483857332581</v>
+        <v>412.7408750394843</v>
       </c>
       <c r="G32" s="3">
-        <v>17.33318367138942</v>
+        <v>44.60952190125041</v>
       </c>
       <c r="H32" s="4">
         <f>IF(F32=0,0,G32/F32)</f>
         <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>1006.03050891829</v>
+        <v>1006.030840012209</v>
       </c>
       <c r="J32" s="3">
-        <v>11.68607605816354</v>
+        <v>32.09737479080761</v>
       </c>
       <c r="K32" s="4">
         <f>IF(I32=0,0,J32/I32)</f>
         <v>0</v>
       </c>
       <c r="L32" s="3">
-        <v>15508.35321860747</v>
+        <v>15352.83741703859</v>
       </c>
       <c r="M32" s="3">
-        <v>1.175133258519694</v>
+        <v>3.522455788802355</v>
       </c>
       <c r="N32" s="4">
         <f>IF(L32=0,0,M32/L32)</f>
         <v>0</v>
       </c>
       <c r="O32" s="3">
-        <v>490.4767894259087</v>
+        <v>503.5634310516943</v>
       </c>
       <c r="P32" s="3">
-        <v>1.324936358721752</v>
+        <v>3.068391177042213</v>
       </c>
       <c r="Q32" s="4">
         <f>IF(O32=0,0,P32/O32)</f>
         <v>0</v>
       </c>
       <c r="S32" s="3">
-        <v>7596.11775664314</v>
+        <v>12734.95565684622</v>
       </c>
       <c r="T32" s="3">
-        <v>317.9172219451793</v>
+        <v>1376.409068355992</v>
       </c>
       <c r="U32" s="4">
         <f>IF(S32=0,0,T32/S32)</f>
         <v>0</v>
       </c>
       <c r="V32" s="3">
-        <v>24943983.79121354</v>
+        <v>24943823.20853924</v>
       </c>
       <c r="W32" s="3">
-        <v>226783.5345008299</v>
+        <v>623654.2003708966</v>
       </c>
       <c r="X32" s="4">
         <f>IF(V32=0,0,W32/V32)</f>
         <v>0</v>
       </c>
       <c r="Y32" s="3">
-        <v>2562179.973832092</v>
+        <v>2561085.175981381</v>
       </c>
       <c r="Z32" s="3">
-        <v>7749.802319143433</v>
+        <v>21651.94560616976</v>
       </c>
       <c r="AA32" s="4">
         <f>IF(Y32=0,0,Z32/Y32)</f>
         <v>0</v>
       </c>
       <c r="AB32" s="3">
-        <v>174653.7692611545</v>
+        <v>172903.801774421</v>
       </c>
       <c r="AC32" s="3">
-        <v>13.02802993147634</v>
+        <v>39.10155138786649</v>
       </c>
       <c r="AD32" s="4">
         <f>IF(AB32=0,0,AC32/AB32)</f>
@@ -2783,80 +2838,80 @@
         <v>0</v>
       </c>
       <c r="F33" s="3">
-        <v>423.4925012827377</v>
+        <v>422.0532339939541</v>
       </c>
       <c r="G33" s="3">
-        <v>33.49612922113162</v>
+        <v>82.11660802380734</v>
       </c>
       <c r="H33" s="4">
         <f>IF(F33=0,0,G33/F33)</f>
         <v>0</v>
       </c>
       <c r="I33" s="3">
-        <v>964.6353829774464</v>
+        <v>964.5986558077452</v>
       </c>
       <c r="J33" s="3">
-        <v>15.53966267093841</v>
+        <v>42.69060008609377</v>
       </c>
       <c r="K33" s="4">
         <f>IF(I33=0,0,J33/I33)</f>
         <v>0</v>
       </c>
       <c r="L33" s="3">
-        <v>16011.09974104909</v>
+        <v>15897.14811387405</v>
       </c>
       <c r="M33" s="3">
-        <v>1.781353609535843</v>
+        <v>4.837213344274089</v>
       </c>
       <c r="N33" s="4">
         <f>IF(L33=0,0,M33/L33)</f>
         <v>0</v>
       </c>
       <c r="O33" s="3">
-        <v>445.5228835589704</v>
+        <v>427.6878840211459</v>
       </c>
       <c r="P33" s="3">
-        <v>2.013518356469227</v>
+        <v>5.825039412285958</v>
       </c>
       <c r="Q33" s="4">
         <f>IF(O33=0,0,P33/O33)</f>
         <v>0</v>
       </c>
       <c r="S33" s="3">
-        <v>7767.503193579848</v>
+        <v>13022.28479122008</v>
       </c>
       <c r="T33" s="3">
-        <v>614.3704786026356</v>
+        <v>2533.675303600032</v>
       </c>
       <c r="U33" s="4">
         <f>IF(S33=0,0,T33/S33)</f>
         <v>0</v>
       </c>
       <c r="V33" s="3">
-        <v>24664122.16385399</v>
+        <v>24665300.63578367</v>
       </c>
       <c r="W33" s="3">
-        <v>312466.0118141025</v>
+        <v>859445.1501166448</v>
       </c>
       <c r="X33" s="4">
         <f>IF(V33=0,0,W33/V33)</f>
         <v>0</v>
       </c>
       <c r="Y33" s="3">
-        <v>2215774.872016895</v>
+        <v>2216806.226901517</v>
       </c>
       <c r="Z33" s="3">
-        <v>10960.99244886357</v>
+        <v>30576.25616931403</v>
       </c>
       <c r="AA33" s="4">
         <f>IF(Y33=0,0,Z33/Y33)</f>
         <v>0</v>
       </c>
       <c r="AB33" s="3">
-        <v>180322.590785081</v>
+        <v>179047.6330362356</v>
       </c>
       <c r="AC33" s="3">
-        <v>19.54204489718541</v>
+        <v>53.76463315828005</v>
       </c>
       <c r="AD33" s="4">
         <f>IF(AB33=0,0,AC33/AB33)</f>
@@ -2880,80 +2935,80 @@
         <v>0</v>
       </c>
       <c r="F34" s="3">
-        <v>383.3772465961786</v>
+        <v>382.0743136549376</v>
       </c>
       <c r="G34" s="3">
-        <v>41.90985526450491</v>
+        <v>98.872168911535</v>
       </c>
       <c r="H34" s="4">
         <f>IF(F34=0,0,G34/F34)</f>
         <v>0</v>
       </c>
       <c r="I34" s="3">
-        <v>794.0332832090369</v>
+        <v>794.1006249062289</v>
       </c>
       <c r="J34" s="3">
-        <v>17.47401316043292</v>
+        <v>48.03179086984182</v>
       </c>
       <c r="K34" s="4">
         <f>IF(I34=0,0,J34/I34)</f>
         <v>0</v>
       </c>
       <c r="L34" s="3">
-        <v>14053.45528341239</v>
+        <v>14099.36149543928</v>
       </c>
       <c r="M34" s="3">
-        <v>2.34422612186335</v>
+        <v>7.771691316105425</v>
       </c>
       <c r="N34" s="4">
         <f>IF(L34=0,0,M34/L34)</f>
         <v>0</v>
       </c>
       <c r="O34" s="3">
-        <v>423.2626485083759</v>
+        <v>410.8336896551561</v>
       </c>
       <c r="P34" s="3">
-        <v>2.302160093775892</v>
+        <v>6.801262350148347</v>
       </c>
       <c r="Q34" s="4">
         <f>IF(O34=0,0,P34/O34)</f>
         <v>0</v>
       </c>
       <c r="S34" s="3">
-        <v>7031.727783282595</v>
+        <v>11788.75109364953</v>
       </c>
       <c r="T34" s="3">
-        <v>768.6911424015352</v>
+        <v>3050.661475348556</v>
       </c>
       <c r="U34" s="4">
         <f>IF(S34=0,0,T34/S34)</f>
         <v>0</v>
       </c>
       <c r="V34" s="3">
-        <v>22724254.79066634</v>
+        <v>22725958.89165936</v>
       </c>
       <c r="W34" s="3">
-        <v>402460.020815663</v>
+        <v>1106195.733125906</v>
       </c>
       <c r="X34" s="4">
         <f>IF(V34=0,0,W34/V34)</f>
         <v>0</v>
       </c>
       <c r="Y34" s="3">
-        <v>2110361.943746436</v>
+        <v>2114085.557833027</v>
       </c>
       <c r="Z34" s="3">
-        <v>13274.22059702082</v>
+        <v>36476.45201556338</v>
       </c>
       <c r="AA34" s="4">
         <f>IF(Y34=0,0,Z34/Y34)</f>
         <v>0</v>
       </c>
       <c r="AB34" s="3">
-        <v>158254.736584929</v>
+        <v>158763.7032537926</v>
       </c>
       <c r="AC34" s="3">
-        <v>26.05605986292358</v>
+        <v>86.34925931482576</v>
       </c>
       <c r="AD34" s="4">
         <f>IF(AB34=0,0,AC34/AB34)</f>
@@ -2977,80 +3032,80 @@
         <v>0</v>
       </c>
       <c r="F35" s="3">
-        <v>339.8250758454431</v>
+        <v>338.6701578384149</v>
       </c>
       <c r="G35" s="3">
-        <v>49.15588258143957</v>
+        <v>111.0000684404046</v>
       </c>
       <c r="H35" s="4">
         <f>IF(F35=0,0,G35/F35)</f>
         <v>0</v>
       </c>
       <c r="I35" s="3">
-        <v>721.6906170167119</v>
+        <v>721.6494802184835</v>
       </c>
       <c r="J35" s="3">
-        <v>18.98791012796736</v>
+        <v>52.18241248611535</v>
       </c>
       <c r="K35" s="4">
         <f>IF(I35=0,0,J35/I35)</f>
         <v>0</v>
       </c>
       <c r="L35" s="3">
-        <v>12426.67038256435</v>
+        <v>12459.036398116</v>
       </c>
       <c r="M35" s="3">
-        <v>2.490720905642957</v>
+        <v>5.284773733304814</v>
       </c>
       <c r="N35" s="4">
         <f>IF(L35=0,0,M35/L35)</f>
         <v>0</v>
       </c>
       <c r="O35" s="3">
-        <v>386.7499979717133</v>
+        <v>388.5202631627004</v>
       </c>
       <c r="P35" s="3">
-        <v>3.202118789545784</v>
+        <v>6.425640266744071</v>
       </c>
       <c r="Q35" s="4">
         <f>IF(O35=0,0,P35/O35)</f>
         <v>0</v>
       </c>
       <c r="S35" s="3">
-        <v>6232.914051353447</v>
+        <v>10449.53311676904</v>
       </c>
       <c r="T35" s="3">
-        <v>901.5944173227599</v>
+        <v>3424.862995118233</v>
       </c>
       <c r="U35" s="4">
         <f>IF(S35=0,0,T35/S35)</f>
         <v>0</v>
       </c>
       <c r="V35" s="3">
-        <v>21494888.75936157</v>
+        <v>21493332.04664342</v>
       </c>
       <c r="W35" s="3">
-        <v>462770.0523576438</v>
+        <v>1271558.913595185</v>
       </c>
       <c r="X35" s="4">
         <f>IF(V35=0,0,W35/V35)</f>
         <v>0</v>
       </c>
       <c r="Y35" s="3">
-        <v>1927070.334488014</v>
+        <v>1925897.452986733</v>
       </c>
       <c r="Z35" s="3">
-        <v>12821.98612079886</v>
+        <v>35243.3810336343</v>
       </c>
       <c r="AA35" s="4">
         <f>IF(Y35=0,0,Z35/Y35)</f>
         <v>0</v>
       </c>
       <c r="AB35" s="3">
-        <v>139955.2400424519</v>
+        <v>140314.2879239626</v>
       </c>
       <c r="AC35" s="3">
-        <v>27.68456360435812</v>
+        <v>58.65232708177064</v>
       </c>
       <c r="AD35" s="4">
         <f>IF(AB35=0,0,AC35/AB35)</f>
@@ -3074,80 +3129,80 @@
         <v>0</v>
       </c>
       <c r="F36" s="3">
-        <v>298.4746794483207</v>
+        <v>297.4602934996698</v>
       </c>
       <c r="G36" s="3">
-        <v>47.84221324221152</v>
+        <v>106.0000459180257</v>
       </c>
       <c r="H36" s="4">
         <f>IF(F36=0,0,G36/F36)</f>
         <v>0</v>
       </c>
       <c r="I36" s="3">
-        <v>613.5010816140716</v>
+        <v>613.496298429298</v>
       </c>
       <c r="J36" s="3">
-        <v>18.4046589318075</v>
+        <v>50.59624545245489</v>
       </c>
       <c r="K36" s="4">
         <f>IF(I36=0,0,J36/I36)</f>
         <v>0</v>
       </c>
       <c r="L36" s="3">
-        <v>9448.065592686806</v>
+        <v>9475.405513778041</v>
       </c>
       <c r="M36" s="3">
-        <v>1.760577471522614</v>
+        <v>8.366401425374672</v>
       </c>
       <c r="N36" s="4">
         <f>IF(L36=0,0,M36/L36)</f>
         <v>0</v>
       </c>
       <c r="O36" s="3">
-        <v>287.6064386127327</v>
+        <v>285.742923347472</v>
       </c>
       <c r="P36" s="3">
-        <v>2.951383382774657</v>
+        <v>6.236481271973287</v>
       </c>
       <c r="Q36" s="4">
         <f>IF(O36=0,0,P36/O36)</f>
         <v>0</v>
       </c>
       <c r="S36" s="3">
-        <v>5474.484244219731</v>
+        <v>9178.019131321482</v>
       </c>
       <c r="T36" s="3">
-        <v>877.4997031144685</v>
+        <v>3270.58928743266</v>
       </c>
       <c r="U36" s="4">
         <f>IF(S36=0,0,T36/S36)</f>
         <v>0</v>
       </c>
       <c r="V36" s="3">
-        <v>20021733.97656191</v>
+        <v>20021798.10615849</v>
       </c>
       <c r="W36" s="3">
-        <v>498447.0926206037</v>
+        <v>1370173.648558669</v>
       </c>
       <c r="X36" s="4">
         <f>IF(V36=0,0,W36/V36)</f>
         <v>0</v>
       </c>
       <c r="Y36" s="3">
-        <v>1405956.318006293</v>
+        <v>1405792.016991551</v>
       </c>
       <c r="Z36" s="3">
-        <v>11174.0957452131</v>
+        <v>30795.86643654411</v>
       </c>
       <c r="AA36" s="4">
         <f>IF(Y36=0,0,Z36/Y36)</f>
         <v>0</v>
       </c>
       <c r="AB36" s="3">
-        <v>106414.5769839078</v>
+        <v>106730.9429757299</v>
       </c>
       <c r="AC36" s="3">
-        <v>19.54204489719996</v>
+        <v>92.86618454611744</v>
       </c>
       <c r="AD36" s="4">
         <f>IF(AB36=0,0,AC36/AB36)</f>
@@ -3294,10 +3349,10 @@
         <v>0</v>
       </c>
       <c r="F41" s="3">
-        <v>155.6881748268545</v>
+        <v>155.3366697637048</v>
       </c>
       <c r="G41" s="3">
-        <v>72.16538725395763</v>
+        <v>81.86999988549339</v>
       </c>
       <c r="H41" s="4">
         <f>IF(F41=0,0,G41/F41)</f>
@@ -3307,7 +3362,7 @@
         <v>382.3073643284127</v>
       </c>
       <c r="J41" s="6">
-        <v>6.931603770051908</v>
+        <v>8.688572781210882</v>
       </c>
       <c r="K41" s="7">
         <f>IF(I41=0,0,J41/I41)</f>
@@ -3334,10 +3389,10 @@
         <v>0</v>
       </c>
       <c r="S41" s="3">
-        <v>2076.357563684252</v>
+        <v>2198.402026122217</v>
       </c>
       <c r="T41" s="3">
-        <v>962.4439866907096</v>
+        <v>1158.665071812607</v>
       </c>
       <c r="U41" s="4">
         <f>IF(S41=0,0,T41/S41)</f>
@@ -3347,7 +3402,7 @@
         <v>9070418.669545408</v>
       </c>
       <c r="W41" s="6">
-        <v>164538.3844167478</v>
+        <v>206244.2943557166</v>
       </c>
       <c r="X41" s="7">
         <f>IF(V41=0,0,W41/V41)</f>
@@ -3391,10 +3446,10 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>148.0950653551477</v>
+        <v>147.7607036391234</v>
       </c>
       <c r="G42" s="3">
-        <v>72.90814487956493</v>
+        <v>82.20269740785589</v>
       </c>
       <c r="H42" s="4">
         <f>IF(F42=0,0,G42/F42)</f>
@@ -3404,7 +3459,7 @@
         <v>245.090682899663</v>
       </c>
       <c r="J42" s="6">
-        <v>6.008397319649958</v>
+        <v>7.531359140255663</v>
       </c>
       <c r="K42" s="7">
         <f>IF(I42=0,0,J42/I42)</f>
@@ -3431,10 +3486,10 @@
         <v>0</v>
       </c>
       <c r="S42" s="3">
-        <v>1975.090975512128</v>
+        <v>2091.183174942721</v>
       </c>
       <c r="T42" s="3">
-        <v>972.3498797723723</v>
+        <v>1163.373573085103</v>
       </c>
       <c r="U42" s="4">
         <f>IF(S42=0,0,T42/S42)</f>
@@ -3444,7 +3499,7 @@
         <v>7100767.677214347</v>
       </c>
       <c r="W42" s="6">
-        <v>189877.8700925186</v>
+        <v>238006.6357756918</v>
       </c>
       <c r="X42" s="7">
         <f>IF(V42=0,0,W42/V42)</f>
@@ -3488,10 +3543,10 @@
         <v>0</v>
       </c>
       <c r="F43" s="3">
-        <v>134.7924084512274</v>
+        <v>134.4880808162132</v>
       </c>
       <c r="G43" s="3">
-        <v>72.9461290521218</v>
+        <v>81.3780121199603</v>
       </c>
       <c r="H43" s="4">
         <f>IF(F43=0,0,G43/F43)</f>
@@ -3501,7 +3556,7 @@
         <v>200.4130880433794</v>
       </c>
       <c r="J43" s="6">
-        <v>6.648335109332984</v>
+        <v>8.333503383573669</v>
       </c>
       <c r="K43" s="7">
         <f>IF(I43=0,0,J43/I43)</f>
@@ -3528,10 +3583,10 @@
         <v>0</v>
       </c>
       <c r="S43" s="3">
-        <v>1797.678193133057</v>
+        <v>1903.342396907326</v>
       </c>
       <c r="T43" s="3">
-        <v>972.8564611108482</v>
+        <v>1151.702215571254</v>
       </c>
       <c r="U43" s="4">
         <f>IF(S43=0,0,T43/S43)</f>
@@ -3541,7 +3596,7 @@
         <v>6292834.208210533</v>
       </c>
       <c r="W43" s="6">
-        <v>222967.1563095488</v>
+        <v>279483.1369019002</v>
       </c>
       <c r="X43" s="7">
         <f>IF(V43=0,0,W43/V43)</f>
@@ -3585,10 +3640,10 @@
         <v>0</v>
       </c>
       <c r="F44" s="3">
-        <v>118.7821311155358</v>
+        <v>118.5139506930648</v>
       </c>
       <c r="G44" s="3">
-        <v>33.21257251634332</v>
+        <v>39.16266033894262</v>
       </c>
       <c r="H44" s="4">
         <f>IF(F44=0,0,G44/F44)</f>
@@ -3598,7 +3653,7 @@
         <v>193.9015574705648</v>
       </c>
       <c r="J44" s="6">
-        <v>2.593667459385906</v>
+        <v>3.251090114021907</v>
       </c>
       <c r="K44" s="7">
         <f>IF(I44=0,0,J44/I44)</f>
@@ -3625,10 +3680,10 @@
         <v>0</v>
       </c>
       <c r="S44" s="3">
-        <v>1584.154844429043</v>
+        <v>1677.268540156761</v>
       </c>
       <c r="T44" s="3">
-        <v>442.9442135243412</v>
+        <v>554.2495018622074</v>
       </c>
       <c r="U44" s="4">
         <f>IF(S44=0,0,T44/S44)</f>
@@ -3638,7 +3693,7 @@
         <v>6053045.584847068</v>
       </c>
       <c r="W44" s="6">
-        <v>92120.66669745091</v>
+        <v>115470.6967978468</v>
       </c>
       <c r="X44" s="7">
         <f>IF(V44=0,0,W44/V44)</f>
@@ -3682,10 +3737,10 @@
         <v>0</v>
       </c>
       <c r="F45" s="3">
-        <v>93.70721146478344</v>
+        <v>93.49564395607489</v>
       </c>
       <c r="G45" s="3">
-        <v>19.08558195037654</v>
+        <v>22.85792253853465</v>
       </c>
       <c r="H45" s="4">
         <f>IF(F45=0,0,G45/F45)</f>
@@ -3695,7 +3750,7 @@
         <v>136.6145524202559</v>
       </c>
       <c r="J45" s="6">
-        <v>1.96286239209451</v>
+        <v>2.460393484535132</v>
       </c>
       <c r="K45" s="7">
         <f>IF(I45=0,0,J45/I45)</f>
@@ -3722,10 +3777,10 @@
         <v>0</v>
       </c>
       <c r="S45" s="3">
-        <v>1249.73959976761</v>
+        <v>1323.196985098892</v>
       </c>
       <c r="T45" s="3">
-        <v>254.5375876109539</v>
+        <v>323.4967203693753</v>
       </c>
       <c r="U45" s="4">
         <f>IF(S45=0,0,T45/S45)</f>
@@ -3735,7 +3790,7 @@
         <v>4890905.466101354</v>
       </c>
       <c r="W45" s="6">
-        <v>76901.85631352663</v>
+        <v>96394.34072632995</v>
       </c>
       <c r="X45" s="7">
         <f>IF(V45=0,0,W45/V45)</f>
@@ -3902,10 +3957,10 @@
         <v>0</v>
       </c>
       <c r="F50" s="3">
-        <v>155.6881748268545</v>
+        <v>155.3366697637048</v>
       </c>
       <c r="G50" s="3">
-        <v>128.1372384421717</v>
+        <v>133.9952818442369</v>
       </c>
       <c r="H50" s="4">
         <f>IF(F50=0,0,G50/F50)</f>
@@ -3915,7 +3970,7 @@
         <v>382.3073643284127</v>
       </c>
       <c r="J50" s="6">
-        <v>24.23689331551536</v>
+        <v>30.38027252396196</v>
       </c>
       <c r="K50" s="7">
         <f>IF(I50=0,0,J50/I50)</f>
@@ -3942,10 +3997,10 @@
         <v>0</v>
       </c>
       <c r="S50" s="3">
-        <v>2076.357563684252</v>
+        <v>2198.402026122217</v>
       </c>
       <c r="T50" s="3">
-        <v>1708.920568469041</v>
+        <v>1896.36806006779</v>
       </c>
       <c r="U50" s="4">
         <f>IF(S50=0,0,T50/S50)</f>
@@ -3955,7 +4010,7 @@
         <v>9070418.669545408</v>
       </c>
       <c r="W50" s="6">
-        <v>608963.1786537524</v>
+        <v>763318.428798628</v>
       </c>
       <c r="X50" s="7">
         <f>IF(V50=0,0,W50/V50)</f>
@@ -3999,10 +4054,10 @@
         <v>0</v>
       </c>
       <c r="F51" s="3">
-        <v>148.0950653551477</v>
+        <v>147.7607036391234</v>
       </c>
       <c r="G51" s="3">
-        <v>124.6861301663065</v>
+        <v>129.7820746858701</v>
       </c>
       <c r="H51" s="4">
         <f>IF(F51=0,0,G51/F51)</f>
@@ -4012,7 +4067,7 @@
         <v>245.090682899663</v>
       </c>
       <c r="J51" s="6">
-        <v>19.96254009473606</v>
+        <v>25.02248949374902</v>
       </c>
       <c r="K51" s="7">
         <f>IF(I51=0,0,J51/I51)</f>
@@ -4039,10 +4094,10 @@
         <v>0</v>
       </c>
       <c r="S51" s="3">
-        <v>1975.090975512128</v>
+        <v>2091.183174942721</v>
       </c>
       <c r="T51" s="3">
-        <v>1662.894370399373</v>
+        <v>1836.740650985853</v>
       </c>
       <c r="U51" s="4">
         <f>IF(S51=0,0,T51/S51)</f>
@@ -4052,7 +4107,7 @@
         <v>7100767.677214347</v>
       </c>
       <c r="W51" s="6">
-        <v>667327.7781731561</v>
+        <v>836476.8330573235</v>
       </c>
       <c r="X51" s="7">
         <f>IF(V51=0,0,W51/V51)</f>
@@ -4096,10 +4151,10 @@
         <v>0</v>
       </c>
       <c r="F52" s="3">
-        <v>134.7924084512274</v>
+        <v>134.4880808162132</v>
       </c>
       <c r="G52" s="3">
-        <v>117.3131609633634</v>
+        <v>121.2448620347747</v>
       </c>
       <c r="H52" s="4">
         <f>IF(F52=0,0,G52/F52)</f>
@@ -4109,7 +4164,7 @@
         <v>200.4130880433794</v>
       </c>
       <c r="J52" s="6">
-        <v>21.28849801111122</v>
+        <v>26.68454090976095</v>
       </c>
       <c r="K52" s="7">
         <f>IF(I52=0,0,J52/I52)</f>
@@ -4136,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="S52" s="3">
-        <v>1797.678193133057</v>
+        <v>1903.342396907326</v>
       </c>
       <c r="T52" s="3">
-        <v>1564.563714340444</v>
+        <v>1715.917759532378</v>
       </c>
       <c r="U52" s="4">
         <f>IF(S52=0,0,T52/S52)</f>
@@ -4149,7 +4204,7 @@
         <v>6292834.208210533</v>
       </c>
       <c r="W52" s="6">
-        <v>757796.3406777447</v>
+        <v>949876.6631412003</v>
       </c>
       <c r="X52" s="7">
         <f>IF(V52=0,0,W52/V52)</f>
@@ -4193,10 +4248,10 @@
         <v>0</v>
       </c>
       <c r="F53" s="3">
-        <v>118.7821311155358</v>
+        <v>118.5139506930648</v>
       </c>
       <c r="G53" s="3">
-        <v>77.085006142639</v>
+        <v>83.96254109871973</v>
       </c>
       <c r="H53" s="4">
         <f>IF(F53=0,0,G53/F53)</f>
@@ -4206,7 +4261,7 @@
         <v>193.9015574705648</v>
       </c>
       <c r="J53" s="6">
-        <v>9.462193079037592</v>
+        <v>11.86059618587699</v>
       </c>
       <c r="K53" s="7">
         <f>IF(I53=0,0,J53/I53)</f>
@@ -4233,10 +4288,10 @@
         <v>0</v>
       </c>
       <c r="S53" s="3">
-        <v>1584.154844429043</v>
+        <v>1677.268540156761</v>
       </c>
       <c r="T53" s="3">
-        <v>1028.055186136768</v>
+        <v>1188.279758736814</v>
       </c>
       <c r="U53" s="4">
         <f>IF(S53=0,0,T53/S53)</f>
@@ -4246,7 +4301,7 @@
         <v>6053045.584847068</v>
       </c>
       <c r="W53" s="6">
-        <v>345144.5598841952</v>
+        <v>432629.1184659526</v>
       </c>
       <c r="X53" s="7">
         <f>IF(V53=0,0,W53/V53)</f>
@@ -4290,10 +4345,10 @@
         <v>0</v>
       </c>
       <c r="F54" s="3">
-        <v>93.70721146478344</v>
+        <v>93.49564395607489</v>
       </c>
       <c r="G54" s="3">
-        <v>50.34256103248683</v>
+        <v>56.21002423112071</v>
       </c>
       <c r="H54" s="4">
         <f>IF(F54=0,0,G54/F54)</f>
@@ -4303,7 +4358,7 @@
         <v>136.6145524202559</v>
       </c>
       <c r="J54" s="6">
-        <v>7.307984633459724</v>
+        <v>9.160355738468628</v>
       </c>
       <c r="K54" s="7">
         <f>IF(I54=0,0,J54/I54)</f>
@@ -4330,10 +4385,10 @@
         <v>0</v>
       </c>
       <c r="S54" s="3">
-        <v>1249.73959976761</v>
+        <v>1323.196985098892</v>
       </c>
       <c r="T54" s="3">
-        <v>671.4007501937136</v>
+        <v>795.512298197524</v>
       </c>
       <c r="U54" s="4">
         <f>IF(S54=0,0,T54/S54)</f>
@@ -4343,7 +4398,7 @@
         <v>4890905.466101354</v>
       </c>
       <c r="W54" s="6">
-        <v>291466.352394985</v>
+        <v>365344.9764395468</v>
       </c>
       <c r="X54" s="7">
         <f>IF(V54=0,0,W54/V54)</f>
@@ -4367,6 +4422,614 @@
       </c>
       <c r="AD54" s="4">
         <f>IF(AB54=0,0,AC54/AB54)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:30">
+      <c r="A56" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="57" spans="1:30">
+      <c r="B57" t="s">
+        <v>28</v>
+      </c>
+      <c r="C57" s="3">
+        <f>C59+C60+C61+C62+C63</f>
+        <v>0</v>
+      </c>
+      <c r="D57" s="3">
+        <f>D59+D60+D61+D62+D63</f>
+        <v>0</v>
+      </c>
+      <c r="E57" s="3">
+        <f>E59+E60+E61+E62+E63</f>
+        <v>0</v>
+      </c>
+      <c r="F57" s="3">
+        <f>F59+F60+F61+F62+F63</f>
+        <v>0</v>
+      </c>
+      <c r="G57" s="3">
+        <f>G59+G60+G61+G62+G63</f>
+        <v>0</v>
+      </c>
+      <c r="H57" s="4">
+        <f>IF(F57=0,0,G57/F57)</f>
+        <v>0</v>
+      </c>
+      <c r="I57" s="3">
+        <f>I59+I60+I61+I62+I63</f>
+        <v>0</v>
+      </c>
+      <c r="J57" s="6">
+        <f>J59+J60+J61+J62+J63</f>
+        <v>0</v>
+      </c>
+      <c r="K57" s="7">
+        <f>IF(I57=0,0,J57/I57)</f>
+        <v>0</v>
+      </c>
+      <c r="L57" s="3">
+        <f>L59+L60+L61+L62+L63</f>
+        <v>0</v>
+      </c>
+      <c r="M57" s="3">
+        <f>M59+M60+M61+M62+M63</f>
+        <v>0</v>
+      </c>
+      <c r="N57" s="4">
+        <f>IF(L57=0,0,M57/L57)</f>
+        <v>0</v>
+      </c>
+      <c r="O57" s="3">
+        <f>O59+O60+O61+O62+O63</f>
+        <v>0</v>
+      </c>
+      <c r="P57" s="3">
+        <f>P59+P60+P61+P62+P63</f>
+        <v>0</v>
+      </c>
+      <c r="Q57" s="4">
+        <f>IF(O57=0,0,P57/O57)</f>
+        <v>0</v>
+      </c>
+      <c r="S57" s="3">
+        <f>S59+S60+S61+S62+S63</f>
+        <v>0</v>
+      </c>
+      <c r="T57" s="3">
+        <f>T59+T60+T61+T62+T63</f>
+        <v>0</v>
+      </c>
+      <c r="U57" s="4">
+        <f>IF(S57=0,0,T57/S57)</f>
+        <v>0</v>
+      </c>
+      <c r="V57" s="3">
+        <f>V59+V60+V61+V62+V63</f>
+        <v>0</v>
+      </c>
+      <c r="W57" s="6">
+        <f>W59+W60+W61+W62+W63</f>
+        <v>0</v>
+      </c>
+      <c r="X57" s="7">
+        <f>IF(V57=0,0,W57/V57)</f>
+        <v>0</v>
+      </c>
+      <c r="Y57" s="3">
+        <f>Y59+Y60+Y61+Y62+Y63</f>
+        <v>0</v>
+      </c>
+      <c r="Z57" s="3">
+        <f>Z59+Z60+Z61+Z62+Z63</f>
+        <v>0</v>
+      </c>
+      <c r="AA57" s="4">
+        <f>IF(Y57=0,0,Z57/Y57)</f>
+        <v>0</v>
+      </c>
+      <c r="AB57" s="3">
+        <f>AB59+AB60+AB61+AB62+AB63</f>
+        <v>0</v>
+      </c>
+      <c r="AC57" s="3">
+        <f>AC59+AC60+AC61+AC62+AC63</f>
+        <v>0</v>
+      </c>
+      <c r="AD57" s="4">
+        <f>IF(AB57=0,0,AC57/AB57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:30">
+      <c r="A58" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="59" spans="1:30">
+      <c r="B59" t="s">
+        <v>30</v>
+      </c>
+      <c r="C59" s="3">
+        <f>J59+M59+G59+P59</f>
+        <v>0</v>
+      </c>
+      <c r="D59" s="3">
+        <f>G59+J59</f>
+        <v>0</v>
+      </c>
+      <c r="E59" s="3">
+        <f>M59+P59</f>
+        <v>0</v>
+      </c>
+      <c r="F59" s="3">
+        <v>155.3366697637048</v>
+      </c>
+      <c r="G59" s="3">
+        <v>127.8303805653116</v>
+      </c>
+      <c r="H59" s="4">
+        <f>IF(F59=0,0,G59/F59)</f>
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
+        <v>382.3073643284127</v>
+      </c>
+      <c r="J59" s="6">
+        <v>25.16365196989442</v>
+      </c>
+      <c r="K59" s="7">
+        <f>IF(I59=0,0,J59/I59)</f>
+        <v>0</v>
+      </c>
+      <c r="L59" s="3">
+        <v>0</v>
+      </c>
+      <c r="M59" s="3">
+        <v>0</v>
+      </c>
+      <c r="N59" s="4">
+        <f>IF(L59=0,0,M59/L59)</f>
+        <v>0</v>
+      </c>
+      <c r="O59" s="3">
+        <v>0</v>
+      </c>
+      <c r="P59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="4">
+        <f>IF(O59=0,0,P59/O59)</f>
+        <v>0</v>
+      </c>
+      <c r="S59" s="3">
+        <v>2198.402026122217</v>
+      </c>
+      <c r="T59" s="3">
+        <v>1809.119302365895</v>
+      </c>
+      <c r="U59" s="4">
+        <f>IF(S59=0,0,T59/S59)</f>
+        <v>0</v>
+      </c>
+      <c r="V59" s="3">
+        <v>9070418.669545408</v>
+      </c>
+      <c r="W59" s="6">
+        <v>623324.3944149893</v>
+      </c>
+      <c r="X59" s="7">
+        <f>IF(V59=0,0,W59/V59)</f>
+        <v>0</v>
+      </c>
+      <c r="Y59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="4">
+        <f>IF(Y59=0,0,Z59/Y59)</f>
+        <v>0</v>
+      </c>
+      <c r="AB59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD59" s="4">
+        <f>IF(AB59=0,0,AC59/AB59)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:30">
+      <c r="B60" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="3">
+        <f>J60+M60+G60+P60</f>
+        <v>0</v>
+      </c>
+      <c r="D60" s="3">
+        <f>G60+J60</f>
+        <v>0</v>
+      </c>
+      <c r="E60" s="3">
+        <f>M60+P60</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="3">
+        <v>147.7607036391234</v>
+      </c>
+      <c r="G60" s="3">
+        <v>124.3897710242896</v>
+      </c>
+      <c r="H60" s="4">
+        <f>IF(F60=0,0,G60/F60)</f>
+        <v>0</v>
+      </c>
+      <c r="I60" s="3">
+        <v>245.090682899663</v>
+      </c>
+      <c r="J60" s="6">
+        <v>21.00591395392729</v>
+      </c>
+      <c r="K60" s="7">
+        <f>IF(I60=0,0,J60/I60)</f>
+        <v>0</v>
+      </c>
+      <c r="L60" s="3">
+        <v>0</v>
+      </c>
+      <c r="M60" s="3">
+        <v>0</v>
+      </c>
+      <c r="N60" s="4">
+        <f>IF(L60=0,0,M60/L60)</f>
+        <v>0</v>
+      </c>
+      <c r="O60" s="3">
+        <v>0</v>
+      </c>
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="4">
+        <f>IF(O60=0,0,P60/O60)</f>
+        <v>0</v>
+      </c>
+      <c r="S60" s="3">
+        <v>2091.183174942721</v>
+      </c>
+      <c r="T60" s="3">
+        <v>1760.426080104955</v>
+      </c>
+      <c r="U60" s="4">
+        <f>IF(S60=0,0,T60/S60)</f>
+        <v>0</v>
+      </c>
+      <c r="V60" s="3">
+        <v>7100767.677214347</v>
+      </c>
+      <c r="W60" s="6">
+        <v>692794.20388046</v>
+      </c>
+      <c r="X60" s="7">
+        <f>IF(V60=0,0,W60/V60)</f>
+        <v>0</v>
+      </c>
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="4">
+        <f>IF(Y60=0,0,Z60/Y60)</f>
+        <v>0</v>
+      </c>
+      <c r="AB60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD60" s="4">
+        <f>IF(AB60=0,0,AC60/AB60)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:30">
+      <c r="B61" t="s">
+        <v>32</v>
+      </c>
+      <c r="C61" s="3">
+        <f>J61+M61+G61+P61</f>
+        <v>0</v>
+      </c>
+      <c r="D61" s="3">
+        <f>G61+J61</f>
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
+        <f>M61+P61</f>
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
+        <v>134.4880808162132</v>
+      </c>
+      <c r="G61" s="3">
+        <v>117.0373671682523</v>
+      </c>
+      <c r="H61" s="4">
+        <f>IF(F61=0,0,G61/F61)</f>
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
+        <v>200.4130880433794</v>
+      </c>
+      <c r="J61" s="6">
+        <v>22.61656617855845</v>
+      </c>
+      <c r="K61" s="7">
+        <f>IF(I61=0,0,J61/I61)</f>
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="4">
+        <f>IF(L61=0,0,M61/L61)</f>
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="4">
+        <f>IF(O61=0,0,P61/O61)</f>
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
+        <v>1903.342396907326</v>
+      </c>
+      <c r="T61" s="3">
+        <v>1656.371193653684</v>
+      </c>
+      <c r="U61" s="4">
+        <f>IF(S61=0,0,T61/S61)</f>
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
+        <v>6292834.208210533</v>
+      </c>
+      <c r="W61" s="6">
+        <v>794041.0575617198</v>
+      </c>
+      <c r="X61" s="7">
+        <f>IF(V61=0,0,W61/V61)</f>
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="4">
+        <f>IF(Y61=0,0,Z61/Y61)</f>
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="4">
+        <f>IF(AB61=0,0,AC61/AB61)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:30">
+      <c r="B62" t="s">
+        <v>33</v>
+      </c>
+      <c r="C62" s="3">
+        <f>J62+M62+G62+P62</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="3">
+        <f>G62+J62</f>
+        <v>0</v>
+      </c>
+      <c r="E62" s="3">
+        <f>M62+P62</f>
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
+        <v>118.5139506930648</v>
+      </c>
+      <c r="G62" s="3">
+        <v>76.88625128893909</v>
+      </c>
+      <c r="H62" s="4">
+        <f>IF(F62=0,0,G62/F62)</f>
+        <v>0</v>
+      </c>
+      <c r="I62" s="3">
+        <v>193.9015574705648</v>
+      </c>
+      <c r="J62" s="6">
+        <v>9.710502579285967</v>
+      </c>
+      <c r="K62" s="7">
+        <f>IF(I62=0,0,J62/I62)</f>
+        <v>0</v>
+      </c>
+      <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3">
+        <v>0</v>
+      </c>
+      <c r="N62" s="4">
+        <f>IF(L62=0,0,M62/L62)</f>
+        <v>0</v>
+      </c>
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="4">
+        <f>IF(O62=0,0,P62/O62)</f>
+        <v>0</v>
+      </c>
+      <c r="S62" s="3">
+        <v>1677.268540156761</v>
+      </c>
+      <c r="T62" s="3">
+        <v>1088.132575982645</v>
+      </c>
+      <c r="U62" s="4">
+        <f>IF(S62=0,0,T62/S62)</f>
+        <v>0</v>
+      </c>
+      <c r="V62" s="3">
+        <v>6053045.584847068</v>
+      </c>
+      <c r="W62" s="6">
+        <v>351805.066879469</v>
+      </c>
+      <c r="X62" s="7">
+        <f>IF(V62=0,0,W62/V62)</f>
+        <v>0</v>
+      </c>
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="4">
+        <f>IF(Y62=0,0,Z62/Y62)</f>
+        <v>0</v>
+      </c>
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="4">
+        <f>IF(AB62=0,0,AC62/AB62)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:30">
+      <c r="B63" t="s">
+        <v>34</v>
+      </c>
+      <c r="C63" s="3">
+        <f>J63+M63+G63+P63</f>
+        <v>0</v>
+      </c>
+      <c r="D63" s="3">
+        <f>G63+J63</f>
+        <v>0</v>
+      </c>
+      <c r="E63" s="3">
+        <f>M63+P63</f>
+        <v>0</v>
+      </c>
+      <c r="F63" s="3">
+        <v>93.49564395607489</v>
+      </c>
+      <c r="G63" s="3">
+        <v>50.20618165273297</v>
+      </c>
+      <c r="H63" s="4">
+        <f>IF(F63=0,0,G63/F63)</f>
+        <v>0</v>
+      </c>
+      <c r="I63" s="3">
+        <v>136.6145524202559</v>
+      </c>
+      <c r="J63" s="6">
+        <v>7.458779051449644</v>
+      </c>
+      <c r="K63" s="7">
+        <f>IF(I63=0,0,J63/I63)</f>
+        <v>0</v>
+      </c>
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="4">
+        <f>IF(L63=0,0,M63/L63)</f>
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="4">
+        <f>IF(O63=0,0,P63/O63)</f>
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>1323.196985098892</v>
+      </c>
+      <c r="T63" s="3">
+        <v>710.5429235551791</v>
+      </c>
+      <c r="U63" s="4">
+        <f>IF(S63=0,0,T63/S63)</f>
+        <v>0</v>
+      </c>
+      <c r="V63" s="3">
+        <v>4890905.466101354</v>
+      </c>
+      <c r="W63" s="6">
+        <v>296120.1093025655</v>
+      </c>
+      <c r="X63" s="7">
+        <f>IF(V63=0,0,W63/V63)</f>
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="4">
+        <f>IF(Y63=0,0,Z63/Y63)</f>
+        <v>0</v>
+      </c>
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD63" s="4">
+        <f>IF(AB63=0,0,AC63/AB63)</f>
         <v>0</v>
       </c>
     </row>

--- a/5000_analyze_results/results_spreadsheet.xlsx
+++ b/5000_analyze_results/results_spreadsheet.xlsx
@@ -1528,7 +1528,7 @@
         <v>362.8529849538489</v>
       </c>
       <c r="G14" s="3">
-        <v>236.1367268275891</v>
+        <v>221.5208507414528</v>
       </c>
       <c r="H14" s="4">
         <f>IF(F14=0,0,G14/F14)</f>
@@ -1538,7 +1538,7 @@
         <v>4771.261231090824</v>
       </c>
       <c r="J14" s="3">
-        <v>574.7557064126702</v>
+        <v>501.4456249828422</v>
       </c>
       <c r="K14" s="4">
         <f>IF(I14=0,0,J14/I14)</f>
@@ -1548,7 +1548,7 @@
         <v>17957.14040242062</v>
       </c>
       <c r="M14" s="3">
-        <v>100.1389094884172</v>
+        <v>85.61686038632318</v>
       </c>
       <c r="N14" s="4">
         <f>IF(L14=0,0,M14/L14)</f>
@@ -1558,7 +1558,7 @@
         <v>506.7963637284521</v>
       </c>
       <c r="P14" s="3">
-        <v>22.007135649256</v>
+        <v>21.08580760516185</v>
       </c>
       <c r="Q14" s="4">
         <f>IF(O14=0,0,P14/O14)</f>
@@ -1568,7 +1568,7 @@
         <v>4684.597214204819</v>
       </c>
       <c r="T14" s="3">
-        <v>3048.632637839994</v>
+        <v>2859.935024108126</v>
       </c>
       <c r="U14" s="4">
         <f>IF(S14=0,0,T14/S14)</f>
@@ -1578,7 +1578,7 @@
         <v>131696392.1412486</v>
       </c>
       <c r="W14" s="3">
-        <v>12551111.5207074</v>
+        <v>10916380.98049854</v>
       </c>
       <c r="X14" s="4">
         <f>IF(V14=0,0,W14/V14)</f>
@@ -1588,7 +1588,7 @@
         <v>3016543.050471412</v>
       </c>
       <c r="Z14" s="3">
-        <v>119816.4398438525</v>
+        <v>111664.6801338429</v>
       </c>
       <c r="AA14" s="4">
         <f>IF(Y14=0,0,Z14/Y14)</f>
@@ -1598,7 +1598,7 @@
         <v>200318.014600175</v>
       </c>
       <c r="AC14" s="3">
-        <v>1112.984928146965</v>
+        <v>951.5780229828379</v>
       </c>
       <c r="AD14" s="4">
         <f>IF(AB14=0,0,AC14/AB14)</f>
@@ -1625,7 +1625,7 @@
         <v>320.5427437766894</v>
       </c>
       <c r="G15" s="3">
-        <v>192.7207779040032</v>
+        <v>181.5437991241076</v>
       </c>
       <c r="H15" s="4">
         <f>IF(F15=0,0,G15/F15)</f>
@@ -1635,7 +1635,7 @@
         <v>4315.21265961095</v>
       </c>
       <c r="J15" s="3">
-        <v>513.5291981071886</v>
+        <v>458.0226267935433</v>
       </c>
       <c r="K15" s="4">
         <f>IF(I15=0,0,J15/I15)</f>
@@ -1645,7 +1645,7 @@
         <v>14810.98291993852</v>
       </c>
       <c r="M15" s="3">
-        <v>66.97132194078527</v>
+        <v>59.16814754312113</v>
       </c>
       <c r="N15" s="4">
         <f>IF(L15=0,0,M15/L15)</f>
@@ -1655,7 +1655,7 @@
         <v>297.573370209569</v>
       </c>
       <c r="P15" s="3">
-        <v>10.47285401756043</v>
+        <v>9.640077714848157</v>
       </c>
       <c r="Q15" s="4">
         <f>IF(O15=0,0,P15/O15)</f>
@@ -1665,7 +1665,7 @@
         <v>4138.352740079671</v>
       </c>
       <c r="T15" s="3">
-        <v>2488.112973366633</v>
+        <v>2343.813089318042</v>
       </c>
       <c r="U15" s="4">
         <f>IF(S15=0,0,T15/S15)</f>
@@ -1675,7 +1675,7 @@
         <v>123352422.8520256</v>
       </c>
       <c r="W15" s="3">
-        <v>11833860.56680924</v>
+        <v>10535349.96345158</v>
       </c>
       <c r="X15" s="4">
         <f>IF(V15=0,0,W15/V15)</f>
@@ -1685,7 +1685,7 @@
         <v>1788522.531513863</v>
       </c>
       <c r="Z15" s="3">
-        <v>68972.54388265847</v>
+        <v>64535.96669535222</v>
       </c>
       <c r="AA15" s="4">
         <f>IF(Y15=0,0,Z15/Y15)</f>
@@ -1695,7 +1695,7 @@
         <v>165227.6716058255</v>
       </c>
       <c r="AC15" s="3">
-        <v>744.3990103840479</v>
+        <v>657.6729120868549</v>
       </c>
       <c r="AD15" s="4">
         <f>IF(AB15=0,0,AC15/AB15)</f>
@@ -1722,7 +1722,7 @@
         <v>287.7720482472399</v>
       </c>
       <c r="G16" s="3">
-        <v>161.6901662622983</v>
+        <v>156.9994691257506</v>
       </c>
       <c r="H16" s="4">
         <f>IF(F16=0,0,G16/F16)</f>
@@ -1732,7 +1732,7 @@
         <v>4220.065012527612</v>
       </c>
       <c r="J16" s="3">
-        <v>463.6088522818093</v>
+        <v>437.7104451988172</v>
       </c>
       <c r="K16" s="4">
         <f>IF(I16=0,0,J16/I16)</f>
@@ -1742,7 +1742,7 @@
         <v>13140.17641177926</v>
       </c>
       <c r="M16" s="3">
-        <v>45.31403995645046</v>
+        <v>42.49657008028775</v>
       </c>
       <c r="N16" s="4">
         <f>IF(L16=0,0,M16/L16)</f>
@@ -1752,7 +1752,7 @@
         <v>350.6722046220511</v>
       </c>
       <c r="P16" s="3">
-        <v>12.10934546388395</v>
+        <v>11.07666530583956</v>
       </c>
       <c r="Q16" s="4">
         <f>IF(O16=0,0,P16/O16)</f>
@@ -1762,7 +1762,7 @@
         <v>3715.268142871963</v>
       </c>
       <c r="T16" s="3">
-        <v>2087.493651273165</v>
+        <v>2026.934615934527</v>
       </c>
       <c r="U16" s="4">
         <f>IF(S16=0,0,T16/S16)</f>
@@ -1772,7 +1772,7 @@
         <v>121045766.1486471</v>
       </c>
       <c r="W16" s="3">
-        <v>10757671.65764305</v>
+        <v>10157526.46538262</v>
       </c>
       <c r="X16" s="4">
         <f>IF(V16=0,0,W16/V16)</f>
@@ -1782,7 +1782,7 @@
         <v>2261372.687672075</v>
       </c>
       <c r="Z16" s="3">
-        <v>74873.55223910837</v>
+        <v>72334.24301970704</v>
       </c>
       <c r="AA16" s="4">
         <f>IF(Y16=0,0,Z16/Y16)</f>
@@ -1792,7 +1792,7 @@
         <v>146579.1514136479</v>
       </c>
       <c r="AC16" s="3">
-        <v>503.4931817808247</v>
+        <v>472.1754240624141</v>
       </c>
       <c r="AD16" s="4">
         <f>IF(AB16=0,0,AC16/AB16)</f>
@@ -1819,7 +1819,7 @@
         <v>271.3548595424364</v>
       </c>
       <c r="G17" s="3">
-        <v>144.676134576367</v>
+        <v>145.6544226624561</v>
       </c>
       <c r="H17" s="4">
         <f>IF(F17=0,0,G17/F17)</f>
@@ -1829,7 +1829,7 @@
         <v>3866.462901477351</v>
       </c>
       <c r="J17" s="3">
-        <v>398.1802336081071</v>
+        <v>401.7632570424508</v>
       </c>
       <c r="K17" s="4">
         <f>IF(I17=0,0,J17/I17)</f>
@@ -1839,7 +1839,7 @@
         <v>12529.63951354596</v>
       </c>
       <c r="M17" s="3">
-        <v>50.28439562279545</v>
+        <v>51.58480659198016</v>
       </c>
       <c r="N17" s="4">
         <f>IF(L17=0,0,M17/L17)</f>
@@ -1849,7 +1849,7 @@
         <v>341.4996444598856</v>
       </c>
       <c r="P17" s="3">
-        <v>11.67196939960052</v>
+        <v>11.6839436237812</v>
       </c>
       <c r="Q17" s="4">
         <f>IF(O17=0,0,P17/O17)</f>
@@ -1859,7 +1859,7 @@
         <v>3503.314763237015</v>
       </c>
       <c r="T17" s="3">
-        <v>1867.834757056148</v>
+        <v>1880.464901585248</v>
       </c>
       <c r="U17" s="4">
         <f>IF(S17=0,0,T17/S17)</f>
@@ -1869,7 +1869,7 @@
         <v>114934295.1461658</v>
       </c>
       <c r="W17" s="3">
-        <v>9734869.333226398</v>
+        <v>9820156.063835561</v>
       </c>
       <c r="X17" s="4">
         <f>IF(V17=0,0,W17/V17)</f>
@@ -1879,7 +1879,7 @@
         <v>2020070.981660255</v>
       </c>
       <c r="Z17" s="3">
-        <v>61669.62522799801</v>
+        <v>62246.74095967971</v>
       </c>
       <c r="AA17" s="4">
         <f>IF(Y17=0,0,Z17/Y17)</f>
@@ -1889,7 +1889,7 @@
         <v>139766.3345807479</v>
       </c>
       <c r="AC17" s="3">
-        <v>558.9015223595488</v>
+        <v>573.3558720757428</v>
       </c>
       <c r="AD17" s="4">
         <f>IF(AB17=0,0,AC17/AB17)</f>
@@ -1916,7 +1916,7 @@
         <v>231.1015430943892</v>
       </c>
       <c r="G18" s="3">
-        <v>78.90054096724134</v>
+        <v>100.2480757259098</v>
       </c>
       <c r="H18" s="4">
         <f>IF(F18=0,0,G18/F18)</f>
@@ -1926,7 +1926,7 @@
         <v>3364.297008165505</v>
       </c>
       <c r="J18" s="3">
-        <v>227.1775098421918</v>
+        <v>323.8860360508836</v>
       </c>
       <c r="K18" s="4">
         <f>IF(I18=0,0,J18/I18)</f>
@@ -1936,7 +1936,7 @@
         <v>11856.76378900309</v>
       </c>
       <c r="M18" s="3">
-        <v>21.89240697437897</v>
+        <v>30.7785680264812</v>
       </c>
       <c r="N18" s="4">
         <f>IF(L18=0,0,M18/L18)</f>
@@ -1946,7 +1946,7 @@
         <v>209.6942036708812</v>
       </c>
       <c r="P18" s="3">
-        <v>3.993387343400682</v>
+        <v>5.412575810603506</v>
       </c>
       <c r="Q18" s="4">
         <f>IF(O18=0,0,P18/O18)</f>
@@ -1956,7 +1956,7 @@
         <v>2983.6261237209</v>
       </c>
       <c r="T18" s="3">
-        <v>1018.641901103288</v>
+        <v>1294.248292692759</v>
       </c>
       <c r="U18" s="4">
         <f>IF(S18=0,0,T18/S18)</f>
@@ -1966,7 +1966,7 @@
         <v>107056308.1865083</v>
       </c>
       <c r="W18" s="3">
-        <v>6047039.221417382</v>
+        <v>8651083.427734584</v>
       </c>
       <c r="X18" s="4">
         <f>IF(V18=0,0,W18/V18)</f>
@@ -1976,7 +1976,7 @@
         <v>1277060.928257236</v>
       </c>
       <c r="Z18" s="3">
-        <v>25179.07844351418</v>
+        <v>32306.4577297885</v>
       </c>
       <c r="AA18" s="4">
         <f>IF(Y18=0,0,Z18/Y18)</f>
@@ -1986,7 +1986,7 @@
         <v>132271.7542529008</v>
       </c>
       <c r="AC18" s="3">
-        <v>243.3148868892749</v>
+        <v>342.0862766166101</v>
       </c>
       <c r="AD18" s="4">
         <f>IF(AB18=0,0,AC18/AB18)</f>
@@ -2143,10 +2143,10 @@
         <v>0</v>
       </c>
       <c r="I23" s="3">
-        <v>1006.030840012209</v>
+        <v>1024.476057384201</v>
       </c>
       <c r="J23" s="3">
-        <v>86.86733689510881</v>
+        <v>88.45317146241956</v>
       </c>
       <c r="K23" s="4">
         <f>IF(I23=0,0,J23/I23)</f>
@@ -2183,10 +2183,10 @@
         <v>0</v>
       </c>
       <c r="V23" s="3">
-        <v>24943823.20853924</v>
+        <v>25177467.03377928</v>
       </c>
       <c r="W23" s="3">
-        <v>1711094.158100959</v>
+        <v>1717883.201918498</v>
       </c>
       <c r="X23" s="4">
         <f>IF(V23=0,0,W23/V23)</f>
@@ -2240,10 +2240,10 @@
         <v>0</v>
       </c>
       <c r="I24" s="3">
-        <v>964.5986558077452</v>
+        <v>968.8874507802924</v>
       </c>
       <c r="J24" s="3">
-        <v>88.73307073881558</v>
+        <v>89.17538361210562</v>
       </c>
       <c r="K24" s="4">
         <f>IF(I24=0,0,J24/I24)</f>
@@ -2280,10 +2280,10 @@
         <v>0</v>
       </c>
       <c r="V24" s="3">
-        <v>24665300.63578367</v>
+        <v>24716781.60947407</v>
       </c>
       <c r="W24" s="3">
-        <v>1812415.629343331</v>
+        <v>1817091.797478788</v>
       </c>
       <c r="X24" s="4">
         <f>IF(V24=0,0,W24/V24)</f>
@@ -2337,10 +2337,10 @@
         <v>0</v>
       </c>
       <c r="I25" s="3">
-        <v>794.1006249062289</v>
+        <v>792.6568327877751</v>
       </c>
       <c r="J25" s="3">
-        <v>82.29511533396365</v>
+        <v>82.16200536793039</v>
       </c>
       <c r="K25" s="4">
         <f>IF(I25=0,0,J25/I25)</f>
@@ -2377,10 +2377,10 @@
         <v>0</v>
       </c>
       <c r="V25" s="3">
-        <v>22725958.89165936</v>
+        <v>22756394.15398703</v>
       </c>
       <c r="W25" s="3">
-        <v>1925420.011185676</v>
+        <v>1928610.932770092</v>
       </c>
       <c r="X25" s="4">
         <f>IF(V25=0,0,W25/V25)</f>
@@ -2434,10 +2434,10 @@
         <v>0</v>
       </c>
       <c r="I26" s="3">
-        <v>721.6494802184835</v>
+        <v>714.5868735320346</v>
       </c>
       <c r="J26" s="3">
-        <v>77.17266564486199</v>
+        <v>76.42945112305088</v>
       </c>
       <c r="K26" s="4">
         <f>IF(I26=0,0,J26/I26)</f>
@@ -2474,10 +2474,10 @@
         <v>0</v>
       </c>
       <c r="V26" s="3">
-        <v>21493332.04664342</v>
+        <v>21413420.36871202</v>
       </c>
       <c r="W26" s="3">
-        <v>1908378.392676797</v>
+        <v>1904400.263435714</v>
       </c>
       <c r="X26" s="4">
         <f>IF(V26=0,0,W26/V26)</f>
@@ -2531,10 +2531,10 @@
         <v>0</v>
       </c>
       <c r="I27" s="3">
-        <v>613.496298429298</v>
+        <v>607.1996095192959</v>
       </c>
       <c r="J27" s="3">
-        <v>69.54268932890368</v>
+        <v>68.60543159336562</v>
       </c>
       <c r="K27" s="4">
         <f>IF(I27=0,0,J27/I27)</f>
@@ -2571,10 +2571,10 @@
         <v>0</v>
       </c>
       <c r="V27" s="3">
-        <v>20021798.10615849</v>
+        <v>19850211.7121278</v>
       </c>
       <c r="W27" s="3">
-        <v>1911129.785046071</v>
+        <v>1891368.106447026</v>
       </c>
       <c r="X27" s="4">
         <f>IF(V27=0,0,W27/V27)</f>
@@ -2751,10 +2751,10 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>1006.030840012209</v>
+        <v>1024.476057384201</v>
       </c>
       <c r="J32" s="3">
-        <v>32.09737479080761</v>
+        <v>32.68420640140481</v>
       </c>
       <c r="K32" s="4">
         <f>IF(I32=0,0,J32/I32)</f>
@@ -2791,10 +2791,10 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
-        <v>24943823.20853924</v>
+        <v>25177467.03377928</v>
       </c>
       <c r="W32" s="3">
-        <v>623654.2003708966</v>
+        <v>626047.5010496005</v>
       </c>
       <c r="X32" s="4">
         <f>IF(V32=0,0,W32/V32)</f>
@@ -2848,10 +2848,10 @@
         <v>0</v>
       </c>
       <c r="I33" s="3">
-        <v>964.5986558077452</v>
+        <v>968.8874507802924</v>
       </c>
       <c r="J33" s="3">
-        <v>42.69060008609377</v>
+        <v>42.90510061431443</v>
       </c>
       <c r="K33" s="4">
         <f>IF(I33=0,0,J33/I33)</f>
@@ -2888,10 +2888,10 @@
         <v>0</v>
       </c>
       <c r="V33" s="3">
-        <v>24665300.63578367</v>
+        <v>24716781.60947407</v>
       </c>
       <c r="W33" s="3">
-        <v>859445.1501166448</v>
+        <v>861736.4243335649</v>
       </c>
       <c r="X33" s="4">
         <f>IF(V33=0,0,W33/V33)</f>
@@ -2945,10 +2945,10 @@
         <v>0</v>
       </c>
       <c r="I34" s="3">
-        <v>794.1006249062289</v>
+        <v>792.6568327877751</v>
       </c>
       <c r="J34" s="3">
-        <v>48.03179086984182</v>
+        <v>47.95474572782649</v>
       </c>
       <c r="K34" s="4">
         <f>IF(I34=0,0,J34/I34)</f>
@@ -2985,10 +2985,10 @@
         <v>0</v>
       </c>
       <c r="V34" s="3">
-        <v>22725958.89165936</v>
+        <v>22756394.15398703</v>
       </c>
       <c r="W34" s="3">
-        <v>1106195.733125906</v>
+        <v>1108080.962424688</v>
       </c>
       <c r="X34" s="4">
         <f>IF(V34=0,0,W34/V34)</f>
@@ -3042,10 +3042,10 @@
         <v>0</v>
       </c>
       <c r="I35" s="3">
-        <v>721.6494802184835</v>
+        <v>714.5868735320346</v>
       </c>
       <c r="J35" s="3">
-        <v>52.18241248611535</v>
+        <v>51.68579927201837</v>
       </c>
       <c r="K35" s="4">
         <f>IF(I35=0,0,J35/I35)</f>
@@ -3082,10 +3082,10 @@
         <v>0</v>
       </c>
       <c r="V35" s="3">
-        <v>21493332.04664342</v>
+        <v>21413420.36871202</v>
       </c>
       <c r="W35" s="3">
-        <v>1271558.913595185</v>
+        <v>1269177.296716779</v>
       </c>
       <c r="X35" s="4">
         <f>IF(V35=0,0,W35/V35)</f>
@@ -3139,10 +3139,10 @@
         <v>0</v>
       </c>
       <c r="I36" s="3">
-        <v>613.496298429298</v>
+        <v>607.1996095192959</v>
       </c>
       <c r="J36" s="3">
-        <v>50.59624545245489</v>
+        <v>49.91319984393485</v>
       </c>
       <c r="K36" s="4">
         <f>IF(I36=0,0,J36/I36)</f>
@@ -3179,10 +3179,10 @@
         <v>0</v>
       </c>
       <c r="V36" s="3">
-        <v>20021798.10615849</v>
+        <v>19850211.7121278</v>
       </c>
       <c r="W36" s="3">
-        <v>1370173.648558669</v>
+        <v>1356137.905176748</v>
       </c>
       <c r="X36" s="4">
         <f>IF(V36=0,0,W36/V36)</f>
@@ -3345,7 +3345,7 @@
         <v>0</v>
       </c>
       <c r="E41" s="3">
-        <f>M41+P41</f>
+        <f>P41+M41</f>
         <v>0</v>
       </c>
       <c r="F41" s="3">
@@ -3442,7 +3442,7 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <f>M42+P42</f>
+        <f>P42+M42</f>
         <v>0</v>
       </c>
       <c r="F42" s="3">
@@ -3539,7 +3539,7 @@
         <v>0</v>
       </c>
       <c r="E43" s="3">
-        <f>M43+P43</f>
+        <f>P43+M43</f>
         <v>0</v>
       </c>
       <c r="F43" s="3">
@@ -3636,7 +3636,7 @@
         <v>0</v>
       </c>
       <c r="E44" s="3">
-        <f>M44+P44</f>
+        <f>P44+M44</f>
         <v>0</v>
       </c>
       <c r="F44" s="3">
@@ -3733,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="E45" s="3">
-        <f>M45+P45</f>
+        <f>P45+M45</f>
         <v>0</v>
       </c>
       <c r="F45" s="3">
@@ -3953,7 +3953,7 @@
         <v>0</v>
       </c>
       <c r="E50" s="3">
-        <f>M50+P50</f>
+        <f>P50+M50</f>
         <v>0</v>
       </c>
       <c r="F50" s="3">
@@ -4050,7 +4050,7 @@
         <v>0</v>
       </c>
       <c r="E51" s="3">
-        <f>M51+P51</f>
+        <f>P51+M51</f>
         <v>0</v>
       </c>
       <c r="F51" s="3">
@@ -4147,7 +4147,7 @@
         <v>0</v>
       </c>
       <c r="E52" s="3">
-        <f>M52+P52</f>
+        <f>P52+M52</f>
         <v>0</v>
       </c>
       <c r="F52" s="3">
@@ -4244,7 +4244,7 @@
         <v>0</v>
       </c>
       <c r="E53" s="3">
-        <f>M53+P53</f>
+        <f>P53+M53</f>
         <v>0</v>
       </c>
       <c r="F53" s="3">
@@ -4341,7 +4341,7 @@
         <v>0</v>
       </c>
       <c r="E54" s="3">
-        <f>M54+P54</f>
+        <f>P54+M54</f>
         <v>0</v>
       </c>
       <c r="F54" s="3">
@@ -4561,7 +4561,7 @@
         <v>0</v>
       </c>
       <c r="E59" s="3">
-        <f>M59+P59</f>
+        <f>P59+M59</f>
         <v>0</v>
       </c>
       <c r="F59" s="3">
@@ -4658,7 +4658,7 @@
         <v>0</v>
       </c>
       <c r="E60" s="3">
-        <f>M60+P60</f>
+        <f>P60+M60</f>
         <v>0</v>
       </c>
       <c r="F60" s="3">
@@ -4755,7 +4755,7 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
-        <f>M61+P61</f>
+        <f>P61+M61</f>
         <v>0</v>
       </c>
       <c r="F61" s="3">
@@ -4852,7 +4852,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="3">
-        <f>M62+P62</f>
+        <f>P62+M62</f>
         <v>0</v>
       </c>
       <c r="F62" s="3">
@@ -4949,7 +4949,7 @@
         <v>0</v>
       </c>
       <c r="E63" s="3">
-        <f>M63+P63</f>
+        <f>P63+M63</f>
         <v>0</v>
       </c>
       <c r="F63" s="3">
